--- a/index.xlsx
+++ b/index.xlsx
@@ -449,37 +449,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Nifty IT</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="C2" t="str">
-        <v>CNXIT</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="D2" s="1">
-        <v>29830.1</v>
+        <v>16312</v>
       </c>
       <c r="E2" s="2">
-        <v>5.22</v>
+        <v>2.79</v>
       </c>
       <c r="F2" s="2">
-        <v>4.39</v>
+        <v>3.64</v>
       </c>
       <c r="G2" s="2">
-        <v>7.67</v>
+        <v>2.52</v>
       </c>
       <c r="H2" s="2">
-        <v>-21.26</v>
+        <v>-25.84</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>31062.78</v>
+        <v>18511.34</v>
       </c>
       <c r="K2" s="1">
-        <v>28512.03</v>
+        <v>15975.59</v>
       </c>
       <c r="L2" s="1">
-        <v>29836.58</v>
+        <v>17358.33</v>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -490,37 +490,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="C3" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="D3" s="1">
-        <v>16007.9</v>
+        <v>10696.5</v>
       </c>
       <c r="E3" s="2">
-        <v>3.19</v>
+        <v>2.79</v>
       </c>
       <c r="F3" s="2">
-        <v>1.71</v>
+        <v>3.61</v>
       </c>
       <c r="G3" s="2">
-        <v>0.61</v>
+        <v>2.5</v>
       </c>
       <c r="H3" s="2">
-        <v>-27.23</v>
+        <v>-27.24</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>18571.46</v>
+        <v>12272.23</v>
       </c>
       <c r="K3" s="1">
-        <v>15907.82</v>
+        <v>10477.56</v>
       </c>
       <c r="L3" s="1">
-        <v>17479.15</v>
+        <v>11388.72</v>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -531,37 +531,37 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>Nifty IT</v>
       </c>
       <c r="C4" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>CNXIT</v>
       </c>
       <c r="D4" s="1">
-        <v>10499.55</v>
+        <v>30697</v>
       </c>
       <c r="E4" s="2">
-        <v>3.19</v>
+        <v>1.74</v>
       </c>
       <c r="F4" s="2">
-        <v>1.71</v>
+        <v>7.43</v>
       </c>
       <c r="G4" s="2">
-        <v>0.61</v>
+        <v>10.8</v>
       </c>
       <c r="H4" s="2">
-        <v>-28.58</v>
+        <v>-18.97</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>12314.42</v>
+        <v>30973.81</v>
       </c>
       <c r="K4" s="1">
-        <v>10433.94</v>
+        <v>29156.09</v>
       </c>
       <c r="L4" s="1">
-        <v>11468.66</v>
+        <v>29790.55</v>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -572,37 +572,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="C5" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="D5" s="1">
-        <v>8386.7</v>
+        <v>8350.5</v>
       </c>
       <c r="E5" s="2">
-        <v>2.92</v>
+        <v>1.69</v>
       </c>
       <c r="F5" s="2">
-        <v>2.64</v>
+        <v>1.84</v>
       </c>
       <c r="G5" s="2">
-        <v>4.49</v>
+        <v>3.38</v>
       </c>
       <c r="H5" s="2">
-        <v>-10.99</v>
+        <v>-16.87</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>8289.11</v>
+        <v>8805.43</v>
       </c>
       <c r="K5" s="1">
-        <v>8199.98</v>
+        <v>8206.58</v>
       </c>
       <c r="L5" s="1">
-        <v>8553.68</v>
+        <v>8429.8</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -613,37 +613,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="C6" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="D6" s="1">
-        <v>13613.4</v>
+        <v>29932.15</v>
       </c>
       <c r="E6" s="2">
-        <v>2.82</v>
+        <v>1.62</v>
       </c>
       <c r="F6" s="2">
-        <v>2.25</v>
+        <v>2.89</v>
       </c>
       <c r="G6" s="2">
-        <v>1.95</v>
+        <v>3.16</v>
       </c>
       <c r="H6" s="2">
-        <v>-10.98</v>
+        <v>-11.07</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>14435.48</v>
+        <v>31030.11</v>
       </c>
       <c r="K6" s="1">
-        <v>13423.7</v>
+        <v>29345.65</v>
       </c>
       <c r="L6" s="1">
-        <v>14165.78</v>
+        <v>30205.2</v>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -654,37 +654,37 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="C7" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="D7" s="1">
-        <v>10662.05</v>
+        <v>11419.05</v>
       </c>
       <c r="E7" s="2">
-        <v>2.69</v>
+        <v>1.54</v>
       </c>
       <c r="F7" s="2">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="G7" s="2">
-        <v>1.16</v>
+        <v>2.46</v>
       </c>
       <c r="H7" s="2">
-        <v>-14.59</v>
+        <v>-13.98</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>11273.07</v>
+        <v>12217.99</v>
       </c>
       <c r="K7" s="1">
-        <v>10520.31</v>
+        <v>11232.17</v>
       </c>
       <c r="L7" s="1">
-        <v>11197.7</v>
+        <v>11609.18</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -695,37 +695,37 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="C8" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="D8" s="1">
-        <v>5513</v>
+        <v>7339.85</v>
       </c>
       <c r="E8" s="2">
-        <v>2.5</v>
+        <v>1.54</v>
       </c>
       <c r="F8" s="2">
-        <v>1.72</v>
+        <v>2.53</v>
       </c>
       <c r="G8" s="2">
-        <v>0.74</v>
+        <v>3.73</v>
       </c>
       <c r="H8" s="2">
-        <v>-13.66</v>
+        <v>-2.94</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>5976.36</v>
+        <v>7337.14</v>
       </c>
       <c r="K8" s="1">
-        <v>5456.12</v>
+        <v>7208.26</v>
       </c>
       <c r="L8" s="1">
-        <v>5743.43</v>
+        <v>7430.9</v>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -736,37 +736,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>CNXREALTY</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="C9" t="str">
-        <v>CNXREALTY</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="D9" s="1">
-        <v>829.95</v>
+        <v>27568.05</v>
       </c>
       <c r="E9" s="2">
-        <v>2.46</v>
+        <v>1.48</v>
       </c>
       <c r="F9" s="2">
-        <v>3.23</v>
+        <v>1.27</v>
       </c>
       <c r="G9" s="2">
-        <v>-2.05</v>
+        <v>3.27</v>
       </c>
       <c r="H9" s="2">
-        <v>-5.47</v>
+        <v>-4.01</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>824.13</v>
+        <v>27396.83</v>
       </c>
       <c r="K9" s="1">
-        <v>825.84</v>
+        <v>27166.14</v>
       </c>
       <c r="L9" s="1">
-        <v>873.18</v>
+        <v>27314.99</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -777,37 +777,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="C10" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="D10" s="1">
-        <v>19269.75</v>
+        <v>25525.5</v>
       </c>
       <c r="E10" s="2">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="F10" s="2">
-        <v>2.15</v>
+        <v>2.68</v>
       </c>
       <c r="G10" s="2">
-        <v>1.72</v>
+        <v>-2.92</v>
       </c>
       <c r="H10" s="2">
-        <v>-10</v>
+        <v>-9.45</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>20164.95</v>
+        <v>26975.88</v>
       </c>
       <c r="K10" s="1">
-        <v>19004.14</v>
+        <v>25427.41</v>
       </c>
       <c r="L10" s="1">
-        <v>20016.05</v>
+        <v>27584.02</v>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -818,37 +818,37 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="C11" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="D11" s="1">
-        <v>5375.05</v>
+        <v>25313.05</v>
       </c>
       <c r="E11" s="2">
-        <v>2.17</v>
+        <v>1.46</v>
       </c>
       <c r="F11" s="2">
-        <v>2.1</v>
+        <v>1.38</v>
       </c>
       <c r="G11" s="2">
-        <v>1.03</v>
+        <v>2.69</v>
       </c>
       <c r="H11" s="2">
-        <v>-8.28</v>
+        <v>-8.33</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>5562.14</v>
+        <v>26273</v>
       </c>
       <c r="K11" s="1">
-        <v>5310.07</v>
+        <v>25009.75</v>
       </c>
       <c r="L11" s="1">
-        <v>5564.77</v>
+        <v>25663.49</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -859,37 +859,37 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="C12" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="D12" s="1">
-        <v>29443</v>
+        <v>5296.65</v>
       </c>
       <c r="E12" s="2">
-        <v>2.08</v>
+        <v>1.44</v>
       </c>
       <c r="F12" s="2">
-        <v>1.21</v>
+        <v>2.23</v>
       </c>
       <c r="G12" s="2">
-        <v>1.48</v>
+        <v>4.07</v>
       </c>
       <c r="H12" s="2">
-        <v>-12.52</v>
+        <v>13.75</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>31072.73</v>
+        <v>5095.48</v>
       </c>
       <c r="K12" s="1">
-        <v>29161.96</v>
+        <v>5236.54</v>
       </c>
       <c r="L12" s="1">
-        <v>30285.11</v>
+        <v>5310.46</v>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -900,37 +900,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>NIFTY</v>
       </c>
       <c r="C13" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>NIFTY</v>
       </c>
       <c r="D13" s="1">
-        <v>7241.7</v>
+        <v>22939.95</v>
       </c>
       <c r="E13" s="2">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="F13" s="2">
-        <v>1.16</v>
+        <v>1.86</v>
       </c>
       <c r="G13" s="2">
-        <v>2.34</v>
+        <v>1.41</v>
       </c>
       <c r="H13" s="2">
-        <v>-4.24</v>
+        <v>-12.21</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>7339.77</v>
+        <v>24198.86</v>
       </c>
       <c r="K13" s="1">
-        <v>7167.99</v>
+        <v>22685.6</v>
       </c>
       <c r="L13" s="1">
-        <v>7447.1</v>
+        <v>23577.63</v>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -941,37 +941,37 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>NIFTY100ESG</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="C14" t="str">
-        <v>NIFTY100ESG</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="D14" s="1">
-        <v>4704.75</v>
+        <v>27169.6</v>
       </c>
       <c r="E14" s="2">
-        <v>1.83</v>
+        <v>1.39</v>
       </c>
       <c r="F14" s="2">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="G14" s="2">
-        <v>0.45</v>
+        <v>2.31</v>
       </c>
       <c r="H14" s="2">
-        <v>-9.2</v>
+        <v>-9.97</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>4928.72</v>
+        <v>28612.29</v>
       </c>
       <c r="K14" s="1">
-        <v>4676.76</v>
+        <v>26891.44</v>
       </c>
       <c r="L14" s="1">
-        <v>4917.93</v>
+        <v>27792.73</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -982,37 +982,37 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="C15" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="D15" s="1">
-        <v>11245.8</v>
+        <v>3825.1</v>
       </c>
       <c r="E15" s="2">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="F15" s="2">
-        <v>0.86</v>
+        <v>1.98</v>
       </c>
       <c r="G15" s="2">
-        <v>0.9</v>
+        <v>1.13</v>
       </c>
       <c r="H15" s="2">
-        <v>-15.29</v>
+        <v>-12.13</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>12237.98</v>
+        <v>4045.25</v>
       </c>
       <c r="K15" s="1">
-        <v>11178.27</v>
+        <v>3785.9</v>
       </c>
       <c r="L15" s="1">
-        <v>11642.13</v>
+        <v>3951.03</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -1023,37 +1023,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="C16" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="D16" s="1">
-        <v>30876.05</v>
+        <v>10790.85</v>
       </c>
       <c r="E16" s="2">
-        <v>1.66</v>
+        <v>1.13</v>
       </c>
       <c r="F16" s="2">
-        <v>1.18</v>
+        <v>3.53</v>
       </c>
       <c r="G16" s="2">
-        <v>-0.09</v>
+        <v>2.38</v>
       </c>
       <c r="H16" s="2">
-        <v>-7.37</v>
+        <v>-13.56</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>32421.12</v>
+        <v>11254.57</v>
       </c>
       <c r="K16" s="1">
-        <v>30778.06</v>
+        <v>10591.88</v>
       </c>
       <c r="L16" s="1">
-        <v>32335.31</v>
+        <v>11153.49</v>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -1064,37 +1064,37 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTY100</v>
       </c>
       <c r="C17" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTY100</v>
       </c>
       <c r="D17" s="1">
-        <v>3788.05</v>
+        <v>23936.6</v>
       </c>
       <c r="E17" s="2">
-        <v>1.63</v>
+        <v>1.05</v>
       </c>
       <c r="F17" s="2">
-        <v>0.99</v>
+        <v>1.65</v>
       </c>
       <c r="G17" s="2">
-        <v>0.15</v>
+        <v>0.85</v>
       </c>
       <c r="H17" s="2">
-        <v>-12.98</v>
+        <v>-10.31</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>4050.94</v>
+        <v>25093.5</v>
       </c>
       <c r="K17" s="1">
-        <v>3777.48</v>
+        <v>23744.45</v>
       </c>
       <c r="L17" s="1">
-        <v>3965.32</v>
+        <v>24705.77</v>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -1105,37 +1105,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="C18" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="D18" s="1">
-        <v>22721.95</v>
+        <v>10565.4</v>
       </c>
       <c r="E18" s="2">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="F18" s="2">
-        <v>0.89</v>
+        <v>2.13</v>
       </c>
       <c r="G18" s="2">
-        <v>0.45</v>
+        <v>-0.46</v>
       </c>
       <c r="H18" s="2">
-        <v>-13.04</v>
+        <v>-13.62</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>24232.79</v>
+        <v>11329.05</v>
       </c>
       <c r="K18" s="1">
-        <v>22630.49</v>
+        <v>10498.26</v>
       </c>
       <c r="L18" s="1">
-        <v>23654.16</v>
+        <v>10948.18</v>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -1146,37 +1146,37 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="C19" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="D19" s="1">
-        <v>36496.45</v>
+        <v>8668.25</v>
       </c>
       <c r="E19" s="2">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="F19" s="2">
-        <v>1.46</v>
+        <v>1.09</v>
       </c>
       <c r="G19" s="2">
-        <v>-0.36</v>
+        <v>-0.75</v>
       </c>
       <c r="H19" s="2">
-        <v>-0.71</v>
+        <v>-9.86</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>37138.09</v>
+        <v>9244.19</v>
       </c>
       <c r="K19" s="1">
-        <v>36500.55</v>
+        <v>8648.11</v>
       </c>
       <c r="L19" s="1">
-        <v>38934.76</v>
+        <v>9077.85</v>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1187,37 +1187,37 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="C20" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="D20" s="1">
-        <v>27124.9</v>
+        <v>8481.7</v>
       </c>
       <c r="E20" s="2">
-        <v>1.54</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2">
-        <v>1.13</v>
+        <v>3.81</v>
       </c>
       <c r="G20" s="2">
-        <v>2.14</v>
+        <v>5.67</v>
       </c>
       <c r="H20" s="2">
-        <v>-10.12</v>
+        <v>-9.99</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>28643.88</v>
+        <v>8276.45</v>
       </c>
       <c r="K20" s="1">
-        <v>26837.14</v>
+        <v>8280.59</v>
       </c>
       <c r="L20" s="1">
-        <v>27888.23</v>
+        <v>8542.69</v>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -1228,37 +1228,37 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="C21" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="D21" s="1">
-        <v>25228.55</v>
+        <v>4735.35</v>
       </c>
       <c r="E21" s="2">
-        <v>1.46</v>
+        <v>0.94</v>
       </c>
       <c r="F21" s="2">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="G21" s="2">
-        <v>2.35</v>
+        <v>1.1</v>
       </c>
       <c r="H21" s="2">
-        <v>-8.64</v>
+        <v>-8.61</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
       </c>
       <c r="J21" s="1">
-        <v>26297.02</v>
+        <v>4923.92</v>
       </c>
       <c r="K21" s="1">
-        <v>24940.93</v>
+        <v>4689.56</v>
       </c>
       <c r="L21" s="1">
-        <v>25734.83</v>
+        <v>4900.05</v>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -1269,37 +1269,37 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="C22" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="D22" s="1">
-        <v>23768.3</v>
+        <v>31010.75</v>
       </c>
       <c r="E22" s="2">
-        <v>1.46</v>
+        <v>0.84</v>
       </c>
       <c r="F22" s="2">
-        <v>0.94</v>
+        <v>1.62</v>
       </c>
       <c r="G22" s="2">
-        <v>0.14</v>
+        <v>0.34</v>
       </c>
       <c r="H22" s="2">
-        <v>-10.94</v>
+        <v>-6.96</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
       </c>
       <c r="J22" s="1">
-        <v>25122.4</v>
+        <v>32397.4</v>
       </c>
       <c r="K22" s="1">
-        <v>23704.71</v>
+        <v>30816.6</v>
       </c>
       <c r="L22" s="1">
-        <v>24785.26</v>
+        <v>32215.2</v>
       </c>
       <c r="M22" t="str">
         <v/>
@@ -1310,37 +1310,37 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="C23" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="D23" s="1">
-        <v>8146.55</v>
+        <v>13769.7</v>
       </c>
       <c r="E23" s="2">
-        <v>1.44</v>
+        <v>0.82</v>
       </c>
       <c r="F23" s="2">
-        <v>0.25</v>
+        <v>3.43</v>
       </c>
       <c r="G23" s="2">
-        <v>1.63</v>
+        <v>3.12</v>
       </c>
       <c r="H23" s="2">
-        <v>-4.53</v>
+        <v>-9.96</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>8578.95</v>
+        <v>14420.68</v>
       </c>
       <c r="K23" s="1">
-        <v>8087.45</v>
+        <v>13521.47</v>
       </c>
       <c r="L23" s="1">
-        <v>8407.58</v>
+        <v>14115.95</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -1351,37 +1351,37 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="C24" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="D24" s="1">
-        <v>9250.5</v>
+        <v>7534.9</v>
       </c>
       <c r="E24" s="2">
-        <v>1.41</v>
+        <v>0.79</v>
       </c>
       <c r="F24" s="2">
-        <v>2.71</v>
+        <v>0.75</v>
       </c>
       <c r="G24" s="2">
-        <v>-0.28</v>
+        <v>-2.2</v>
       </c>
       <c r="H24" s="2">
-        <v>19.4</v>
+        <v>-12.43</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <v>8798.3</v>
+        <v>7708.14</v>
       </c>
       <c r="K24" s="1">
-        <v>9186.01</v>
+        <v>7536</v>
       </c>
       <c r="L24" s="1">
-        <v>9532.91</v>
+        <v>7821.74</v>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -1392,37 +1392,37 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>NIFTYFMCG</v>
+        <v>NIFTY200</v>
       </c>
       <c r="C25" t="str">
-        <v>NIFTYFMCG</v>
+        <v>NIFTY200</v>
       </c>
       <c r="D25" s="1">
-        <v>44731.15</v>
+        <v>13249.55</v>
       </c>
       <c r="E25" s="2">
-        <v>1.4</v>
+        <v>0.73</v>
       </c>
       <c r="F25" s="2">
-        <v>-0.3</v>
+        <v>1.43</v>
       </c>
       <c r="G25" s="2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H25" s="2">
-        <v>-19.37</v>
+        <v>-8.83</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <v>49297.84</v>
+        <v>13818.97</v>
       </c>
       <c r="K25" s="1">
-        <v>44682.35</v>
+        <v>13173.34</v>
       </c>
       <c r="L25" s="1">
-        <v>46513.81</v>
+        <v>13720.31</v>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -1433,37 +1433,37 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="C26" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="D26" s="1">
-        <v>13190.55</v>
+        <v>10987.75</v>
       </c>
       <c r="E26" s="2">
-        <v>1.38</v>
+        <v>0.71</v>
       </c>
       <c r="F26" s="2">
-        <v>0.98</v>
+        <v>0.77</v>
       </c>
       <c r="G26" s="2">
-        <v>0.16</v>
+        <v>-0.77</v>
       </c>
       <c r="H26" s="2">
-        <v>-9.24</v>
+        <v>-10.59</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>13832.5</v>
+        <v>11523.11</v>
       </c>
       <c r="K26" s="1">
-        <v>13157.18</v>
+        <v>10975</v>
       </c>
       <c r="L26" s="1">
-        <v>13763.27</v>
+        <v>11581.4</v>
       </c>
       <c r="M26" t="str">
         <v/>
@@ -1474,37 +1474,37 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="C27" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="D27" s="1">
-        <v>8219.3</v>
+        <v>55634.55</v>
       </c>
       <c r="E27" s="2">
-        <v>1.35</v>
+        <v>0.58</v>
       </c>
       <c r="F27" s="2">
-        <v>0.24</v>
+        <v>0.68</v>
       </c>
       <c r="G27" s="2">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="H27" s="2">
-        <v>-18.17</v>
+        <v>-6.63</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>8823.61</v>
+        <v>56943.89</v>
       </c>
       <c r="K27" s="1">
-        <v>8166.37</v>
+        <v>55235.58</v>
       </c>
       <c r="L27" s="1">
-        <v>8451.55</v>
+        <v>56519.41</v>
       </c>
       <c r="M27" t="str">
         <v/>
@@ -1515,37 +1515,37 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="C28" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="D28" s="1">
-        <v>32685.6</v>
+        <v>18814.2</v>
       </c>
       <c r="E28" s="2">
-        <v>1.29</v>
+        <v>0.55</v>
       </c>
       <c r="F28" s="2">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="G28" s="2">
-        <v>-0.53</v>
+        <v>0.15</v>
       </c>
       <c r="H28" s="2">
-        <v>-3.74</v>
+        <v>-10.96</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>33725.15</v>
+        <v>19913.31</v>
       </c>
       <c r="K28" s="1">
-        <v>32662.44</v>
+        <v>18746.04</v>
       </c>
       <c r="L28" s="1">
-        <v>34301.31</v>
+        <v>19658.9</v>
       </c>
       <c r="M28" t="str">
         <v/>
@@ -1556,37 +1556,37 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="C29" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="D29" s="1">
-        <v>18753.95</v>
+        <v>827.05</v>
       </c>
       <c r="E29" s="2">
-        <v>1.27</v>
+        <v>0.52</v>
       </c>
       <c r="F29" s="2">
-        <v>0.69</v>
+        <v>2.87</v>
       </c>
       <c r="G29" s="2">
-        <v>-0.17</v>
+        <v>-2.4</v>
       </c>
       <c r="H29" s="2">
-        <v>-11.25</v>
+        <v>-5.8</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <v>19937.35</v>
+        <v>823.54</v>
       </c>
       <c r="K29" s="1">
-        <v>18735.22</v>
+        <v>825.61</v>
       </c>
       <c r="L29" s="1">
-        <v>19741.51</v>
+        <v>870.09</v>
       </c>
       <c r="M29" t="str">
         <v/>
@@ -1597,37 +1597,37 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>NIFTYAUTO</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="C30" t="str">
-        <v>NIFTYAUTO</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="D30" s="1">
-        <v>25391.85</v>
+        <v>5562.4</v>
       </c>
       <c r="E30" s="2">
-        <v>1.23</v>
+        <v>0.51</v>
       </c>
       <c r="F30" s="2">
-        <v>2.14</v>
+        <v>2.63</v>
       </c>
       <c r="G30" s="2">
-        <v>-3.43</v>
+        <v>1.64</v>
       </c>
       <c r="H30" s="2">
-        <v>-9.92</v>
+        <v>-12.89</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>27001.36</v>
+        <v>5968</v>
       </c>
       <c r="K30" s="1">
-        <v>25460.92</v>
+        <v>5487.04</v>
       </c>
       <c r="L30" s="1">
-        <v>27734.58</v>
+        <v>5723.75</v>
       </c>
       <c r="M30" t="str">
         <v/>
@@ -1644,31 +1644,31 @@
         <v>NIFTY500</v>
       </c>
       <c r="D31" s="1">
-        <v>22090</v>
+        <v>22142.1</v>
       </c>
       <c r="E31" s="2">
-        <v>1.22</v>
+        <v>0.47</v>
       </c>
       <c r="F31" s="2">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="G31" s="2">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="H31" s="2">
-        <v>-7.46</v>
+        <v>-7.24</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>22897.65</v>
+        <v>22879.74</v>
       </c>
       <c r="K31" s="1">
-        <v>22042.37</v>
+        <v>22059.85</v>
       </c>
       <c r="L31" s="1">
-        <v>22997.67</v>
+        <v>22931.41</v>
       </c>
       <c r="M31" t="str">
         <v/>
@@ -1679,37 +1679,37 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="C32" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="D32" s="1">
-        <v>15755.2</v>
+        <v>9051.4</v>
       </c>
       <c r="E32" s="2">
-        <v>1.21</v>
+        <v>0.45</v>
       </c>
       <c r="F32" s="2">
-        <v>0.99</v>
+        <v>1.43</v>
       </c>
       <c r="G32" s="2">
-        <v>-0.02</v>
+        <v>-2.78</v>
       </c>
       <c r="H32" s="2">
-        <v>-6.52</v>
+        <v>-4.87</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>16329.48</v>
+        <v>9767.57</v>
       </c>
       <c r="K32" s="1">
-        <v>15731.54</v>
+        <v>9066.2</v>
       </c>
       <c r="L32" s="1">
-        <v>16463.7</v>
+        <v>9577.71</v>
       </c>
       <c r="M32" t="str">
         <v/>
@@ -1720,37 +1720,37 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="C33" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="D33" s="1">
-        <v>23009.4</v>
+        <v>24854.45</v>
       </c>
       <c r="E33" s="2">
-        <v>1.18</v>
+        <v>0.43</v>
       </c>
       <c r="F33" s="2">
-        <v>1.32</v>
+        <v>0.65</v>
       </c>
       <c r="G33" s="2">
-        <v>1.07</v>
+        <v>-1.45</v>
       </c>
       <c r="H33" s="2">
-        <v>-4.36</v>
+        <v>-8.21</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>23533.65</v>
+        <v>26300.64</v>
       </c>
       <c r="K33" s="1">
-        <v>22900.46</v>
+        <v>24919.5</v>
       </c>
       <c r="L33" s="1">
-        <v>23978.91</v>
+        <v>26361.15</v>
       </c>
       <c r="M33" t="str">
         <v/>
@@ -1761,37 +1761,37 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>Nifty Total Market</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="C34" t="str">
-        <v>NIFTYTOTALMKT</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="D34" s="1">
-        <v>12505.7</v>
+        <v>3481.82</v>
       </c>
       <c r="E34" s="2">
-        <v>1.18</v>
+        <v>0.43</v>
       </c>
       <c r="F34" s="2">
-        <v>1.02</v>
+        <v>-0.66</v>
       </c>
       <c r="G34" s="2">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H34" s="2">
-        <v>-6.63</v>
+        <v>-0.32</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>12890.03</v>
+        <v>3495.53</v>
       </c>
       <c r="K34" s="1">
-        <v>12482.02</v>
+        <v>3494.32</v>
       </c>
       <c r="L34" s="1">
-        <v>13003.54</v>
+        <v>3542.21</v>
       </c>
       <c r="M34" t="str">
         <v/>
@@ -1802,37 +1802,37 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>Nifty Total Market</v>
       </c>
       <c r="C35" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTYTOTALMKT</v>
       </c>
       <c r="D35" s="1">
-        <v>10948.6</v>
+        <v>12528.15</v>
       </c>
       <c r="E35" s="2">
-        <v>1.16</v>
+        <v>0.37</v>
       </c>
       <c r="F35" s="2">
-        <v>0.41</v>
+        <v>1.2</v>
       </c>
       <c r="G35" s="2">
-        <v>-1.12</v>
+        <v>0.18</v>
       </c>
       <c r="H35" s="2">
-        <v>-10.91</v>
+        <v>-6.46</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>11536.45</v>
+        <v>12881.07</v>
       </c>
       <c r="K35" s="1">
-        <v>10985.98</v>
+        <v>12490.32</v>
       </c>
       <c r="L35" s="1">
-        <v>11632.8</v>
+        <v>12968</v>
       </c>
       <c r="M35" t="str">
         <v/>
@@ -1843,37 +1843,37 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="C36" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="D36" s="1">
-        <v>12088.25</v>
+        <v>3301.94</v>
       </c>
       <c r="E36" s="2">
-        <v>1.15</v>
+        <v>0.36</v>
       </c>
       <c r="F36" s="2">
-        <v>0.73</v>
+        <v>-0.04</v>
       </c>
       <c r="G36" s="2">
-        <v>-5.27</v>
+        <v>-0.59</v>
       </c>
       <c r="H36" s="2">
-        <v>8.24</v>
+        <v>1.85</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>12446.46</v>
+        <v>3294.09</v>
       </c>
       <c r="K36" s="1">
-        <v>12302.69</v>
+        <v>3305.32</v>
       </c>
       <c r="L36" s="1">
-        <v>12974.43</v>
+        <v>3357.48</v>
       </c>
       <c r="M36" t="str">
         <v/>
@@ -1884,37 +1884,37 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="C37" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="D37" s="1">
-        <v>9196.6</v>
+        <v>15716.55</v>
       </c>
       <c r="E37" s="2">
-        <v>1.08</v>
+        <v>0.34</v>
       </c>
       <c r="F37" s="2">
-        <v>1.31</v>
+        <v>-0.88</v>
       </c>
       <c r="G37" s="2">
-        <v>-1.75</v>
+        <v>-2.61</v>
       </c>
       <c r="H37" s="2">
-        <v>-6.67</v>
+        <v>7.35</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>10004.81</v>
+        <v>15422.76</v>
       </c>
       <c r="K37" s="1">
-        <v>9226.9</v>
+        <v>15913.88</v>
       </c>
       <c r="L37" s="1">
-        <v>9628.33</v>
+        <v>16440.51</v>
       </c>
       <c r="M37" t="str">
         <v/>
@@ -1925,37 +1925,37 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="C38" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="D38" s="1">
-        <v>7480.6</v>
+        <v>15775.1</v>
       </c>
       <c r="E38" s="2">
-        <v>1.08</v>
+        <v>0.32</v>
       </c>
       <c r="F38" s="2">
-        <v>0.02</v>
+        <v>1.12</v>
       </c>
       <c r="G38" s="2">
-        <v>-2.91</v>
+        <v>0.11</v>
       </c>
       <c r="H38" s="2">
-        <v>-13.06</v>
+        <v>-6.41</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
       </c>
       <c r="J38" s="1">
-        <v>7719.22</v>
+        <v>16318.14</v>
       </c>
       <c r="K38" s="1">
-        <v>7549.71</v>
+        <v>15738.55</v>
       </c>
       <c r="L38" s="1">
-        <v>7845.27</v>
+        <v>16414.14</v>
       </c>
       <c r="M38" t="str">
         <v/>
@@ -1966,37 +1966,37 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="C39" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="D39" s="1">
-        <v>59459.2</v>
+        <v>15727.55</v>
       </c>
       <c r="E39" s="2">
-        <v>1.06</v>
+        <v>0.32</v>
       </c>
       <c r="F39" s="2">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="G39" s="2">
-        <v>0.21</v>
+        <v>-1.81</v>
       </c>
       <c r="H39" s="2">
-        <v>-1.7</v>
+        <v>-1.55</v>
       </c>
       <c r="I39" s="1">
         <v>0</v>
       </c>
       <c r="J39" s="1">
-        <v>60375.93</v>
+        <v>16013.29</v>
       </c>
       <c r="K39" s="1">
-        <v>59342.71</v>
+        <v>15774.19</v>
       </c>
       <c r="L39" s="1">
-        <v>62189.01</v>
+        <v>16544.75</v>
       </c>
       <c r="M39" t="str">
         <v/>
@@ -2007,37 +2007,37 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="C40" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="D40" s="1">
-        <v>15762.55</v>
+        <v>25812.7</v>
       </c>
       <c r="E40" s="2">
-        <v>1.05</v>
+        <v>0.29</v>
       </c>
       <c r="F40" s="2">
-        <v>1.1</v>
+        <v>-0.58</v>
       </c>
       <c r="G40" s="2">
-        <v>0.08</v>
+        <v>-2.37</v>
       </c>
       <c r="H40" s="2">
-        <v>-4.38</v>
+        <v>13.59</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
       </c>
       <c r="J40" s="1">
-        <v>16043.94</v>
+        <v>24302.2</v>
       </c>
       <c r="K40" s="1">
-        <v>15730.42</v>
+        <v>26095.24</v>
       </c>
       <c r="L40" s="1">
-        <v>16361.02</v>
+        <v>26539.33</v>
       </c>
       <c r="M40" t="str">
         <v/>
@@ -2048,37 +2048,37 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="C41" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="D41" s="1">
-        <v>55481.05</v>
+        <v>3074.79</v>
       </c>
       <c r="E41" s="2">
-        <v>1.03</v>
+        <v>0.28</v>
       </c>
       <c r="F41" s="2">
-        <v>0.41</v>
+        <v>-0.35</v>
       </c>
       <c r="G41" s="2">
-        <v>1.55</v>
+        <v>-0.95</v>
       </c>
       <c r="H41" s="2">
-        <v>-6.88</v>
+        <v>0.73</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
       </c>
       <c r="J41" s="1">
-        <v>56982.16</v>
+        <v>3085.64</v>
       </c>
       <c r="K41" s="1">
-        <v>55109.35</v>
+        <v>3083.68</v>
       </c>
       <c r="L41" s="1">
-        <v>56623.5</v>
+        <v>3125.97</v>
       </c>
       <c r="M41" t="str">
         <v/>
@@ -2089,37 +2089,37 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="C42" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="D42" s="1">
-        <v>16320.95</v>
+        <v>2609.85</v>
       </c>
       <c r="E42" s="2">
-        <v>1</v>
+        <v>0.26</v>
       </c>
       <c r="F42" s="2">
-        <v>1.94</v>
+        <v>-0.34</v>
       </c>
       <c r="G42" s="2">
-        <v>0.2</v>
+        <v>-1.08</v>
       </c>
       <c r="H42" s="2">
-        <v>1.98</v>
+        <v>-0.08</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
       </c>
       <c r="J42" s="1">
-        <v>16136.89</v>
+        <v>2632.57</v>
       </c>
       <c r="K42" s="1">
-        <v>16246.23</v>
+        <v>2618.31</v>
       </c>
       <c r="L42" s="1">
-        <v>16960.34</v>
+        <v>2656.02</v>
       </c>
       <c r="M42" t="str">
         <v/>
@@ -2130,37 +2130,37 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>Nifty midcap 150</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="C43" t="str">
-        <v>NIFTYMIDCAP150</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="D43" s="1">
-        <v>21829.4</v>
+        <v>843.25</v>
       </c>
       <c r="E43" s="2">
-        <v>0.97</v>
+        <v>0.25</v>
       </c>
       <c r="F43" s="2">
-        <v>1.05</v>
+        <v>-0.47</v>
       </c>
       <c r="G43" s="2">
-        <v>-0.17</v>
+        <v>-1.4</v>
       </c>
       <c r="H43" s="2">
-        <v>-2.01</v>
+        <v>-5.41</v>
       </c>
       <c r="I43" s="1">
         <v>0</v>
       </c>
       <c r="J43" s="1">
-        <v>22206.26</v>
+        <v>874.91</v>
       </c>
       <c r="K43" s="1">
-        <v>21822.11</v>
+        <v>847.09</v>
       </c>
       <c r="L43" s="1">
-        <v>22857.54</v>
+        <v>864.56</v>
       </c>
       <c r="M43" t="str">
         <v/>
@@ -2171,37 +2171,37 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="C44" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="D44" s="1">
-        <v>13761.95</v>
+        <v>2981.95</v>
       </c>
       <c r="E44" s="2">
-        <v>0.94</v>
+        <v>0.23</v>
       </c>
       <c r="F44" s="2">
-        <v>1.26</v>
+        <v>-0.35</v>
       </c>
       <c r="G44" s="2">
-        <v>0.22</v>
+        <v>-1.06</v>
       </c>
       <c r="H44" s="2">
-        <v>-0.11</v>
+        <v>0.51</v>
       </c>
       <c r="I44" s="1">
         <v>0</v>
       </c>
       <c r="J44" s="1">
-        <v>14006.79</v>
+        <v>3001.29</v>
       </c>
       <c r="K44" s="1">
-        <v>13736.81</v>
+        <v>2991.9</v>
       </c>
       <c r="L44" s="1">
-        <v>14501.62</v>
+        <v>3034.08</v>
       </c>
       <c r="M44" t="str">
         <v/>
@@ -2212,37 +2212,37 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="C45" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="D45" s="1">
-        <v>24812.55</v>
+        <v>5410.35</v>
       </c>
       <c r="E45" s="2">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="F45" s="2">
-        <v>0.48</v>
+        <v>2.77</v>
       </c>
       <c r="G45" s="2">
-        <v>-1.61</v>
+        <v>1.69</v>
       </c>
       <c r="H45" s="2">
-        <v>-8.36</v>
+        <v>-7.67</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
       </c>
       <c r="J45" s="1">
-        <v>26324.49</v>
+        <v>5557.34</v>
       </c>
       <c r="K45" s="1">
-        <v>24975.28</v>
+        <v>5341.58</v>
       </c>
       <c r="L45" s="1">
-        <v>26478.13</v>
+        <v>5550.05</v>
       </c>
       <c r="M45" t="str">
         <v/>
@@ -2253,37 +2253,37 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="C46" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="D46" s="1">
-        <v>8578.5</v>
+        <v>13566.25</v>
       </c>
       <c r="E46" s="2">
-        <v>0.93</v>
+        <v>0.15</v>
       </c>
       <c r="F46" s="2">
-        <v>0.05</v>
+        <v>0.62</v>
       </c>
       <c r="G46" s="2">
-        <v>-1.78</v>
+        <v>-1.34</v>
       </c>
       <c r="H46" s="2">
-        <v>-10.79</v>
+        <v>-6.25</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
       </c>
       <c r="J46" s="1">
-        <v>9254.18</v>
+        <v>14167.39</v>
       </c>
       <c r="K46" s="1">
-        <v>8657.71</v>
+        <v>13607.04</v>
       </c>
       <c r="L46" s="1">
-        <v>9111.43</v>
+        <v>14242.8</v>
       </c>
       <c r="M46" t="str">
         <v/>
@@ -2294,37 +2294,37 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="C47" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="D47" s="1">
-        <v>6051.5</v>
+        <v>15101.25</v>
       </c>
       <c r="E47" s="2">
-        <v>0.93</v>
+        <v>0.12</v>
       </c>
       <c r="F47" s="2">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="G47" s="2">
-        <v>-2.85</v>
+        <v>-2.29</v>
       </c>
       <c r="H47" s="2">
-        <v>-4.93</v>
+        <v>-2.02</v>
       </c>
       <c r="I47" s="1">
         <v>0</v>
       </c>
       <c r="J47" s="1">
-        <v>6753.07</v>
+        <v>15635.18</v>
       </c>
       <c r="K47" s="1">
-        <v>6101.67</v>
+        <v>15185.15</v>
       </c>
       <c r="L47" s="1">
-        <v>6361.15</v>
+        <v>16022.32</v>
       </c>
       <c r="M47" t="str">
         <v/>
@@ -2335,37 +2335,37 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="C48" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="D48" s="1">
-        <v>8955.45</v>
+        <v>32676.25</v>
       </c>
       <c r="E48" s="2">
-        <v>0.9</v>
+        <v>0.11</v>
       </c>
       <c r="F48" s="2">
-        <v>0.36</v>
+        <v>1.19</v>
       </c>
       <c r="G48" s="2">
-        <v>-3.81</v>
+        <v>-0.56</v>
       </c>
       <c r="H48" s="2">
-        <v>-5.88</v>
+        <v>-3.77</v>
       </c>
       <c r="I48" s="1">
         <v>0</v>
       </c>
       <c r="J48" s="1">
-        <v>9770.4</v>
+        <v>33713.45</v>
       </c>
       <c r="K48" s="1">
-        <v>9082.42</v>
+        <v>32661.9</v>
       </c>
       <c r="L48" s="1">
-        <v>9615.1</v>
+        <v>34183.52</v>
       </c>
       <c r="M48" t="str">
         <v/>
@@ -2376,37 +2376,37 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="C49" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="D49" s="1">
-        <v>16974</v>
+        <v>15751.35</v>
       </c>
       <c r="E49" s="2">
-        <v>0.87</v>
+        <v>0.11</v>
       </c>
       <c r="F49" s="2">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="G49" s="2">
-        <v>-0.32</v>
+        <v>0.01</v>
       </c>
       <c r="H49" s="2">
-        <v>-1.62</v>
+        <v>-4.45</v>
       </c>
       <c r="I49" s="1">
         <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>17239.11</v>
+        <v>16036.55</v>
       </c>
       <c r="K49" s="1">
-        <v>16983.25</v>
+        <v>15734.79</v>
       </c>
       <c r="L49" s="1">
-        <v>17855.02</v>
+        <v>16319.35</v>
       </c>
       <c r="M49" t="str">
         <v/>
@@ -2417,37 +2417,37 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="C50" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="D50" s="1">
-        <v>68927.95</v>
+        <v>3283.82</v>
       </c>
       <c r="E50" s="2">
-        <v>0.84</v>
+        <v>0.05</v>
       </c>
       <c r="F50" s="2">
-        <v>1.12</v>
+        <v>-0.42</v>
       </c>
       <c r="G50" s="2">
-        <v>-1.17</v>
+        <v>-0.75</v>
       </c>
       <c r="H50" s="2">
-        <v>-0.63</v>
+        <v>1.9</v>
       </c>
       <c r="I50" s="1">
         <v>0</v>
       </c>
       <c r="J50" s="1">
-        <v>70050.43</v>
+        <v>3279.01</v>
       </c>
       <c r="K50" s="1">
-        <v>69149.15</v>
+        <v>3293.74</v>
       </c>
       <c r="L50" s="1">
-        <v>72405.82</v>
+        <v>3326.73</v>
       </c>
       <c r="M50" t="str">
         <v/>
@@ -2458,37 +2458,37 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="C51" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="D51" s="1">
-        <v>13544.75</v>
+        <v>199.43</v>
       </c>
       <c r="E51" s="2">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="F51" s="2">
-        <v>0.46</v>
+        <v>1.34</v>
       </c>
       <c r="G51" s="2">
-        <v>-1.49</v>
+        <v>1.34</v>
       </c>
       <c r="H51" s="2">
-        <v>-6.4</v>
+        <v>-19.95</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
       </c>
       <c r="J51" s="1">
-        <v>14176.49</v>
+        <v>181.6</v>
       </c>
       <c r="K51" s="1">
-        <v>13631.76</v>
+        <v>197.64</v>
       </c>
       <c r="L51" s="1">
-        <v>14291.1</v>
+        <v>193.41</v>
       </c>
       <c r="M51" t="str">
         <v/>
@@ -2499,37 +2499,37 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="C52" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="D52" s="1">
-        <v>27324.35</v>
+        <v>11994.95</v>
       </c>
       <c r="E52" s="2">
-        <v>0.74</v>
+        <v>-0.1</v>
       </c>
       <c r="F52" s="2">
-        <v>0.37</v>
+        <v>-0.05</v>
       </c>
       <c r="G52" s="2">
-        <v>2.36</v>
+        <v>-6</v>
       </c>
       <c r="H52" s="2">
-        <v>-4.86</v>
+        <v>7.41</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
       </c>
       <c r="J52" s="1">
-        <v>27408.21</v>
+        <v>12459.49</v>
       </c>
       <c r="K52" s="1">
-        <v>27056.84</v>
+        <v>12202.71</v>
       </c>
       <c r="L52" s="1">
-        <v>27338.4</v>
+        <v>12935.53</v>
       </c>
       <c r="M52" t="str">
         <v/>
@@ -2540,37 +2540,37 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="C53" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="D53" s="1">
-        <v>20406.2</v>
+        <v>1602.7</v>
       </c>
       <c r="E53" s="2">
-        <v>0.74</v>
+        <v>-0.1</v>
       </c>
       <c r="F53" s="2">
-        <v>1.2</v>
+        <v>-0.23</v>
       </c>
       <c r="G53" s="2">
-        <v>-0.04</v>
+        <v>-0.26</v>
       </c>
       <c r="H53" s="2">
-        <v>0.93</v>
+        <v>2.29</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
       </c>
       <c r="J53" s="1">
-        <v>20268.28</v>
+        <v>1585.94</v>
       </c>
       <c r="K53" s="1">
-        <v>20384.16</v>
+        <v>1605.64</v>
       </c>
       <c r="L53" s="1">
-        <v>21172.3</v>
+        <v>1609.85</v>
       </c>
       <c r="M53" t="str">
         <v/>
@@ -2581,37 +2581,37 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="C54" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="D54" s="1">
-        <v>15149.7</v>
+        <v>1309.07</v>
       </c>
       <c r="E54" s="2">
-        <v>0.72</v>
+        <v>-0.17</v>
       </c>
       <c r="F54" s="2">
-        <v>1.32</v>
+        <v>-0.46</v>
       </c>
       <c r="G54" s="2">
-        <v>-1.97</v>
+        <v>-0.49</v>
       </c>
       <c r="H54" s="2">
-        <v>-1.71</v>
+        <v>0.84</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
       </c>
       <c r="J54" s="1">
-        <v>15637.66</v>
+        <v>1307.8</v>
       </c>
       <c r="K54" s="1">
-        <v>15230.51</v>
+        <v>1313.57</v>
       </c>
       <c r="L54" s="1">
-        <v>16078.97</v>
+        <v>1323.98</v>
       </c>
       <c r="M54" t="str">
         <v/>
@@ -2622,37 +2622,37 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="C55" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="D55" s="1">
-        <v>15731.85</v>
+        <v>49532.2</v>
       </c>
       <c r="E55" s="2">
-        <v>0.68</v>
+        <v>-0.2</v>
       </c>
       <c r="F55" s="2">
-        <v>1.24</v>
+        <v>-1.35</v>
       </c>
       <c r="G55" s="2">
-        <v>-1.78</v>
+        <v>-2.84</v>
       </c>
       <c r="H55" s="2">
-        <v>-1.52</v>
+        <v>12.92</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
       </c>
       <c r="J55" s="1">
-        <v>16015.26</v>
+        <v>47237.49</v>
       </c>
       <c r="K55" s="1">
-        <v>15808.31</v>
+        <v>50290.29</v>
       </c>
       <c r="L55" s="1">
-        <v>16593.07</v>
+        <v>51831.54</v>
       </c>
       <c r="M55" t="str">
         <v/>
@@ -2663,37 +2663,37 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="C56" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="D56" s="1">
-        <v>25446.95</v>
+        <v>1447.62</v>
       </c>
       <c r="E56" s="2">
-        <v>0.64</v>
+        <v>-0.2</v>
       </c>
       <c r="F56" s="2">
-        <v>0.95</v>
+        <v>-0.39</v>
       </c>
       <c r="G56" s="2">
-        <v>0.21</v>
+        <v>-0.43</v>
       </c>
       <c r="H56" s="2">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
       </c>
       <c r="J56" s="1">
-        <v>25475.68</v>
+        <v>1440.34</v>
       </c>
       <c r="K56" s="1">
-        <v>25434.82</v>
+        <v>1452.02</v>
       </c>
       <c r="L56" s="1">
-        <v>26371.66</v>
+        <v>1459.89</v>
       </c>
       <c r="M56" t="str">
         <v/>
@@ -2704,37 +2704,37 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>CNXMNC</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="C57" t="str">
-        <v>CNXMNC</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="D57" s="1">
-        <v>29829.35</v>
+        <v>1265.62</v>
       </c>
       <c r="E57" s="2">
-        <v>0.58</v>
+        <v>-0.21</v>
       </c>
       <c r="F57" s="2">
-        <v>0.31</v>
+        <v>-0.54</v>
       </c>
       <c r="G57" s="2">
-        <v>-1.67</v>
+        <v>-0.6</v>
       </c>
       <c r="H57" s="2">
-        <v>-2.42</v>
+        <v>0.32</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
       </c>
       <c r="J57" s="1">
-        <v>31435.94</v>
+        <v>1268.29</v>
       </c>
       <c r="K57" s="1">
-        <v>30088.94</v>
+        <v>1270.78</v>
       </c>
       <c r="L57" s="1">
-        <v>32071.49</v>
+        <v>1282.55</v>
       </c>
       <c r="M57" t="str">
         <v/>
@@ -2745,37 +2745,37 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="C58" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="D58" s="1">
-        <v>5285.75</v>
+        <v>19356.75</v>
       </c>
       <c r="E58" s="2">
-        <v>0.51</v>
+        <v>-0.26</v>
       </c>
       <c r="F58" s="2">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="G58" s="2">
-        <v>3.85</v>
+        <v>2.18</v>
       </c>
       <c r="H58" s="2">
-        <v>13.52</v>
+        <v>-9.59</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
       </c>
       <c r="J58" s="1">
-        <v>5090.26</v>
+        <v>20143.42</v>
       </c>
       <c r="K58" s="1">
-        <v>5223.52</v>
+        <v>19128.26</v>
       </c>
       <c r="L58" s="1">
-        <v>5311.02</v>
+        <v>19955.07</v>
       </c>
       <c r="M58" t="str">
         <v/>
@@ -2786,37 +2786,37 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="C59" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="D59" s="1">
-        <v>50016.15</v>
+        <v>6076.45</v>
       </c>
       <c r="E59" s="2">
-        <v>0.49</v>
+        <v>-0.35</v>
       </c>
       <c r="F59" s="2">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="G59" s="2">
-        <v>0.89</v>
+        <v>-2.45</v>
       </c>
       <c r="H59" s="2">
-        <v>5.15</v>
+        <v>-4.54</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
       </c>
       <c r="J59" s="1">
-        <v>49047.05</v>
+        <v>6751.03</v>
       </c>
       <c r="K59" s="1">
-        <v>49801.26</v>
+        <v>6096.46</v>
       </c>
       <c r="L59" s="1">
-        <v>51183.39</v>
+        <v>6342.48</v>
       </c>
       <c r="M59" t="str">
         <v/>
@@ -2827,37 +2827,37 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="C60" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="D60" s="1">
-        <v>10349.6</v>
+        <v>36425.8</v>
       </c>
       <c r="E60" s="2">
-        <v>0.49</v>
+        <v>-0.39</v>
       </c>
       <c r="F60" s="2">
-        <v>0.04</v>
+        <v>1.27</v>
       </c>
       <c r="G60" s="2">
-        <v>-2.5</v>
+        <v>-0.55</v>
       </c>
       <c r="H60" s="2">
-        <v>-15.38</v>
+        <v>-0.9</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
       </c>
       <c r="J60" s="1">
-        <v>11344.44</v>
+        <v>37133.89</v>
       </c>
       <c r="K60" s="1">
-        <v>10489.26</v>
+        <v>36497.08</v>
       </c>
       <c r="L60" s="1">
-        <v>10979.41</v>
+        <v>38776</v>
       </c>
       <c r="M60" t="str">
         <v/>
@@ -2868,37 +2868,37 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="C61" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="D61" s="1">
-        <v>48031.95</v>
+        <v>16930.9</v>
       </c>
       <c r="E61" s="2">
-        <v>0.46</v>
+        <v>-0.39</v>
       </c>
       <c r="F61" s="2">
-        <v>1.6</v>
+        <v>0.86</v>
       </c>
       <c r="G61" s="2">
-        <v>0.36</v>
+        <v>-0.57</v>
       </c>
       <c r="H61" s="2">
-        <v>9.2</v>
+        <v>-1.87</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
       </c>
       <c r="J61" s="1">
-        <v>44840.98</v>
+        <v>17234.81</v>
       </c>
       <c r="K61" s="1">
-        <v>47859.9</v>
+        <v>16975.83</v>
       </c>
       <c r="L61" s="1">
-        <v>48475.09</v>
+        <v>17803.23</v>
       </c>
       <c r="M61" t="str">
         <v/>
@@ -2909,37 +2909,37 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>Nifty midcap 150</v>
       </c>
       <c r="C62" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>NIFTYMIDCAP150</v>
       </c>
       <c r="D62" s="1">
-        <v>1631.7</v>
+        <v>21729.2</v>
       </c>
       <c r="E62" s="2">
-        <v>0.42</v>
+        <v>-0.42</v>
       </c>
       <c r="F62" s="2">
-        <v>5.05</v>
+        <v>0.58</v>
       </c>
       <c r="G62" s="2">
-        <v>3.06</v>
+        <v>-0.63</v>
       </c>
       <c r="H62" s="2">
-        <v>12.94</v>
+        <v>-2.46</v>
       </c>
       <c r="I62" s="1">
         <v>0</v>
       </c>
       <c r="J62" s="1">
-        <v>1462.59</v>
+        <v>22200.59</v>
       </c>
       <c r="K62" s="1">
-        <v>1579.58</v>
+        <v>21804.96</v>
       </c>
       <c r="L62" s="1">
-        <v>1567.04</v>
+        <v>22793.2</v>
       </c>
       <c r="M62" t="str">
         <v/>
@@ -2950,37 +2950,37 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="C63" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="D63" s="1">
-        <v>3299.35</v>
+        <v>22994.6</v>
       </c>
       <c r="E63" s="2">
-        <v>0.4</v>
+        <v>-0.43</v>
       </c>
       <c r="F63" s="2">
-        <v>-0.12</v>
+        <v>1.25</v>
       </c>
       <c r="G63" s="2">
-        <v>-0.67</v>
+        <v>1</v>
       </c>
       <c r="H63" s="2">
-        <v>1.77</v>
+        <v>-4.42</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
       </c>
       <c r="J63" s="1">
-        <v>3293.29</v>
+        <v>23521.33</v>
       </c>
       <c r="K63" s="1">
-        <v>3309.6</v>
+        <v>22946.24</v>
       </c>
       <c r="L63" s="1">
-        <v>3360.71</v>
+        <v>23911.93</v>
       </c>
       <c r="M63" t="str">
         <v/>
@@ -2991,37 +2991,37 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>CNXPSE</v>
       </c>
       <c r="C64" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>CNXPSE</v>
       </c>
       <c r="D64" s="1">
-        <v>9732.3</v>
+        <v>9239.3</v>
       </c>
       <c r="E64" s="2">
-        <v>0.35</v>
+        <v>-0.45</v>
       </c>
       <c r="F64" s="2">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="G64" s="2">
-        <v>1.03</v>
+        <v>-1.29</v>
       </c>
       <c r="H64" s="2">
-        <v>13.09</v>
+        <v>-6.23</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
       </c>
       <c r="J64" s="1">
-        <v>8954.64</v>
+        <v>10000.53</v>
       </c>
       <c r="K64" s="1">
-        <v>9671.01</v>
+        <v>9237.18</v>
       </c>
       <c r="L64" s="1">
-        <v>9855.91</v>
+        <v>9599.87</v>
       </c>
       <c r="M64" t="str">
         <v/>
@@ -3032,37 +3032,37 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="C65" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="D65" s="1">
-        <v>17833.45</v>
+        <v>68661.15</v>
       </c>
       <c r="E65" s="2">
-        <v>0.34</v>
+        <v>-0.49</v>
       </c>
       <c r="F65" s="2">
-        <v>1.47</v>
+        <v>0.73</v>
       </c>
       <c r="G65" s="2">
-        <v>0.19</v>
+        <v>-1.56</v>
       </c>
       <c r="H65" s="2">
-        <v>6.88</v>
+        <v>-1.01</v>
       </c>
       <c r="I65" s="1">
         <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>16925.81</v>
+        <v>70049.03</v>
       </c>
       <c r="K65" s="1">
-        <v>17789.78</v>
+        <v>69038.13</v>
       </c>
       <c r="L65" s="1">
-        <v>18189.06</v>
+        <v>72182.64</v>
       </c>
       <c r="M65" t="str">
         <v/>
@@ -3073,37 +3073,37 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>CNXENERGY</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="C66" t="str">
-        <v>CNXENERGY</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="D66" s="1">
-        <v>35975.9</v>
+        <v>59111.6</v>
       </c>
       <c r="E66" s="2">
-        <v>0.33</v>
+        <v>-0.5</v>
       </c>
       <c r="F66" s="2">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="G66" s="2">
-        <v>-1.8</v>
+        <v>-0.37</v>
       </c>
       <c r="H66" s="2">
-        <v>1.84</v>
+        <v>-2.27</v>
       </c>
       <c r="I66" s="1">
         <v>0</v>
       </c>
       <c r="J66" s="1">
-        <v>37699.53</v>
+        <v>60360.38</v>
       </c>
       <c r="K66" s="1">
-        <v>36314.99</v>
+        <v>59310.56</v>
       </c>
       <c r="L66" s="1">
-        <v>37758.86</v>
+        <v>62016.01</v>
       </c>
       <c r="M66" t="str">
         <v/>
@@ -3114,37 +3114,37 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="C67" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="D67" s="1">
-        <v>29407.35</v>
+        <v>13697.65</v>
       </c>
       <c r="E67" s="2">
-        <v>0.3</v>
+        <v>-0.55</v>
       </c>
       <c r="F67" s="2">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="G67" s="2">
-        <v>-0.38</v>
+        <v>-0.24</v>
       </c>
       <c r="H67" s="2">
-        <v>-5.59</v>
+        <v>-0.58</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
       </c>
       <c r="J67" s="1">
-        <v>30459.68</v>
+        <v>14004.55</v>
       </c>
       <c r="K67" s="1">
-        <v>29481.79</v>
+        <v>13735.1</v>
       </c>
       <c r="L67" s="1">
-        <v>30542.33</v>
+        <v>14455.65</v>
       </c>
       <c r="M67" t="str">
         <v/>
@@ -3155,37 +3155,37 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="C68" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="D68" s="1">
-        <v>2983.34</v>
+        <v>28439.25</v>
       </c>
       <c r="E68" s="2">
-        <v>0.22</v>
+        <v>-0.62</v>
       </c>
       <c r="F68" s="2">
-        <v>-0.31</v>
+        <v>1.68</v>
       </c>
       <c r="G68" s="2">
-        <v>-1.01</v>
-      </c>
-      <c r="H68" s="2">
-        <v>0.55</v>
+        <v>0.27</v>
+      </c>
+      <c r="H68" t="str">
+        <v/>
       </c>
       <c r="I68" s="1">
         <v>0</v>
       </c>
-      <c r="J68" s="1">
-        <v>3001.03</v>
+      <c r="J68" t="str">
+        <v/>
       </c>
       <c r="K68" s="1">
-        <v>2998.3</v>
+        <v>28389.21</v>
       </c>
       <c r="L68" s="1">
-        <v>3036.89</v>
+        <v>29566.8</v>
       </c>
       <c r="M68" t="str">
         <v/>
@@ -3196,37 +3196,37 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="C69" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="D69" s="1">
-        <v>60906.75</v>
+        <v>49537.55</v>
       </c>
       <c r="E69" s="2">
-        <v>0.21</v>
+        <v>-0.67</v>
       </c>
       <c r="F69" s="2">
-        <v>0.52</v>
+        <v>0.23</v>
       </c>
       <c r="G69" s="2">
-        <v>0.22</v>
+        <v>-0.08</v>
       </c>
       <c r="H69" s="2">
-        <v>-1.63</v>
+        <v>4.15</v>
       </c>
       <c r="I69" s="1">
         <v>0</v>
       </c>
       <c r="J69" s="1">
-        <v>61809.49</v>
+        <v>49059.66</v>
       </c>
       <c r="K69" s="1">
-        <v>61020.21</v>
+        <v>49763.68</v>
       </c>
       <c r="L69" s="1">
-        <v>63104.39</v>
+        <v>51116.29</v>
       </c>
       <c r="M69" t="str">
         <v/>
@@ -3237,37 +3237,37 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="C70" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="D70" s="1">
-        <v>2610.15</v>
+        <v>20256.35</v>
       </c>
       <c r="E70" s="2">
-        <v>0.21</v>
+        <v>-0.71</v>
       </c>
       <c r="F70" s="2">
-        <v>-0.33</v>
+        <v>0.45</v>
       </c>
       <c r="G70" s="2">
-        <v>-1.06</v>
+        <v>-0.78</v>
       </c>
       <c r="H70" s="2">
-        <v>-0.07</v>
+        <v>0.19</v>
       </c>
       <c r="I70" s="1">
         <v>0</v>
       </c>
       <c r="J70" s="1">
-        <v>2632.51</v>
+        <v>20269.36</v>
       </c>
       <c r="K70" s="1">
-        <v>2623.94</v>
+        <v>20363.33</v>
       </c>
       <c r="L70" s="1">
-        <v>2658.53</v>
+        <v>21125.93</v>
       </c>
       <c r="M70" t="str">
         <v/>
@@ -3278,37 +3278,37 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="C71" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="D71" s="1">
-        <v>3074.98</v>
+        <v>36146</v>
       </c>
       <c r="E71" s="2">
-        <v>0.2</v>
+        <v>-0.98</v>
       </c>
       <c r="F71" s="2">
-        <v>-0.34</v>
+        <v>1</v>
       </c>
       <c r="G71" s="2">
-        <v>-0.94</v>
+        <v>-1.34</v>
       </c>
       <c r="H71" s="2">
-        <v>0.74</v>
+        <v>2.32</v>
       </c>
       <c r="I71" s="1">
         <v>0</v>
       </c>
       <c r="J71" s="1">
-        <v>3085.26</v>
+        <v>37711.58</v>
       </c>
       <c r="K71" s="1">
-        <v>3089.94</v>
+        <v>36312.31</v>
       </c>
       <c r="L71" s="1">
-        <v>3128.66</v>
+        <v>37656.78</v>
       </c>
       <c r="M71" t="str">
         <v/>
@@ -3319,37 +3319,37 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="C72" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="D72" s="1">
-        <v>843.68</v>
+        <v>25177.45</v>
       </c>
       <c r="E72" s="2">
-        <v>0.2</v>
+        <v>-1.01</v>
       </c>
       <c r="F72" s="2">
-        <v>-0.42</v>
+        <v>-0.12</v>
       </c>
       <c r="G72" s="2">
-        <v>-1.35</v>
+        <v>-0.85</v>
       </c>
       <c r="H72" s="2">
-        <v>-5.36</v>
+        <v>0.77</v>
       </c>
       <c r="I72" s="1">
         <v>0</v>
       </c>
       <c r="J72" s="1">
-        <v>875.37</v>
+        <v>25475.55</v>
       </c>
       <c r="K72" s="1">
-        <v>849.44</v>
+        <v>25387.93</v>
       </c>
       <c r="L72" s="1">
-        <v>865.87</v>
+        <v>26324.01</v>
       </c>
       <c r="M72" t="str">
         <v/>
@@ -3360,37 +3360,37 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="C73" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="D73" s="1">
-        <v>25800.4</v>
+        <v>60220.05</v>
       </c>
       <c r="E73" s="2">
-        <v>0.18</v>
+        <v>-1.03</v>
       </c>
       <c r="F73" s="2">
-        <v>1.03</v>
+        <v>-0.62</v>
       </c>
       <c r="G73" s="2">
-        <v>-1.71</v>
+        <v>-0.91</v>
       </c>
       <c r="H73" s="2">
-        <v>14.44</v>
+        <v>-2.74</v>
       </c>
       <c r="I73" s="1">
         <v>0</v>
       </c>
       <c r="J73" s="1">
-        <v>23533.97</v>
+        <v>61786.34</v>
       </c>
       <c r="K73" s="1">
-        <v>25906.14</v>
+        <v>60848.88</v>
       </c>
       <c r="L73" s="1">
-        <v>26190.74</v>
+        <v>62983.37</v>
       </c>
       <c r="M73" t="str">
         <v/>
@@ -3401,37 +3401,37 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="C74" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="D74" s="1">
-        <v>28359.3</v>
+        <v>29052.4</v>
       </c>
       <c r="E74" s="2">
-        <v>0.15</v>
+        <v>-1.09</v>
       </c>
       <c r="F74" s="2">
-        <v>1.39</v>
+        <v>-0.5</v>
       </c>
       <c r="G74" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="H74" t="str">
-        <v/>
+        <v>-1.58</v>
+      </c>
+      <c r="H74" s="2">
+        <v>-6.73</v>
       </c>
       <c r="I74" s="1">
         <v>0</v>
       </c>
-      <c r="J74" t="str">
-        <v/>
+      <c r="J74" s="1">
+        <v>30436.75</v>
       </c>
       <c r="K74" s="1">
-        <v>28325.02</v>
+        <v>29387.64</v>
       </c>
       <c r="L74" s="1">
-        <v>29645.34</v>
+        <v>30474.55</v>
       </c>
       <c r="M74" t="str">
         <v/>
@@ -3442,37 +3442,37 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="C75" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="D75" s="1">
-        <v>3479.96</v>
+        <v>9191.25</v>
       </c>
       <c r="E75" s="2">
-        <v>0.15</v>
+        <v>-1.11</v>
       </c>
       <c r="F75" s="2">
-        <v>-0.71</v>
+        <v>2.05</v>
       </c>
       <c r="G75" s="2">
-        <v>-1.19</v>
+        <v>-0.92</v>
       </c>
       <c r="H75" s="2">
-        <v>-0.37</v>
+        <v>18.64</v>
       </c>
       <c r="I75" s="1">
         <v>0</v>
       </c>
       <c r="J75" s="1">
-        <v>3495.32</v>
+        <v>8813.13</v>
       </c>
       <c r="K75" s="1">
-        <v>3503.8</v>
+        <v>9203.04</v>
       </c>
       <c r="L75" s="1">
-        <v>3545.1</v>
+        <v>9525.45</v>
       </c>
       <c r="M75" t="str">
         <v/>
@@ -3483,37 +3483,37 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="C76" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="D76" s="1">
-        <v>53193.45</v>
+        <v>9567.75</v>
       </c>
       <c r="E76" s="2">
-        <v>0.12</v>
+        <v>-1.15</v>
       </c>
       <c r="F76" s="2">
-        <v>0.89</v>
+        <v>0.18</v>
       </c>
       <c r="G76" s="2">
-        <v>0.57</v>
+        <v>-0.68</v>
       </c>
       <c r="H76" s="2">
-        <v>0.92</v>
+        <v>11.17</v>
       </c>
       <c r="I76" s="1">
         <v>0</v>
       </c>
       <c r="J76" s="1">
-        <v>52581.8</v>
+        <v>8964.67</v>
       </c>
       <c r="K76" s="1">
-        <v>53166.01</v>
+        <v>9653.42</v>
       </c>
       <c r="L76" s="1">
-        <v>54411.53</v>
+        <v>9850.66</v>
       </c>
       <c r="M76" t="str">
         <v/>
@@ -3524,37 +3524,37 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="C77" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="D77" s="1">
-        <v>19447.4</v>
+        <v>47493.1</v>
       </c>
       <c r="E77" s="2">
-        <v>0.11</v>
+        <v>-1.17</v>
       </c>
       <c r="F77" s="2">
-        <v>1.53</v>
+        <v>0.46</v>
       </c>
       <c r="G77" s="2">
-        <v>1.05</v>
+        <v>-0.76</v>
       </c>
       <c r="H77" s="2">
-        <v>9.79</v>
+        <v>7.97</v>
       </c>
       <c r="I77" s="1">
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>18150.19</v>
+        <v>44875.34</v>
       </c>
       <c r="K77" s="1">
-        <v>19360.4</v>
+        <v>47821.92</v>
       </c>
       <c r="L77" s="1">
-        <v>19726.47</v>
+        <v>48481.22</v>
       </c>
       <c r="M77" t="str">
         <v/>
@@ -3565,37 +3565,37 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="C78" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="D78" s="1">
-        <v>15860.65</v>
+        <v>16134.3</v>
       </c>
       <c r="E78" s="2">
-        <v>0.08</v>
+        <v>-1.18</v>
       </c>
       <c r="F78" s="2">
-        <v>0.03</v>
+        <v>0.77</v>
       </c>
       <c r="G78" s="2">
-        <v>-1.72</v>
+        <v>-0.95</v>
       </c>
       <c r="H78" s="2">
-        <v>8.34</v>
+        <v>0.81</v>
       </c>
       <c r="I78" s="1">
         <v>0</v>
       </c>
       <c r="J78" s="1">
-        <v>15413.92</v>
+        <v>16135.62</v>
       </c>
       <c r="K78" s="1">
-        <v>16023.23</v>
+        <v>16237.94</v>
       </c>
       <c r="L78" s="1">
-        <v>16483.52</v>
+        <v>16928.81</v>
       </c>
       <c r="M78" t="str">
         <v/>
@@ -3606,37 +3606,37 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="C79" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="D79" s="1">
-        <v>3289.43</v>
+        <v>44730.7</v>
       </c>
       <c r="E79" s="2">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="F79" s="2">
-        <v>-0.25</v>
+        <v>-0.3</v>
       </c>
       <c r="G79" s="2">
-        <v>-0.58</v>
+        <v>0.5</v>
       </c>
       <c r="H79" s="2">
-        <v>2.07</v>
+        <v>-19.37</v>
       </c>
       <c r="I79" s="1">
         <v>0</v>
       </c>
       <c r="J79" s="1">
-        <v>3278.25</v>
+        <v>49195.8</v>
       </c>
       <c r="K79" s="1">
-        <v>3299.08</v>
+        <v>44778.81</v>
       </c>
       <c r="L79" s="1">
-        <v>3328.9</v>
+        <v>46324</v>
       </c>
       <c r="M79" t="str">
         <v/>
@@ -3647,37 +3647,37 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="C80" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="D80" s="1">
-        <v>196.79</v>
+        <v>17613.55</v>
       </c>
       <c r="E80" s="2">
-        <v>0</v>
+        <v>-1.23</v>
       </c>
       <c r="F80" s="2">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="G80" s="2">
-        <v>0</v>
+        <v>-1.04</v>
       </c>
       <c r="H80" s="2">
-        <v>-21.01</v>
+        <v>5.57</v>
       </c>
       <c r="I80" s="1">
         <v>0</v>
       </c>
       <c r="J80" s="1">
-        <v>182.1</v>
+        <v>16937.04</v>
       </c>
       <c r="K80" s="1">
-        <v>196.76</v>
+        <v>17764.07</v>
       </c>
       <c r="L80" s="1">
-        <v>192.73</v>
+        <v>18170.76</v>
       </c>
       <c r="M80" t="str">
         <v/>
@@ -3688,37 +3688,37 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>CNXPHARMA</v>
+        <v>NIFTY50PR1XINV</v>
       </c>
       <c r="C81" t="str">
-        <v>CNXPHARMA</v>
+        <v>NIFTY50PR1XINV</v>
       </c>
       <c r="D81" s="1">
-        <v>26075</v>
+        <v>232.9</v>
       </c>
       <c r="E81" s="2">
-        <v>-0.01</v>
+        <v>-1.38</v>
       </c>
       <c r="F81" s="2">
-        <v>0.44</v>
+        <v>-1.79</v>
       </c>
       <c r="G81" s="2">
-        <v>-1.37</v>
+        <v>-1.29</v>
       </c>
       <c r="H81" s="2">
-        <v>14.75</v>
+        <v>16.45</v>
       </c>
       <c r="I81" s="1">
         <v>0</v>
       </c>
       <c r="J81" s="1">
-        <v>24273.47</v>
+        <v>218.42</v>
       </c>
       <c r="K81" s="1">
-        <v>26251.6</v>
+        <v>235.46</v>
       </c>
       <c r="L81" s="1">
-        <v>26573.54</v>
+        <v>226.11</v>
       </c>
       <c r="M81" t="str">
         <v/>
@@ -3729,37 +3729,37 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="C82" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="D82" s="1">
-        <v>1603.44</v>
+        <v>188.9</v>
       </c>
       <c r="E82" s="2">
-        <v>-0.1</v>
+        <v>-1.38</v>
       </c>
       <c r="F82" s="2">
-        <v>-0.18</v>
+        <v>-1.79</v>
       </c>
       <c r="G82" s="2">
-        <v>-0.22</v>
+        <v>-1.31</v>
       </c>
       <c r="H82" s="2">
-        <v>2.33</v>
+        <v>15.43</v>
       </c>
       <c r="I82" s="1">
         <v>0</v>
       </c>
       <c r="J82" s="1">
-        <v>1585.55</v>
+        <v>178.04</v>
       </c>
       <c r="K82" s="1">
-        <v>1606.72</v>
+        <v>190.99</v>
       </c>
       <c r="L82" s="1">
-        <v>1610.11</v>
+        <v>183.44</v>
       </c>
       <c r="M82" t="str">
         <v/>
@@ -3770,37 +3770,37 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="C83" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="D83" s="1">
-        <v>49995.6</v>
+        <v>19115.6</v>
       </c>
       <c r="E83" s="2">
-        <v>-0.19</v>
+        <v>-1.39</v>
       </c>
       <c r="F83" s="2">
-        <v>-0.43</v>
+        <v>-0.2</v>
       </c>
       <c r="G83" s="2">
-        <v>-1.93</v>
+        <v>-0.68</v>
       </c>
       <c r="H83" s="2">
-        <v>13.97</v>
+        <v>7.91</v>
       </c>
       <c r="I83" s="1">
         <v>0</v>
       </c>
       <c r="J83" s="1">
-        <v>47182.16</v>
+        <v>18166.43</v>
       </c>
       <c r="K83" s="1">
-        <v>50642.44</v>
+        <v>19319.52</v>
       </c>
       <c r="L83" s="1">
-        <v>51921.29</v>
+        <v>19711.98</v>
       </c>
       <c r="M83" t="str">
         <v/>
@@ -3811,37 +3811,37 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>CNXMNC</v>
       </c>
       <c r="C84" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>CNXMNC</v>
       </c>
       <c r="D84" s="1">
-        <v>1448.63</v>
+        <v>29487.55</v>
       </c>
       <c r="E84" s="2">
-        <v>-0.28</v>
+        <v>-1.45</v>
       </c>
       <c r="F84" s="2">
-        <v>-0.32</v>
+        <v>-0.84</v>
       </c>
       <c r="G84" s="2">
-        <v>-0.36</v>
+        <v>-2.8</v>
       </c>
       <c r="H84" s="2">
-        <v>1.68</v>
+        <v>-3.53</v>
       </c>
       <c r="I84" s="1">
         <v>0</v>
       </c>
       <c r="J84" s="1">
-        <v>1440.09</v>
+        <v>31428.99</v>
       </c>
       <c r="K84" s="1">
-        <v>1453.57</v>
+        <v>29954.52</v>
       </c>
       <c r="L84" s="1">
-        <v>1460.5</v>
+        <v>31920.11</v>
       </c>
       <c r="M84" t="str">
         <v/>
@@ -3852,37 +3852,37 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="C85" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="D85" s="1">
-        <v>1309.37</v>
+        <v>8042.55</v>
       </c>
       <c r="E85" s="2">
-        <v>-0.43</v>
+        <v>-1.53</v>
       </c>
       <c r="F85" s="2">
-        <v>-0.44</v>
+        <v>-1.03</v>
       </c>
       <c r="G85" s="2">
-        <v>-0.47</v>
+        <v>0.33</v>
       </c>
       <c r="H85" s="2">
-        <v>0.86</v>
+        <v>-5.75</v>
       </c>
       <c r="I85" s="1">
         <v>0</v>
       </c>
       <c r="J85" s="1">
-        <v>1307.66</v>
+        <v>8576.38</v>
       </c>
       <c r="K85" s="1">
-        <v>1315.28</v>
+        <v>8091.2</v>
       </c>
       <c r="L85" s="1">
-        <v>1324.87</v>
+        <v>8392.45</v>
       </c>
       <c r="M85" t="str">
         <v/>
@@ -3893,37 +3893,37 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="C86" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="D86" s="1">
-        <v>1265.92</v>
+        <v>1615.9</v>
       </c>
       <c r="E86" s="2">
-        <v>-0.51</v>
+        <v>-1.55</v>
       </c>
       <c r="F86" s="2">
-        <v>-0.51</v>
+        <v>4.03</v>
       </c>
       <c r="G86" s="2">
-        <v>-0.57</v>
+        <v>2.07</v>
       </c>
       <c r="H86" s="2">
-        <v>0.35</v>
+        <v>11.85</v>
       </c>
       <c r="I86" s="1">
         <v>0</v>
       </c>
       <c r="J86" s="1">
-        <v>1268.18</v>
+        <v>1464.8</v>
       </c>
       <c r="K86" s="1">
-        <v>1272.75</v>
+        <v>1595.38</v>
       </c>
       <c r="L86" s="1">
-        <v>1283.53</v>
+        <v>1568.8</v>
       </c>
       <c r="M86" t="str">
         <v/>
@@ -3934,37 +3934,37 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="C87" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="D87" s="1">
-        <v>55337.55</v>
+        <v>52148.6</v>
       </c>
       <c r="E87" s="2">
-        <v>-0.6</v>
+        <v>-1.66</v>
       </c>
       <c r="F87" s="2">
-        <v>0</v>
+        <v>-1.09</v>
       </c>
       <c r="G87" s="2">
-        <v>2.33</v>
+        <v>-1.41</v>
       </c>
       <c r="H87" s="2">
-        <v>10</v>
+        <v>-1.06</v>
       </c>
       <c r="I87" s="1">
         <v>0</v>
       </c>
       <c r="J87" s="1">
-        <v>52117.49</v>
+        <v>52572.02</v>
       </c>
       <c r="K87" s="1">
-        <v>55117.99</v>
+        <v>52960.69</v>
       </c>
       <c r="L87" s="1">
-        <v>55870.88</v>
+        <v>54354.16</v>
       </c>
       <c r="M87" t="str">
         <v/>
@@ -3975,37 +3975,37 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>NIFTY50PR1XINV</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="C88" t="str">
-        <v>NIFTY50PR1XINV</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="D88" s="1">
-        <v>235.1</v>
+        <v>25528.3</v>
       </c>
       <c r="E88" s="2">
-        <v>-1.59</v>
+        <v>-1.75</v>
       </c>
       <c r="F88" s="2">
-        <v>-0.86</v>
+        <v>-0.03</v>
       </c>
       <c r="G88" s="2">
-        <v>-0.36</v>
+        <v>-2.75</v>
       </c>
       <c r="H88" s="2">
-        <v>17.55</v>
+        <v>13.23</v>
       </c>
       <c r="I88" s="1">
         <v>0</v>
       </c>
       <c r="J88" s="1">
-        <v>218.07</v>
+        <v>23564.99</v>
       </c>
       <c r="K88" s="1">
-        <v>236.01</v>
+        <v>25848.94</v>
       </c>
       <c r="L88" s="1">
-        <v>225.31</v>
+        <v>26198.14</v>
       </c>
       <c r="M88" t="str">
         <v/>
@@ -4016,37 +4016,37 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="C89" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="D89" s="1">
-        <v>190.7</v>
+        <v>53689.85</v>
       </c>
       <c r="E89" s="2">
-        <v>-1.6</v>
+        <v>-2.23</v>
       </c>
       <c r="F89" s="2">
-        <v>-0.86</v>
+        <v>-2.98</v>
       </c>
       <c r="G89" s="2">
-        <v>-0.37</v>
+        <v>-0.72</v>
       </c>
       <c r="H89" s="2">
-        <v>16.53</v>
+        <v>6.72</v>
       </c>
       <c r="I89" s="1">
         <v>0</v>
       </c>
       <c r="J89" s="1">
-        <v>177.77</v>
+        <v>52149.55</v>
       </c>
       <c r="K89" s="1">
-        <v>191.43</v>
+        <v>54827.74</v>
       </c>
       <c r="L89" s="1">
-        <v>182.8</v>
+        <v>55842.94</v>
       </c>
       <c r="M89" t="str">
         <v/>
@@ -4063,31 +4063,31 @@
         <v>INDIAVIX</v>
       </c>
       <c r="D90" s="1">
-        <v>14.12</v>
+        <v>14.02</v>
       </c>
       <c r="E90" s="2">
-        <v>-7.41</v>
+        <v>-4.17</v>
       </c>
       <c r="F90" s="2">
-        <v>-1.81</v>
+        <v>-2.5</v>
       </c>
       <c r="G90" s="2">
-        <v>4.67</v>
+        <v>3.93</v>
       </c>
       <c r="H90" s="2">
-        <v>48.95</v>
+        <v>47.89</v>
       </c>
       <c r="I90" s="1">
         <v>0</v>
       </c>
       <c r="J90" s="1">
-        <v>14.71</v>
+        <v>14.76</v>
       </c>
       <c r="K90" s="1">
-        <v>14.12</v>
+        <v>14.18</v>
       </c>
       <c r="L90" s="1">
-        <v>12.17</v>
+        <v>12.26</v>
       </c>
       <c r="M90" t="str">
         <v/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -449,37 +449,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>India VIX</v>
       </c>
       <c r="C2" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>INDIAVIX</v>
       </c>
       <c r="D2" s="1">
-        <v>16312</v>
+        <v>14.77</v>
       </c>
       <c r="E2" s="2">
-        <v>2.79</v>
+        <v>5.05</v>
       </c>
       <c r="F2" s="2">
-        <v>3.64</v>
+        <v>5.05</v>
       </c>
       <c r="G2" s="2">
-        <v>2.52</v>
+        <v>9.49</v>
       </c>
       <c r="H2" s="2">
-        <v>-25.84</v>
+        <v>55.8</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>18511.34</v>
+        <v>14.81</v>
       </c>
       <c r="K2" s="1">
-        <v>15975.59</v>
+        <v>14.27</v>
       </c>
       <c r="L2" s="1">
-        <v>17358.33</v>
+        <v>12.36</v>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -490,37 +490,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="C3" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="D3" s="1">
-        <v>10696.5</v>
+        <v>8294.1</v>
       </c>
       <c r="E3" s="2">
-        <v>2.79</v>
+        <v>2.46</v>
       </c>
       <c r="F3" s="2">
-        <v>3.61</v>
+        <v>2.46</v>
       </c>
       <c r="G3" s="2">
-        <v>2.5</v>
+        <v>3.47</v>
       </c>
       <c r="H3" s="2">
-        <v>-27.24</v>
+        <v>-2.8</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>12272.23</v>
+        <v>8575.33</v>
       </c>
       <c r="K3" s="1">
-        <v>10477.56</v>
+        <v>8128.49</v>
       </c>
       <c r="L3" s="1">
-        <v>11388.72</v>
+        <v>8374.79</v>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -531,37 +531,37 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Nifty IT</v>
+        <v>NIFTY50PR1XINV</v>
       </c>
       <c r="C4" t="str">
-        <v>CNXIT</v>
+        <v>NIFTY50PR1XINV</v>
       </c>
       <c r="D4" s="1">
-        <v>30697</v>
+        <v>233.5</v>
       </c>
       <c r="E4" s="2">
-        <v>1.74</v>
+        <v>1.15</v>
       </c>
       <c r="F4" s="2">
-        <v>7.43</v>
+        <v>1.15</v>
       </c>
       <c r="G4" s="2">
-        <v>10.8</v>
+        <v>-1.04</v>
       </c>
       <c r="H4" s="2">
-        <v>-18.97</v>
+        <v>16.75</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>30973.81</v>
+        <v>218.74</v>
       </c>
       <c r="K4" s="1">
-        <v>29156.09</v>
+        <v>234.35</v>
       </c>
       <c r="L4" s="1">
-        <v>29790.55</v>
+        <v>226.77</v>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -572,37 +572,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="C5" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="D5" s="1">
-        <v>8350.5</v>
+        <v>189.35</v>
       </c>
       <c r="E5" s="2">
-        <v>1.69</v>
+        <v>1.15</v>
       </c>
       <c r="F5" s="2">
-        <v>1.84</v>
+        <v>1.15</v>
       </c>
       <c r="G5" s="2">
-        <v>3.38</v>
+        <v>-1.07</v>
       </c>
       <c r="H5" s="2">
-        <v>-16.87</v>
+        <v>15.7</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>8805.43</v>
+        <v>178.28</v>
       </c>
       <c r="K5" s="1">
-        <v>8206.58</v>
+        <v>190.07</v>
       </c>
       <c r="L5" s="1">
-        <v>8429.8</v>
+        <v>183.97</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -613,37 +613,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="C6" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="D6" s="1">
-        <v>29932.15</v>
+        <v>3284.34</v>
       </c>
       <c r="E6" s="2">
-        <v>1.62</v>
+        <v>0.09</v>
       </c>
       <c r="F6" s="2">
-        <v>2.89</v>
+        <v>0.09</v>
       </c>
       <c r="G6" s="2">
-        <v>3.16</v>
+        <v>-0.73</v>
       </c>
       <c r="H6" s="2">
-        <v>-11.07</v>
+        <v>1.91</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>31030.11</v>
+        <v>3279.61</v>
       </c>
       <c r="K6" s="1">
-        <v>29345.65</v>
+        <v>3289.81</v>
       </c>
       <c r="L6" s="1">
-        <v>30205.2</v>
+        <v>3324.09</v>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -654,37 +654,37 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="C7" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="D7" s="1">
-        <v>11419.05</v>
+        <v>1602.59</v>
       </c>
       <c r="E7" s="2">
-        <v>1.54</v>
+        <v>0.07</v>
       </c>
       <c r="F7" s="2">
-        <v>2.41</v>
+        <v>0.07</v>
       </c>
       <c r="G7" s="2">
-        <v>2.46</v>
+        <v>-0.27</v>
       </c>
       <c r="H7" s="2">
-        <v>-13.98</v>
+        <v>2.28</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>12217.99</v>
+        <v>1586.32</v>
       </c>
       <c r="K7" s="1">
-        <v>11232.17</v>
+        <v>1604.46</v>
       </c>
       <c r="L7" s="1">
-        <v>11609.18</v>
+        <v>1609.47</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -695,37 +695,37 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="C8" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="D8" s="1">
-        <v>7339.85</v>
+        <v>1308.53</v>
       </c>
       <c r="E8" s="2">
-        <v>1.54</v>
+        <v>0.06</v>
       </c>
       <c r="F8" s="2">
-        <v>2.53</v>
+        <v>0.06</v>
       </c>
       <c r="G8" s="2">
-        <v>3.73</v>
+        <v>-0.53</v>
       </c>
       <c r="H8" s="2">
-        <v>-2.94</v>
+        <v>0.8</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>7337.14</v>
+        <v>1307.91</v>
       </c>
       <c r="K8" s="1">
-        <v>7208.26</v>
+        <v>1311.79</v>
       </c>
       <c r="L8" s="1">
-        <v>7430.9</v>
+        <v>1323.02</v>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -736,37 +736,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="C9" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="D9" s="1">
-        <v>27568.05</v>
+        <v>1447.65</v>
       </c>
       <c r="E9" s="2">
-        <v>1.48</v>
+        <v>0.04</v>
       </c>
       <c r="F9" s="2">
-        <v>1.27</v>
+        <v>0.04</v>
       </c>
       <c r="G9" s="2">
-        <v>3.27</v>
+        <v>-0.43</v>
       </c>
       <c r="H9" s="2">
-        <v>-4.01</v>
+        <v>1.61</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>27396.83</v>
+        <v>1440.58</v>
       </c>
       <c r="K9" s="1">
-        <v>27166.14</v>
+        <v>1450.48</v>
       </c>
       <c r="L9" s="1">
-        <v>27314.99</v>
+        <v>1459.16</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -777,37 +777,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>NIFTYAUTO</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="C10" t="str">
-        <v>NIFTYAUTO</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="D10" s="1">
-        <v>25525.5</v>
+        <v>1264.7</v>
       </c>
       <c r="E10" s="2">
-        <v>1.47</v>
+        <v>0.03</v>
       </c>
       <c r="F10" s="2">
-        <v>2.68</v>
+        <v>0.03</v>
       </c>
       <c r="G10" s="2">
-        <v>-2.92</v>
+        <v>-0.67</v>
       </c>
       <c r="H10" s="2">
-        <v>-9.45</v>
+        <v>0.25</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>26975.88</v>
+        <v>1268.34</v>
       </c>
       <c r="K10" s="1">
-        <v>25427.41</v>
+        <v>1268.71</v>
       </c>
       <c r="L10" s="1">
-        <v>27584.02</v>
+        <v>1281.51</v>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -818,37 +818,37 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="C11" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="D11" s="1">
-        <v>25313.05</v>
+        <v>202.16</v>
       </c>
       <c r="E11" s="2">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="H11" s="2">
-        <v>-8.33</v>
+        <v>-18.86</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>26273</v>
+        <v>181.13</v>
       </c>
       <c r="K11" s="1">
-        <v>25009.75</v>
+        <v>199.13</v>
       </c>
       <c r="L11" s="1">
-        <v>25663.49</v>
+        <v>194.2</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -859,37 +859,37 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="C12" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="D12" s="1">
-        <v>5296.65</v>
+        <v>3486.59</v>
       </c>
       <c r="E12" s="2">
-        <v>1.44</v>
+        <v>-0.03</v>
       </c>
       <c r="F12" s="2">
-        <v>2.23</v>
+        <v>-0.03</v>
       </c>
       <c r="G12" s="2">
-        <v>4.07</v>
+        <v>-1</v>
       </c>
       <c r="H12" s="2">
-        <v>13.75</v>
+        <v>-0.18</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>5095.48</v>
+        <v>3495.63</v>
       </c>
       <c r="K12" s="1">
-        <v>5236.54</v>
+        <v>3491.27</v>
       </c>
       <c r="L12" s="1">
-        <v>5310.46</v>
+        <v>3539.34</v>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -900,37 +900,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="C13" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="D13" s="1">
-        <v>22939.95</v>
+        <v>2981.18</v>
       </c>
       <c r="E13" s="2">
-        <v>1.4</v>
+        <v>-0.05</v>
       </c>
       <c r="F13" s="2">
-        <v>1.86</v>
+        <v>-0.05</v>
       </c>
       <c r="G13" s="2">
-        <v>1.41</v>
+        <v>-1.09</v>
       </c>
       <c r="H13" s="2">
-        <v>-12.21</v>
+        <v>0.48</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>24198.86</v>
+        <v>3001.37</v>
       </c>
       <c r="K13" s="1">
-        <v>22685.6</v>
+        <v>2988.4</v>
       </c>
       <c r="L13" s="1">
-        <v>23577.63</v>
+        <v>3030.95</v>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -941,37 +941,37 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="C14" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="D14" s="1">
-        <v>27169.6</v>
+        <v>3073.57</v>
       </c>
       <c r="E14" s="2">
-        <v>1.39</v>
+        <v>-0.08</v>
       </c>
       <c r="F14" s="2">
-        <v>1.3</v>
+        <v>-0.08</v>
       </c>
       <c r="G14" s="2">
-        <v>2.31</v>
+        <v>-0.99</v>
       </c>
       <c r="H14" s="2">
-        <v>-9.97</v>
+        <v>0.69</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>28612.29</v>
+        <v>3085.84</v>
       </c>
       <c r="K14" s="1">
-        <v>26891.44</v>
+        <v>3080.32</v>
       </c>
       <c r="L14" s="1">
-        <v>27792.73</v>
+        <v>3122.97</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -982,37 +982,37 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="C15" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="D15" s="1">
-        <v>3825.1</v>
+        <v>2608.99</v>
       </c>
       <c r="E15" s="2">
-        <v>1.3</v>
+        <v>-0.08</v>
       </c>
       <c r="F15" s="2">
-        <v>1.98</v>
+        <v>-0.08</v>
       </c>
       <c r="G15" s="2">
-        <v>1.13</v>
+        <v>-1.11</v>
       </c>
       <c r="H15" s="2">
-        <v>-12.13</v>
+        <v>-0.11</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>4045.25</v>
+        <v>2632.47</v>
       </c>
       <c r="K15" s="1">
-        <v>3785.9</v>
+        <v>2615.26</v>
       </c>
       <c r="L15" s="1">
-        <v>3951.03</v>
+        <v>2653.16</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -1023,37 +1023,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="C16" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="D16" s="1">
-        <v>10790.85</v>
+        <v>10544.4</v>
       </c>
       <c r="E16" s="2">
-        <v>1.13</v>
+        <v>-0.12</v>
       </c>
       <c r="F16" s="2">
-        <v>3.53</v>
+        <v>-0.12</v>
       </c>
       <c r="G16" s="2">
-        <v>2.38</v>
+        <v>-0.66</v>
       </c>
       <c r="H16" s="2">
-        <v>-13.56</v>
+        <v>-13.79</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>11254.57</v>
+        <v>11315.17</v>
       </c>
       <c r="K16" s="1">
-        <v>10591.88</v>
+        <v>10520.12</v>
       </c>
       <c r="L16" s="1">
-        <v>11153.49</v>
+        <v>10920.58</v>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -1064,37 +1064,37 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="C17" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="D17" s="1">
-        <v>23936.6</v>
+        <v>842.29</v>
       </c>
       <c r="E17" s="2">
-        <v>1.05</v>
+        <v>-0.14</v>
       </c>
       <c r="F17" s="2">
-        <v>1.65</v>
+        <v>-0.14</v>
       </c>
       <c r="G17" s="2">
-        <v>0.85</v>
+        <v>-1.51</v>
       </c>
       <c r="H17" s="2">
-        <v>-10.31</v>
+        <v>-5.51</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>25093.5</v>
+        <v>874.39</v>
       </c>
       <c r="K17" s="1">
-        <v>23744.45</v>
+        <v>845.59</v>
       </c>
       <c r="L17" s="1">
-        <v>24705.77</v>
+        <v>863.13</v>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -1105,37 +1105,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="C18" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="D18" s="1">
-        <v>10565.4</v>
+        <v>1643.9</v>
       </c>
       <c r="E18" s="2">
-        <v>1.04</v>
+        <v>-0.26</v>
       </c>
       <c r="F18" s="2">
-        <v>2.13</v>
+        <v>-0.26</v>
       </c>
       <c r="G18" s="2">
-        <v>-0.46</v>
+        <v>3.83</v>
       </c>
       <c r="H18" s="2">
-        <v>-13.62</v>
+        <v>13.79</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>11329.05</v>
+        <v>1467.11</v>
       </c>
       <c r="K18" s="1">
-        <v>10498.26</v>
+        <v>1612.22</v>
       </c>
       <c r="L18" s="1">
-        <v>10948.18</v>
+        <v>1572.07</v>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -1146,37 +1146,37 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="C19" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="D19" s="1">
-        <v>8668.25</v>
+        <v>53699.95</v>
       </c>
       <c r="E19" s="2">
-        <v>1.03</v>
+        <v>-0.27</v>
       </c>
       <c r="F19" s="2">
-        <v>1.09</v>
+        <v>-0.27</v>
       </c>
       <c r="G19" s="2">
-        <v>-0.75</v>
+        <v>-0.7</v>
       </c>
       <c r="H19" s="2">
-        <v>-9.86</v>
+        <v>6.74</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>9244.19</v>
+        <v>52179.54</v>
       </c>
       <c r="K19" s="1">
-        <v>8648.11</v>
+        <v>54484.23</v>
       </c>
       <c r="L19" s="1">
-        <v>9077.85</v>
+        <v>55763.52</v>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1187,37 +1187,37 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="C20" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="D20" s="1">
-        <v>8481.7</v>
+        <v>3293.93</v>
       </c>
       <c r="E20" s="2">
-        <v>1</v>
+        <v>-0.28</v>
       </c>
       <c r="F20" s="2">
-        <v>3.81</v>
+        <v>-0.28</v>
       </c>
       <c r="G20" s="2">
-        <v>5.67</v>
+        <v>-0.83</v>
       </c>
       <c r="H20" s="2">
-        <v>-9.99</v>
+        <v>1.6</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>8276.45</v>
+        <v>3294.67</v>
       </c>
       <c r="K20" s="1">
-        <v>8280.59</v>
+        <v>3302.32</v>
       </c>
       <c r="L20" s="1">
-        <v>8542.69</v>
+        <v>3353.88</v>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -1228,37 +1228,37 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>NIFTY100ESG</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="C21" t="str">
-        <v>NIFTY100ESG</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="D21" s="1">
-        <v>4735.35</v>
+        <v>52153.85</v>
       </c>
       <c r="E21" s="2">
-        <v>0.94</v>
+        <v>-0.3</v>
       </c>
       <c r="F21" s="2">
-        <v>2.1</v>
+        <v>-0.3</v>
       </c>
       <c r="G21" s="2">
-        <v>1.1</v>
+        <v>-1.4</v>
       </c>
       <c r="H21" s="2">
-        <v>-8.61</v>
+        <v>-1.05</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
       </c>
       <c r="J21" s="1">
-        <v>4923.92</v>
+        <v>52561.74</v>
       </c>
       <c r="K21" s="1">
-        <v>4689.56</v>
+        <v>52721.92</v>
       </c>
       <c r="L21" s="1">
-        <v>4900.05</v>
+        <v>54265.33</v>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -1269,37 +1269,37 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="C22" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="D22" s="1">
-        <v>31010.75</v>
+        <v>68695.85</v>
       </c>
       <c r="E22" s="2">
-        <v>0.84</v>
+        <v>-0.42</v>
       </c>
       <c r="F22" s="2">
-        <v>1.62</v>
+        <v>-0.42</v>
       </c>
       <c r="G22" s="2">
-        <v>0.34</v>
+        <v>-1.51</v>
       </c>
       <c r="H22" s="2">
-        <v>-6.96</v>
+        <v>-0.96</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
       </c>
       <c r="J22" s="1">
-        <v>32397.4</v>
+        <v>70047.92</v>
       </c>
       <c r="K22" s="1">
-        <v>30816.6</v>
+        <v>68969.8</v>
       </c>
       <c r="L22" s="1">
-        <v>32215.2</v>
+        <v>71956.6</v>
       </c>
       <c r="M22" t="str">
         <v/>
@@ -1310,37 +1310,37 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="C23" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="D23" s="1">
-        <v>13769.7</v>
+        <v>12066.4</v>
       </c>
       <c r="E23" s="2">
-        <v>0.82</v>
+        <v>-0.55</v>
       </c>
       <c r="F23" s="2">
-        <v>3.43</v>
+        <v>-0.55</v>
       </c>
       <c r="G23" s="2">
-        <v>3.12</v>
+        <v>-5.44</v>
       </c>
       <c r="H23" s="2">
-        <v>-9.96</v>
+        <v>8.05</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>14420.68</v>
+        <v>12472.86</v>
       </c>
       <c r="K23" s="1">
-        <v>13521.47</v>
+        <v>12170.45</v>
       </c>
       <c r="L23" s="1">
-        <v>14115.95</v>
+        <v>12892.37</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -1351,37 +1351,37 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="C24" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="D24" s="1">
-        <v>7534.9</v>
+        <v>6031.35</v>
       </c>
       <c r="E24" s="2">
-        <v>0.79</v>
+        <v>-0.56</v>
       </c>
       <c r="F24" s="2">
-        <v>0.75</v>
+        <v>-0.56</v>
       </c>
       <c r="G24" s="2">
-        <v>-2.2</v>
+        <v>-3.17</v>
       </c>
       <c r="H24" s="2">
-        <v>-12.43</v>
+        <v>-5.25</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <v>7708.14</v>
+        <v>6748.38</v>
       </c>
       <c r="K24" s="1">
-        <v>7536</v>
+        <v>6081.57</v>
       </c>
       <c r="L24" s="1">
-        <v>7821.74</v>
+        <v>6324.49</v>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -1392,37 +1392,37 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="C25" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="D25" s="1">
-        <v>13249.55</v>
+        <v>28924.95</v>
       </c>
       <c r="E25" s="2">
-        <v>0.73</v>
+        <v>-0.57</v>
       </c>
       <c r="F25" s="2">
-        <v>1.43</v>
+        <v>-0.57</v>
       </c>
       <c r="G25" s="2">
-        <v>0.6</v>
+        <v>-2.01</v>
       </c>
       <c r="H25" s="2">
-        <v>-8.83</v>
+        <v>-7.14</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <v>13818.97</v>
+        <v>30414.07</v>
       </c>
       <c r="K25" s="1">
-        <v>13173.34</v>
+        <v>29261.63</v>
       </c>
       <c r="L25" s="1">
-        <v>13720.31</v>
+        <v>30395.42</v>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -1433,37 +1433,37 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="C26" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="D26" s="1">
-        <v>10987.75</v>
+        <v>5598.5</v>
       </c>
       <c r="E26" s="2">
-        <v>0.71</v>
+        <v>-0.59</v>
       </c>
       <c r="F26" s="2">
-        <v>0.77</v>
+        <v>-0.59</v>
       </c>
       <c r="G26" s="2">
-        <v>-0.77</v>
+        <v>2.3</v>
       </c>
       <c r="H26" s="2">
-        <v>-10.59</v>
+        <v>-12.32</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>11523.11</v>
+        <v>5960.48</v>
       </c>
       <c r="K26" s="1">
-        <v>10975</v>
+        <v>5529.85</v>
       </c>
       <c r="L26" s="1">
-        <v>11581.4</v>
+        <v>5706.91</v>
       </c>
       <c r="M26" t="str">
         <v/>
@@ -1474,37 +1474,37 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>BANKNIFTY</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="C27" t="str">
-        <v>BANKNIFTY</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="D27" s="1">
-        <v>55634.55</v>
+        <v>35974.45</v>
       </c>
       <c r="E27" s="2">
-        <v>0.58</v>
+        <v>-0.6</v>
       </c>
       <c r="F27" s="2">
-        <v>0.68</v>
+        <v>-0.6</v>
       </c>
       <c r="G27" s="2">
-        <v>1.83</v>
+        <v>-1.81</v>
       </c>
       <c r="H27" s="2">
-        <v>-6.63</v>
+        <v>1.84</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>56943.89</v>
+        <v>37721.97</v>
       </c>
       <c r="K27" s="1">
-        <v>55235.58</v>
+        <v>36241.05</v>
       </c>
       <c r="L27" s="1">
-        <v>56519.41</v>
+        <v>37551.17</v>
       </c>
       <c r="M27" t="str">
         <v/>
@@ -1515,37 +1515,37 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="C28" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="D28" s="1">
-        <v>18814.2</v>
+        <v>9525.85</v>
       </c>
       <c r="E28" s="2">
-        <v>0.55</v>
+        <v>-0.6</v>
       </c>
       <c r="F28" s="2">
-        <v>1.01</v>
+        <v>-0.6</v>
       </c>
       <c r="G28" s="2">
-        <v>0.15</v>
+        <v>-1.11</v>
       </c>
       <c r="H28" s="2">
-        <v>-10.96</v>
+        <v>10.69</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>19913.31</v>
+        <v>8973.96</v>
       </c>
       <c r="K28" s="1">
-        <v>18746.04</v>
+        <v>9620.27</v>
       </c>
       <c r="L28" s="1">
-        <v>19658.9</v>
+        <v>9837.16</v>
       </c>
       <c r="M28" t="str">
         <v/>
@@ -1556,37 +1556,37 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>CNXREALTY</v>
+        <v>CNXPSE</v>
       </c>
       <c r="C29" t="str">
-        <v>CNXREALTY</v>
+        <v>CNXPSE</v>
       </c>
       <c r="D29" s="1">
-        <v>827.05</v>
+        <v>9190.6</v>
       </c>
       <c r="E29" s="2">
-        <v>0.52</v>
+        <v>-0.61</v>
       </c>
       <c r="F29" s="2">
-        <v>2.87</v>
+        <v>-0.61</v>
       </c>
       <c r="G29" s="2">
-        <v>-2.4</v>
+        <v>-1.81</v>
       </c>
       <c r="H29" s="2">
-        <v>-5.8</v>
+        <v>-6.73</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <v>823.54</v>
+        <v>9995.43</v>
       </c>
       <c r="K29" s="1">
-        <v>825.61</v>
+        <v>9232.39</v>
       </c>
       <c r="L29" s="1">
-        <v>870.09</v>
+        <v>9571.2</v>
       </c>
       <c r="M29" t="str">
         <v/>
@@ -1597,37 +1597,37 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="C30" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="D30" s="1">
-        <v>5562.4</v>
+        <v>25046.05</v>
       </c>
       <c r="E30" s="2">
-        <v>0.51</v>
+        <v>-0.63</v>
       </c>
       <c r="F30" s="2">
-        <v>2.63</v>
+        <v>-0.63</v>
       </c>
       <c r="G30" s="2">
-        <v>1.64</v>
+        <v>-1.37</v>
       </c>
       <c r="H30" s="2">
-        <v>-12.89</v>
+        <v>0.24</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>5968</v>
+        <v>25476.47</v>
       </c>
       <c r="K30" s="1">
-        <v>5487.04</v>
+        <v>25301.13</v>
       </c>
       <c r="L30" s="1">
-        <v>5723.75</v>
+        <v>26266.15</v>
       </c>
       <c r="M30" t="str">
         <v/>
@@ -1638,37 +1638,37 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>NIFTY500</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="C31" t="str">
-        <v>NIFTY500</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="D31" s="1">
-        <v>22142.1</v>
+        <v>15078.3</v>
       </c>
       <c r="E31" s="2">
-        <v>0.47</v>
+        <v>-0.63</v>
       </c>
       <c r="F31" s="2">
-        <v>1.26</v>
+        <v>-0.63</v>
       </c>
       <c r="G31" s="2">
-        <v>0.32</v>
+        <v>-2.43</v>
       </c>
       <c r="H31" s="2">
-        <v>-7.24</v>
+        <v>-2.17</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>22879.74</v>
+        <v>15633.9</v>
       </c>
       <c r="K31" s="1">
-        <v>22059.85</v>
+        <v>15166.49</v>
       </c>
       <c r="L31" s="1">
-        <v>22931.41</v>
+        <v>15964.18</v>
       </c>
       <c r="M31" t="str">
         <v/>
@@ -1679,37 +1679,37 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="C32" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="D32" s="1">
-        <v>9051.4</v>
+        <v>55488.1</v>
       </c>
       <c r="E32" s="2">
-        <v>0.45</v>
+        <v>-0.64</v>
       </c>
       <c r="F32" s="2">
-        <v>1.43</v>
+        <v>-0.64</v>
       </c>
       <c r="G32" s="2">
-        <v>-2.78</v>
+        <v>1.57</v>
       </c>
       <c r="H32" s="2">
-        <v>-4.87</v>
+        <v>-6.87</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>9767.57</v>
+        <v>56910.46</v>
       </c>
       <c r="K32" s="1">
-        <v>9066.2</v>
+        <v>55393.42</v>
       </c>
       <c r="L32" s="1">
-        <v>9577.71</v>
+        <v>56433.5</v>
       </c>
       <c r="M32" t="str">
         <v/>
@@ -1726,31 +1726,31 @@
         <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="D33" s="1">
-        <v>24854.45</v>
+        <v>24753.65</v>
       </c>
       <c r="E33" s="2">
-        <v>0.43</v>
+        <v>-0.64</v>
       </c>
       <c r="F33" s="2">
-        <v>0.65</v>
+        <v>-0.64</v>
       </c>
       <c r="G33" s="2">
-        <v>-1.45</v>
+        <v>-1.85</v>
       </c>
       <c r="H33" s="2">
-        <v>-8.21</v>
+        <v>-8.58</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>26300.64</v>
+        <v>26278.33</v>
       </c>
       <c r="K33" s="1">
-        <v>24919.5</v>
+        <v>24891.72</v>
       </c>
       <c r="L33" s="1">
-        <v>26361.15</v>
+        <v>26249.17</v>
       </c>
       <c r="M33" t="str">
         <v/>
@@ -1761,37 +1761,37 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="C34" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="D34" s="1">
-        <v>3481.82</v>
+        <v>25615</v>
       </c>
       <c r="E34" s="2">
-        <v>0.43</v>
+        <v>-0.65</v>
       </c>
       <c r="F34" s="2">
-        <v>-0.66</v>
+        <v>-0.65</v>
       </c>
       <c r="G34" s="2">
-        <v>-1.14</v>
+        <v>-3.11</v>
       </c>
       <c r="H34" s="2">
-        <v>-0.32</v>
+        <v>12.72</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>3495.53</v>
+        <v>24332</v>
       </c>
       <c r="K34" s="1">
-        <v>3494.32</v>
+        <v>25961.9</v>
       </c>
       <c r="L34" s="1">
-        <v>3542.21</v>
+        <v>26504.8</v>
       </c>
       <c r="M34" t="str">
         <v/>
@@ -1802,37 +1802,37 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>Nifty Total Market</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="C35" t="str">
-        <v>NIFTYTOTALMKT</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="D35" s="1">
-        <v>12528.15</v>
+        <v>9039.85</v>
       </c>
       <c r="E35" s="2">
-        <v>0.37</v>
+        <v>-0.66</v>
       </c>
       <c r="F35" s="2">
-        <v>1.2</v>
+        <v>-0.66</v>
       </c>
       <c r="G35" s="2">
-        <v>0.18</v>
+        <v>-2.9</v>
       </c>
       <c r="H35" s="2">
-        <v>-6.46</v>
+        <v>-5</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>12881.07</v>
+        <v>9765.12</v>
       </c>
       <c r="K35" s="1">
-        <v>12490.32</v>
+        <v>9068.56</v>
       </c>
       <c r="L35" s="1">
-        <v>12968</v>
+        <v>9541.65</v>
       </c>
       <c r="M35" t="str">
         <v/>
@@ -1843,37 +1843,37 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="C36" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="D36" s="1">
-        <v>3301.94</v>
+        <v>32625.05</v>
       </c>
       <c r="E36" s="2">
-        <v>0.36</v>
+        <v>-0.68</v>
       </c>
       <c r="F36" s="2">
-        <v>-0.04</v>
+        <v>-0.68</v>
       </c>
       <c r="G36" s="2">
-        <v>-0.59</v>
+        <v>-0.72</v>
       </c>
       <c r="H36" s="2">
-        <v>1.85</v>
+        <v>-3.92</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>3294.09</v>
+        <v>33702.89</v>
       </c>
       <c r="K36" s="1">
-        <v>3305.32</v>
+        <v>32686.26</v>
       </c>
       <c r="L36" s="1">
-        <v>3357.48</v>
+        <v>34069.02</v>
       </c>
       <c r="M36" t="str">
         <v/>
@@ -1884,37 +1884,37 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="C37" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="D37" s="1">
-        <v>15716.55</v>
+        <v>8666.5</v>
       </c>
       <c r="E37" s="2">
-        <v>0.34</v>
+        <v>-0.68</v>
       </c>
       <c r="F37" s="2">
-        <v>-0.88</v>
+        <v>-0.68</v>
       </c>
       <c r="G37" s="2">
-        <v>-2.61</v>
+        <v>-0.77</v>
       </c>
       <c r="H37" s="2">
-        <v>7.35</v>
+        <v>-9.88</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>15422.76</v>
+        <v>9235.48</v>
       </c>
       <c r="K37" s="1">
-        <v>15913.88</v>
+        <v>8665.13</v>
       </c>
       <c r="L37" s="1">
-        <v>16440.51</v>
+        <v>9047.92</v>
       </c>
       <c r="M37" t="str">
         <v/>
@@ -1925,37 +1925,37 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="C38" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="D38" s="1">
-        <v>15775.1</v>
+        <v>25591.25</v>
       </c>
       <c r="E38" s="2">
-        <v>0.32</v>
+        <v>-0.69</v>
       </c>
       <c r="F38" s="2">
-        <v>1.12</v>
+        <v>-0.69</v>
       </c>
       <c r="G38" s="2">
-        <v>0.11</v>
+        <v>-2.67</v>
       </c>
       <c r="H38" s="2">
-        <v>-6.41</v>
+        <v>-9.22</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
       </c>
       <c r="J38" s="1">
-        <v>16318.14</v>
+        <v>26954.81</v>
       </c>
       <c r="K38" s="1">
-        <v>15738.55</v>
+        <v>25514.14</v>
       </c>
       <c r="L38" s="1">
-        <v>16414.14</v>
+        <v>27441.73</v>
       </c>
       <c r="M38" t="str">
         <v/>
@@ -1966,37 +1966,37 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="C39" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="D39" s="1">
-        <v>15727.55</v>
+        <v>47321.65</v>
       </c>
       <c r="E39" s="2">
-        <v>0.32</v>
+        <v>-0.75</v>
       </c>
       <c r="F39" s="2">
-        <v>1.21</v>
+        <v>-0.75</v>
       </c>
       <c r="G39" s="2">
-        <v>-1.81</v>
+        <v>-1.12</v>
       </c>
       <c r="H39" s="2">
-        <v>-1.55</v>
+        <v>7.58</v>
       </c>
       <c r="I39" s="1">
         <v>0</v>
       </c>
       <c r="J39" s="1">
-        <v>16013.29</v>
+        <v>44905.83</v>
       </c>
       <c r="K39" s="1">
-        <v>15774.19</v>
+        <v>47713.56</v>
       </c>
       <c r="L39" s="1">
-        <v>16544.75</v>
+        <v>48453.83</v>
       </c>
       <c r="M39" t="str">
         <v/>
@@ -2007,37 +2007,37 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>CNXPHARMA</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="C40" t="str">
-        <v>CNXPHARMA</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="D40" s="1">
-        <v>25812.7</v>
+        <v>13528.95</v>
       </c>
       <c r="E40" s="2">
-        <v>0.29</v>
+        <v>-0.75</v>
       </c>
       <c r="F40" s="2">
-        <v>-0.58</v>
+        <v>-0.75</v>
       </c>
       <c r="G40" s="2">
-        <v>-2.37</v>
+        <v>-1.61</v>
       </c>
       <c r="H40" s="2">
-        <v>13.59</v>
+        <v>-6.51</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
       </c>
       <c r="J40" s="1">
-        <v>24302.2</v>
+        <v>14159.07</v>
       </c>
       <c r="K40" s="1">
-        <v>26095.24</v>
+        <v>13598.82</v>
       </c>
       <c r="L40" s="1">
-        <v>26539.33</v>
+        <v>14196.36</v>
       </c>
       <c r="M40" t="str">
         <v/>
@@ -2048,37 +2048,37 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="C41" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="D41" s="1">
-        <v>3074.79</v>
+        <v>49213.65</v>
       </c>
       <c r="E41" s="2">
-        <v>0.28</v>
+        <v>-0.79</v>
       </c>
       <c r="F41" s="2">
-        <v>-0.35</v>
+        <v>-0.79</v>
       </c>
       <c r="G41" s="2">
-        <v>-0.95</v>
+        <v>-0.73</v>
       </c>
       <c r="H41" s="2">
-        <v>0.73</v>
+        <v>3.46</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
       </c>
       <c r="J41" s="1">
-        <v>3085.64</v>
+        <v>49073.99</v>
       </c>
       <c r="K41" s="1">
-        <v>3083.68</v>
+        <v>49647.66</v>
       </c>
       <c r="L41" s="1">
-        <v>3125.97</v>
+        <v>51027.93</v>
       </c>
       <c r="M41" t="str">
         <v/>
@@ -2089,37 +2089,37 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="C42" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="D42" s="1">
-        <v>2609.85</v>
+        <v>15660.05</v>
       </c>
       <c r="E42" s="2">
-        <v>0.26</v>
+        <v>-0.8</v>
       </c>
       <c r="F42" s="2">
-        <v>-0.34</v>
+        <v>-0.8</v>
       </c>
       <c r="G42" s="2">
-        <v>-1.08</v>
+        <v>-2.23</v>
       </c>
       <c r="H42" s="2">
-        <v>-0.08</v>
+        <v>-1.97</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
       </c>
       <c r="J42" s="1">
-        <v>2632.57</v>
+        <v>16012.47</v>
       </c>
       <c r="K42" s="1">
-        <v>2618.31</v>
+        <v>15758.92</v>
       </c>
       <c r="L42" s="1">
-        <v>2656.02</v>
+        <v>16493.32</v>
       </c>
       <c r="M42" t="str">
         <v/>
@@ -2130,37 +2130,37 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="C43" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="D43" s="1">
-        <v>843.25</v>
+        <v>15557.6</v>
       </c>
       <c r="E43" s="2">
-        <v>0.25</v>
+        <v>-0.8</v>
       </c>
       <c r="F43" s="2">
-        <v>-0.47</v>
+        <v>-0.8</v>
       </c>
       <c r="G43" s="2">
-        <v>-1.4</v>
+        <v>-3.6</v>
       </c>
       <c r="H43" s="2">
-        <v>-5.41</v>
+        <v>6.27</v>
       </c>
       <c r="I43" s="1">
         <v>0</v>
       </c>
       <c r="J43" s="1">
-        <v>874.91</v>
+        <v>15431.78</v>
       </c>
       <c r="K43" s="1">
-        <v>847.09</v>
+        <v>15815.79</v>
       </c>
       <c r="L43" s="1">
-        <v>864.56</v>
+        <v>16397.36</v>
       </c>
       <c r="M43" t="str">
         <v/>
@@ -2171,37 +2171,37 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="C44" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="D44" s="1">
-        <v>2981.95</v>
+        <v>59774.7</v>
       </c>
       <c r="E44" s="2">
-        <v>0.23</v>
+        <v>-0.81</v>
       </c>
       <c r="F44" s="2">
-        <v>-0.35</v>
+        <v>-0.81</v>
       </c>
       <c r="G44" s="2">
-        <v>-1.06</v>
+        <v>-1.64</v>
       </c>
       <c r="H44" s="2">
-        <v>0.51</v>
+        <v>-3.46</v>
       </c>
       <c r="I44" s="1">
         <v>0</v>
       </c>
       <c r="J44" s="1">
-        <v>3001.29</v>
+        <v>61762.81</v>
       </c>
       <c r="K44" s="1">
-        <v>2991.9</v>
+        <v>60577.64</v>
       </c>
       <c r="L44" s="1">
-        <v>3034.08</v>
+        <v>62840.3</v>
       </c>
       <c r="M44" t="str">
         <v/>
@@ -2218,31 +2218,31 @@
         <v>NIFTY50VALUE30</v>
       </c>
       <c r="D45" s="1">
-        <v>5410.35</v>
+        <v>5424.75</v>
       </c>
       <c r="E45" s="2">
-        <v>0.2</v>
+        <v>-0.86</v>
       </c>
       <c r="F45" s="2">
-        <v>2.77</v>
+        <v>-0.86</v>
       </c>
       <c r="G45" s="2">
-        <v>1.69</v>
+        <v>1.96</v>
       </c>
       <c r="H45" s="2">
-        <v>-7.67</v>
+        <v>-7.43</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
       </c>
       <c r="J45" s="1">
-        <v>5557.34</v>
+        <v>5553.17</v>
       </c>
       <c r="K45" s="1">
-        <v>5341.58</v>
+        <v>5376.4</v>
       </c>
       <c r="L45" s="1">
-        <v>5550.05</v>
+        <v>5537.7</v>
       </c>
       <c r="M45" t="str">
         <v/>
@@ -2253,37 +2253,37 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="C46" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="D46" s="1">
-        <v>13566.25</v>
+        <v>48866.6</v>
       </c>
       <c r="E46" s="2">
-        <v>0.15</v>
+        <v>-0.87</v>
       </c>
       <c r="F46" s="2">
-        <v>0.62</v>
+        <v>-0.87</v>
       </c>
       <c r="G46" s="2">
-        <v>-1.34</v>
+        <v>-4.15</v>
       </c>
       <c r="H46" s="2">
-        <v>-6.25</v>
+        <v>11.4</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
       </c>
       <c r="J46" s="1">
-        <v>14167.39</v>
+        <v>47289.89</v>
       </c>
       <c r="K46" s="1">
-        <v>13607.04</v>
+        <v>49886.15</v>
       </c>
       <c r="L46" s="1">
-        <v>14242.8</v>
+        <v>51712.18</v>
       </c>
       <c r="M46" t="str">
         <v/>
@@ -2294,37 +2294,37 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="C47" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="D47" s="1">
-        <v>15101.25</v>
+        <v>7498.05</v>
       </c>
       <c r="E47" s="2">
-        <v>0.12</v>
+        <v>-0.88</v>
       </c>
       <c r="F47" s="2">
-        <v>0.99</v>
+        <v>-0.88</v>
       </c>
       <c r="G47" s="2">
-        <v>-2.29</v>
+        <v>-2.68</v>
       </c>
       <c r="H47" s="2">
-        <v>-2.02</v>
+        <v>-12.85</v>
       </c>
       <c r="I47" s="1">
         <v>0</v>
       </c>
       <c r="J47" s="1">
-        <v>15635.18</v>
+        <v>7697.42</v>
       </c>
       <c r="K47" s="1">
-        <v>15185.15</v>
+        <v>7532.36</v>
       </c>
       <c r="L47" s="1">
-        <v>16022.32</v>
+        <v>7797.25</v>
       </c>
       <c r="M47" t="str">
         <v/>
@@ -2335,37 +2335,37 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="C48" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="D48" s="1">
-        <v>32676.25</v>
+        <v>13827.75</v>
       </c>
       <c r="E48" s="2">
-        <v>0.11</v>
+        <v>-0.9</v>
       </c>
       <c r="F48" s="2">
-        <v>1.19</v>
+        <v>-0.9</v>
       </c>
       <c r="G48" s="2">
-        <v>-0.56</v>
+        <v>3.56</v>
       </c>
       <c r="H48" s="2">
-        <v>-3.77</v>
+        <v>-9.58</v>
       </c>
       <c r="I48" s="1">
         <v>0</v>
       </c>
       <c r="J48" s="1">
-        <v>33713.45</v>
+        <v>14407.78</v>
       </c>
       <c r="K48" s="1">
-        <v>32661.9</v>
+        <v>13643.53</v>
       </c>
       <c r="L48" s="1">
-        <v>34183.52</v>
+        <v>14077.98</v>
       </c>
       <c r="M48" t="str">
         <v/>
@@ -2376,37 +2376,37 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="C49" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="D49" s="1">
-        <v>15751.35</v>
+        <v>30908.4</v>
       </c>
       <c r="E49" s="2">
-        <v>0.11</v>
+        <v>-0.93</v>
       </c>
       <c r="F49" s="2">
-        <v>1.03</v>
+        <v>-0.93</v>
       </c>
       <c r="G49" s="2">
         <v>0.01</v>
       </c>
       <c r="H49" s="2">
-        <v>-4.45</v>
+        <v>-7.27</v>
       </c>
       <c r="I49" s="1">
         <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>16036.55</v>
+        <v>32376.25</v>
       </c>
       <c r="K49" s="1">
-        <v>15734.79</v>
+        <v>30895.21</v>
       </c>
       <c r="L49" s="1">
-        <v>16319.35</v>
+        <v>32105.82</v>
       </c>
       <c r="M49" t="str">
         <v/>
@@ -2417,37 +2417,37 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>CNXMNC</v>
       </c>
       <c r="C50" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>CNXMNC</v>
       </c>
       <c r="D50" s="1">
-        <v>3283.82</v>
+        <v>29239.8</v>
       </c>
       <c r="E50" s="2">
-        <v>0.05</v>
+        <v>-0.93</v>
       </c>
       <c r="F50" s="2">
-        <v>-0.42</v>
+        <v>-0.93</v>
       </c>
       <c r="G50" s="2">
-        <v>-0.75</v>
+        <v>-3.61</v>
       </c>
       <c r="H50" s="2">
-        <v>1.9</v>
+        <v>-4.35</v>
       </c>
       <c r="I50" s="1">
         <v>0</v>
       </c>
       <c r="J50" s="1">
-        <v>3279.01</v>
+        <v>31419.18</v>
       </c>
       <c r="K50" s="1">
-        <v>3293.74</v>
+        <v>29759.56</v>
       </c>
       <c r="L50" s="1">
-        <v>3326.73</v>
+        <v>31753.46</v>
       </c>
       <c r="M50" t="str">
         <v/>
@@ -2458,37 +2458,37 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="C51" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="D51" s="1">
-        <v>199.43</v>
+        <v>18743.65</v>
       </c>
       <c r="E51" s="2">
-        <v>0</v>
+        <v>-0.93</v>
       </c>
       <c r="F51" s="2">
-        <v>1.34</v>
+        <v>-0.93</v>
       </c>
       <c r="G51" s="2">
-        <v>1.34</v>
+        <v>-0.22</v>
       </c>
       <c r="H51" s="2">
-        <v>-19.95</v>
+        <v>-11.29</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
       </c>
       <c r="J51" s="1">
-        <v>181.6</v>
+        <v>19890.8</v>
       </c>
       <c r="K51" s="1">
-        <v>197.64</v>
+        <v>18774.85</v>
       </c>
       <c r="L51" s="1">
-        <v>193.41</v>
+        <v>19583.61</v>
       </c>
       <c r="M51" t="str">
         <v/>
@@ -2499,37 +2499,37 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="C52" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="D52" s="1">
-        <v>11994.95</v>
+        <v>9124.3</v>
       </c>
       <c r="E52" s="2">
-        <v>-0.1</v>
+        <v>-0.94</v>
       </c>
       <c r="F52" s="2">
-        <v>-0.05</v>
+        <v>-0.94</v>
       </c>
       <c r="G52" s="2">
-        <v>-6</v>
+        <v>-1.64</v>
       </c>
       <c r="H52" s="2">
-        <v>7.41</v>
+        <v>17.77</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
       </c>
       <c r="J52" s="1">
-        <v>12459.49</v>
+        <v>8827.02</v>
       </c>
       <c r="K52" s="1">
-        <v>12202.71</v>
+        <v>9190.46</v>
       </c>
       <c r="L52" s="1">
-        <v>12935.53</v>
+        <v>9511</v>
       </c>
       <c r="M52" t="str">
         <v/>
@@ -2540,37 +2540,37 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="C53" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="D53" s="1">
-        <v>1602.7</v>
+        <v>10919.1</v>
       </c>
       <c r="E53" s="2">
-        <v>-0.1</v>
+        <v>-0.96</v>
       </c>
       <c r="F53" s="2">
-        <v>-0.23</v>
+        <v>-0.96</v>
       </c>
       <c r="G53" s="2">
-        <v>-0.26</v>
+        <v>3.6</v>
       </c>
       <c r="H53" s="2">
-        <v>2.29</v>
+        <v>-12.53</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
       </c>
       <c r="J53" s="1">
-        <v>1585.94</v>
+        <v>11239.26</v>
       </c>
       <c r="K53" s="1">
-        <v>1605.64</v>
+        <v>10717.61</v>
       </c>
       <c r="L53" s="1">
-        <v>1609.85</v>
+        <v>11122.31</v>
       </c>
       <c r="M53" t="str">
         <v/>
@@ -2581,37 +2581,37 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>NIFTY100</v>
       </c>
       <c r="C54" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>NIFTY100</v>
       </c>
       <c r="D54" s="1">
-        <v>1309.07</v>
+        <v>23895.45</v>
       </c>
       <c r="E54" s="2">
-        <v>-0.17</v>
+        <v>-0.98</v>
       </c>
       <c r="F54" s="2">
-        <v>-0.46</v>
+        <v>-0.98</v>
       </c>
       <c r="G54" s="2">
-        <v>-0.49</v>
+        <v>0.68</v>
       </c>
       <c r="H54" s="2">
-        <v>0.84</v>
+        <v>-10.47</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
       </c>
       <c r="J54" s="1">
-        <v>1307.8</v>
+        <v>25067.57</v>
       </c>
       <c r="K54" s="1">
-        <v>1313.57</v>
+        <v>23835.75</v>
       </c>
       <c r="L54" s="1">
-        <v>1323.98</v>
+        <v>24637.3</v>
       </c>
       <c r="M54" t="str">
         <v/>
@@ -2622,37 +2622,37 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="C55" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="D55" s="1">
-        <v>49532.2</v>
+        <v>5190.85</v>
       </c>
       <c r="E55" s="2">
-        <v>-0.2</v>
+        <v>-0.98</v>
       </c>
       <c r="F55" s="2">
-        <v>-1.35</v>
+        <v>-0.98</v>
       </c>
       <c r="G55" s="2">
-        <v>-2.84</v>
+        <v>1.99</v>
       </c>
       <c r="H55" s="2">
-        <v>12.92</v>
+        <v>11.48</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
       </c>
       <c r="J55" s="1">
-        <v>47237.49</v>
+        <v>5100.82</v>
       </c>
       <c r="K55" s="1">
-        <v>50290.29</v>
+        <v>5229.32</v>
       </c>
       <c r="L55" s="1">
-        <v>51831.54</v>
+        <v>5309.82</v>
       </c>
       <c r="M55" t="str">
         <v/>
@@ -2663,37 +2663,37 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="C56" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="D56" s="1">
-        <v>1447.62</v>
+        <v>18935.75</v>
       </c>
       <c r="E56" s="2">
-        <v>-0.2</v>
+        <v>-1.01</v>
       </c>
       <c r="F56" s="2">
-        <v>-0.39</v>
+        <v>-1.01</v>
       </c>
       <c r="G56" s="2">
-        <v>-0.43</v>
+        <v>-1.61</v>
       </c>
       <c r="H56" s="2">
-        <v>1.61</v>
+        <v>6.9</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
       </c>
       <c r="J56" s="1">
-        <v>1440.34</v>
+        <v>18179.82</v>
       </c>
       <c r="K56" s="1">
-        <v>1452.02</v>
+        <v>19223.48</v>
       </c>
       <c r="L56" s="1">
-        <v>1459.89</v>
+        <v>19680.38</v>
       </c>
       <c r="M56" t="str">
         <v/>
@@ -2704,37 +2704,37 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTY200</v>
       </c>
       <c r="C57" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTY200</v>
       </c>
       <c r="D57" s="1">
-        <v>1265.62</v>
+        <v>13203.35</v>
       </c>
       <c r="E57" s="2">
-        <v>-0.21</v>
+        <v>-1.01</v>
       </c>
       <c r="F57" s="2">
-        <v>-0.54</v>
+        <v>-1.01</v>
       </c>
       <c r="G57" s="2">
-        <v>-0.6</v>
+        <v>0.25</v>
       </c>
       <c r="H57" s="2">
-        <v>0.32</v>
+        <v>-9.15</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
       </c>
       <c r="J57" s="1">
-        <v>1268.29</v>
+        <v>13806.77</v>
       </c>
       <c r="K57" s="1">
-        <v>1270.78</v>
+        <v>13206.34</v>
       </c>
       <c r="L57" s="1">
-        <v>1282.55</v>
+        <v>13681.72</v>
       </c>
       <c r="M57" t="str">
         <v/>
@@ -2745,37 +2745,37 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTY500</v>
       </c>
       <c r="C58" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTY500</v>
       </c>
       <c r="D58" s="1">
-        <v>19356.75</v>
+        <v>22041.6</v>
       </c>
       <c r="E58" s="2">
-        <v>-0.26</v>
+        <v>-1.03</v>
       </c>
       <c r="F58" s="2">
-        <v>2.62</v>
+        <v>-1.03</v>
       </c>
       <c r="G58" s="2">
-        <v>2.18</v>
+        <v>-0.14</v>
       </c>
       <c r="H58" s="2">
-        <v>-9.59</v>
+        <v>-7.67</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
       </c>
       <c r="J58" s="1">
-        <v>20143.42</v>
+        <v>22863.34</v>
       </c>
       <c r="K58" s="1">
-        <v>19128.26</v>
+        <v>22092.51</v>
       </c>
       <c r="L58" s="1">
-        <v>19955.07</v>
+        <v>22869.12</v>
       </c>
       <c r="M58" t="str">
         <v/>
@@ -2786,37 +2786,37 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="C59" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="D59" s="1">
-        <v>6076.45</v>
+        <v>15678.75</v>
       </c>
       <c r="E59" s="2">
-        <v>-0.35</v>
+        <v>-1.04</v>
       </c>
       <c r="F59" s="2">
-        <v>1.21</v>
+        <v>-1.04</v>
       </c>
       <c r="G59" s="2">
-        <v>-2.45</v>
+        <v>-0.5</v>
       </c>
       <c r="H59" s="2">
-        <v>-4.54</v>
+        <v>-6.98</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
       </c>
       <c r="J59" s="1">
-        <v>6751.03</v>
+        <v>16307.73</v>
       </c>
       <c r="K59" s="1">
-        <v>6096.46</v>
+        <v>15746.43</v>
       </c>
       <c r="L59" s="1">
-        <v>6342.48</v>
+        <v>16366.58</v>
       </c>
       <c r="M59" t="str">
         <v/>
@@ -2827,37 +2827,37 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="C60" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="D60" s="1">
-        <v>36425.8</v>
+        <v>16767.85</v>
       </c>
       <c r="E60" s="2">
-        <v>-0.39</v>
+        <v>-1.05</v>
       </c>
       <c r="F60" s="2">
-        <v>1.27</v>
+        <v>-1.05</v>
       </c>
       <c r="G60" s="2">
-        <v>-0.55</v>
+        <v>-1.53</v>
       </c>
       <c r="H60" s="2">
-        <v>-0.9</v>
+        <v>-2.82</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
       </c>
       <c r="J60" s="1">
-        <v>37133.89</v>
+        <v>17231.35</v>
       </c>
       <c r="K60" s="1">
-        <v>36497.08</v>
+        <v>16936.71</v>
       </c>
       <c r="L60" s="1">
-        <v>38776</v>
+        <v>17751.15</v>
       </c>
       <c r="M60" t="str">
         <v/>
@@ -2868,37 +2868,37 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="C61" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="D61" s="1">
-        <v>16930.9</v>
+        <v>15656.8</v>
       </c>
       <c r="E61" s="2">
-        <v>-0.39</v>
+        <v>-1.05</v>
       </c>
       <c r="F61" s="2">
-        <v>0.86</v>
+        <v>-1.05</v>
       </c>
       <c r="G61" s="2">
-        <v>-0.57</v>
+        <v>-0.59</v>
       </c>
       <c r="H61" s="2">
-        <v>-1.87</v>
+        <v>-5.02</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
       </c>
       <c r="J61" s="1">
-        <v>17234.81</v>
+        <v>16029.65</v>
       </c>
       <c r="K61" s="1">
-        <v>16975.83</v>
+        <v>15736.72</v>
       </c>
       <c r="L61" s="1">
-        <v>17803.23</v>
+        <v>16277.41</v>
       </c>
       <c r="M61" t="str">
         <v/>
@@ -2909,37 +2909,37 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>Nifty midcap 150</v>
+        <v>Nifty Total Market</v>
       </c>
       <c r="C62" t="str">
-        <v>NIFTYMIDCAP150</v>
+        <v>NIFTYTOTALMKT</v>
       </c>
       <c r="D62" s="1">
-        <v>21729.2</v>
+        <v>12469.05</v>
       </c>
       <c r="E62" s="2">
-        <v>-0.42</v>
+        <v>-1.05</v>
       </c>
       <c r="F62" s="2">
-        <v>0.58</v>
+        <v>-1.05</v>
       </c>
       <c r="G62" s="2">
-        <v>-0.63</v>
+        <v>-0.29</v>
       </c>
       <c r="H62" s="2">
-        <v>-2.46</v>
+        <v>-6.9</v>
       </c>
       <c r="I62" s="1">
         <v>0</v>
       </c>
       <c r="J62" s="1">
-        <v>22200.59</v>
+        <v>12872.91</v>
       </c>
       <c r="K62" s="1">
-        <v>21804.96</v>
+        <v>12505.65</v>
       </c>
       <c r="L62" s="1">
-        <v>22793.2</v>
+        <v>12934.02</v>
       </c>
       <c r="M62" t="str">
         <v/>
@@ -2950,37 +2950,37 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="C63" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="D63" s="1">
-        <v>22994.6</v>
+        <v>10938.6</v>
       </c>
       <c r="E63" s="2">
-        <v>-0.43</v>
+        <v>-1.05</v>
       </c>
       <c r="F63" s="2">
-        <v>1.25</v>
+        <v>-1.05</v>
       </c>
       <c r="G63" s="2">
-        <v>1</v>
+        <v>-1.21</v>
       </c>
       <c r="H63" s="2">
-        <v>-4.42</v>
+        <v>-10.99</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
       </c>
       <c r="J63" s="1">
-        <v>23521.33</v>
+        <v>11510.65</v>
       </c>
       <c r="K63" s="1">
-        <v>22946.24</v>
+        <v>10982.36</v>
       </c>
       <c r="L63" s="1">
-        <v>23911.93</v>
+        <v>11533.73</v>
       </c>
       <c r="M63" t="str">
         <v/>
@@ -2991,37 +2991,37 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>CNXPSE</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="C64" t="str">
-        <v>CNXPSE</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="D64" s="1">
-        <v>9239.3</v>
+        <v>58487.95</v>
       </c>
       <c r="E64" s="2">
-        <v>-0.45</v>
+        <v>-1.09</v>
       </c>
       <c r="F64" s="2">
-        <v>1.78</v>
+        <v>-1.09</v>
       </c>
       <c r="G64" s="2">
-        <v>-1.29</v>
+        <v>-1.42</v>
       </c>
       <c r="H64" s="2">
-        <v>-6.23</v>
+        <v>-3.3</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
       </c>
       <c r="J64" s="1">
-        <v>10000.53</v>
+        <v>60345.06</v>
       </c>
       <c r="K64" s="1">
-        <v>9237.18</v>
+        <v>59144.52</v>
       </c>
       <c r="L64" s="1">
-        <v>9599.87</v>
+        <v>61831.43</v>
       </c>
       <c r="M64" t="str">
         <v/>
@@ -3032,37 +3032,37 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>Nifty midcap 150</v>
       </c>
       <c r="C65" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTYMIDCAP150</v>
       </c>
       <c r="D65" s="1">
-        <v>68661.15</v>
+        <v>21499.3</v>
       </c>
       <c r="E65" s="2">
-        <v>-0.49</v>
+        <v>-1.09</v>
       </c>
       <c r="F65" s="2">
-        <v>0.73</v>
+        <v>-1.09</v>
       </c>
       <c r="G65" s="2">
-        <v>-1.56</v>
+        <v>-1.68</v>
       </c>
       <c r="H65" s="2">
-        <v>-1.01</v>
+        <v>-3.49</v>
       </c>
       <c r="I65" s="1">
         <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>70049.03</v>
+        <v>22194.72</v>
       </c>
       <c r="K65" s="1">
-        <v>69038.13</v>
+        <v>21742.54</v>
       </c>
       <c r="L65" s="1">
-        <v>72182.64</v>
+        <v>22724.19</v>
       </c>
       <c r="M65" t="str">
         <v/>
@@ -3073,37 +3073,37 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="C66" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="D66" s="1">
-        <v>59111.6</v>
+        <v>4737.1</v>
       </c>
       <c r="E66" s="2">
-        <v>-0.5</v>
+        <v>-1.09</v>
       </c>
       <c r="F66" s="2">
-        <v>0.55</v>
+        <v>-1.09</v>
       </c>
       <c r="G66" s="2">
-        <v>-0.37</v>
+        <v>1.14</v>
       </c>
       <c r="H66" s="2">
-        <v>-2.27</v>
+        <v>-8.57</v>
       </c>
       <c r="I66" s="1">
         <v>0</v>
       </c>
       <c r="J66" s="1">
-        <v>60360.38</v>
+        <v>4919.82</v>
       </c>
       <c r="K66" s="1">
-        <v>59310.56</v>
+        <v>4714.02</v>
       </c>
       <c r="L66" s="1">
-        <v>62016.01</v>
+        <v>4884.75</v>
       </c>
       <c r="M66" t="str">
         <v/>
@@ -3114,37 +3114,37 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTY</v>
       </c>
       <c r="C67" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTY</v>
       </c>
       <c r="D67" s="1">
-        <v>13697.65</v>
+        <v>22888.95</v>
       </c>
       <c r="E67" s="2">
-        <v>-0.55</v>
+        <v>-1.11</v>
       </c>
       <c r="F67" s="2">
-        <v>0.78</v>
+        <v>-1.11</v>
       </c>
       <c r="G67" s="2">
-        <v>-0.24</v>
+        <v>1.19</v>
       </c>
       <c r="H67" s="2">
-        <v>-0.58</v>
+        <v>-12.4</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
       </c>
       <c r="J67" s="1">
-        <v>14004.55</v>
+        <v>24168.4</v>
       </c>
       <c r="K67" s="1">
-        <v>13735.1</v>
+        <v>22798.07</v>
       </c>
       <c r="L67" s="1">
-        <v>14455.65</v>
+        <v>23514.27</v>
       </c>
       <c r="M67" t="str">
         <v/>
@@ -3155,37 +3155,37 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="C68" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="D68" s="1">
-        <v>28439.25</v>
+        <v>20045.25</v>
       </c>
       <c r="E68" s="2">
-        <v>-0.62</v>
+        <v>-1.11</v>
       </c>
       <c r="F68" s="2">
-        <v>1.68</v>
+        <v>-1.11</v>
       </c>
       <c r="G68" s="2">
-        <v>0.27</v>
-      </c>
-      <c r="H68" t="str">
-        <v/>
+        <v>-1.81</v>
+      </c>
+      <c r="H68" s="2">
+        <v>-0.85</v>
       </c>
       <c r="I68" s="1">
         <v>0</v>
       </c>
-      <c r="J68" t="str">
-        <v/>
+      <c r="J68" s="1">
+        <v>20269.45</v>
       </c>
       <c r="K68" s="1">
-        <v>28389.21</v>
+        <v>20294.36</v>
       </c>
       <c r="L68" s="1">
-        <v>29566.8</v>
+        <v>21071.25</v>
       </c>
       <c r="M68" t="str">
         <v/>
@@ -3196,37 +3196,37 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="C69" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="D69" s="1">
-        <v>49537.55</v>
+        <v>13565.15</v>
       </c>
       <c r="E69" s="2">
-        <v>-0.67</v>
+        <v>-1.11</v>
       </c>
       <c r="F69" s="2">
-        <v>0.23</v>
+        <v>-1.11</v>
       </c>
       <c r="G69" s="2">
-        <v>-0.08</v>
+        <v>-1.21</v>
       </c>
       <c r="H69" s="2">
-        <v>4.15</v>
+        <v>-1.54</v>
       </c>
       <c r="I69" s="1">
         <v>0</v>
       </c>
       <c r="J69" s="1">
-        <v>49059.66</v>
+        <v>14003.41</v>
       </c>
       <c r="K69" s="1">
-        <v>49763.68</v>
+        <v>13704.6</v>
       </c>
       <c r="L69" s="1">
-        <v>51116.29</v>
+        <v>14407.94</v>
       </c>
       <c r="M69" t="str">
         <v/>
@@ -3237,37 +3237,37 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="C70" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="D70" s="1">
-        <v>20256.35</v>
+        <v>35840.55</v>
       </c>
       <c r="E70" s="2">
-        <v>-0.71</v>
+        <v>-1.12</v>
       </c>
       <c r="F70" s="2">
-        <v>0.45</v>
+        <v>-1.12</v>
       </c>
       <c r="G70" s="2">
-        <v>-0.78</v>
+        <v>-2.15</v>
       </c>
       <c r="H70" s="2">
-        <v>0.19</v>
+        <v>-2.49</v>
       </c>
       <c r="I70" s="1">
         <v>0</v>
       </c>
       <c r="J70" s="1">
-        <v>20269.36</v>
+        <v>37126.93</v>
       </c>
       <c r="K70" s="1">
-        <v>20363.33</v>
+        <v>36345.95</v>
       </c>
       <c r="L70" s="1">
-        <v>21125.93</v>
+        <v>38605.84</v>
       </c>
       <c r="M70" t="str">
         <v/>
@@ -3278,37 +3278,37 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>CNXENERGY</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="C71" t="str">
-        <v>CNXENERGY</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="D71" s="1">
-        <v>36146</v>
+        <v>17435.15</v>
       </c>
       <c r="E71" s="2">
-        <v>-0.98</v>
+        <v>-1.15</v>
       </c>
       <c r="F71" s="2">
-        <v>1</v>
+        <v>-1.15</v>
       </c>
       <c r="G71" s="2">
-        <v>-1.34</v>
+        <v>-2.04</v>
       </c>
       <c r="H71" s="2">
-        <v>2.32</v>
+        <v>4.5</v>
       </c>
       <c r="I71" s="1">
         <v>0</v>
       </c>
       <c r="J71" s="1">
-        <v>37711.58</v>
+        <v>16946.17</v>
       </c>
       <c r="K71" s="1">
-        <v>36312.31</v>
+        <v>17687.1</v>
       </c>
       <c r="L71" s="1">
-        <v>37656.78</v>
+        <v>18138.87</v>
       </c>
       <c r="M71" t="str">
         <v/>
@@ -3319,37 +3319,37 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="C72" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="D72" s="1">
-        <v>25177.45</v>
+        <v>7373.5</v>
       </c>
       <c r="E72" s="2">
-        <v>-1.01</v>
+        <v>-1.15</v>
       </c>
       <c r="F72" s="2">
-        <v>-0.12</v>
+        <v>-1.15</v>
       </c>
       <c r="G72" s="2">
-        <v>-0.85</v>
+        <v>4.2</v>
       </c>
       <c r="H72" s="2">
-        <v>0.77</v>
+        <v>-2.5</v>
       </c>
       <c r="I72" s="1">
         <v>0</v>
       </c>
       <c r="J72" s="1">
-        <v>25475.55</v>
+        <v>7336.18</v>
       </c>
       <c r="K72" s="1">
-        <v>25387.93</v>
+        <v>7277.83</v>
       </c>
       <c r="L72" s="1">
-        <v>26324.01</v>
+        <v>7418.47</v>
       </c>
       <c r="M72" t="str">
         <v/>
@@ -3360,37 +3360,37 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="C73" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="D73" s="1">
-        <v>60220.05</v>
+        <v>22698.65</v>
       </c>
       <c r="E73" s="2">
-        <v>-1.03</v>
+        <v>-1.16</v>
       </c>
       <c r="F73" s="2">
-        <v>-0.62</v>
+        <v>-1.16</v>
       </c>
       <c r="G73" s="2">
-        <v>-0.91</v>
+        <v>-0.3</v>
       </c>
       <c r="H73" s="2">
-        <v>-2.74</v>
+        <v>-5.65</v>
       </c>
       <c r="I73" s="1">
         <v>0</v>
       </c>
       <c r="J73" s="1">
-        <v>61786.34</v>
+        <v>23508.76</v>
       </c>
       <c r="K73" s="1">
-        <v>60848.88</v>
+        <v>22906.09</v>
       </c>
       <c r="L73" s="1">
-        <v>62983.37</v>
+        <v>23833.06</v>
       </c>
       <c r="M73" t="str">
         <v/>
@@ -3401,37 +3401,37 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="C74" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="D74" s="1">
-        <v>29052.4</v>
+        <v>19244.1</v>
       </c>
       <c r="E74" s="2">
-        <v>-1.09</v>
+        <v>-1.16</v>
       </c>
       <c r="F74" s="2">
-        <v>-0.5</v>
+        <v>-1.16</v>
       </c>
       <c r="G74" s="2">
-        <v>-1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H74" s="2">
-        <v>-6.73</v>
+        <v>-10.12</v>
       </c>
       <c r="I74" s="1">
         <v>0</v>
       </c>
       <c r="J74" s="1">
-        <v>30436.75</v>
+        <v>20122.6</v>
       </c>
       <c r="K74" s="1">
-        <v>29387.64</v>
+        <v>19201.68</v>
       </c>
       <c r="L74" s="1">
-        <v>30474.55</v>
+        <v>19894.51</v>
       </c>
       <c r="M74" t="str">
         <v/>
@@ -3442,37 +3442,37 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="C75" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="D75" s="1">
-        <v>9191.25</v>
+        <v>816.05</v>
       </c>
       <c r="E75" s="2">
-        <v>-1.11</v>
+        <v>-1.2</v>
       </c>
       <c r="F75" s="2">
-        <v>2.05</v>
+        <v>-1.2</v>
       </c>
       <c r="G75" s="2">
-        <v>-0.92</v>
+        <v>-3.69</v>
       </c>
       <c r="H75" s="2">
-        <v>18.64</v>
+        <v>-7.05</v>
       </c>
       <c r="I75" s="1">
         <v>0</v>
       </c>
       <c r="J75" s="1">
-        <v>8813.13</v>
+        <v>822.91</v>
       </c>
       <c r="K75" s="1">
-        <v>9203.04</v>
+        <v>824.12</v>
       </c>
       <c r="L75" s="1">
-        <v>9525.45</v>
+        <v>867.25</v>
       </c>
       <c r="M75" t="str">
         <v/>
@@ -3483,37 +3483,37 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="C76" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="D76" s="1">
-        <v>9567.75</v>
+        <v>11392.1</v>
       </c>
       <c r="E76" s="2">
-        <v>-1.15</v>
+        <v>-1.22</v>
       </c>
       <c r="F76" s="2">
-        <v>0.18</v>
+        <v>-1.22</v>
       </c>
       <c r="G76" s="2">
-        <v>-0.68</v>
+        <v>2.21</v>
       </c>
       <c r="H76" s="2">
-        <v>11.17</v>
+        <v>-14.19</v>
       </c>
       <c r="I76" s="1">
         <v>0</v>
       </c>
       <c r="J76" s="1">
-        <v>8964.67</v>
+        <v>12199.92</v>
       </c>
       <c r="K76" s="1">
-        <v>9653.42</v>
+        <v>11310.44</v>
       </c>
       <c r="L76" s="1">
-        <v>9850.66</v>
+        <v>11584.13</v>
       </c>
       <c r="M76" t="str">
         <v/>
@@ -3524,37 +3524,37 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="C77" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="D77" s="1">
-        <v>47493.1</v>
+        <v>30099.85</v>
       </c>
       <c r="E77" s="2">
-        <v>-1.17</v>
+        <v>-1.25</v>
       </c>
       <c r="F77" s="2">
-        <v>0.46</v>
+        <v>-1.25</v>
       </c>
       <c r="G77" s="2">
-        <v>-0.76</v>
+        <v>3.74</v>
       </c>
       <c r="H77" s="2">
-        <v>7.97</v>
+        <v>-10.57</v>
       </c>
       <c r="I77" s="1">
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>44875.34</v>
+        <v>30995.16</v>
       </c>
       <c r="K77" s="1">
-        <v>47821.92</v>
+        <v>29659.55</v>
       </c>
       <c r="L77" s="1">
-        <v>48481.22</v>
+        <v>30157.43</v>
       </c>
       <c r="M77" t="str">
         <v/>
@@ -3571,31 +3571,31 @@
         <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="D78" s="1">
-        <v>16134.3</v>
+        <v>15866</v>
       </c>
       <c r="E78" s="2">
-        <v>-1.18</v>
+        <v>-1.27</v>
       </c>
       <c r="F78" s="2">
-        <v>0.77</v>
+        <v>-1.27</v>
       </c>
       <c r="G78" s="2">
-        <v>-0.95</v>
+        <v>-2.6</v>
       </c>
       <c r="H78" s="2">
-        <v>0.81</v>
+        <v>-0.86</v>
       </c>
       <c r="I78" s="1">
         <v>0</v>
       </c>
       <c r="J78" s="1">
-        <v>16135.62</v>
+        <v>16134.51</v>
       </c>
       <c r="K78" s="1">
-        <v>16237.94</v>
+        <v>16147.79</v>
       </c>
       <c r="L78" s="1">
-        <v>16928.81</v>
+        <v>16888.42</v>
       </c>
       <c r="M78" t="str">
         <v/>
@@ -3606,37 +3606,37 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>NIFTYFMCG</v>
+        <v>Nifty IT</v>
       </c>
       <c r="C79" t="str">
-        <v>NIFTYFMCG</v>
+        <v>CNXIT</v>
       </c>
       <c r="D79" s="1">
-        <v>44730.7</v>
+        <v>31516.3</v>
       </c>
       <c r="E79" s="2">
-        <v>-1.2</v>
+        <v>-1.28</v>
       </c>
       <c r="F79" s="2">
-        <v>-0.3</v>
+        <v>-1.28</v>
       </c>
       <c r="G79" s="2">
-        <v>0.5</v>
+        <v>13.76</v>
       </c>
       <c r="H79" s="2">
-        <v>-19.37</v>
+        <v>-16.81</v>
       </c>
       <c r="I79" s="1">
         <v>0</v>
       </c>
       <c r="J79" s="1">
-        <v>49195.8</v>
+        <v>30903.39</v>
       </c>
       <c r="K79" s="1">
-        <v>44778.81</v>
+        <v>29999.76</v>
       </c>
       <c r="L79" s="1">
-        <v>46324</v>
+        <v>29809.61</v>
       </c>
       <c r="M79" t="str">
         <v/>
@@ -3647,37 +3647,37 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="C80" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="D80" s="1">
-        <v>17613.55</v>
+        <v>8336.65</v>
       </c>
       <c r="E80" s="2">
-        <v>-1.23</v>
+        <v>-1.32</v>
       </c>
       <c r="F80" s="2">
-        <v>0.22</v>
+        <v>-1.32</v>
       </c>
       <c r="G80" s="2">
-        <v>-1.04</v>
+        <v>3.21</v>
       </c>
       <c r="H80" s="2">
-        <v>5.57</v>
+        <v>-17</v>
       </c>
       <c r="I80" s="1">
         <v>0</v>
       </c>
       <c r="J80" s="1">
-        <v>16937.04</v>
+        <v>8788.93</v>
       </c>
       <c r="K80" s="1">
-        <v>17764.07</v>
+        <v>8269.57</v>
       </c>
       <c r="L80" s="1">
-        <v>18170.76</v>
+        <v>8415.39</v>
       </c>
       <c r="M80" t="str">
         <v/>
@@ -3688,37 +3688,37 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>NIFTY50PR1XINV</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="C81" t="str">
-        <v>NIFTY50PR1XINV</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="D81" s="1">
-        <v>232.9</v>
+        <v>8552.4</v>
       </c>
       <c r="E81" s="2">
-        <v>-1.38</v>
+        <v>-1.36</v>
       </c>
       <c r="F81" s="2">
-        <v>-1.79</v>
+        <v>-1.36</v>
       </c>
       <c r="G81" s="2">
-        <v>-1.29</v>
+        <v>6.55</v>
       </c>
       <c r="H81" s="2">
-        <v>16.45</v>
+        <v>-9.23</v>
       </c>
       <c r="I81" s="1">
         <v>0</v>
       </c>
       <c r="J81" s="1">
-        <v>218.42</v>
+        <v>8266.39</v>
       </c>
       <c r="K81" s="1">
-        <v>235.46</v>
+        <v>8389.27</v>
       </c>
       <c r="L81" s="1">
-        <v>226.11</v>
+        <v>8541.32</v>
       </c>
       <c r="M81" t="str">
         <v/>
@@ -3729,37 +3729,37 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="C82" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="D82" s="1">
-        <v>188.9</v>
+        <v>3813</v>
       </c>
       <c r="E82" s="2">
-        <v>-1.38</v>
+        <v>-1.36</v>
       </c>
       <c r="F82" s="2">
-        <v>-1.79</v>
+        <v>-1.36</v>
       </c>
       <c r="G82" s="2">
-        <v>-1.31</v>
+        <v>0.81</v>
       </c>
       <c r="H82" s="2">
-        <v>15.43</v>
+        <v>-12.41</v>
       </c>
       <c r="I82" s="1">
         <v>0</v>
       </c>
       <c r="J82" s="1">
-        <v>178.04</v>
+        <v>4040.15</v>
       </c>
       <c r="K82" s="1">
-        <v>190.99</v>
+        <v>3803.95</v>
       </c>
       <c r="L82" s="1">
-        <v>183.44</v>
+        <v>3939.04</v>
       </c>
       <c r="M82" t="str">
         <v/>
@@ -3770,37 +3770,37 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="C83" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="D83" s="1">
-        <v>19115.6</v>
+        <v>26836.5</v>
       </c>
       <c r="E83" s="2">
-        <v>-1.39</v>
+        <v>-1.38</v>
       </c>
       <c r="F83" s="2">
-        <v>-0.2</v>
+        <v>-1.38</v>
       </c>
       <c r="G83" s="2">
-        <v>-0.68</v>
+        <v>1.05</v>
       </c>
       <c r="H83" s="2">
-        <v>7.91</v>
+        <v>-11.07</v>
       </c>
       <c r="I83" s="1">
         <v>0</v>
       </c>
       <c r="J83" s="1">
-        <v>18166.43</v>
+        <v>28581.69</v>
       </c>
       <c r="K83" s="1">
-        <v>19319.52</v>
+        <v>26935.59</v>
       </c>
       <c r="L83" s="1">
-        <v>19711.98</v>
+        <v>27702.92</v>
       </c>
       <c r="M83" t="str">
         <v/>
@@ -3811,37 +3811,37 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="C84" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="D84" s="1">
-        <v>29487.55</v>
+        <v>43975.5</v>
       </c>
       <c r="E84" s="2">
-        <v>-1.45</v>
+        <v>-1.44</v>
       </c>
       <c r="F84" s="2">
-        <v>-0.84</v>
+        <v>-1.44</v>
       </c>
       <c r="G84" s="2">
-        <v>-2.8</v>
+        <v>-1.2</v>
       </c>
       <c r="H84" s="2">
-        <v>-3.53</v>
+        <v>-20.73</v>
       </c>
       <c r="I84" s="1">
         <v>0</v>
       </c>
       <c r="J84" s="1">
-        <v>31428.99</v>
+        <v>49087.83</v>
       </c>
       <c r="K84" s="1">
-        <v>29954.52</v>
+        <v>44615.97</v>
       </c>
       <c r="L84" s="1">
-        <v>31920.11</v>
+        <v>46121.99</v>
       </c>
       <c r="M84" t="str">
         <v/>
@@ -3852,37 +3852,37 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="C85" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="D85" s="1">
-        <v>8042.55</v>
+        <v>24987.1</v>
       </c>
       <c r="E85" s="2">
-        <v>-1.53</v>
+        <v>-1.58</v>
       </c>
       <c r="F85" s="2">
-        <v>-1.03</v>
+        <v>-1.58</v>
       </c>
       <c r="G85" s="2">
-        <v>0.33</v>
+        <v>1.37</v>
       </c>
       <c r="H85" s="2">
-        <v>-5.75</v>
+        <v>-9.51</v>
       </c>
       <c r="I85" s="1">
         <v>0</v>
       </c>
       <c r="J85" s="1">
-        <v>8576.38</v>
+        <v>26250.15</v>
       </c>
       <c r="K85" s="1">
-        <v>8091.2</v>
+        <v>25067.99</v>
       </c>
       <c r="L85" s="1">
-        <v>8392.45</v>
+        <v>25597.84</v>
       </c>
       <c r="M85" t="str">
         <v/>
@@ -3893,37 +3893,37 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="C86" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="D86" s="1">
-        <v>1615.9</v>
+        <v>27914.3</v>
       </c>
       <c r="E86" s="2">
-        <v>-1.55</v>
+        <v>-1.59</v>
       </c>
       <c r="F86" s="2">
-        <v>4.03</v>
+        <v>-1.59</v>
       </c>
       <c r="G86" s="2">
-        <v>2.07</v>
-      </c>
-      <c r="H86" s="2">
-        <v>11.85</v>
+        <v>-1.58</v>
+      </c>
+      <c r="H86" t="str">
+        <v/>
       </c>
       <c r="I86" s="1">
         <v>0</v>
       </c>
-      <c r="J86" s="1">
-        <v>1464.8</v>
+      <c r="J86" t="str">
+        <v/>
       </c>
       <c r="K86" s="1">
-        <v>1595.38</v>
+        <v>28297.32</v>
       </c>
       <c r="L86" s="1">
-        <v>1568.8</v>
+        <v>29468.3</v>
       </c>
       <c r="M86" t="str">
         <v/>
@@ -3934,37 +3934,37 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="C87" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="D87" s="1">
-        <v>52148.6</v>
+        <v>25306.15</v>
       </c>
       <c r="E87" s="2">
-        <v>-1.66</v>
+        <v>-1.67</v>
       </c>
       <c r="F87" s="2">
-        <v>-1.09</v>
+        <v>-1.67</v>
       </c>
       <c r="G87" s="2">
-        <v>-1.41</v>
+        <v>-3.6</v>
       </c>
       <c r="H87" s="2">
-        <v>-1.06</v>
+        <v>12.24</v>
       </c>
       <c r="I87" s="1">
         <v>0</v>
       </c>
       <c r="J87" s="1">
-        <v>52572.02</v>
+        <v>23595.54</v>
       </c>
       <c r="K87" s="1">
-        <v>52960.69</v>
+        <v>25736.65</v>
       </c>
       <c r="L87" s="1">
-        <v>54354.16</v>
+        <v>26179.41</v>
       </c>
       <c r="M87" t="str">
         <v/>
@@ -3975,37 +3975,37 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="C88" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="D88" s="1">
-        <v>25528.3</v>
+        <v>27189.1</v>
       </c>
       <c r="E88" s="2">
-        <v>-1.75</v>
+        <v>-1.85</v>
       </c>
       <c r="F88" s="2">
-        <v>-0.03</v>
+        <v>-1.85</v>
       </c>
       <c r="G88" s="2">
-        <v>-2.75</v>
+        <v>1.85</v>
       </c>
       <c r="H88" s="2">
-        <v>13.23</v>
+        <v>-5.33</v>
       </c>
       <c r="I88" s="1">
         <v>0</v>
       </c>
       <c r="J88" s="1">
-        <v>23564.99</v>
+        <v>27387.51</v>
       </c>
       <c r="K88" s="1">
-        <v>25848.94</v>
+        <v>27263.36</v>
       </c>
       <c r="L88" s="1">
-        <v>26198.14</v>
+        <v>27306.52</v>
       </c>
       <c r="M88" t="str">
         <v/>
@@ -4016,37 +4016,37 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="C89" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="D89" s="1">
-        <v>53689.85</v>
+        <v>16229.05</v>
       </c>
       <c r="E89" s="2">
-        <v>-2.23</v>
+        <v>-2.27</v>
       </c>
       <c r="F89" s="2">
-        <v>-2.98</v>
+        <v>-2.27</v>
       </c>
       <c r="G89" s="2">
-        <v>-0.72</v>
+        <v>2</v>
       </c>
       <c r="H89" s="2">
-        <v>6.72</v>
+        <v>-26.22</v>
       </c>
       <c r="I89" s="1">
         <v>0</v>
       </c>
       <c r="J89" s="1">
-        <v>52149.55</v>
+        <v>18456.36</v>
       </c>
       <c r="K89" s="1">
-        <v>54827.74</v>
+        <v>16125.26</v>
       </c>
       <c r="L89" s="1">
-        <v>55842.94</v>
+        <v>17256.4</v>
       </c>
       <c r="M89" t="str">
         <v/>
@@ -4057,37 +4057,37 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>India VIX</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="C90" t="str">
-        <v>INDIAVIX</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="D90" s="1">
-        <v>14.02</v>
+        <v>10639.55</v>
       </c>
       <c r="E90" s="2">
-        <v>-4.17</v>
+        <v>-2.27</v>
       </c>
       <c r="F90" s="2">
-        <v>-2.5</v>
+        <v>-2.27</v>
       </c>
       <c r="G90" s="2">
-        <v>3.93</v>
+        <v>1.95</v>
       </c>
       <c r="H90" s="2">
-        <v>47.89</v>
+        <v>-27.62</v>
       </c>
       <c r="I90" s="1">
         <v>0</v>
       </c>
       <c r="J90" s="1">
-        <v>14.76</v>
+        <v>12233.4</v>
       </c>
       <c r="K90" s="1">
-        <v>14.18</v>
+        <v>10574.3</v>
       </c>
       <c r="L90" s="1">
-        <v>12.26</v>
+        <v>11321.07</v>
       </c>
       <c r="M90" t="str">
         <v/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -32,10 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
     <numFmt numFmtId="60" formatCode="#,##,##0.##"/>
     <numFmt numFmtId="61" formatCode="#,##,##0.##&quot;%&quot;"/>
+    <numFmt numFmtId="62" formatCode="0.##"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -66,10 +67,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="61" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="62" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:S90"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -441,6 +443,24 @@
         <v>SMA50</v>
       </c>
       <c r="M1" t="str">
+        <v>macd_line</v>
+      </c>
+      <c r="N1" t="str">
+        <v>macd_signal</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Weekly MACD_Line</v>
+      </c>
+      <c r="P1" t="str">
+        <v>weekly macd_signal</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>MONTHLY macd_line</v>
+      </c>
+      <c r="R1" t="str">
+        <v>MONTLY macd_signal</v>
+      </c>
+      <c r="S1" t="str">
         <v>Add Column</v>
       </c>
     </row>
@@ -481,7 +501,25 @@
       <c r="L2" s="1">
         <v>12.36</v>
       </c>
-      <c r="M2" t="str">
+      <c r="M2" s="3">
+        <v>0.66</v>
+      </c>
+      <c r="N2" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="O2" s="3">
+        <v>-0.36</v>
+      </c>
+      <c r="P2" s="3">
+        <v>-0.76</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>-0.09</v>
+      </c>
+      <c r="R2" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="S2" t="str">
         <v/>
       </c>
     </row>
@@ -522,7 +560,25 @@
       <c r="L3" s="1">
         <v>8374.79</v>
       </c>
-      <c r="M3" t="str">
+      <c r="M3" s="3">
+        <v>-56.26</v>
+      </c>
+      <c r="N3" s="3">
+        <v>-87.73</v>
+      </c>
+      <c r="O3" s="3">
+        <v>-72.14</v>
+      </c>
+      <c r="P3" s="3">
+        <v>-29.08</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>578.77</v>
+      </c>
+      <c r="R3" s="3">
+        <v>686.08</v>
+      </c>
+      <c r="S3" t="str">
         <v/>
       </c>
     </row>
@@ -563,7 +619,25 @@
       <c r="L4" s="1">
         <v>226.77</v>
       </c>
-      <c r="M4" t="str">
+      <c r="M4" s="3">
+        <v>2.01</v>
+      </c>
+      <c r="N4" s="3">
+        <v>2.91</v>
+      </c>
+      <c r="O4" s="3">
+        <v>4.51</v>
+      </c>
+      <c r="P4" s="3">
+        <v>3.42</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>-0.82</v>
+      </c>
+      <c r="R4" s="3">
+        <v>-4.81</v>
+      </c>
+      <c r="S4" t="str">
         <v/>
       </c>
     </row>
@@ -604,7 +678,25 @@
       <c r="L5" s="1">
         <v>183.97</v>
       </c>
-      <c r="M5" t="str">
+      <c r="M5" s="3">
+        <v>1.61</v>
+      </c>
+      <c r="N5" s="3">
+        <v>2.34</v>
+      </c>
+      <c r="O5" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="P5" s="3">
+        <v>2.45</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>-2.64</v>
+      </c>
+      <c r="R5" s="3">
+        <v>-6.06</v>
+      </c>
+      <c r="S5" t="str">
         <v/>
       </c>
     </row>
@@ -645,7 +737,25 @@
       <c r="L6" s="1">
         <v>3324.09</v>
       </c>
-      <c r="M6" t="str">
+      <c r="M6" s="3">
+        <v>-11.82</v>
+      </c>
+      <c r="N6" s="3">
+        <v>-10.63</v>
+      </c>
+      <c r="O6" s="3">
+        <v>8.31</v>
+      </c>
+      <c r="P6" s="3">
+        <v>18.11</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>140.08</v>
+      </c>
+      <c r="R6" s="3">
+        <v>155.52</v>
+      </c>
+      <c r="S6" t="str">
         <v/>
       </c>
     </row>
@@ -686,7 +796,25 @@
       <c r="L7" s="1">
         <v>1609.47</v>
       </c>
-      <c r="M7" t="str">
+      <c r="M7" s="3">
+        <v>-1.88</v>
+      </c>
+      <c r="N7" s="3">
+        <v>-1.26</v>
+      </c>
+      <c r="O7" s="3">
+        <v>7.04</v>
+      </c>
+      <c r="P7" s="3">
+        <v>9.39</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>35</v>
+      </c>
+      <c r="R7" s="3">
+        <v>33.14</v>
+      </c>
+      <c r="S7" t="str">
         <v/>
       </c>
     </row>
@@ -727,7 +855,25 @@
       <c r="L8" s="1">
         <v>1323.02</v>
       </c>
-      <c r="M8" t="str">
+      <c r="M8" s="3">
+        <v>-3.88</v>
+      </c>
+      <c r="N8" s="3">
+        <v>-3.27</v>
+      </c>
+      <c r="O8" s="3">
+        <v>2.37</v>
+      </c>
+      <c r="P8" s="3">
+        <v>5.74</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>24.16</v>
+      </c>
+      <c r="R8" s="3">
+        <v>24.25</v>
+      </c>
+      <c r="S8" t="str">
         <v/>
       </c>
     </row>
@@ -768,7 +914,25 @@
       <c r="L9" s="1">
         <v>1459.16</v>
       </c>
-      <c r="M9" t="str">
+      <c r="M9" s="3">
+        <v>-3.08</v>
+      </c>
+      <c r="N9" s="3">
+        <v>-2.45</v>
+      </c>
+      <c r="O9" s="3">
+        <v>4.37</v>
+      </c>
+      <c r="P9" s="3">
+        <v>7.36</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>29.31</v>
+      </c>
+      <c r="R9" s="3">
+        <v>28.58</v>
+      </c>
+      <c r="S9" t="str">
         <v/>
       </c>
     </row>
@@ -809,7 +973,25 @@
       <c r="L10" s="1">
         <v>1281.51</v>
       </c>
-      <c r="M10" t="str">
+      <c r="M10" s="3">
+        <v>-4.53</v>
+      </c>
+      <c r="N10" s="3">
+        <v>-3.79</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1.39</v>
+      </c>
+      <c r="P10" s="3">
+        <v>4.98</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>21.48</v>
+      </c>
+      <c r="R10" s="3">
+        <v>21.99</v>
+      </c>
+      <c r="S10" t="str">
         <v/>
       </c>
     </row>
@@ -850,7 +1032,25 @@
       <c r="L11" s="1">
         <v>194.2</v>
       </c>
-      <c r="M11" t="str">
+      <c r="M11" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="N11" s="3">
+        <v>2.54</v>
+      </c>
+      <c r="O11" s="3">
+        <v>11.77</v>
+      </c>
+      <c r="P11" s="3">
+        <v>5.66</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>5.31</v>
+      </c>
+      <c r="R11" s="3">
+        <v>7.65</v>
+      </c>
+      <c r="S11" t="str">
         <v/>
       </c>
     </row>
@@ -891,7 +1091,25 @@
       <c r="L12" s="1">
         <v>3539.34</v>
       </c>
-      <c r="M12" t="str">
+      <c r="M12" s="3">
+        <v>-16.47</v>
+      </c>
+      <c r="N12" s="3">
+        <v>-14.31</v>
+      </c>
+      <c r="O12" s="3">
+        <v>4.22</v>
+      </c>
+      <c r="P12" s="3">
+        <v>15.71</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>120.26</v>
+      </c>
+      <c r="R12" s="3">
+        <v>142.19</v>
+      </c>
+      <c r="S12" t="str">
         <v/>
       </c>
     </row>
@@ -906,19 +1124,19 @@
         <v>NIFTYGS813YR</v>
       </c>
       <c r="D13" s="1">
-        <v>2981.18</v>
+        <v>2980.67</v>
       </c>
       <c r="E13" s="2">
-        <v>-0.05</v>
+        <v>-0.07</v>
       </c>
       <c r="F13" s="2">
-        <v>-0.05</v>
+        <v>-0.07</v>
       </c>
       <c r="G13" s="2">
-        <v>-1.09</v>
+        <v>-1.1</v>
       </c>
       <c r="H13" s="2">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
@@ -927,12 +1145,30 @@
         <v>3001.37</v>
       </c>
       <c r="K13" s="1">
-        <v>2988.4</v>
+        <v>2988.3</v>
       </c>
       <c r="L13" s="1">
-        <v>3030.95</v>
-      </c>
-      <c r="M13" t="str">
+        <v>3030.94</v>
+      </c>
+      <c r="M13" s="3">
+        <v>-15.04</v>
+      </c>
+      <c r="N13" s="3">
+        <v>-13.48</v>
+      </c>
+      <c r="O13" s="3">
+        <v>1.13</v>
+      </c>
+      <c r="P13" s="3">
+        <v>11.58</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>115.58</v>
+      </c>
+      <c r="R13" s="3">
+        <v>132.99</v>
+      </c>
+      <c r="S13" t="str">
         <v/>
       </c>
     </row>
@@ -947,19 +1183,19 @@
         <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="D14" s="1">
-        <v>3073.57</v>
+        <v>3073.25</v>
       </c>
       <c r="E14" s="2">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="F14" s="2">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="G14" s="2">
-        <v>-0.99</v>
+        <v>-1</v>
       </c>
       <c r="H14" s="2">
-        <v>0.69</v>
+        <v>0.68</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
@@ -968,12 +1204,30 @@
         <v>3085.84</v>
       </c>
       <c r="K14" s="1">
-        <v>3080.32</v>
+        <v>3080.26</v>
       </c>
       <c r="L14" s="1">
-        <v>3122.97</v>
-      </c>
-      <c r="M14" t="str">
+        <v>3122.96</v>
+      </c>
+      <c r="M14" s="3">
+        <v>-14.85</v>
+      </c>
+      <c r="N14" s="3">
+        <v>-13.41</v>
+      </c>
+      <c r="O14" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="P14" s="3">
+        <v>14.14</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>119.5</v>
+      </c>
+      <c r="R14" s="3">
+        <v>136.75</v>
+      </c>
+      <c r="S14" t="str">
         <v/>
       </c>
     </row>
@@ -988,19 +1242,19 @@
         <v>NIFTYGS10YR</v>
       </c>
       <c r="D15" s="1">
-        <v>2608.99</v>
+        <v>2608.21</v>
       </c>
       <c r="E15" s="2">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="F15" s="2">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="G15" s="2">
-        <v>-1.11</v>
+        <v>-1.14</v>
       </c>
       <c r="H15" s="2">
-        <v>-0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
@@ -1009,12 +1263,30 @@
         <v>2632.47</v>
       </c>
       <c r="K15" s="1">
-        <v>2615.26</v>
+        <v>2615.12</v>
       </c>
       <c r="L15" s="1">
-        <v>2653.16</v>
-      </c>
-      <c r="M15" t="str">
+        <v>2653.15</v>
+      </c>
+      <c r="M15" s="3">
+        <v>-13.45</v>
+      </c>
+      <c r="N15" s="3">
+        <v>-12.09</v>
+      </c>
+      <c r="O15" s="3">
+        <v>-1.22</v>
+      </c>
+      <c r="P15" s="3">
+        <v>7.61</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>90.59</v>
+      </c>
+      <c r="R15" s="3">
+        <v>106.53</v>
+      </c>
+      <c r="S15" t="str">
         <v/>
       </c>
     </row>
@@ -1055,7 +1327,25 @@
       <c r="L16" s="1">
         <v>10920.58</v>
       </c>
-      <c r="M16" t="str">
+      <c r="M16" s="3">
+        <v>-129.66</v>
+      </c>
+      <c r="N16" s="3">
+        <v>-148.15</v>
+      </c>
+      <c r="O16" s="3">
+        <v>-217.36</v>
+      </c>
+      <c r="P16" s="3">
+        <v>-158.68</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>81.1</v>
+      </c>
+      <c r="R16" s="3">
+        <v>281.02</v>
+      </c>
+      <c r="S16" t="str">
         <v/>
       </c>
     </row>
@@ -1070,19 +1360,19 @@
         <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="D17" s="1">
-        <v>842.29</v>
+        <v>842.03</v>
       </c>
       <c r="E17" s="2">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
       <c r="F17" s="2">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
       <c r="G17" s="2">
-        <v>-1.51</v>
+        <v>-1.54</v>
       </c>
       <c r="H17" s="2">
-        <v>-5.51</v>
+        <v>-5.54</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
@@ -1091,12 +1381,30 @@
         <v>874.39</v>
       </c>
       <c r="K17" s="1">
-        <v>845.59</v>
+        <v>845.54</v>
       </c>
       <c r="L17" s="1">
-        <v>863.13</v>
-      </c>
-      <c r="M17" t="str">
+        <v>863.12</v>
+      </c>
+      <c r="M17" s="3">
+        <v>-6.21</v>
+      </c>
+      <c r="N17" s="3">
+        <v>-5.74</v>
+      </c>
+      <c r="O17" s="3">
+        <v>-8.45</v>
+      </c>
+      <c r="P17" s="3">
+        <v>-5.57</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>-16.9</v>
+      </c>
+      <c r="R17" s="3">
+        <v>-14.13</v>
+      </c>
+      <c r="S17" t="str">
         <v/>
       </c>
     </row>
@@ -1137,7 +1445,25 @@
       <c r="L18" s="1">
         <v>1572.07</v>
       </c>
-      <c r="M18" t="str">
+      <c r="M18" s="3">
+        <v>21.7</v>
+      </c>
+      <c r="N18" s="3">
+        <v>12.12</v>
+      </c>
+      <c r="O18" s="3">
+        <v>37.41</v>
+      </c>
+      <c r="P18" s="3">
+        <v>32.59</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-68.54</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-104.6</v>
+      </c>
+      <c r="S18" t="str">
         <v/>
       </c>
     </row>
@@ -1178,7 +1504,25 @@
       <c r="L19" s="1">
         <v>55763.52</v>
       </c>
-      <c r="M19" t="str">
+      <c r="M19" s="3">
+        <v>-379.62</v>
+      </c>
+      <c r="N19" s="3">
+        <v>-291.78</v>
+      </c>
+      <c r="O19" s="3">
+        <v>790.27</v>
+      </c>
+      <c r="P19" s="3">
+        <v>1172.96</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>3756.85</v>
+      </c>
+      <c r="R19" s="3">
+        <v>3900.21</v>
+      </c>
+      <c r="S19" t="str">
         <v/>
       </c>
     </row>
@@ -1193,7 +1537,7 @@
         <v>NIFTYGS1115YR</v>
       </c>
       <c r="D20" s="1">
-        <v>3293.93</v>
+        <v>3294.03</v>
       </c>
       <c r="E20" s="2">
         <v>-0.28</v>
@@ -1205,7 +1549,7 @@
         <v>-0.83</v>
       </c>
       <c r="H20" s="2">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
@@ -1214,12 +1558,30 @@
         <v>3294.67</v>
       </c>
       <c r="K20" s="1">
-        <v>3302.32</v>
+        <v>3302.34</v>
       </c>
       <c r="L20" s="1">
-        <v>3353.88</v>
-      </c>
-      <c r="M20" t="str">
+        <v>3353.89</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-17.29</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-16.97</v>
+      </c>
+      <c r="O20" s="3">
+        <v>8.25</v>
+      </c>
+      <c r="P20" s="3">
+        <v>21.63</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>137.13</v>
+      </c>
+      <c r="R20" s="3">
+        <v>154.03</v>
+      </c>
+      <c r="S20" t="str">
         <v/>
       </c>
     </row>
@@ -1260,7 +1622,25 @@
       <c r="L21" s="1">
         <v>54265.33</v>
       </c>
-      <c r="M21" t="str">
+      <c r="M21" s="3">
+        <v>-513.88</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-448.09</v>
+      </c>
+      <c r="O21" s="3">
+        <v>119.23</v>
+      </c>
+      <c r="P21" s="3">
+        <v>462.24</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-663.92</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-1104.48</v>
+      </c>
+      <c r="S21" t="str">
         <v/>
       </c>
     </row>
@@ -1301,7 +1681,25 @@
       <c r="L22" s="1">
         <v>71956.6</v>
       </c>
-      <c r="M22" t="str">
+      <c r="M22" s="3">
+        <v>-936.03</v>
+      </c>
+      <c r="N22" s="3">
+        <v>-988.8</v>
+      </c>
+      <c r="O22" s="3">
+        <v>-115.29</v>
+      </c>
+      <c r="P22" s="3">
+        <v>595.35</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>2746.93</v>
+      </c>
+      <c r="R22" s="3">
+        <v>3199.01</v>
+      </c>
+      <c r="S22" t="str">
         <v/>
       </c>
     </row>
@@ -1342,7 +1740,25 @@
       <c r="L23" s="1">
         <v>12892.37</v>
       </c>
-      <c r="M23" t="str">
+      <c r="M23" s="3">
+        <v>-269.43</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-239.21</v>
+      </c>
+      <c r="O23" s="3">
+        <v>31.91</v>
+      </c>
+      <c r="P23" s="3">
+        <v>212.27</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>1154.3</v>
+      </c>
+      <c r="R23" s="3">
+        <v>1133.55</v>
+      </c>
+      <c r="S23" t="str">
         <v/>
       </c>
     </row>
@@ -1383,7 +1799,25 @@
       <c r="L24" s="1">
         <v>6324.49</v>
       </c>
-      <c r="M24" t="str">
+      <c r="M24" s="3">
+        <v>-92.33</v>
+      </c>
+      <c r="N24" s="3">
+        <v>-91.23</v>
+      </c>
+      <c r="O24" s="3">
+        <v>-197.33</v>
+      </c>
+      <c r="P24" s="3">
+        <v>-145.89</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>235.3</v>
+      </c>
+      <c r="R24" s="3">
+        <v>404.21</v>
+      </c>
+      <c r="S24" t="str">
         <v/>
       </c>
     </row>
@@ -1424,7 +1858,25 @@
       <c r="L25" s="1">
         <v>30395.42</v>
       </c>
-      <c r="M25" t="str">
+      <c r="M25" s="3">
+        <v>-375.34</v>
+      </c>
+      <c r="N25" s="3">
+        <v>-355.55</v>
+      </c>
+      <c r="O25" s="3">
+        <v>-301.38</v>
+      </c>
+      <c r="P25" s="3">
+        <v>-78.74</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>1491.04</v>
+      </c>
+      <c r="R25" s="3">
+        <v>2007.93</v>
+      </c>
+      <c r="S25" t="str">
         <v/>
       </c>
     </row>
@@ -1465,7 +1917,25 @@
       <c r="L26" s="1">
         <v>5706.91</v>
       </c>
-      <c r="M26" t="str">
+      <c r="M26" s="3">
+        <v>-39.72</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-71.03</v>
+      </c>
+      <c r="O26" s="3">
+        <v>-115.29</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-95.05</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>28.8</v>
+      </c>
+      <c r="R26" s="3">
+        <v>140.24</v>
+      </c>
+      <c r="S26" t="str">
         <v/>
       </c>
     </row>
@@ -1506,7 +1976,25 @@
       <c r="L27" s="1">
         <v>37551.17</v>
       </c>
-      <c r="M27" t="str">
+      <c r="M27" s="3">
+        <v>-461.17</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-471.75</v>
+      </c>
+      <c r="O27" s="3">
+        <v>-476.48</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-64.34</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>1005.91</v>
+      </c>
+      <c r="R27" s="3">
+        <v>1242.5</v>
+      </c>
+      <c r="S27" t="str">
         <v/>
       </c>
     </row>
@@ -1547,7 +2035,25 @@
       <c r="L28" s="1">
         <v>9837.16</v>
       </c>
-      <c r="M28" t="str">
+      <c r="M28" s="3">
+        <v>-70.49</v>
+      </c>
+      <c r="N28" s="3">
+        <v>-62.77</v>
+      </c>
+      <c r="O28" s="3">
+        <v>219.67</v>
+      </c>
+      <c r="P28" s="3">
+        <v>298.45</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>750.26</v>
+      </c>
+      <c r="R28" s="3">
+        <v>721.68</v>
+      </c>
+      <c r="S28" t="str">
         <v/>
       </c>
     </row>
@@ -1588,7 +2094,25 @@
       <c r="L29" s="1">
         <v>9571.2</v>
       </c>
-      <c r="M29" t="str">
+      <c r="M29" s="3">
+        <v>-116.71</v>
+      </c>
+      <c r="N29" s="3">
+        <v>-127.3</v>
+      </c>
+      <c r="O29" s="3">
+        <v>-220.01</v>
+      </c>
+      <c r="P29" s="3">
+        <v>-145.27</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>800.38</v>
+      </c>
+      <c r="R29" s="3">
+        <v>1093.5</v>
+      </c>
+      <c r="S29" t="str">
         <v/>
       </c>
     </row>
@@ -1629,7 +2153,25 @@
       <c r="L30" s="1">
         <v>26266.15</v>
       </c>
-      <c r="M30" t="str">
+      <c r="M30" s="3">
+        <v>-308.66</v>
+      </c>
+      <c r="N30" s="3">
+        <v>-307.25</v>
+      </c>
+      <c r="O30" s="3">
+        <v>-1.77</v>
+      </c>
+      <c r="P30" s="3">
+        <v>226.74</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>111.86</v>
+      </c>
+      <c r="R30" s="3">
+        <v>-46.08</v>
+      </c>
+      <c r="S30" t="str">
         <v/>
       </c>
     </row>
@@ -1670,7 +2212,25 @@
       <c r="L31" s="1">
         <v>15964.18</v>
       </c>
-      <c r="M31" t="str">
+      <c r="M31" s="3">
+        <v>-254.6</v>
+      </c>
+      <c r="N31" s="3">
+        <v>-263.86</v>
+      </c>
+      <c r="O31" s="3">
+        <v>-74.41</v>
+      </c>
+      <c r="P31" s="3">
+        <v>105.38</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>1265.85</v>
+      </c>
+      <c r="R31" s="3">
+        <v>1447.65</v>
+      </c>
+      <c r="S31" t="str">
         <v/>
       </c>
     </row>
@@ -1711,7 +2271,25 @@
       <c r="L32" s="1">
         <v>56433.5</v>
       </c>
-      <c r="M32" t="str">
+      <c r="M32" s="3">
+        <v>-244.5</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-408.33</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-306.23</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-90.13</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>1705.86</v>
+      </c>
+      <c r="R32" s="3">
+        <v>2296.75</v>
+      </c>
+      <c r="S32" t="str">
         <v/>
       </c>
     </row>
@@ -1752,7 +2330,25 @@
       <c r="L33" s="1">
         <v>26249.17</v>
       </c>
-      <c r="M33" t="str">
+      <c r="M33" s="3">
+        <v>-435.9</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-463.99</v>
+      </c>
+      <c r="O33" s="3">
+        <v>-331.06</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-64.27</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>1160.65</v>
+      </c>
+      <c r="R33" s="3">
+        <v>1598.86</v>
+      </c>
+      <c r="S33" t="str">
         <v/>
       </c>
     </row>
@@ -1793,7 +2389,25 @@
       <c r="L34" s="1">
         <v>26504.8</v>
       </c>
-      <c r="M34" t="str">
+      <c r="M34" s="3">
+        <v>-232.47</v>
+      </c>
+      <c r="N34" s="3">
+        <v>-146.16</v>
+      </c>
+      <c r="O34" s="3">
+        <v>600.81</v>
+      </c>
+      <c r="P34" s="3">
+        <v>797.18</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>1776.15</v>
+      </c>
+      <c r="R34" s="3">
+        <v>1607.67</v>
+      </c>
+      <c r="S34" t="str">
         <v/>
       </c>
     </row>
@@ -1834,7 +2448,25 @@
       <c r="L35" s="1">
         <v>9541.65</v>
       </c>
-      <c r="M35" t="str">
+      <c r="M35" s="3">
+        <v>-162.81</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-170.28</v>
+      </c>
+      <c r="O35" s="3">
+        <v>-173.46</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-64.9</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>396.78</v>
+      </c>
+      <c r="R35" s="3">
+        <v>509.72</v>
+      </c>
+      <c r="S35" t="str">
         <v/>
       </c>
     </row>
@@ -1875,7 +2507,25 @@
       <c r="L36" s="1">
         <v>34069.02</v>
       </c>
-      <c r="M36" t="str">
+      <c r="M36" s="3">
+        <v>-413.87</v>
+      </c>
+      <c r="N36" s="3">
+        <v>-478.8</v>
+      </c>
+      <c r="O36" s="3">
+        <v>-214.67</v>
+      </c>
+      <c r="P36" s="3">
+        <v>103.15</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>2028.91</v>
+      </c>
+      <c r="R36" s="3">
+        <v>2435.7</v>
+      </c>
+      <c r="S36" t="str">
         <v/>
       </c>
     </row>
@@ -1916,7 +2566,25 @@
       <c r="L37" s="1">
         <v>9047.92</v>
       </c>
-      <c r="M37" t="str">
+      <c r="M37" s="3">
+        <v>-121.13</v>
+      </c>
+      <c r="N37" s="3">
+        <v>-138.2</v>
+      </c>
+      <c r="O37" s="3">
+        <v>-158.3</v>
+      </c>
+      <c r="P37" s="3">
+        <v>-78.79</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>272.98</v>
+      </c>
+      <c r="R37" s="3">
+        <v>433.98</v>
+      </c>
+      <c r="S37" t="str">
         <v/>
       </c>
     </row>
@@ -1957,7 +2625,25 @@
       <c r="L38" s="1">
         <v>27441.73</v>
       </c>
-      <c r="M38" t="str">
+      <c r="M38" s="3">
+        <v>-557.94</v>
+      </c>
+      <c r="N38" s="3">
+        <v>-651.27</v>
+      </c>
+      <c r="O38" s="3">
+        <v>-250.8</v>
+      </c>
+      <c r="P38" s="3">
+        <v>102.74</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>1507.35</v>
+      </c>
+      <c r="R38" s="3">
+        <v>1816.97</v>
+      </c>
+      <c r="S38" t="str">
         <v/>
       </c>
     </row>
@@ -1998,7 +2684,25 @@
       <c r="L39" s="1">
         <v>48453.83</v>
       </c>
-      <c r="M39" t="str">
+      <c r="M39" s="3">
+        <v>-244.43</v>
+      </c>
+      <c r="N39" s="3">
+        <v>-212.11</v>
+      </c>
+      <c r="O39" s="3">
+        <v>882.81</v>
+      </c>
+      <c r="P39" s="3">
+        <v>1147.23</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>-226.03</v>
+      </c>
+      <c r="R39" s="3">
+        <v>-997.05</v>
+      </c>
+      <c r="S39" t="str">
         <v/>
       </c>
     </row>
@@ -2039,7 +2743,25 @@
       <c r="L40" s="1">
         <v>14196.36</v>
       </c>
-      <c r="M40" t="str">
+      <c r="M40" s="3">
+        <v>-193.83</v>
+      </c>
+      <c r="N40" s="3">
+        <v>-207.46</v>
+      </c>
+      <c r="O40" s="3">
+        <v>-154.36</v>
+      </c>
+      <c r="P40" s="3">
+        <v>-12.01</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>86.95</v>
+      </c>
+      <c r="R40" s="3">
+        <v>120.57</v>
+      </c>
+      <c r="S40" t="str">
         <v/>
       </c>
     </row>
@@ -2080,7 +2802,25 @@
       <c r="L41" s="1">
         <v>51027.93</v>
       </c>
-      <c r="M41" t="str">
+      <c r="M41" s="3">
+        <v>-415.43</v>
+      </c>
+      <c r="N41" s="3">
+        <v>-431.09</v>
+      </c>
+      <c r="O41" s="3">
+        <v>190.45</v>
+      </c>
+      <c r="P41" s="3">
+        <v>574.97</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>135.15</v>
+      </c>
+      <c r="R41" s="3">
+        <v>-284.13</v>
+      </c>
+      <c r="S41" t="str">
         <v/>
       </c>
     </row>
@@ -2121,7 +2861,25 @@
       <c r="L42" s="1">
         <v>16493.32</v>
       </c>
-      <c r="M42" t="str">
+      <c r="M42" s="3">
+        <v>-233.31</v>
+      </c>
+      <c r="N42" s="3">
+        <v>-241.96</v>
+      </c>
+      <c r="O42" s="3">
+        <v>-23.91</v>
+      </c>
+      <c r="P42" s="3">
+        <v>140.68</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>379.4</v>
+      </c>
+      <c r="R42" s="3">
+        <v>332.77</v>
+      </c>
+      <c r="S42" t="str">
         <v/>
       </c>
     </row>
@@ -2162,7 +2920,25 @@
       <c r="L43" s="1">
         <v>16397.36</v>
       </c>
-      <c r="M43" t="str">
+      <c r="M43" s="3">
+        <v>-236.97</v>
+      </c>
+      <c r="N43" s="3">
+        <v>-185.1</v>
+      </c>
+      <c r="O43" s="3">
+        <v>174.74</v>
+      </c>
+      <c r="P43" s="3">
+        <v>341.22</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>982.44</v>
+      </c>
+      <c r="R43" s="3">
+        <v>994.96</v>
+      </c>
+      <c r="S43" t="str">
         <v/>
       </c>
     </row>
@@ -2203,7 +2979,25 @@
       <c r="L44" s="1">
         <v>62840.3</v>
       </c>
-      <c r="M44" t="str">
+      <c r="M44" s="3">
+        <v>-751.49</v>
+      </c>
+      <c r="N44" s="3">
+        <v>-708.63</v>
+      </c>
+      <c r="O44" s="3">
+        <v>-272.63</v>
+      </c>
+      <c r="P44" s="3">
+        <v>235.93</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>-12.35</v>
+      </c>
+      <c r="R44" s="3">
+        <v>-175.4</v>
+      </c>
+      <c r="S44" t="str">
         <v/>
       </c>
     </row>
@@ -2244,7 +3038,25 @@
       <c r="L45" s="1">
         <v>5537.7</v>
       </c>
-      <c r="M45" t="str">
+      <c r="M45" s="3">
+        <v>-33.54</v>
+      </c>
+      <c r="N45" s="3">
+        <v>-61.47</v>
+      </c>
+      <c r="O45" s="3">
+        <v>-40.87</v>
+      </c>
+      <c r="P45" s="3">
+        <v>-16.55</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>192.26</v>
+      </c>
+      <c r="R45" s="3">
+        <v>262.12</v>
+      </c>
+      <c r="S45" t="str">
         <v/>
       </c>
     </row>
@@ -2285,7 +3097,25 @@
       <c r="L46" s="1">
         <v>51712.18</v>
       </c>
-      <c r="M46" t="str">
+      <c r="M46" s="3">
+        <v>-742.76</v>
+      </c>
+      <c r="N46" s="3">
+        <v>-535.44</v>
+      </c>
+      <c r="O46" s="3">
+        <v>986.94</v>
+      </c>
+      <c r="P46" s="3">
+        <v>1570.37</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>2197.92</v>
+      </c>
+      <c r="R46" s="3">
+        <v>1477.16</v>
+      </c>
+      <c r="S46" t="str">
         <v/>
       </c>
     </row>
@@ -2326,7 +3156,25 @@
       <c r="L47" s="1">
         <v>7797.25</v>
       </c>
-      <c r="M47" t="str">
+      <c r="M47" s="3">
+        <v>-85.41</v>
+      </c>
+      <c r="N47" s="3">
+        <v>-86.41</v>
+      </c>
+      <c r="O47" s="3">
+        <v>-56.58</v>
+      </c>
+      <c r="P47" s="3">
+        <v>-16.6</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>-294.39</v>
+      </c>
+      <c r="R47" s="3">
+        <v>-246.06</v>
+      </c>
+      <c r="S47" t="str">
         <v/>
       </c>
     </row>
@@ -2367,7 +3215,25 @@
       <c r="L48" s="1">
         <v>14077.98</v>
       </c>
-      <c r="M48" t="str">
+      <c r="M48" s="3">
+        <v>-87.76</v>
+      </c>
+      <c r="N48" s="3">
+        <v>-177.27</v>
+      </c>
+      <c r="O48" s="3">
+        <v>-209.7</v>
+      </c>
+      <c r="P48" s="3">
+        <v>-159.38</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>-529.62</v>
+      </c>
+      <c r="R48" s="3">
+        <v>-490.47</v>
+      </c>
+      <c r="S48" t="str">
         <v/>
       </c>
     </row>
@@ -2408,7 +3274,25 @@
       <c r="L49" s="1">
         <v>32105.82</v>
       </c>
-      <c r="M49" t="str">
+      <c r="M49" s="3">
+        <v>-349.66</v>
+      </c>
+      <c r="N49" s="3">
+        <v>-440.21</v>
+      </c>
+      <c r="O49" s="3">
+        <v>-363.4</v>
+      </c>
+      <c r="P49" s="3">
+        <v>-109.75</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>1850.76</v>
+      </c>
+      <c r="R49" s="3">
+        <v>2377.64</v>
+      </c>
+      <c r="S49" t="str">
         <v/>
       </c>
     </row>
@@ -2449,7 +3333,25 @@
       <c r="L50" s="1">
         <v>31753.46</v>
       </c>
-      <c r="M50" t="str">
+      <c r="M50" s="3">
+        <v>-646.57</v>
+      </c>
+      <c r="N50" s="3">
+        <v>-629.11</v>
+      </c>
+      <c r="O50" s="3">
+        <v>-404.61</v>
+      </c>
+      <c r="P50" s="3">
+        <v>84.87</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>2038.85</v>
+      </c>
+      <c r="R50" s="3">
+        <v>2407.67</v>
+      </c>
+      <c r="S50" t="str">
         <v/>
       </c>
     </row>
@@ -2490,7 +3392,25 @@
       <c r="L51" s="1">
         <v>19583.61</v>
       </c>
-      <c r="M51" t="str">
+      <c r="M51" s="3">
+        <v>-232.6</v>
+      </c>
+      <c r="N51" s="3">
+        <v>-284.84</v>
+      </c>
+      <c r="O51" s="3">
+        <v>-295.29</v>
+      </c>
+      <c r="P51" s="3">
+        <v>-144.6</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>760.52</v>
+      </c>
+      <c r="R51" s="3">
+        <v>1111.92</v>
+      </c>
+      <c r="S51" t="str">
         <v/>
       </c>
     </row>
@@ -2531,7 +3451,25 @@
       <c r="L52" s="1">
         <v>9511</v>
       </c>
-      <c r="M52" t="str">
+      <c r="M52" s="3">
+        <v>-89.98</v>
+      </c>
+      <c r="N52" s="3">
+        <v>-101.8</v>
+      </c>
+      <c r="O52" s="3">
+        <v>126.12</v>
+      </c>
+      <c r="P52" s="3">
+        <v>239.91</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>628</v>
+      </c>
+      <c r="R52" s="3">
+        <v>527.7</v>
+      </c>
+      <c r="S52" t="str">
         <v/>
       </c>
     </row>
@@ -2572,7 +3510,25 @@
       <c r="L53" s="1">
         <v>11122.31</v>
       </c>
-      <c r="M53" t="str">
+      <c r="M53" s="3">
+        <v>-79.61</v>
+      </c>
+      <c r="N53" s="3">
+        <v>-160.82</v>
+      </c>
+      <c r="O53" s="3">
+        <v>-112.2</v>
+      </c>
+      <c r="P53" s="3">
+        <v>-75.56</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>33.84</v>
+      </c>
+      <c r="R53" s="3">
+        <v>177.01</v>
+      </c>
+      <c r="S53" t="str">
         <v/>
       </c>
     </row>
@@ -2613,7 +3569,25 @@
       <c r="L54" s="1">
         <v>24637.3</v>
       </c>
-      <c r="M54" t="str">
+      <c r="M54" s="3">
+        <v>-217.66</v>
+      </c>
+      <c r="N54" s="3">
+        <v>-296.58</v>
+      </c>
+      <c r="O54" s="3">
+        <v>-327.95</v>
+      </c>
+      <c r="P54" s="3">
+        <v>-193.05</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>344.58</v>
+      </c>
+      <c r="R54" s="3">
+        <v>711.08</v>
+      </c>
+      <c r="S54" t="str">
         <v/>
       </c>
     </row>
@@ -2654,7 +3628,25 @@
       <c r="L55" s="1">
         <v>5309.82</v>
       </c>
-      <c r="M55" t="str">
+      <c r="M55" s="3">
+        <v>-20.36</v>
+      </c>
+      <c r="N55" s="3">
+        <v>-30.17</v>
+      </c>
+      <c r="O55" s="3">
+        <v>38.14</v>
+      </c>
+      <c r="P55" s="3">
+        <v>88.65</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>374.58</v>
+      </c>
+      <c r="R55" s="3">
+        <v>327.38</v>
+      </c>
+      <c r="S55" t="str">
         <v/>
       </c>
     </row>
@@ -2695,7 +3687,25 @@
       <c r="L56" s="1">
         <v>19680.38</v>
       </c>
-      <c r="M56" t="str">
+      <c r="M56" s="3">
+        <v>-154.16</v>
+      </c>
+      <c r="N56" s="3">
+        <v>-129.79</v>
+      </c>
+      <c r="O56" s="3">
+        <v>339.32</v>
+      </c>
+      <c r="P56" s="3">
+        <v>496.14</v>
+      </c>
+      <c r="Q56" s="3">
+        <v>892.77</v>
+      </c>
+      <c r="R56" s="3">
+        <v>862.73</v>
+      </c>
+      <c r="S56" t="str">
         <v/>
       </c>
     </row>
@@ -2736,7 +3746,25 @@
       <c r="L57" s="1">
         <v>13681.72</v>
       </c>
-      <c r="M57" t="str">
+      <c r="M57" s="3">
+        <v>-134.36</v>
+      </c>
+      <c r="N57" s="3">
+        <v>-171.64</v>
+      </c>
+      <c r="O57" s="3">
+        <v>-155.64</v>
+      </c>
+      <c r="P57" s="3">
+        <v>-66.26</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>280.21</v>
+      </c>
+      <c r="R57" s="3">
+        <v>466.43</v>
+      </c>
+      <c r="S57" t="str">
         <v/>
       </c>
     </row>
@@ -2777,7 +3805,25 @@
       <c r="L58" s="1">
         <v>22869.12</v>
       </c>
-      <c r="M58" t="str">
+      <c r="M58" s="3">
+        <v>-225.46</v>
+      </c>
+      <c r="N58" s="3">
+        <v>-275.42</v>
+      </c>
+      <c r="O58" s="3">
+        <v>-192.69</v>
+      </c>
+      <c r="P58" s="3">
+        <v>-35.73</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>533.73</v>
+      </c>
+      <c r="R58" s="3">
+        <v>808.69</v>
+      </c>
+      <c r="S58" t="str">
         <v/>
       </c>
     </row>
@@ -2818,7 +3864,25 @@
       <c r="L59" s="1">
         <v>16366.58</v>
       </c>
-      <c r="M59" t="str">
+      <c r="M59" s="3">
+        <v>-185.36</v>
+      </c>
+      <c r="N59" s="3">
+        <v>-216.84</v>
+      </c>
+      <c r="O59" s="3">
+        <v>-133.4</v>
+      </c>
+      <c r="P59" s="3">
+        <v>0.61</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>929.32</v>
+      </c>
+      <c r="R59" s="3">
+        <v>1181.35</v>
+      </c>
+      <c r="S59" t="str">
         <v/>
       </c>
     </row>
@@ -2859,7 +3923,25 @@
       <c r="L60" s="1">
         <v>17751.15</v>
       </c>
-      <c r="M60" t="str">
+      <c r="M60" s="3">
+        <v>-261.77</v>
+      </c>
+      <c r="N60" s="3">
+        <v>-278.24</v>
+      </c>
+      <c r="O60" s="3">
+        <v>-33.85</v>
+      </c>
+      <c r="P60" s="3">
+        <v>164.81</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>915.94</v>
+      </c>
+      <c r="R60" s="3">
+        <v>1051.43</v>
+      </c>
+      <c r="S60" t="str">
         <v/>
       </c>
     </row>
@@ -2900,7 +3982,25 @@
       <c r="L61" s="1">
         <v>16277.41</v>
       </c>
-      <c r="M61" t="str">
+      <c r="M61" s="3">
+        <v>-162.34</v>
+      </c>
+      <c r="N61" s="3">
+        <v>-186.97</v>
+      </c>
+      <c r="O61" s="3">
+        <v>-59.62</v>
+      </c>
+      <c r="P61" s="3">
+        <v>64.71</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>933.56</v>
+      </c>
+      <c r="R61" s="3">
+        <v>1151.4</v>
+      </c>
+      <c r="S61" t="str">
         <v/>
       </c>
     </row>
@@ -2941,7 +4041,25 @@
       <c r="L62" s="1">
         <v>12934.02</v>
       </c>
-      <c r="M62" t="str">
+      <c r="M62" s="3">
+        <v>-125.26</v>
+      </c>
+      <c r="N62" s="3">
+        <v>-150.83</v>
+      </c>
+      <c r="O62" s="3">
+        <v>-86.46</v>
+      </c>
+      <c r="P62" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>640.24</v>
+      </c>
+      <c r="R62" s="3">
+        <v>828.13</v>
+      </c>
+      <c r="S62" t="str">
         <v/>
       </c>
     </row>
@@ -2982,7 +4100,25 @@
       <c r="L63" s="1">
         <v>11533.73</v>
       </c>
-      <c r="M63" t="str">
+      <c r="M63" s="3">
+        <v>-165.76</v>
+      </c>
+      <c r="N63" s="3">
+        <v>-187.83</v>
+      </c>
+      <c r="O63" s="3">
+        <v>-142.76</v>
+      </c>
+      <c r="P63" s="3">
+        <v>-39.79</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>225.56</v>
+      </c>
+      <c r="R63" s="3">
+        <v>395.78</v>
+      </c>
+      <c r="S63" t="str">
         <v/>
       </c>
     </row>
@@ -3023,7 +4159,25 @@
       <c r="L64" s="1">
         <v>61831.43</v>
       </c>
-      <c r="M64" t="str">
+      <c r="M64" s="3">
+        <v>-847.38</v>
+      </c>
+      <c r="N64" s="3">
+        <v>-899.29</v>
+      </c>
+      <c r="O64" s="3">
+        <v>-224.86</v>
+      </c>
+      <c r="P64" s="3">
+        <v>439.1</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>2942.36</v>
+      </c>
+      <c r="R64" s="3">
+        <v>3494.39</v>
+      </c>
+      <c r="S64" t="str">
         <v/>
       </c>
     </row>
@@ -3064,7 +4218,25 @@
       <c r="L65" s="1">
         <v>22724.19</v>
       </c>
-      <c r="M65" t="str">
+      <c r="M65" s="3">
+        <v>-313.55</v>
+      </c>
+      <c r="N65" s="3">
+        <v>-328.14</v>
+      </c>
+      <c r="O65" s="3">
+        <v>-80.46</v>
+      </c>
+      <c r="P65" s="3">
+        <v>162.72</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>1726.57</v>
+      </c>
+      <c r="R65" s="3">
+        <v>2031.93</v>
+      </c>
+      <c r="S65" t="str">
         <v/>
       </c>
     </row>
@@ -3105,7 +4277,25 @@
       <c r="L66" s="1">
         <v>4884.75</v>
       </c>
-      <c r="M66" t="str">
+      <c r="M66" s="3">
+        <v>-43.77</v>
+      </c>
+      <c r="N66" s="3">
+        <v>-63.54</v>
+      </c>
+      <c r="O66" s="3">
+        <v>-47.12</v>
+      </c>
+      <c r="P66" s="3">
+        <v>-16.54</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>223.49</v>
+      </c>
+      <c r="R66" s="3">
+        <v>300.13</v>
+      </c>
+      <c r="S66" t="str">
         <v/>
       </c>
     </row>
@@ -3146,7 +4336,25 @@
       <c r="L67" s="1">
         <v>23514.27</v>
       </c>
-      <c r="M67" t="str">
+      <c r="M67" s="3">
+        <v>-185.04</v>
+      </c>
+      <c r="N67" s="3">
+        <v>-273.79</v>
+      </c>
+      <c r="O67" s="3">
+        <v>-378</v>
+      </c>
+      <c r="P67" s="3">
+        <v>-273.57</v>
+      </c>
+      <c r="Q67" s="3">
+        <v>200.23</v>
+      </c>
+      <c r="R67" s="3">
+        <v>600.9</v>
+      </c>
+      <c r="S67" t="str">
         <v/>
       </c>
     </row>
@@ -3187,7 +4395,25 @@
       <c r="L68" s="1">
         <v>21071.25</v>
       </c>
-      <c r="M68" t="str">
+      <c r="M68" s="3">
+        <v>-252.22</v>
+      </c>
+      <c r="N68" s="3">
+        <v>-253.81</v>
+      </c>
+      <c r="O68" s="3">
+        <v>46.95</v>
+      </c>
+      <c r="P68" s="3">
+        <v>255.26</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>1600.32</v>
+      </c>
+      <c r="R68" s="3">
+        <v>1827.81</v>
+      </c>
+      <c r="S68" t="str">
         <v/>
       </c>
     </row>
@@ -3228,7 +4454,25 @@
       <c r="L69" s="1">
         <v>14407.94</v>
       </c>
-      <c r="M69" t="str">
+      <c r="M69" s="3">
+        <v>-218.84</v>
+      </c>
+      <c r="N69" s="3">
+        <v>-240.63</v>
+      </c>
+      <c r="O69" s="3">
+        <v>-53.14</v>
+      </c>
+      <c r="P69" s="3">
+        <v>130.65</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>887.23</v>
+      </c>
+      <c r="R69" s="3">
+        <v>1004.13</v>
+      </c>
+      <c r="S69" t="str">
         <v/>
       </c>
     </row>
@@ -3269,7 +4513,25 @@
       <c r="L70" s="1">
         <v>38605.84</v>
       </c>
-      <c r="M70" t="str">
+      <c r="M70" s="3">
+        <v>-700.92</v>
+      </c>
+      <c r="N70" s="3">
+        <v>-737.05</v>
+      </c>
+      <c r="O70" s="3">
+        <v>-143</v>
+      </c>
+      <c r="P70" s="3">
+        <v>326.12</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>685.97</v>
+      </c>
+      <c r="R70" s="3">
+        <v>949.36</v>
+      </c>
+      <c r="S70" t="str">
         <v/>
       </c>
     </row>
@@ -3310,7 +4572,25 @@
       <c r="L71" s="1">
         <v>18138.87</v>
       </c>
-      <c r="M71" t="str">
+      <c r="M71" s="3">
+        <v>-154.43</v>
+      </c>
+      <c r="N71" s="3">
+        <v>-136.52</v>
+      </c>
+      <c r="O71" s="3">
+        <v>238.04</v>
+      </c>
+      <c r="P71" s="3">
+        <v>389.47</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>1339.23</v>
+      </c>
+      <c r="R71" s="3">
+        <v>1435.09</v>
+      </c>
+      <c r="S71" t="str">
         <v/>
       </c>
     </row>
@@ -3351,7 +4631,25 @@
       <c r="L72" s="1">
         <v>7418.47</v>
       </c>
-      <c r="M72" t="str">
+      <c r="M72" s="3">
+        <v>-14.64</v>
+      </c>
+      <c r="N72" s="3">
+        <v>-58.79</v>
+      </c>
+      <c r="O72" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="P72" s="3">
+        <v>32.07</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>473.87</v>
+      </c>
+      <c r="R72" s="3">
+        <v>552.98</v>
+      </c>
+      <c r="S72" t="str">
         <v/>
       </c>
     </row>
@@ -3392,7 +4690,25 @@
       <c r="L73" s="1">
         <v>23833.06</v>
       </c>
-      <c r="M73" t="str">
+      <c r="M73" s="3">
+        <v>-257.13</v>
+      </c>
+      <c r="N73" s="3">
+        <v>-301.12</v>
+      </c>
+      <c r="O73" s="3">
+        <v>-179.1</v>
+      </c>
+      <c r="P73" s="3">
+        <v>36.28</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>1041.01</v>
+      </c>
+      <c r="R73" s="3">
+        <v>1363.04</v>
+      </c>
+      <c r="S73" t="str">
         <v/>
       </c>
     </row>
@@ -3433,7 +4749,25 @@
       <c r="L74" s="1">
         <v>19894.51</v>
       </c>
-      <c r="M74" t="str">
+      <c r="M74" s="3">
+        <v>-157.5</v>
+      </c>
+      <c r="N74" s="3">
+        <v>-252.48</v>
+      </c>
+      <c r="O74" s="3">
+        <v>-258.22</v>
+      </c>
+      <c r="P74" s="3">
+        <v>-137.4</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>507.8</v>
+      </c>
+      <c r="R74" s="3">
+        <v>799.61</v>
+      </c>
+      <c r="S74" t="str">
         <v/>
       </c>
     </row>
@@ -3474,7 +4808,25 @@
       <c r="L75" s="1">
         <v>867.25</v>
       </c>
-      <c r="M75" t="str">
+      <c r="M75" s="3">
+        <v>-13.57</v>
+      </c>
+      <c r="N75" s="3">
+        <v>-14.54</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0.89</v>
+      </c>
+      <c r="P75" s="3">
+        <v>10.72</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>2.54</v>
+      </c>
+      <c r="R75" s="3">
+        <v>10.09</v>
+      </c>
+      <c r="S75" t="str">
         <v/>
       </c>
     </row>
@@ -3515,7 +4867,25 @@
       <c r="L76" s="1">
         <v>11584.13</v>
       </c>
-      <c r="M76" t="str">
+      <c r="M76" s="3">
+        <v>-59.98</v>
+      </c>
+      <c r="N76" s="3">
+        <v>-115.63</v>
+      </c>
+      <c r="O76" s="3">
+        <v>-258.76</v>
+      </c>
+      <c r="P76" s="3">
+        <v>-234.58</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>-124.74</v>
+      </c>
+      <c r="R76" s="3">
+        <v>115.49</v>
+      </c>
+      <c r="S76" t="str">
         <v/>
       </c>
     </row>
@@ -3556,7 +4926,25 @@
       <c r="L77" s="1">
         <v>30157.43</v>
       </c>
-      <c r="M77" t="str">
+      <c r="M77" s="3">
+        <v>-65.9</v>
+      </c>
+      <c r="N77" s="3">
+        <v>-249.18</v>
+      </c>
+      <c r="O77" s="3">
+        <v>-346.4</v>
+      </c>
+      <c r="P77" s="3">
+        <v>-314.78</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>495.29</v>
+      </c>
+      <c r="R77" s="3">
+        <v>993.55</v>
+      </c>
+      <c r="S77" t="str">
         <v/>
       </c>
     </row>
@@ -3597,7 +4985,25 @@
       <c r="L78" s="1">
         <v>16888.42</v>
       </c>
-      <c r="M78" t="str">
+      <c r="M78" s="3">
+        <v>-238.03</v>
+      </c>
+      <c r="N78" s="3">
+        <v>-235.4</v>
+      </c>
+      <c r="O78" s="3">
+        <v>43.53</v>
+      </c>
+      <c r="P78" s="3">
+        <v>234.52</v>
+      </c>
+      <c r="Q78" s="3">
+        <v>1565.9</v>
+      </c>
+      <c r="R78" s="3">
+        <v>1751.51</v>
+      </c>
+      <c r="S78" t="str">
         <v/>
       </c>
     </row>
@@ -3638,7 +5044,25 @@
       <c r="L79" s="1">
         <v>29809.61</v>
       </c>
-      <c r="M79" t="str">
+      <c r="M79" s="3">
+        <v>395.38</v>
+      </c>
+      <c r="N79" s="3">
+        <v>-87.44</v>
+      </c>
+      <c r="O79" s="3">
+        <v>-195.07</v>
+      </c>
+      <c r="P79" s="3">
+        <v>-527.2</v>
+      </c>
+      <c r="Q79" s="3">
+        <v>-1699.24</v>
+      </c>
+      <c r="R79" s="3">
+        <v>-1155.4</v>
+      </c>
+      <c r="S79" t="str">
         <v/>
       </c>
     </row>
@@ -3679,7 +5103,25 @@
       <c r="L80" s="1">
         <v>8415.39</v>
       </c>
-      <c r="M80" t="str">
+      <c r="M80" s="3">
+        <v>-20.17</v>
+      </c>
+      <c r="N80" s="3">
+        <v>-63.71</v>
+      </c>
+      <c r="O80" s="3">
+        <v>-157.19</v>
+      </c>
+      <c r="P80" s="3">
+        <v>-157.96</v>
+      </c>
+      <c r="Q80" s="3">
+        <v>-302.52</v>
+      </c>
+      <c r="R80" s="3">
+        <v>-191.83</v>
+      </c>
+      <c r="S80" t="str">
         <v/>
       </c>
     </row>
@@ -3720,7 +5162,25 @@
       <c r="L81" s="1">
         <v>8541.32</v>
       </c>
-      <c r="M81" t="str">
+      <c r="M81" s="3">
+        <v>-4.23</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-71.71</v>
+      </c>
+      <c r="O81" s="3">
+        <v>68.86</v>
+      </c>
+      <c r="P81" s="3">
+        <v>59.81</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>375.34</v>
+      </c>
+      <c r="R81" s="3">
+        <v>514.31</v>
+      </c>
+      <c r="S81" t="str">
         <v/>
       </c>
     </row>
@@ -3761,7 +5221,25 @@
       <c r="L82" s="1">
         <v>3939.04</v>
       </c>
-      <c r="M82" t="str">
+      <c r="M82" s="3">
+        <v>-36.3</v>
+      </c>
+      <c r="N82" s="3">
+        <v>-50.99</v>
+      </c>
+      <c r="O82" s="3">
+        <v>-64.32</v>
+      </c>
+      <c r="P82" s="3">
+        <v>-42.15</v>
+      </c>
+      <c r="Q82" s="3">
+        <v>127.86</v>
+      </c>
+      <c r="R82" s="3">
+        <v>207.1</v>
+      </c>
+      <c r="S82" t="str">
         <v/>
       </c>
     </row>
@@ -3802,7 +5280,25 @@
       <c r="L83" s="1">
         <v>27702.92</v>
       </c>
-      <c r="M83" t="str">
+      <c r="M83" s="3">
+        <v>-198.76</v>
+      </c>
+      <c r="N83" s="3">
+        <v>-288.55</v>
+      </c>
+      <c r="O83" s="3">
+        <v>-456.58</v>
+      </c>
+      <c r="P83" s="3">
+        <v>-290.92</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>1333.07</v>
+      </c>
+      <c r="R83" s="3">
+        <v>1904.53</v>
+      </c>
+      <c r="S83" t="str">
         <v/>
       </c>
     </row>
@@ -3843,7 +5339,25 @@
       <c r="L84" s="1">
         <v>46121.99</v>
       </c>
-      <c r="M84" t="str">
+      <c r="M84" s="3">
+        <v>-456.81</v>
+      </c>
+      <c r="N84" s="3">
+        <v>-504.62</v>
+      </c>
+      <c r="O84" s="3">
+        <v>-1598.77</v>
+      </c>
+      <c r="P84" s="3">
+        <v>-1340.83</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>-2116.54</v>
+      </c>
+      <c r="R84" s="3">
+        <v>-956.12</v>
+      </c>
+      <c r="S84" t="str">
         <v/>
       </c>
     </row>
@@ -3884,7 +5398,25 @@
       <c r="L85" s="1">
         <v>25597.84</v>
       </c>
-      <c r="M85" t="str">
+      <c r="M85" s="3">
+        <v>-121.71</v>
+      </c>
+      <c r="N85" s="3">
+        <v>-206.59</v>
+      </c>
+      <c r="O85" s="3">
+        <v>-331.83</v>
+      </c>
+      <c r="P85" s="3">
+        <v>-217.64</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>674.52</v>
+      </c>
+      <c r="R85" s="3">
+        <v>1086.46</v>
+      </c>
+      <c r="S85" t="str">
         <v/>
       </c>
     </row>
@@ -3925,7 +5457,25 @@
       <c r="L86" s="1">
         <v>29468.3</v>
       </c>
-      <c r="M86" t="str">
+      <c r="M86" s="3">
+        <v>-354.18</v>
+      </c>
+      <c r="N86" s="3">
+        <v>-394.92</v>
+      </c>
+      <c r="O86" s="3">
+        <v>-130.04</v>
+      </c>
+      <c r="P86" s="3">
+        <v>183.71</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>282.81</v>
+      </c>
+      <c r="R86" s="3">
+        <v>197.84</v>
+      </c>
+      <c r="S86" t="str">
         <v/>
       </c>
     </row>
@@ -3966,7 +5516,25 @@
       <c r="L87" s="1">
         <v>26179.41</v>
       </c>
-      <c r="M87" t="str">
+      <c r="M87" s="3">
+        <v>-172.58</v>
+      </c>
+      <c r="N87" s="3">
+        <v>-106.49</v>
+      </c>
+      <c r="O87" s="3">
+        <v>683.83</v>
+      </c>
+      <c r="P87" s="3">
+        <v>871.75</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>2363.37</v>
+      </c>
+      <c r="R87" s="3">
+        <v>2365.37</v>
+      </c>
+      <c r="S87" t="str">
         <v/>
       </c>
     </row>
@@ -4007,7 +5575,25 @@
       <c r="L88" s="1">
         <v>27306.52</v>
       </c>
-      <c r="M88" t="str">
+      <c r="M88" s="3">
+        <v>29.87</v>
+      </c>
+      <c r="N88" s="3">
+        <v>-52.8</v>
+      </c>
+      <c r="O88" s="3">
+        <v>-11.17</v>
+      </c>
+      <c r="P88" s="3">
+        <v>23.26</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>672.45</v>
+      </c>
+      <c r="R88" s="3">
+        <v>880.38</v>
+      </c>
+      <c r="S88" t="str">
         <v/>
       </c>
     </row>
@@ -4048,7 +5634,25 @@
       <c r="L89" s="1">
         <v>17256.4</v>
       </c>
-      <c r="M89" t="str">
+      <c r="M89" s="3">
+        <v>-299.59</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-425.54</v>
+      </c>
+      <c r="O89" s="3">
+        <v>-658.68</v>
+      </c>
+      <c r="P89" s="3">
+        <v>-508.53</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>280.73</v>
+      </c>
+      <c r="R89" s="3">
+        <v>929.94</v>
+      </c>
+      <c r="S89" t="str">
         <v/>
       </c>
     </row>
@@ -4089,13 +5693,31 @@
       <c r="L90" s="1">
         <v>11321.07</v>
       </c>
-      <c r="M90" t="str">
+      <c r="M90" s="3">
+        <v>-198.96</v>
+      </c>
+      <c r="N90" s="3">
+        <v>-281.64</v>
+      </c>
+      <c r="O90" s="3">
+        <v>-477.57</v>
+      </c>
+      <c r="P90" s="3">
+        <v>-383.86</v>
+      </c>
+      <c r="Q90" s="3">
+        <v>-3.9</v>
+      </c>
+      <c r="R90" s="3">
+        <v>426.64</v>
+      </c>
+      <c r="S90" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M90"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S90"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/index.xlsx
+++ b/index.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S90"/>
+  <dimension ref="A1:T90"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -458,9 +458,12 @@
         <v>MONTHLY macd_line</v>
       </c>
       <c r="R1" t="str">
-        <v>MONTLY macd_signal</v>
+        <v>MONTHLY macd_signal</v>
       </c>
       <c r="S1" t="str">
+        <v>rsi</v>
+      </c>
+      <c r="T1" t="str">
         <v>Add Column</v>
       </c>
     </row>
@@ -519,7 +522,10 @@
       <c r="R2" s="3">
         <v>0.02</v>
       </c>
-      <c r="S2" t="str">
+      <c r="S2" s="3">
+        <v>57.58</v>
+      </c>
+      <c r="T2" t="str">
         <v/>
       </c>
     </row>
@@ -578,7 +584,10 @@
       <c r="R3" s="3">
         <v>686.08</v>
       </c>
-      <c r="S3" t="str">
+      <c r="S3" s="3">
+        <v>54.74</v>
+      </c>
+      <c r="T3" t="str">
         <v/>
       </c>
     </row>
@@ -637,7 +646,10 @@
       <c r="R4" s="3">
         <v>-4.81</v>
       </c>
-      <c r="S4" t="str">
+      <c r="S4" s="3">
+        <v>52.73</v>
+      </c>
+      <c r="T4" t="str">
         <v/>
       </c>
     </row>
@@ -696,7 +708,10 @@
       <c r="R5" s="3">
         <v>-6.06</v>
       </c>
-      <c r="S5" t="str">
+      <c r="S5" s="3">
+        <v>52.58</v>
+      </c>
+      <c r="T5" t="str">
         <v/>
       </c>
     </row>
@@ -755,7 +770,10 @@
       <c r="R6" s="3">
         <v>155.52</v>
       </c>
-      <c r="S6" t="str">
+      <c r="S6" s="3">
+        <v>29.05</v>
+      </c>
+      <c r="T6" t="str">
         <v/>
       </c>
     </row>
@@ -814,7 +832,10 @@
       <c r="R7" s="3">
         <v>33.14</v>
       </c>
-      <c r="S7" t="str">
+      <c r="S7" s="3">
+        <v>34.94</v>
+      </c>
+      <c r="T7" t="str">
         <v/>
       </c>
     </row>
@@ -873,7 +894,10 @@
       <c r="R8" s="3">
         <v>24.25</v>
       </c>
-      <c r="S8" t="str">
+      <c r="S8" s="3">
+        <v>25.89</v>
+      </c>
+      <c r="T8" t="str">
         <v/>
       </c>
     </row>
@@ -932,7 +956,10 @@
       <c r="R9" s="3">
         <v>28.58</v>
       </c>
-      <c r="S9" t="str">
+      <c r="S9" s="3">
+        <v>28.35</v>
+      </c>
+      <c r="T9" t="str">
         <v/>
       </c>
     </row>
@@ -991,7 +1018,10 @@
       <c r="R10" s="3">
         <v>21.99</v>
       </c>
-      <c r="S10" t="str">
+      <c r="S10" s="3">
+        <v>24.26</v>
+      </c>
+      <c r="T10" t="str">
         <v/>
       </c>
     </row>
@@ -1050,7 +1080,10 @@
       <c r="R11" s="3">
         <v>7.65</v>
       </c>
-      <c r="S11" t="str">
+      <c r="S11" s="3">
+        <v>100</v>
+      </c>
+      <c r="T11" t="str">
         <v/>
       </c>
     </row>
@@ -1109,7 +1142,10 @@
       <c r="R12" s="3">
         <v>142.19</v>
       </c>
-      <c r="S12" t="str">
+      <c r="S12" s="3">
+        <v>39.64</v>
+      </c>
+      <c r="T12" t="str">
         <v/>
       </c>
     </row>
@@ -1168,7 +1204,10 @@
       <c r="R13" s="3">
         <v>132.99</v>
       </c>
-      <c r="S13" t="str">
+      <c r="S13" s="3">
+        <v>30.27</v>
+      </c>
+      <c r="T13" t="str">
         <v/>
       </c>
     </row>
@@ -1227,7 +1266,10 @@
       <c r="R14" s="3">
         <v>136.75</v>
       </c>
-      <c r="S14" t="str">
+      <c r="S14" s="3">
+        <v>32.67</v>
+      </c>
+      <c r="T14" t="str">
         <v/>
       </c>
     </row>
@@ -1286,7 +1328,10 @@
       <c r="R15" s="3">
         <v>106.53</v>
       </c>
-      <c r="S15" t="str">
+      <c r="S15" s="3">
+        <v>31.48</v>
+      </c>
+      <c r="T15" t="str">
         <v/>
       </c>
     </row>
@@ -1345,7 +1390,10 @@
       <c r="R16" s="3">
         <v>281.02</v>
       </c>
-      <c r="S16" t="str">
+      <c r="S16" s="3">
+        <v>43.56</v>
+      </c>
+      <c r="T16" t="str">
         <v/>
       </c>
     </row>
@@ -1404,7 +1452,10 @@
       <c r="R17" s="3">
         <v>-14.13</v>
       </c>
-      <c r="S17" t="str">
+      <c r="S17" s="3">
+        <v>25.1</v>
+      </c>
+      <c r="T17" t="str">
         <v/>
       </c>
     </row>
@@ -1463,7 +1514,10 @@
       <c r="R18" s="3">
         <v>-104.6</v>
       </c>
-      <c r="S18" t="str">
+      <c r="S18" s="3">
+        <v>61.69</v>
+      </c>
+      <c r="T18" t="str">
         <v/>
       </c>
     </row>
@@ -1522,7 +1576,10 @@
       <c r="R19" s="3">
         <v>3900.21</v>
       </c>
-      <c r="S19" t="str">
+      <c r="S19" s="3">
+        <v>40.27</v>
+      </c>
+      <c r="T19" t="str">
         <v/>
       </c>
     </row>
@@ -1581,7 +1638,10 @@
       <c r="R20" s="3">
         <v>154.03</v>
       </c>
-      <c r="S20" t="str">
+      <c r="S20" s="3">
+        <v>35.31</v>
+      </c>
+      <c r="T20" t="str">
         <v/>
       </c>
     </row>
@@ -1640,7 +1700,10 @@
       <c r="R21" s="3">
         <v>-1104.48</v>
       </c>
-      <c r="S21" t="str">
+      <c r="S21" s="3">
+        <v>39</v>
+      </c>
+      <c r="T21" t="str">
         <v/>
       </c>
     </row>
@@ -1699,7 +1762,10 @@
       <c r="R22" s="3">
         <v>3199.01</v>
       </c>
-      <c r="S22" t="str">
+      <c r="S22" s="3">
+        <v>39.51</v>
+      </c>
+      <c r="T22" t="str">
         <v/>
       </c>
     </row>
@@ -1758,7 +1824,10 @@
       <c r="R23" s="3">
         <v>1133.55</v>
       </c>
-      <c r="S23" t="str">
+      <c r="S23" s="3">
+        <v>37.88</v>
+      </c>
+      <c r="T23" t="str">
         <v/>
       </c>
     </row>
@@ -1817,7 +1886,10 @@
       <c r="R24" s="3">
         <v>404.21</v>
       </c>
-      <c r="S24" t="str">
+      <c r="S24" s="3">
+        <v>34.75</v>
+      </c>
+      <c r="T24" t="str">
         <v/>
       </c>
     </row>
@@ -1876,7 +1948,10 @@
       <c r="R25" s="3">
         <v>2007.93</v>
       </c>
-      <c r="S25" t="str">
+      <c r="S25" s="3">
+        <v>36.72</v>
+      </c>
+      <c r="T25" t="str">
         <v/>
       </c>
     </row>
@@ -1935,7 +2010,10 @@
       <c r="R26" s="3">
         <v>140.24</v>
       </c>
-      <c r="S26" t="str">
+      <c r="S26" s="3">
+        <v>52.38</v>
+      </c>
+      <c r="T26" t="str">
         <v/>
       </c>
     </row>
@@ -1994,7 +2072,10 @@
       <c r="R27" s="3">
         <v>1242.5</v>
       </c>
-      <c r="S27" t="str">
+      <c r="S27" s="3">
+        <v>37.17</v>
+      </c>
+      <c r="T27" t="str">
         <v/>
       </c>
     </row>
@@ -2053,7 +2134,10 @@
       <c r="R28" s="3">
         <v>721.68</v>
       </c>
-      <c r="S28" t="str">
+      <c r="S28" s="3">
+        <v>40.87</v>
+      </c>
+      <c r="T28" t="str">
         <v/>
       </c>
     </row>
@@ -2112,7 +2196,10 @@
       <c r="R29" s="3">
         <v>1093.5</v>
       </c>
-      <c r="S29" t="str">
+      <c r="S29" s="3">
+        <v>39.06</v>
+      </c>
+      <c r="T29" t="str">
         <v/>
       </c>
     </row>
@@ -2171,7 +2258,10 @@
       <c r="R30" s="3">
         <v>-46.08</v>
       </c>
-      <c r="S30" t="str">
+      <c r="S30" s="3">
+        <v>38.56</v>
+      </c>
+      <c r="T30" t="str">
         <v/>
       </c>
     </row>
@@ -2230,7 +2320,10 @@
       <c r="R31" s="3">
         <v>1447.65</v>
       </c>
-      <c r="S31" t="str">
+      <c r="S31" s="3">
+        <v>36.81</v>
+      </c>
+      <c r="T31" t="str">
         <v/>
       </c>
     </row>
@@ -2289,7 +2382,10 @@
       <c r="R32" s="3">
         <v>2296.75</v>
       </c>
-      <c r="S32" t="str">
+      <c r="S32" s="3">
+        <v>48.25</v>
+      </c>
+      <c r="T32" t="str">
         <v/>
       </c>
     </row>
@@ -2348,7 +2444,10 @@
       <c r="R33" s="3">
         <v>1598.86</v>
       </c>
-      <c r="S33" t="str">
+      <c r="S33" s="3">
+        <v>35.34</v>
+      </c>
+      <c r="T33" t="str">
         <v/>
       </c>
     </row>
@@ -2407,7 +2506,10 @@
       <c r="R34" s="3">
         <v>1607.67</v>
       </c>
-      <c r="S34" t="str">
+      <c r="S34" s="3">
+        <v>36.7</v>
+      </c>
+      <c r="T34" t="str">
         <v/>
       </c>
     </row>
@@ -2466,7 +2568,10 @@
       <c r="R35" s="3">
         <v>509.72</v>
       </c>
-      <c r="S35" t="str">
+      <c r="S35" s="3">
+        <v>38.35</v>
+      </c>
+      <c r="T35" t="str">
         <v/>
       </c>
     </row>
@@ -2525,7 +2630,10 @@
       <c r="R36" s="3">
         <v>2435.7</v>
       </c>
-      <c r="S36" t="str">
+      <c r="S36" s="3">
+        <v>40.77</v>
+      </c>
+      <c r="T36" t="str">
         <v/>
       </c>
     </row>
@@ -2584,7 +2692,10 @@
       <c r="R37" s="3">
         <v>433.98</v>
       </c>
-      <c r="S37" t="str">
+      <c r="S37" s="3">
+        <v>42.27</v>
+      </c>
+      <c r="T37" t="str">
         <v/>
       </c>
     </row>
@@ -2643,7 +2754,10 @@
       <c r="R38" s="3">
         <v>1816.97</v>
       </c>
-      <c r="S38" t="str">
+      <c r="S38" s="3">
+        <v>41.75</v>
+      </c>
+      <c r="T38" t="str">
         <v/>
       </c>
     </row>
@@ -2702,7 +2816,10 @@
       <c r="R39" s="3">
         <v>-997.05</v>
       </c>
-      <c r="S39" t="str">
+      <c r="S39" s="3">
+        <v>42.55</v>
+      </c>
+      <c r="T39" t="str">
         <v/>
       </c>
     </row>
@@ -2761,7 +2878,10 @@
       <c r="R40" s="3">
         <v>120.57</v>
       </c>
-      <c r="S40" t="str">
+      <c r="S40" s="3">
+        <v>37.92</v>
+      </c>
+      <c r="T40" t="str">
         <v/>
       </c>
     </row>
@@ -2820,7 +2940,10 @@
       <c r="R41" s="3">
         <v>-284.13</v>
       </c>
-      <c r="S41" t="str">
+      <c r="S41" s="3">
+        <v>39.46</v>
+      </c>
+      <c r="T41" t="str">
         <v/>
       </c>
     </row>
@@ -2879,7 +3002,10 @@
       <c r="R42" s="3">
         <v>332.77</v>
       </c>
-      <c r="S42" t="str">
+      <c r="S42" s="3">
+        <v>37.61</v>
+      </c>
+      <c r="T42" t="str">
         <v/>
       </c>
     </row>
@@ -2938,7 +3064,10 @@
       <c r="R43" s="3">
         <v>994.96</v>
       </c>
-      <c r="S43" t="str">
+      <c r="S43" s="3">
+        <v>31.75</v>
+      </c>
+      <c r="T43" t="str">
         <v/>
       </c>
     </row>
@@ -2997,7 +3126,10 @@
       <c r="R44" s="3">
         <v>-175.4</v>
       </c>
-      <c r="S44" t="str">
+      <c r="S44" s="3">
+        <v>35.21</v>
+      </c>
+      <c r="T44" t="str">
         <v/>
       </c>
     </row>
@@ -3056,7 +3188,10 @@
       <c r="R45" s="3">
         <v>262.12</v>
       </c>
-      <c r="S45" t="str">
+      <c r="S45" s="3">
+        <v>51.23</v>
+      </c>
+      <c r="T45" t="str">
         <v/>
       </c>
     </row>
@@ -3115,7 +3250,10 @@
       <c r="R46" s="3">
         <v>1477.16</v>
       </c>
-      <c r="S46" t="str">
+      <c r="S46" s="3">
+        <v>30.28</v>
+      </c>
+      <c r="T46" t="str">
         <v/>
       </c>
     </row>
@@ -3174,7 +3312,10 @@
       <c r="R47" s="3">
         <v>-246.06</v>
       </c>
-      <c r="S47" t="str">
+      <c r="S47" s="3">
+        <v>42.35</v>
+      </c>
+      <c r="T47" t="str">
         <v/>
       </c>
     </row>
@@ -3233,7 +3374,10 @@
       <c r="R48" s="3">
         <v>-490.47</v>
       </c>
-      <c r="S48" t="str">
+      <c r="S48" s="3">
+        <v>52.82</v>
+      </c>
+      <c r="T48" t="str">
         <v/>
       </c>
     </row>
@@ -3292,7 +3436,10 @@
       <c r="R49" s="3">
         <v>2377.64</v>
       </c>
-      <c r="S49" t="str">
+      <c r="S49" s="3">
+        <v>43.96</v>
+      </c>
+      <c r="T49" t="str">
         <v/>
       </c>
     </row>
@@ -3351,7 +3498,10 @@
       <c r="R50" s="3">
         <v>2407.67</v>
       </c>
-      <c r="S50" t="str">
+      <c r="S50" s="3">
+        <v>29.24</v>
+      </c>
+      <c r="T50" t="str">
         <v/>
       </c>
     </row>
@@ -3410,7 +3560,10 @@
       <c r="R51" s="3">
         <v>1111.92</v>
       </c>
-      <c r="S51" t="str">
+      <c r="S51" s="3">
+        <v>41.67</v>
+      </c>
+      <c r="T51" t="str">
         <v/>
       </c>
     </row>
@@ -3469,7 +3622,10 @@
       <c r="R52" s="3">
         <v>527.7</v>
       </c>
-      <c r="S52" t="str">
+      <c r="S52" s="3">
+        <v>43.27</v>
+      </c>
+      <c r="T52" t="str">
         <v/>
       </c>
     </row>
@@ -3528,7 +3684,10 @@
       <c r="R53" s="3">
         <v>177.01</v>
       </c>
-      <c r="S53" t="str">
+      <c r="S53" s="3">
+        <v>54.85</v>
+      </c>
+      <c r="T53" t="str">
         <v/>
       </c>
     </row>
@@ -3587,7 +3746,10 @@
       <c r="R54" s="3">
         <v>711.08</v>
       </c>
-      <c r="S54" t="str">
+      <c r="S54" s="3">
+        <v>46.2</v>
+      </c>
+      <c r="T54" t="str">
         <v/>
       </c>
     </row>
@@ -3646,7 +3808,10 @@
       <c r="R55" s="3">
         <v>327.38</v>
       </c>
-      <c r="S55" t="str">
+      <c r="S55" s="3">
+        <v>45.87</v>
+      </c>
+      <c r="T55" t="str">
         <v/>
       </c>
     </row>
@@ -3705,7 +3870,10 @@
       <c r="R56" s="3">
         <v>862.73</v>
       </c>
-      <c r="S56" t="str">
+      <c r="S56" s="3">
+        <v>37.74</v>
+      </c>
+      <c r="T56" t="str">
         <v/>
       </c>
     </row>
@@ -3764,7 +3932,10 @@
       <c r="R57" s="3">
         <v>466.43</v>
       </c>
-      <c r="S57" t="str">
+      <c r="S57" s="3">
+        <v>43.96</v>
+      </c>
+      <c r="T57" t="str">
         <v/>
       </c>
     </row>
@@ -3823,7 +3994,10 @@
       <c r="R58" s="3">
         <v>808.69</v>
       </c>
-      <c r="S58" t="str">
+      <c r="S58" s="3">
+        <v>42.32</v>
+      </c>
+      <c r="T58" t="str">
         <v/>
       </c>
     </row>
@@ -3882,7 +4056,10 @@
       <c r="R59" s="3">
         <v>1181.35</v>
       </c>
-      <c r="S59" t="str">
+      <c r="S59" s="3">
+        <v>40.18</v>
+      </c>
+      <c r="T59" t="str">
         <v/>
       </c>
     </row>
@@ -3941,7 +4118,10 @@
       <c r="R60" s="3">
         <v>1051.43</v>
       </c>
-      <c r="S60" t="str">
+      <c r="S60" s="3">
+        <v>35.32</v>
+      </c>
+      <c r="T60" t="str">
         <v/>
       </c>
     </row>
@@ -4000,7 +4180,10 @@
       <c r="R61" s="3">
         <v>1151.4</v>
       </c>
-      <c r="S61" t="str">
+      <c r="S61" s="3">
+        <v>39.94</v>
+      </c>
+      <c r="T61" t="str">
         <v/>
       </c>
     </row>
@@ -4059,7 +4242,10 @@
       <c r="R62" s="3">
         <v>828.13</v>
       </c>
-      <c r="S62" t="str">
+      <c r="S62" s="3">
+        <v>41.93</v>
+      </c>
+      <c r="T62" t="str">
         <v/>
       </c>
     </row>
@@ -4118,7 +4304,10 @@
       <c r="R63" s="3">
         <v>395.78</v>
       </c>
-      <c r="S63" t="str">
+      <c r="S63" s="3">
+        <v>40.46</v>
+      </c>
+      <c r="T63" t="str">
         <v/>
       </c>
     </row>
@@ -4177,7 +4366,10 @@
       <c r="R64" s="3">
         <v>3494.39</v>
       </c>
-      <c r="S64" t="str">
+      <c r="S64" s="3">
+        <v>35.55</v>
+      </c>
+      <c r="T64" t="str">
         <v/>
       </c>
     </row>
@@ -4236,7 +4428,10 @@
       <c r="R65" s="3">
         <v>2031.93</v>
       </c>
-      <c r="S65" t="str">
+      <c r="S65" s="3">
+        <v>34.69</v>
+      </c>
+      <c r="T65" t="str">
         <v/>
       </c>
     </row>
@@ -4295,7 +4490,10 @@
       <c r="R66" s="3">
         <v>300.13</v>
       </c>
-      <c r="S66" t="str">
+      <c r="S66" s="3">
+        <v>47.48</v>
+      </c>
+      <c r="T66" t="str">
         <v/>
       </c>
     </row>
@@ -4354,7 +4552,10 @@
       <c r="R67" s="3">
         <v>600.9</v>
       </c>
-      <c r="S67" t="str">
+      <c r="S67" s="3">
+        <v>47.72</v>
+      </c>
+      <c r="T67" t="str">
         <v/>
       </c>
     </row>
@@ -4413,7 +4614,10 @@
       <c r="R68" s="3">
         <v>1827.81</v>
       </c>
-      <c r="S68" t="str">
+      <c r="S68" s="3">
+        <v>35.17</v>
+      </c>
+      <c r="T68" t="str">
         <v/>
       </c>
     </row>
@@ -4472,7 +4676,10 @@
       <c r="R69" s="3">
         <v>1004.13</v>
       </c>
-      <c r="S69" t="str">
+      <c r="S69" s="3">
+        <v>36.03</v>
+      </c>
+      <c r="T69" t="str">
         <v/>
       </c>
     </row>
@@ -4531,7 +4738,10 @@
       <c r="R70" s="3">
         <v>949.36</v>
       </c>
-      <c r="S70" t="str">
+      <c r="S70" s="3">
+        <v>34.08</v>
+      </c>
+      <c r="T70" t="str">
         <v/>
       </c>
     </row>
@@ -4590,7 +4800,10 @@
       <c r="R71" s="3">
         <v>1435.09</v>
       </c>
-      <c r="S71" t="str">
+      <c r="S71" s="3">
+        <v>36.74</v>
+      </c>
+      <c r="T71" t="str">
         <v/>
       </c>
     </row>
@@ -4649,7 +4862,10 @@
       <c r="R72" s="3">
         <v>552.98</v>
       </c>
-      <c r="S72" t="str">
+      <c r="S72" s="3">
+        <v>54.92</v>
+      </c>
+      <c r="T72" t="str">
         <v/>
       </c>
     </row>
@@ -4708,7 +4924,10 @@
       <c r="R73" s="3">
         <v>1363.04</v>
       </c>
-      <c r="S73" t="str">
+      <c r="S73" s="3">
+        <v>38.63</v>
+      </c>
+      <c r="T73" t="str">
         <v/>
       </c>
     </row>
@@ -4767,7 +4986,10 @@
       <c r="R74" s="3">
         <v>799.61</v>
       </c>
-      <c r="S74" t="str">
+      <c r="S74" s="3">
+        <v>46.93</v>
+      </c>
+      <c r="T74" t="str">
         <v/>
       </c>
     </row>
@@ -4826,7 +5048,10 @@
       <c r="R75" s="3">
         <v>10.09</v>
       </c>
-      <c r="S75" t="str">
+      <c r="S75" s="3">
+        <v>41.05</v>
+      </c>
+      <c r="T75" t="str">
         <v/>
       </c>
     </row>
@@ -4885,7 +5110,10 @@
       <c r="R76" s="3">
         <v>115.49</v>
       </c>
-      <c r="S76" t="str">
+      <c r="S76" s="3">
+        <v>50.91</v>
+      </c>
+      <c r="T76" t="str">
         <v/>
       </c>
     </row>
@@ -4944,7 +5172,10 @@
       <c r="R77" s="3">
         <v>993.55</v>
       </c>
-      <c r="S77" t="str">
+      <c r="S77" s="3">
+        <v>55.9</v>
+      </c>
+      <c r="T77" t="str">
         <v/>
       </c>
     </row>
@@ -5003,7 +5234,10 @@
       <c r="R78" s="3">
         <v>1751.51</v>
       </c>
-      <c r="S78" t="str">
+      <c r="S78" s="3">
+        <v>35.7</v>
+      </c>
+      <c r="T78" t="str">
         <v/>
       </c>
     </row>
@@ -5062,7 +5296,10 @@
       <c r="R79" s="3">
         <v>-1155.4</v>
       </c>
-      <c r="S79" t="str">
+      <c r="S79" s="3">
+        <v>68.53</v>
+      </c>
+      <c r="T79" t="str">
         <v/>
       </c>
     </row>
@@ -5121,7 +5358,10 @@
       <c r="R80" s="3">
         <v>-191.83</v>
       </c>
-      <c r="S80" t="str">
+      <c r="S80" s="3">
+        <v>52.96</v>
+      </c>
+      <c r="T80" t="str">
         <v/>
       </c>
     </row>
@@ -5180,7 +5420,10 @@
       <c r="R81" s="3">
         <v>514.31</v>
       </c>
-      <c r="S81" t="str">
+      <c r="S81" s="3">
+        <v>58.1</v>
+      </c>
+      <c r="T81" t="str">
         <v/>
       </c>
     </row>
@@ -5239,7 +5482,10 @@
       <c r="R82" s="3">
         <v>207.1</v>
       </c>
-      <c r="S82" t="str">
+      <c r="S82" s="3">
+        <v>46.26</v>
+      </c>
+      <c r="T82" t="str">
         <v/>
       </c>
     </row>
@@ -5298,7 +5544,10 @@
       <c r="R83" s="3">
         <v>1904.53</v>
       </c>
-      <c r="S83" t="str">
+      <c r="S83" s="3">
+        <v>44.54</v>
+      </c>
+      <c r="T83" t="str">
         <v/>
       </c>
     </row>
@@ -5357,7 +5606,10 @@
       <c r="R84" s="3">
         <v>-956.12</v>
       </c>
-      <c r="S84" t="str">
+      <c r="S84" s="3">
+        <v>40.88</v>
+      </c>
+      <c r="T84" t="str">
         <v/>
       </c>
     </row>
@@ -5416,7 +5668,10 @@
       <c r="R85" s="3">
         <v>1086.46</v>
       </c>
-      <c r="S85" t="str">
+      <c r="S85" s="3">
+        <v>46.17</v>
+      </c>
+      <c r="T85" t="str">
         <v/>
       </c>
     </row>
@@ -5475,7 +5730,10 @@
       <c r="R86" s="3">
         <v>197.84</v>
       </c>
-      <c r="S86" t="str">
+      <c r="S86" s="3">
+        <v>37.94</v>
+      </c>
+      <c r="T86" t="str">
         <v/>
       </c>
     </row>
@@ -5534,7 +5792,10 @@
       <c r="R87" s="3">
         <v>2365.37</v>
       </c>
-      <c r="S87" t="str">
+      <c r="S87" s="3">
+        <v>39.28</v>
+      </c>
+      <c r="T87" t="str">
         <v/>
       </c>
     </row>
@@ -5593,7 +5854,10 @@
       <c r="R88" s="3">
         <v>880.38</v>
       </c>
-      <c r="S88" t="str">
+      <c r="S88" s="3">
+        <v>49.64</v>
+      </c>
+      <c r="T88" t="str">
         <v/>
       </c>
     </row>
@@ -5652,7 +5916,10 @@
       <c r="R89" s="3">
         <v>929.94</v>
       </c>
-      <c r="S89" t="str">
+      <c r="S89" s="3">
+        <v>46.74</v>
+      </c>
+      <c r="T89" t="str">
         <v/>
       </c>
     </row>
@@ -5711,13 +5978,16 @@
       <c r="R90" s="3">
         <v>426.64</v>
       </c>
-      <c r="S90" t="str">
+      <c r="S90" s="3">
+        <v>46.61</v>
+      </c>
+      <c r="T90" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S90"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T90"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/index.xlsx
+++ b/index.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T90"/>
+  <dimension ref="A1:Y90"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -464,6 +464,21 @@
         <v>rsi</v>
       </c>
       <c r="T1" t="str">
+        <v>adx_di_positive</v>
+      </c>
+      <c r="U1" t="str">
+        <v>adx_di_negative</v>
+      </c>
+      <c r="V1" t="str">
+        <v>adx</v>
+      </c>
+      <c r="W1" t="str">
+        <v>market_cap</v>
+      </c>
+      <c r="X1" t="str">
+        <v>earning_per_share</v>
+      </c>
+      <c r="Y1" t="str">
         <v>Add Column</v>
       </c>
     </row>
@@ -478,54 +493,69 @@
         <v>INDIAVIX</v>
       </c>
       <c r="D2" s="1">
-        <v>14.77</v>
+        <v>16.86</v>
       </c>
       <c r="E2" s="2">
-        <v>5.05</v>
+        <v>6.98</v>
       </c>
       <c r="F2" s="2">
-        <v>5.05</v>
+        <v>19.91</v>
       </c>
       <c r="G2" s="2">
-        <v>9.49</v>
+        <v>24.98</v>
       </c>
       <c r="H2" s="2">
-        <v>55.8</v>
+        <v>77.85</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>14.81</v>
+        <v>14.91</v>
       </c>
       <c r="K2" s="1">
-        <v>14.27</v>
+        <v>15.13</v>
       </c>
       <c r="L2" s="1">
-        <v>12.36</v>
+        <v>12.6</v>
       </c>
       <c r="M2" s="3">
-        <v>0.66</v>
+        <v>0.9</v>
       </c>
       <c r="N2" s="3">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="O2" s="3">
-        <v>-0.36</v>
+        <v>-0.19</v>
       </c>
       <c r="P2" s="3">
-        <v>-0.76</v>
+        <v>-0.73</v>
       </c>
       <c r="Q2" s="3">
-        <v>-0.09</v>
+        <v>0.08</v>
       </c>
       <c r="R2" s="3">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="S2" s="3">
-        <v>57.58</v>
-      </c>
-      <c r="T2" t="str">
+        <v>66.5</v>
+      </c>
+      <c r="T2" s="3">
+        <v>19.58</v>
+      </c>
+      <c r="U2" s="3">
+        <v>13.36</v>
+      </c>
+      <c r="V2" s="3">
+        <v>17.68</v>
+      </c>
+      <c r="W2" s="3">
+        <v>0</v>
+      </c>
+      <c r="X2" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="str">
         <v/>
       </c>
     </row>
@@ -534,60 +564,75 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="C3" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="D3" s="1">
-        <v>8294.1</v>
+        <v>204.22</v>
       </c>
       <c r="E3" s="2">
-        <v>2.46</v>
+        <v>1.02</v>
       </c>
       <c r="F3" s="2">
-        <v>2.46</v>
+        <v>1.02</v>
       </c>
       <c r="G3" s="2">
-        <v>3.47</v>
+        <v>3.78</v>
       </c>
       <c r="H3" s="2">
-        <v>-2.8</v>
+        <v>-18.03</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>8575.33</v>
+        <v>180.43</v>
       </c>
       <c r="K3" s="1">
-        <v>8128.49</v>
+        <v>200.88</v>
       </c>
       <c r="L3" s="1">
-        <v>8374.79</v>
+        <v>195.12</v>
       </c>
       <c r="M3" s="3">
-        <v>-56.26</v>
+        <v>2.78</v>
       </c>
       <c r="N3" s="3">
-        <v>-87.73</v>
+        <v>2.61</v>
       </c>
       <c r="O3" s="3">
-        <v>-72.14</v>
+        <v>11.94</v>
       </c>
       <c r="P3" s="3">
-        <v>-29.08</v>
+        <v>5.7</v>
       </c>
       <c r="Q3" s="3">
-        <v>578.77</v>
+        <v>5.47</v>
       </c>
       <c r="R3" s="3">
-        <v>686.08</v>
+        <v>7.68</v>
       </c>
       <c r="S3" s="3">
-        <v>54.74</v>
-      </c>
-      <c r="T3" t="str">
+        <v>100</v>
+      </c>
+      <c r="T3" s="3">
+        <v>99.62</v>
+      </c>
+      <c r="U3" s="3">
+        <v>0.38</v>
+      </c>
+      <c r="V3" s="3">
+        <v>97</v>
+      </c>
+      <c r="W3" s="3">
+        <v>0</v>
+      </c>
+      <c r="X3" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="str">
         <v/>
       </c>
     </row>
@@ -602,54 +647,69 @@
         <v>NIFTY50PR1XINV</v>
       </c>
       <c r="D4" s="1">
-        <v>233.5</v>
+        <v>236.6</v>
       </c>
       <c r="E4" s="2">
-        <v>1.15</v>
+        <v>0.4</v>
       </c>
       <c r="F4" s="2">
-        <v>1.15</v>
+        <v>2.49</v>
       </c>
       <c r="G4" s="2">
-        <v>-1.04</v>
+        <v>0.28</v>
       </c>
       <c r="H4" s="2">
-        <v>16.75</v>
+        <v>18.3</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>218.74</v>
+        <v>219.26</v>
       </c>
       <c r="K4" s="1">
-        <v>234.35</v>
+        <v>234.95</v>
       </c>
       <c r="L4" s="1">
-        <v>226.77</v>
+        <v>227.92</v>
       </c>
       <c r="M4" s="3">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="N4" s="3">
-        <v>2.91</v>
+        <v>2.4</v>
       </c>
       <c r="O4" s="3">
-        <v>4.51</v>
+        <v>4.76</v>
       </c>
       <c r="P4" s="3">
-        <v>3.42</v>
+        <v>3.47</v>
       </c>
       <c r="Q4" s="3">
-        <v>-0.82</v>
+        <v>-0.58</v>
       </c>
       <c r="R4" s="3">
-        <v>-4.81</v>
+        <v>-4.76</v>
       </c>
       <c r="S4" s="3">
-        <v>52.73</v>
-      </c>
-      <c r="T4" t="str">
+        <v>58.23</v>
+      </c>
+      <c r="T4" s="3">
+        <v>28.84</v>
+      </c>
+      <c r="U4" s="3">
+        <v>12.4</v>
+      </c>
+      <c r="V4" s="3">
+        <v>43.12</v>
+      </c>
+      <c r="W4" s="3">
+        <v>0</v>
+      </c>
+      <c r="X4" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="str">
         <v/>
       </c>
     </row>
@@ -664,54 +724,69 @@
         <v>NIFTY50TR1XINV</v>
       </c>
       <c r="D5" s="1">
-        <v>189.35</v>
+        <v>191.9</v>
       </c>
       <c r="E5" s="2">
-        <v>1.15</v>
+        <v>0.39</v>
       </c>
       <c r="F5" s="2">
-        <v>1.15</v>
+        <v>2.51</v>
       </c>
       <c r="G5" s="2">
-        <v>-1.07</v>
+        <v>0.26</v>
       </c>
       <c r="H5" s="2">
-        <v>15.7</v>
+        <v>17.26</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>178.28</v>
+        <v>178.68</v>
       </c>
       <c r="K5" s="1">
-        <v>190.07</v>
+        <v>190.56</v>
       </c>
       <c r="L5" s="1">
-        <v>183.97</v>
+        <v>184.9</v>
       </c>
       <c r="M5" s="3">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="N5" s="3">
-        <v>2.34</v>
+        <v>1.92</v>
       </c>
       <c r="O5" s="3">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P5" s="3">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="Q5" s="3">
-        <v>-2.64</v>
+        <v>-2.44</v>
       </c>
       <c r="R5" s="3">
-        <v>-6.06</v>
+        <v>-6.02</v>
       </c>
       <c r="S5" s="3">
-        <v>52.58</v>
-      </c>
-      <c r="T5" t="str">
+        <v>58.14</v>
+      </c>
+      <c r="T5" s="3">
+        <v>28.85</v>
+      </c>
+      <c r="U5" s="3">
+        <v>12.58</v>
+      </c>
+      <c r="V5" s="3">
+        <v>42.66</v>
+      </c>
+      <c r="W5" s="3">
+        <v>0</v>
+      </c>
+      <c r="X5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="str">
         <v/>
       </c>
     </row>
@@ -726,54 +801,69 @@
         <v>NIFTYGS48YR</v>
       </c>
       <c r="D6" s="1">
+        <v>3276.92</v>
+      </c>
+      <c r="E6" s="2">
+        <v>-0.01</v>
+      </c>
+      <c r="F6" s="2">
+        <v>-0.14</v>
+      </c>
+      <c r="G6" s="2">
+        <v>-0.96</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1.68</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>3280.43</v>
+      </c>
+      <c r="K6" s="1">
         <v>3284.34</v>
       </c>
-      <c r="E6" s="2">
-        <v>0.09</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.09</v>
-      </c>
-      <c r="G6" s="2">
-        <v>-0.73</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1.91</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>3279.61</v>
-      </c>
-      <c r="K6" s="1">
-        <v>3289.81</v>
-      </c>
       <c r="L6" s="1">
-        <v>3324.09</v>
+        <v>3319.89</v>
       </c>
       <c r="M6" s="3">
-        <v>-11.82</v>
+        <v>-12.05</v>
       </c>
       <c r="N6" s="3">
-        <v>-10.63</v>
+        <v>-11.31</v>
       </c>
       <c r="O6" s="3">
-        <v>8.31</v>
+        <v>7.72</v>
       </c>
       <c r="P6" s="3">
-        <v>18.11</v>
+        <v>17.99</v>
       </c>
       <c r="Q6" s="3">
-        <v>140.08</v>
+        <v>139.48</v>
       </c>
       <c r="R6" s="3">
-        <v>155.52</v>
+        <v>155.41</v>
       </c>
       <c r="S6" s="3">
-        <v>29.05</v>
-      </c>
-      <c r="T6" t="str">
+        <v>25.04</v>
+      </c>
+      <c r="T6" s="3">
+        <v>10.4</v>
+      </c>
+      <c r="U6" s="3">
+        <v>45.94</v>
+      </c>
+      <c r="V6" s="3">
+        <v>48.97</v>
+      </c>
+      <c r="W6" s="3">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="str">
         <v/>
       </c>
     </row>
@@ -782,60 +872,75 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="C7" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="D7" s="1">
-        <v>1602.59</v>
+        <v>3284.16</v>
       </c>
       <c r="E7" s="2">
-        <v>0.07</v>
+        <v>-0.05</v>
       </c>
       <c r="F7" s="2">
-        <v>0.07</v>
+        <v>-0.57</v>
       </c>
       <c r="G7" s="2">
-        <v>-0.27</v>
+        <v>-1.13</v>
       </c>
       <c r="H7" s="2">
-        <v>2.28</v>
+        <v>1.3</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>1586.32</v>
+        <v>3295.35</v>
       </c>
       <c r="K7" s="1">
-        <v>1604.46</v>
+        <v>3294.53</v>
       </c>
       <c r="L7" s="1">
-        <v>1609.47</v>
+        <v>3347.55</v>
       </c>
       <c r="M7" s="3">
-        <v>-1.88</v>
+        <v>-17.47</v>
       </c>
       <c r="N7" s="3">
-        <v>-1.26</v>
+        <v>-17.24</v>
       </c>
       <c r="O7" s="3">
-        <v>7.04</v>
+        <v>7.47</v>
       </c>
       <c r="P7" s="3">
-        <v>9.39</v>
+        <v>21.48</v>
       </c>
       <c r="Q7" s="3">
-        <v>35</v>
+        <v>136.34</v>
       </c>
       <c r="R7" s="3">
-        <v>33.14</v>
+        <v>153.87</v>
       </c>
       <c r="S7" s="3">
-        <v>34.94</v>
-      </c>
-      <c r="T7" t="str">
+        <v>32.06</v>
+      </c>
+      <c r="T7" s="3">
+        <v>8.59</v>
+      </c>
+      <c r="U7" s="3">
+        <v>37.49</v>
+      </c>
+      <c r="V7" s="3">
+        <v>50.12</v>
+      </c>
+      <c r="W7" s="3">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="str">
         <v/>
       </c>
     </row>
@@ -844,60 +949,75 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="C8" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="D8" s="1">
-        <v>1308.53</v>
+        <v>2965.74</v>
       </c>
       <c r="E8" s="2">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="F8" s="2">
-        <v>0.06</v>
+        <v>-0.57</v>
       </c>
       <c r="G8" s="2">
-        <v>-0.53</v>
+        <v>-1.6</v>
       </c>
       <c r="H8" s="2">
-        <v>0.8</v>
+        <v>-0.04</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>1307.91</v>
+        <v>3001.35</v>
       </c>
       <c r="K8" s="1">
-        <v>1311.79</v>
+        <v>2979.03</v>
       </c>
       <c r="L8" s="1">
-        <v>1323.02</v>
+        <v>3025.27</v>
       </c>
       <c r="M8" s="3">
-        <v>-3.88</v>
+        <v>-16.31</v>
       </c>
       <c r="N8" s="3">
-        <v>-3.27</v>
+        <v>-14.7</v>
       </c>
       <c r="O8" s="3">
-        <v>2.37</v>
+        <v>-0.06</v>
       </c>
       <c r="P8" s="3">
-        <v>5.74</v>
+        <v>11.34</v>
       </c>
       <c r="Q8" s="3">
-        <v>24.16</v>
+        <v>114.39</v>
       </c>
       <c r="R8" s="3">
-        <v>24.25</v>
+        <v>132.76</v>
       </c>
       <c r="S8" s="3">
-        <v>25.89</v>
-      </c>
-      <c r="T8" t="str">
+        <v>24.53</v>
+      </c>
+      <c r="T8" s="3">
+        <v>11.19</v>
+      </c>
+      <c r="U8" s="3">
+        <v>46.17</v>
+      </c>
+      <c r="V8" s="3">
+        <v>50.89</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="str">
         <v/>
       </c>
     </row>
@@ -906,60 +1026,75 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="C9" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="D9" s="1">
-        <v>1447.65</v>
+        <v>2595.75</v>
       </c>
       <c r="E9" s="2">
-        <v>0.04</v>
+        <v>-0.07</v>
       </c>
       <c r="F9" s="2">
-        <v>0.04</v>
+        <v>-0.59</v>
       </c>
       <c r="G9" s="2">
-        <v>-0.43</v>
+        <v>-1.61</v>
       </c>
       <c r="H9" s="2">
-        <v>1.61</v>
+        <v>-0.62</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>1440.58</v>
+        <v>2632.21</v>
       </c>
       <c r="K9" s="1">
-        <v>1450.48</v>
+        <v>2607.13</v>
       </c>
       <c r="L9" s="1">
-        <v>1459.16</v>
+        <v>2648</v>
       </c>
       <c r="M9" s="3">
-        <v>-3.08</v>
+        <v>-14.46</v>
       </c>
       <c r="N9" s="3">
-        <v>-2.45</v>
+        <v>-13.13</v>
       </c>
       <c r="O9" s="3">
-        <v>4.37</v>
+        <v>-2.22</v>
       </c>
       <c r="P9" s="3">
-        <v>7.36</v>
+        <v>7.41</v>
       </c>
       <c r="Q9" s="3">
-        <v>29.31</v>
+        <v>89.59</v>
       </c>
       <c r="R9" s="3">
-        <v>28.58</v>
+        <v>106.33</v>
       </c>
       <c r="S9" s="3">
-        <v>28.35</v>
-      </c>
-      <c r="T9" t="str">
+        <v>26.14</v>
+      </c>
+      <c r="T9" s="3">
+        <v>14.19</v>
+      </c>
+      <c r="U9" s="3">
+        <v>40.39</v>
+      </c>
+      <c r="V9" s="3">
+        <v>38.57</v>
+      </c>
+      <c r="W9" s="3">
+        <v>0</v>
+      </c>
+      <c r="X9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="str">
         <v/>
       </c>
     </row>
@@ -968,60 +1103,75 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="C10" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="D10" s="1">
-        <v>1264.7</v>
+        <v>837.21</v>
       </c>
       <c r="E10" s="2">
-        <v>0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="F10" s="2">
-        <v>0.03</v>
+        <v>-0.75</v>
       </c>
       <c r="G10" s="2">
-        <v>-0.67</v>
+        <v>-2.1</v>
       </c>
       <c r="H10" s="2">
-        <v>0.25</v>
+        <v>-6.08</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>1268.34</v>
+        <v>873.57</v>
       </c>
       <c r="K10" s="1">
-        <v>1268.71</v>
+        <v>842.1</v>
       </c>
       <c r="L10" s="1">
-        <v>1281.51</v>
+        <v>860.68</v>
       </c>
       <c r="M10" s="3">
-        <v>-4.53</v>
+        <v>-6.56</v>
       </c>
       <c r="N10" s="3">
-        <v>-3.79</v>
+        <v>-6.1</v>
       </c>
       <c r="O10" s="3">
-        <v>1.39</v>
+        <v>-8.84</v>
       </c>
       <c r="P10" s="3">
-        <v>4.98</v>
+        <v>-5.65</v>
       </c>
       <c r="Q10" s="3">
-        <v>21.48</v>
+        <v>-17.29</v>
       </c>
       <c r="R10" s="3">
-        <v>21.99</v>
+        <v>-14.21</v>
       </c>
       <c r="S10" s="3">
-        <v>24.26</v>
-      </c>
-      <c r="T10" t="str">
+        <v>20.5</v>
+      </c>
+      <c r="T10" s="3">
+        <v>9.83</v>
+      </c>
+      <c r="U10" s="3">
+        <v>45.2</v>
+      </c>
+      <c r="V10" s="3">
+        <v>53.22</v>
+      </c>
+      <c r="W10" s="3">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="str">
         <v/>
       </c>
     </row>
@@ -1030,60 +1180,75 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="C11" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="D11" s="1">
-        <v>202.16</v>
+        <v>3057.33</v>
       </c>
       <c r="E11" s="2">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="F11" s="2">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="G11" s="2">
-        <v>2.73</v>
+        <v>-1.51</v>
       </c>
       <c r="H11" s="2">
-        <v>-18.86</v>
+        <v>0.16</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>181.13</v>
+        <v>3085.96</v>
       </c>
       <c r="K11" s="1">
-        <v>199.13</v>
+        <v>3071.1</v>
       </c>
       <c r="L11" s="1">
-        <v>194.2</v>
+        <v>3117.26</v>
       </c>
       <c r="M11" s="3">
-        <v>2.5</v>
+        <v>-16.11</v>
       </c>
       <c r="N11" s="3">
-        <v>2.54</v>
+        <v>-14.56</v>
       </c>
       <c r="O11" s="3">
-        <v>11.77</v>
+        <v>2.23</v>
       </c>
       <c r="P11" s="3">
-        <v>5.66</v>
+        <v>13.89</v>
       </c>
       <c r="Q11" s="3">
-        <v>5.31</v>
+        <v>118.23</v>
       </c>
       <c r="R11" s="3">
-        <v>7.65</v>
+        <v>136.49</v>
       </c>
       <c r="S11" s="3">
-        <v>100</v>
-      </c>
-      <c r="T11" t="str">
+        <v>26.6</v>
+      </c>
+      <c r="T11" s="3">
+        <v>11.51</v>
+      </c>
+      <c r="U11" s="3">
+        <v>44.83</v>
+      </c>
+      <c r="V11" s="3">
+        <v>48.31</v>
+      </c>
+      <c r="W11" s="3">
+        <v>0</v>
+      </c>
+      <c r="X11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="str">
         <v/>
       </c>
     </row>
@@ -1092,60 +1257,75 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="C12" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="D12" s="1">
-        <v>3486.59</v>
+        <v>29934.75</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.03</v>
+        <v>-0.21</v>
       </c>
       <c r="F12" s="2">
-        <v>-0.03</v>
+        <v>-1.79</v>
       </c>
       <c r="G12" s="2">
-        <v>-1</v>
+        <v>3.17</v>
       </c>
       <c r="H12" s="2">
-        <v>-0.18</v>
+        <v>-11.06</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>3495.63</v>
+        <v>30941.95</v>
       </c>
       <c r="K12" s="1">
-        <v>3491.27</v>
+        <v>29821.3</v>
       </c>
       <c r="L12" s="1">
-        <v>3539.34</v>
+        <v>30083.38</v>
       </c>
       <c r="M12" s="3">
-        <v>-16.47</v>
+        <v>21.38</v>
       </c>
       <c r="N12" s="3">
-        <v>-14.31</v>
+        <v>-124.43</v>
       </c>
       <c r="O12" s="3">
-        <v>4.22</v>
+        <v>-359.57</v>
       </c>
       <c r="P12" s="3">
-        <v>15.71</v>
+        <v>-317.41</v>
       </c>
       <c r="Q12" s="3">
-        <v>120.26</v>
+        <v>482.12</v>
       </c>
       <c r="R12" s="3">
-        <v>142.19</v>
+        <v>990.92</v>
       </c>
       <c r="S12" s="3">
-        <v>39.64</v>
-      </c>
-      <c r="T12" t="str">
+        <v>52.88</v>
+      </c>
+      <c r="T12" s="3">
+        <v>19.34</v>
+      </c>
+      <c r="U12" s="3">
+        <v>24.14</v>
+      </c>
+      <c r="V12" s="3">
+        <v>27.11</v>
+      </c>
+      <c r="W12" s="3">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="str">
         <v/>
       </c>
     </row>
@@ -1154,60 +1334,75 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="C13" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="D13" s="1">
-        <v>2980.67</v>
+        <v>1596.15</v>
       </c>
       <c r="E13" s="2">
-        <v>-0.07</v>
+        <v>-0.22</v>
       </c>
       <c r="F13" s="2">
-        <v>-0.07</v>
+        <v>-0.33</v>
       </c>
       <c r="G13" s="2">
-        <v>-1.1</v>
+        <v>-0.67</v>
       </c>
       <c r="H13" s="2">
-        <v>0.46</v>
+        <v>1.87</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>3001.37</v>
+        <v>1586.81</v>
       </c>
       <c r="K13" s="1">
-        <v>2988.3</v>
+        <v>1601.81</v>
       </c>
       <c r="L13" s="1">
-        <v>3030.94</v>
+        <v>1608.58</v>
       </c>
       <c r="M13" s="3">
-        <v>-15.04</v>
+        <v>-2.7</v>
       </c>
       <c r="N13" s="3">
-        <v>-13.48</v>
+        <v>-1.81</v>
       </c>
       <c r="O13" s="3">
-        <v>1.13</v>
+        <v>6.53</v>
       </c>
       <c r="P13" s="3">
-        <v>11.58</v>
+        <v>9.29</v>
       </c>
       <c r="Q13" s="3">
-        <v>115.58</v>
+        <v>34.48</v>
       </c>
       <c r="R13" s="3">
-        <v>132.99</v>
+        <v>33.04</v>
       </c>
       <c r="S13" s="3">
-        <v>30.27</v>
-      </c>
-      <c r="T13" t="str">
+        <v>23.28</v>
+      </c>
+      <c r="T13" s="3">
+        <v>19.64</v>
+      </c>
+      <c r="U13" s="3">
+        <v>70.91</v>
+      </c>
+      <c r="V13" s="3">
+        <v>28.2</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="str">
         <v/>
       </c>
     </row>
@@ -1216,60 +1411,75 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="C14" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="D14" s="1">
-        <v>3073.25</v>
+        <v>10889.35</v>
       </c>
       <c r="E14" s="2">
-        <v>-0.09</v>
+        <v>-0.25</v>
       </c>
       <c r="F14" s="2">
-        <v>-0.09</v>
+        <v>-1.23</v>
       </c>
       <c r="G14" s="2">
-        <v>-1</v>
+        <v>3.32</v>
       </c>
       <c r="H14" s="2">
-        <v>0.68</v>
+        <v>-12.77</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>3085.84</v>
+        <v>11216.63</v>
       </c>
       <c r="K14" s="1">
-        <v>3080.26</v>
+        <v>10811.35</v>
       </c>
       <c r="L14" s="1">
-        <v>3122.96</v>
+        <v>11067.8</v>
       </c>
       <c r="M14" s="3">
-        <v>-14.85</v>
+        <v>-22.75</v>
       </c>
       <c r="N14" s="3">
-        <v>-13.41</v>
+        <v>-98.95</v>
       </c>
       <c r="O14" s="3">
-        <v>3.5</v>
+        <v>-114.58</v>
       </c>
       <c r="P14" s="3">
-        <v>14.14</v>
+        <v>-76.04</v>
       </c>
       <c r="Q14" s="3">
-        <v>119.5</v>
+        <v>31.47</v>
       </c>
       <c r="R14" s="3">
-        <v>136.75</v>
+        <v>176.53</v>
       </c>
       <c r="S14" s="3">
-        <v>32.67</v>
-      </c>
-      <c r="T14" t="str">
+        <v>52.9</v>
+      </c>
+      <c r="T14" s="3">
+        <v>19.03</v>
+      </c>
+      <c r="U14" s="3">
+        <v>23.31</v>
+      </c>
+      <c r="V14" s="3">
+        <v>32.43</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="str">
         <v/>
       </c>
     </row>
@@ -1278,60 +1488,75 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="C15" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="D15" s="1">
-        <v>2608.21</v>
+        <v>10726.75</v>
       </c>
       <c r="E15" s="2">
-        <v>-0.11</v>
+        <v>-0.25</v>
       </c>
       <c r="F15" s="2">
-        <v>-0.11</v>
+        <v>-2.97</v>
       </c>
       <c r="G15" s="2">
-        <v>-1.14</v>
+        <v>-3.12</v>
       </c>
       <c r="H15" s="2">
-        <v>-0.14</v>
+        <v>-12.72</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>2632.47</v>
+        <v>11488.94</v>
       </c>
       <c r="K15" s="1">
-        <v>2615.12</v>
+        <v>10883.66</v>
       </c>
       <c r="L15" s="1">
-        <v>2653.15</v>
+        <v>11448.4</v>
       </c>
       <c r="M15" s="3">
-        <v>-13.45</v>
+        <v>-176.46</v>
       </c>
       <c r="N15" s="3">
-        <v>-12.09</v>
+        <v>-180.36</v>
       </c>
       <c r="O15" s="3">
-        <v>-1.22</v>
+        <v>-159.66</v>
       </c>
       <c r="P15" s="3">
-        <v>7.61</v>
+        <v>-43.17</v>
       </c>
       <c r="Q15" s="3">
-        <v>90.59</v>
+        <v>208.66</v>
       </c>
       <c r="R15" s="3">
-        <v>106.53</v>
+        <v>392.4</v>
       </c>
       <c r="S15" s="3">
-        <v>31.48</v>
-      </c>
-      <c r="T15" t="str">
+        <v>34.37</v>
+      </c>
+      <c r="T15" s="3">
+        <v>9.32</v>
+      </c>
+      <c r="U15" s="3">
+        <v>36.63</v>
+      </c>
+      <c r="V15" s="3">
+        <v>47.5</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="str">
         <v/>
       </c>
     </row>
@@ -1340,60 +1565,75 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="C16" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="D16" s="1">
-        <v>10544.4</v>
+        <v>8281.2</v>
       </c>
       <c r="E16" s="2">
-        <v>-0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="F16" s="2">
-        <v>-0.12</v>
+        <v>-1.98</v>
       </c>
       <c r="G16" s="2">
-        <v>-0.66</v>
+        <v>2.53</v>
       </c>
       <c r="H16" s="2">
-        <v>-13.79</v>
+        <v>-17.56</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>11315.17</v>
+        <v>8763.47</v>
       </c>
       <c r="K16" s="1">
-        <v>10520.12</v>
+        <v>8285.07</v>
       </c>
       <c r="L16" s="1">
-        <v>10920.58</v>
+        <v>8388.81</v>
       </c>
       <c r="M16" s="3">
-        <v>-129.66</v>
+        <v>-8.14</v>
       </c>
       <c r="N16" s="3">
-        <v>-148.15</v>
+        <v>-37.3</v>
       </c>
       <c r="O16" s="3">
-        <v>-217.36</v>
+        <v>-161.61</v>
       </c>
       <c r="P16" s="3">
-        <v>-158.68</v>
+        <v>-158.84</v>
       </c>
       <c r="Q16" s="3">
-        <v>81.1</v>
+        <v>-306.95</v>
       </c>
       <c r="R16" s="3">
-        <v>281.02</v>
+        <v>-192.72</v>
       </c>
       <c r="S16" s="3">
-        <v>43.56</v>
-      </c>
-      <c r="T16" t="str">
+        <v>49.51</v>
+      </c>
+      <c r="T16" s="3">
+        <v>17.93</v>
+      </c>
+      <c r="U16" s="3">
+        <v>24.71</v>
+      </c>
+      <c r="V16" s="3">
+        <v>22.6</v>
+      </c>
+      <c r="W16" s="3">
+        <v>0</v>
+      </c>
+      <c r="X16" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="str">
         <v/>
       </c>
     </row>
@@ -1402,60 +1642,75 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>Nifty IT</v>
       </c>
       <c r="C17" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>CNXIT</v>
       </c>
       <c r="D17" s="1">
-        <v>842.03</v>
+        <v>31995.5</v>
       </c>
       <c r="E17" s="2">
-        <v>-0.18</v>
+        <v>-0.27</v>
       </c>
       <c r="F17" s="2">
-        <v>-0.18</v>
+        <v>0.22</v>
       </c>
       <c r="G17" s="2">
-        <v>-1.54</v>
+        <v>15.49</v>
       </c>
       <c r="H17" s="2">
-        <v>-5.54</v>
+        <v>-15.54</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>874.39</v>
+        <v>30815.06</v>
       </c>
       <c r="K17" s="1">
-        <v>845.54</v>
+        <v>30967.15</v>
       </c>
       <c r="L17" s="1">
-        <v>863.12</v>
+        <v>29839.55</v>
       </c>
       <c r="M17" s="3">
-        <v>-6.21</v>
+        <v>749.33</v>
       </c>
       <c r="N17" s="3">
-        <v>-5.74</v>
+        <v>287.49</v>
       </c>
       <c r="O17" s="3">
-        <v>-8.45</v>
+        <v>-156.84</v>
       </c>
       <c r="P17" s="3">
-        <v>-5.57</v>
+        <v>-519.55</v>
       </c>
       <c r="Q17" s="3">
-        <v>-16.9</v>
+        <v>-1661.02</v>
       </c>
       <c r="R17" s="3">
-        <v>-14.13</v>
+        <v>-1147.75</v>
       </c>
       <c r="S17" s="3">
-        <v>25.1</v>
-      </c>
-      <c r="T17" t="str">
+        <v>68.05</v>
+      </c>
+      <c r="T17" s="3">
+        <v>30.99</v>
+      </c>
+      <c r="U17" s="3">
+        <v>13.96</v>
+      </c>
+      <c r="V17" s="3">
+        <v>30.24</v>
+      </c>
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+      <c r="X17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="str">
         <v/>
       </c>
     </row>
@@ -1464,60 +1719,75 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="C18" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="D18" s="1">
-        <v>1643.9</v>
+        <v>3451.53</v>
       </c>
       <c r="E18" s="2">
-        <v>-0.26</v>
+        <v>-0.3</v>
       </c>
       <c r="F18" s="2">
-        <v>-0.26</v>
+        <v>-1.03</v>
       </c>
       <c r="G18" s="2">
-        <v>3.83</v>
+        <v>-2</v>
       </c>
       <c r="H18" s="2">
-        <v>13.79</v>
+        <v>-1.18</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>1467.11</v>
+        <v>3495.25</v>
       </c>
       <c r="K18" s="1">
-        <v>1612.22</v>
+        <v>3476.87</v>
       </c>
       <c r="L18" s="1">
-        <v>1572.07</v>
+        <v>3532.03</v>
       </c>
       <c r="M18" s="3">
-        <v>21.7</v>
+        <v>-19.7</v>
       </c>
       <c r="N18" s="3">
-        <v>12.12</v>
+        <v>-16.41</v>
       </c>
       <c r="O18" s="3">
-        <v>37.41</v>
+        <v>1.42</v>
       </c>
       <c r="P18" s="3">
-        <v>32.59</v>
+        <v>15.15</v>
       </c>
       <c r="Q18" s="3">
-        <v>-68.54</v>
+        <v>117.46</v>
       </c>
       <c r="R18" s="3">
-        <v>-104.6</v>
+        <v>141.63</v>
       </c>
       <c r="S18" s="3">
-        <v>61.69</v>
-      </c>
-      <c r="T18" t="str">
+        <v>30.33</v>
+      </c>
+      <c r="T18" s="3">
+        <v>15.28</v>
+      </c>
+      <c r="U18" s="3">
+        <v>39.06</v>
+      </c>
+      <c r="V18" s="3">
+        <v>31.32</v>
+      </c>
+      <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="str">
         <v/>
       </c>
     </row>
@@ -1526,60 +1796,75 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="C19" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="D19" s="1">
-        <v>53699.95</v>
+        <v>1440.45</v>
       </c>
       <c r="E19" s="2">
-        <v>-0.27</v>
+        <v>-0.35</v>
       </c>
       <c r="F19" s="2">
-        <v>-0.27</v>
+        <v>-0.45</v>
       </c>
       <c r="G19" s="2">
-        <v>-0.7</v>
+        <v>-0.92</v>
       </c>
       <c r="H19" s="2">
-        <v>6.74</v>
+        <v>1.11</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>52179.54</v>
+        <v>1440.86</v>
       </c>
       <c r="K19" s="1">
-        <v>54484.23</v>
+        <v>1447.48</v>
       </c>
       <c r="L19" s="1">
-        <v>55763.52</v>
+        <v>1457.8</v>
       </c>
       <c r="M19" s="3">
-        <v>-379.62</v>
+        <v>-3.84</v>
       </c>
       <c r="N19" s="3">
-        <v>-291.78</v>
+        <v>-2.97</v>
       </c>
       <c r="O19" s="3">
-        <v>790.27</v>
+        <v>3.8</v>
       </c>
       <c r="P19" s="3">
-        <v>1172.96</v>
+        <v>7.24</v>
       </c>
       <c r="Q19" s="3">
-        <v>3756.85</v>
+        <v>28.73</v>
       </c>
       <c r="R19" s="3">
-        <v>3900.21</v>
+        <v>28.47</v>
       </c>
       <c r="S19" s="3">
-        <v>40.27</v>
-      </c>
-      <c r="T19" t="str">
+        <v>18.6</v>
+      </c>
+      <c r="T19" s="3">
+        <v>18.03</v>
+      </c>
+      <c r="U19" s="3">
+        <v>75.39</v>
+      </c>
+      <c r="V19" s="3">
+        <v>34.98</v>
+      </c>
+      <c r="W19" s="3">
+        <v>0</v>
+      </c>
+      <c r="X19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="str">
         <v/>
       </c>
     </row>
@@ -1588,60 +1873,75 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="C20" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="D20" s="1">
-        <v>3294.03</v>
+        <v>11280.35</v>
       </c>
       <c r="E20" s="2">
-        <v>-0.28</v>
+        <v>-0.36</v>
       </c>
       <c r="F20" s="2">
-        <v>-0.28</v>
+        <v>-2.18</v>
       </c>
       <c r="G20" s="2">
-        <v>-0.83</v>
+        <v>1.21</v>
       </c>
       <c r="H20" s="2">
-        <v>1.61</v>
+        <v>-15.03</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>3294.67</v>
+        <v>12171.5</v>
       </c>
       <c r="K20" s="1">
-        <v>3302.34</v>
+        <v>11317.59</v>
       </c>
       <c r="L20" s="1">
-        <v>3353.89</v>
+        <v>11538.09</v>
       </c>
       <c r="M20" s="3">
-        <v>-17.29</v>
+        <v>-43.96</v>
       </c>
       <c r="N20" s="3">
-        <v>-16.97</v>
+        <v>-81.17</v>
       </c>
       <c r="O20" s="3">
-        <v>8.25</v>
+        <v>-267.67</v>
       </c>
       <c r="P20" s="3">
-        <v>21.63</v>
+        <v>-236.36</v>
       </c>
       <c r="Q20" s="3">
-        <v>137.13</v>
+        <v>-133.65</v>
       </c>
       <c r="R20" s="3">
-        <v>154.03</v>
+        <v>113.71</v>
       </c>
       <c r="S20" s="3">
-        <v>35.31</v>
-      </c>
-      <c r="T20" t="str">
+        <v>46.06</v>
+      </c>
+      <c r="T20" s="3">
+        <v>16.2</v>
+      </c>
+      <c r="U20" s="3">
+        <v>27.76</v>
+      </c>
+      <c r="V20" s="3">
+        <v>29.04</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="str">
         <v/>
       </c>
     </row>
@@ -1650,60 +1950,75 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>NIFTY</v>
       </c>
       <c r="C21" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>NIFTY</v>
       </c>
       <c r="D21" s="1">
-        <v>52153.85</v>
+        <v>22600</v>
       </c>
       <c r="E21" s="2">
-        <v>-0.3</v>
+        <v>-0.39</v>
       </c>
       <c r="F21" s="2">
-        <v>-0.3</v>
+        <v>-2.36</v>
       </c>
       <c r="G21" s="2">
-        <v>-1.4</v>
+        <v>-0.09</v>
       </c>
       <c r="H21" s="2">
-        <v>-1.05</v>
+        <v>-13.51</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
       </c>
       <c r="J21" s="1">
-        <v>52561.74</v>
+        <v>24118.84</v>
       </c>
       <c r="K21" s="1">
-        <v>52721.92</v>
+        <v>22747.25</v>
       </c>
       <c r="L21" s="1">
-        <v>54265.33</v>
+        <v>23403.72</v>
       </c>
       <c r="M21" s="3">
-        <v>-513.88</v>
+        <v>-169.46</v>
       </c>
       <c r="N21" s="3">
-        <v>-448.09</v>
+        <v>-222.63</v>
       </c>
       <c r="O21" s="3">
-        <v>119.23</v>
+        <v>-401.05</v>
       </c>
       <c r="P21" s="3">
-        <v>462.24</v>
+        <v>-278.18</v>
       </c>
       <c r="Q21" s="3">
-        <v>-663.92</v>
+        <v>177.18</v>
       </c>
       <c r="R21" s="3">
-        <v>-1104.48</v>
+        <v>596.29</v>
       </c>
       <c r="S21" s="3">
-        <v>39</v>
-      </c>
-      <c r="T21" t="str">
+        <v>42.39</v>
+      </c>
+      <c r="T21" s="3">
+        <v>13.43</v>
+      </c>
+      <c r="U21" s="3">
+        <v>28.3</v>
+      </c>
+      <c r="V21" s="3">
+        <v>36.33</v>
+      </c>
+      <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="str">
         <v/>
       </c>
     </row>
@@ -1712,60 +2027,75 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="C22" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="D22" s="1">
-        <v>68695.85</v>
+        <v>1300.19</v>
       </c>
       <c r="E22" s="2">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="F22" s="2">
-        <v>-0.42</v>
+        <v>-0.58</v>
       </c>
       <c r="G22" s="2">
-        <v>-1.51</v>
+        <v>-1.17</v>
       </c>
       <c r="H22" s="2">
-        <v>-0.96</v>
+        <v>0.16</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
       </c>
       <c r="J22" s="1">
-        <v>70047.92</v>
+        <v>1308</v>
       </c>
       <c r="K22" s="1">
-        <v>68969.8</v>
+        <v>1308.25</v>
       </c>
       <c r="L22" s="1">
-        <v>71956.6</v>
+        <v>1321.23</v>
       </c>
       <c r="M22" s="3">
-        <v>-936.03</v>
+        <v>-4.72</v>
       </c>
       <c r="N22" s="3">
-        <v>-988.8</v>
+        <v>-3.8</v>
       </c>
       <c r="O22" s="3">
-        <v>-115.29</v>
+        <v>1.7</v>
       </c>
       <c r="P22" s="3">
-        <v>595.35</v>
+        <v>5.61</v>
       </c>
       <c r="Q22" s="3">
-        <v>2746.93</v>
+        <v>23.49</v>
       </c>
       <c r="R22" s="3">
-        <v>3199.01</v>
+        <v>24.11</v>
       </c>
       <c r="S22" s="3">
-        <v>39.51</v>
-      </c>
-      <c r="T22" t="str">
+        <v>16.61</v>
+      </c>
+      <c r="T22" s="3">
+        <v>17.75</v>
+      </c>
+      <c r="U22" s="3">
+        <v>80.17</v>
+      </c>
+      <c r="V22" s="3">
+        <v>39.45</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="str">
         <v/>
       </c>
     </row>
@@ -1774,60 +2104,75 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="C23" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="D23" s="1">
-        <v>12066.4</v>
+        <v>18563.55</v>
       </c>
       <c r="E23" s="2">
-        <v>-0.55</v>
+        <v>-0.42</v>
       </c>
       <c r="F23" s="2">
-        <v>-0.55</v>
+        <v>-1.88</v>
       </c>
       <c r="G23" s="2">
-        <v>-5.44</v>
+        <v>-1.18</v>
       </c>
       <c r="H23" s="2">
-        <v>8.05</v>
+        <v>-12.15</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>12472.86</v>
+        <v>19854.88</v>
       </c>
       <c r="K23" s="1">
-        <v>12170.45</v>
+        <v>18709.42</v>
       </c>
       <c r="L23" s="1">
-        <v>12892.37</v>
+        <v>19462.17</v>
       </c>
       <c r="M23" s="3">
-        <v>-269.43</v>
+        <v>-216.15</v>
       </c>
       <c r="N23" s="3">
-        <v>-239.21</v>
+        <v>-252.08</v>
       </c>
       <c r="O23" s="3">
-        <v>31.91</v>
+        <v>-309.66</v>
       </c>
       <c r="P23" s="3">
-        <v>212.27</v>
+        <v>-147.47</v>
       </c>
       <c r="Q23" s="3">
-        <v>1154.3</v>
+        <v>746.15</v>
       </c>
       <c r="R23" s="3">
-        <v>1133.55</v>
+        <v>1109.05</v>
       </c>
       <c r="S23" s="3">
-        <v>37.88</v>
-      </c>
-      <c r="T23" t="str">
+        <v>37.55</v>
+      </c>
+      <c r="T23" s="3">
+        <v>9.64</v>
+      </c>
+      <c r="U23" s="3">
+        <v>28.24</v>
+      </c>
+      <c r="V23" s="3">
+        <v>48.95</v>
+      </c>
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="str">
         <v/>
       </c>
     </row>
@@ -1836,60 +2181,75 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>NIFTYCPSE</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="C24" t="str">
-        <v>NIFTYCPSE</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="D24" s="1">
-        <v>6031.35</v>
+        <v>8554.25</v>
       </c>
       <c r="E24" s="2">
-        <v>-0.56</v>
+        <v>-0.44</v>
       </c>
       <c r="F24" s="2">
-        <v>-0.56</v>
+        <v>-1.96</v>
       </c>
       <c r="G24" s="2">
-        <v>-3.17</v>
+        <v>-2.06</v>
       </c>
       <c r="H24" s="2">
-        <v>-5.25</v>
+        <v>-11.04</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <v>6748.38</v>
+        <v>9221.18</v>
       </c>
       <c r="K24" s="1">
-        <v>6081.57</v>
+        <v>8630.32</v>
       </c>
       <c r="L24" s="1">
-        <v>6324.49</v>
+        <v>8996.44</v>
       </c>
       <c r="M24" s="3">
-        <v>-92.33</v>
+        <v>-113.42</v>
       </c>
       <c r="N24" s="3">
-        <v>-91.23</v>
+        <v>-126.4</v>
       </c>
       <c r="O24" s="3">
-        <v>-197.33</v>
+        <v>-167.26</v>
       </c>
       <c r="P24" s="3">
-        <v>-145.89</v>
+        <v>-80.58</v>
       </c>
       <c r="Q24" s="3">
-        <v>235.3</v>
+        <v>264.02</v>
       </c>
       <c r="R24" s="3">
-        <v>404.21</v>
+        <v>432.19</v>
       </c>
       <c r="S24" s="3">
-        <v>34.75</v>
-      </c>
-      <c r="T24" t="str">
+        <v>37.31</v>
+      </c>
+      <c r="T24" s="3">
+        <v>13.74</v>
+      </c>
+      <c r="U24" s="3">
+        <v>31.24</v>
+      </c>
+      <c r="V24" s="3">
+        <v>42.52</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="str">
         <v/>
       </c>
     </row>
@@ -1898,60 +2258,75 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="C25" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="D25" s="1">
-        <v>28924.95</v>
+        <v>7283.05</v>
       </c>
       <c r="E25" s="2">
-        <v>-0.57</v>
+        <v>-0.44</v>
       </c>
       <c r="F25" s="2">
-        <v>-0.57</v>
+        <v>-2.36</v>
       </c>
       <c r="G25" s="2">
-        <v>-2.01</v>
+        <v>2.92</v>
       </c>
       <c r="H25" s="2">
-        <v>-7.14</v>
+        <v>-3.69</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <v>30414.07</v>
+        <v>7333.45</v>
       </c>
       <c r="K25" s="1">
-        <v>29261.63</v>
+        <v>7294.32</v>
       </c>
       <c r="L25" s="1">
-        <v>30395.42</v>
+        <v>7395.36</v>
       </c>
       <c r="M25" s="3">
-        <v>-375.34</v>
+        <v>-3.25</v>
       </c>
       <c r="N25" s="3">
-        <v>-355.55</v>
+        <v>-32.05</v>
       </c>
       <c r="O25" s="3">
-        <v>-301.38</v>
+        <v>-4.23</v>
       </c>
       <c r="P25" s="3">
-        <v>-78.74</v>
+        <v>30.63</v>
       </c>
       <c r="Q25" s="3">
-        <v>1491.04</v>
+        <v>466.66</v>
       </c>
       <c r="R25" s="3">
-        <v>2007.93</v>
+        <v>551.54</v>
       </c>
       <c r="S25" s="3">
-        <v>36.72</v>
-      </c>
-      <c r="T25" t="str">
+        <v>49.44</v>
+      </c>
+      <c r="T25" s="3">
+        <v>19.57</v>
+      </c>
+      <c r="U25" s="3">
+        <v>26.75</v>
+      </c>
+      <c r="V25" s="3">
+        <v>27.99</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="str">
         <v/>
       </c>
     </row>
@@ -1960,60 +2335,75 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="C26" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="D26" s="1">
-        <v>5598.5</v>
+        <v>1255.18</v>
       </c>
       <c r="E26" s="2">
-        <v>-0.59</v>
+        <v>-0.5</v>
       </c>
       <c r="F26" s="2">
-        <v>-0.59</v>
+        <v>-0.72</v>
       </c>
       <c r="G26" s="2">
-        <v>2.3</v>
+        <v>-1.42</v>
       </c>
       <c r="H26" s="2">
-        <v>-12.32</v>
+        <v>-0.5</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>5960.48</v>
+        <v>1268.31</v>
       </c>
       <c r="K26" s="1">
-        <v>5529.85</v>
+        <v>1264.42</v>
       </c>
       <c r="L26" s="1">
-        <v>5706.91</v>
+        <v>1279.52</v>
       </c>
       <c r="M26" s="3">
-        <v>-39.72</v>
+        <v>-5.57</v>
       </c>
       <c r="N26" s="3">
-        <v>-71.03</v>
+        <v>-4.46</v>
       </c>
       <c r="O26" s="3">
-        <v>-115.29</v>
+        <v>0.63</v>
       </c>
       <c r="P26" s="3">
-        <v>-95.05</v>
+        <v>4.83</v>
       </c>
       <c r="Q26" s="3">
-        <v>28.8</v>
+        <v>20.72</v>
       </c>
       <c r="R26" s="3">
-        <v>140.24</v>
+        <v>21.84</v>
       </c>
       <c r="S26" s="3">
-        <v>52.38</v>
-      </c>
-      <c r="T26" t="str">
+        <v>15.49</v>
+      </c>
+      <c r="T26" s="3">
+        <v>15.75</v>
+      </c>
+      <c r="U26" s="3">
+        <v>81.79</v>
+      </c>
+      <c r="V26" s="3">
+        <v>42.25</v>
+      </c>
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="str">
         <v/>
       </c>
     </row>
@@ -2022,60 +2412,75 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>CNXENERGY</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="C27" t="str">
-        <v>CNXENERGY</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="D27" s="1">
-        <v>35974.45</v>
+        <v>3753.2</v>
       </c>
       <c r="E27" s="2">
-        <v>-0.6</v>
+        <v>-0.55</v>
       </c>
       <c r="F27" s="2">
-        <v>-0.6</v>
+        <v>-2.91</v>
       </c>
       <c r="G27" s="2">
-        <v>-1.81</v>
+        <v>-0.77</v>
       </c>
       <c r="H27" s="2">
-        <v>1.84</v>
+        <v>-13.78</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>37721.97</v>
+        <v>4031.76</v>
       </c>
       <c r="K27" s="1">
-        <v>36241.05</v>
+        <v>3789.4</v>
       </c>
       <c r="L27" s="1">
-        <v>37551.17</v>
+        <v>3917.9</v>
       </c>
       <c r="M27" s="3">
-        <v>-461.17</v>
+        <v>-35.3</v>
       </c>
       <c r="N27" s="3">
-        <v>-471.75</v>
+        <v>-43.02</v>
       </c>
       <c r="O27" s="3">
-        <v>-476.48</v>
+        <v>-69.09</v>
       </c>
       <c r="P27" s="3">
-        <v>-64.34</v>
+        <v>-43.1</v>
       </c>
       <c r="Q27" s="3">
-        <v>1005.91</v>
+        <v>123.09</v>
       </c>
       <c r="R27" s="3">
-        <v>1242.5</v>
+        <v>206.14</v>
       </c>
       <c r="S27" s="3">
-        <v>37.17</v>
-      </c>
-      <c r="T27" t="str">
+        <v>40.11</v>
+      </c>
+      <c r="T27" s="3">
+        <v>14.07</v>
+      </c>
+      <c r="U27" s="3">
+        <v>31.41</v>
+      </c>
+      <c r="V27" s="3">
+        <v>37.56</v>
+      </c>
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="str">
         <v/>
       </c>
     </row>
@@ -2084,60 +2489,75 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="C28" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="D28" s="1">
-        <v>9525.85</v>
+        <v>24862.3</v>
       </c>
       <c r="E28" s="2">
         <v>-0.6</v>
       </c>
       <c r="F28" s="2">
-        <v>-0.6</v>
+        <v>-3.52</v>
       </c>
       <c r="G28" s="2">
-        <v>-1.11</v>
+        <v>-5.44</v>
       </c>
       <c r="H28" s="2">
-        <v>10.69</v>
+        <v>-11.8</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>8973.96</v>
+        <v>26911.8</v>
       </c>
       <c r="K28" s="1">
-        <v>9620.27</v>
+        <v>25282.21</v>
       </c>
       <c r="L28" s="1">
-        <v>9837.16</v>
+        <v>27168.61</v>
       </c>
       <c r="M28" s="3">
-        <v>-70.49</v>
+        <v>-551.37</v>
       </c>
       <c r="N28" s="3">
-        <v>-62.77</v>
+        <v>-601.04</v>
       </c>
       <c r="O28" s="3">
-        <v>219.67</v>
+        <v>-308.95</v>
       </c>
       <c r="P28" s="3">
-        <v>298.45</v>
+        <v>91.11</v>
       </c>
       <c r="Q28" s="3">
-        <v>750.26</v>
+        <v>1449.2</v>
       </c>
       <c r="R28" s="3">
-        <v>721.68</v>
+        <v>1805.34</v>
       </c>
       <c r="S28" s="3">
-        <v>40.87</v>
-      </c>
-      <c r="T28" t="str">
+        <v>34.23</v>
+      </c>
+      <c r="T28" s="3">
+        <v>10.26</v>
+      </c>
+      <c r="U28" s="3">
+        <v>36.28</v>
+      </c>
+      <c r="V28" s="3">
+        <v>55.28</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="str">
         <v/>
       </c>
     </row>
@@ -2146,60 +2566,75 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="C29" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="D29" s="1">
-        <v>9190.6</v>
+        <v>10380.55</v>
       </c>
       <c r="E29" s="2">
-        <v>-0.61</v>
+        <v>-0.62</v>
       </c>
       <c r="F29" s="2">
-        <v>-0.61</v>
+        <v>-1.67</v>
       </c>
       <c r="G29" s="2">
-        <v>-1.81</v>
+        <v>-2.2</v>
       </c>
       <c r="H29" s="2">
-        <v>-6.73</v>
+        <v>-15.13</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <v>9995.43</v>
+        <v>11291.49</v>
       </c>
       <c r="K29" s="1">
-        <v>9232.39</v>
+        <v>10485.64</v>
       </c>
       <c r="L29" s="1">
-        <v>9571.2</v>
+        <v>10870.59</v>
       </c>
       <c r="M29" s="3">
-        <v>-116.71</v>
+        <v>-120.55</v>
       </c>
       <c r="N29" s="3">
-        <v>-127.3</v>
+        <v>-134.21</v>
       </c>
       <c r="O29" s="3">
-        <v>-220.01</v>
+        <v>-230.43</v>
       </c>
       <c r="P29" s="3">
-        <v>-145.27</v>
+        <v>-161.29</v>
       </c>
       <c r="Q29" s="3">
-        <v>800.38</v>
+        <v>68.02</v>
       </c>
       <c r="R29" s="3">
-        <v>1093.5</v>
+        <v>278.4</v>
       </c>
       <c r="S29" s="3">
-        <v>39.06</v>
-      </c>
-      <c r="T29" t="str">
+        <v>36.85</v>
+      </c>
+      <c r="T29" s="3">
+        <v>16.24</v>
+      </c>
+      <c r="U29" s="3">
+        <v>33.12</v>
+      </c>
+      <c r="V29" s="3">
+        <v>31.51</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="str">
         <v/>
       </c>
     </row>
@@ -2208,60 +2643,75 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="C30" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="D30" s="1">
-        <v>25046.05</v>
+        <v>30366.85</v>
       </c>
       <c r="E30" s="2">
-        <v>-0.63</v>
+        <v>-0.64</v>
       </c>
       <c r="F30" s="2">
-        <v>-0.63</v>
+        <v>-2.67</v>
       </c>
       <c r="G30" s="2">
-        <v>-1.37</v>
+        <v>-1.74</v>
       </c>
       <c r="H30" s="2">
-        <v>0.24</v>
+        <v>-8.89</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>25476.47</v>
+        <v>32337.72</v>
       </c>
       <c r="K30" s="1">
-        <v>25301.13</v>
+        <v>30731.31</v>
       </c>
       <c r="L30" s="1">
-        <v>26266.15</v>
+        <v>31919.58</v>
       </c>
       <c r="M30" s="3">
-        <v>-308.66</v>
+        <v>-352.25</v>
       </c>
       <c r="N30" s="3">
-        <v>-307.25</v>
+        <v>-393.41</v>
       </c>
       <c r="O30" s="3">
-        <v>-1.77</v>
+        <v>-406.6</v>
       </c>
       <c r="P30" s="3">
-        <v>226.74</v>
+        <v>-118.39</v>
       </c>
       <c r="Q30" s="3">
-        <v>111.86</v>
+        <v>1807.56</v>
       </c>
       <c r="R30" s="3">
-        <v>-46.08</v>
+        <v>2369</v>
       </c>
       <c r="S30" s="3">
-        <v>38.56</v>
-      </c>
-      <c r="T30" t="str">
+        <v>37.19</v>
+      </c>
+      <c r="T30" s="3">
+        <v>11.25</v>
+      </c>
+      <c r="U30" s="3">
+        <v>32.05</v>
+      </c>
+      <c r="V30" s="3">
+        <v>44.89</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="str">
         <v/>
       </c>
     </row>
@@ -2270,60 +2720,75 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="C31" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="D31" s="1">
-        <v>15078.3</v>
+        <v>24348.8</v>
       </c>
       <c r="E31" s="2">
-        <v>-0.63</v>
+        <v>-0.68</v>
       </c>
       <c r="F31" s="2">
-        <v>-0.63</v>
+        <v>-2.27</v>
       </c>
       <c r="G31" s="2">
-        <v>-2.43</v>
+        <v>-3.45</v>
       </c>
       <c r="H31" s="2">
-        <v>-2.17</v>
+        <v>-10.08</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>15633.9</v>
+        <v>26241.6</v>
       </c>
       <c r="K31" s="1">
-        <v>15166.49</v>
+        <v>24699.33</v>
       </c>
       <c r="L31" s="1">
-        <v>15964.18</v>
+        <v>26060.84</v>
       </c>
       <c r="M31" s="3">
-        <v>-254.6</v>
+        <v>-437.51</v>
       </c>
       <c r="N31" s="3">
-        <v>-263.86</v>
+        <v>-449.38</v>
       </c>
       <c r="O31" s="3">
-        <v>-74.41</v>
+        <v>-363.36</v>
       </c>
       <c r="P31" s="3">
-        <v>105.38</v>
+        <v>-70.73</v>
       </c>
       <c r="Q31" s="3">
-        <v>1265.85</v>
+        <v>1128.35</v>
       </c>
       <c r="R31" s="3">
-        <v>1447.65</v>
+        <v>1592.4</v>
       </c>
       <c r="S31" s="3">
-        <v>36.81</v>
-      </c>
-      <c r="T31" t="str">
+        <v>29.59</v>
+      </c>
+      <c r="T31" s="3">
+        <v>8.42</v>
+      </c>
+      <c r="U31" s="3">
+        <v>34.6</v>
+      </c>
+      <c r="V31" s="3">
+        <v>52.1</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="str">
         <v/>
       </c>
     </row>
@@ -2332,60 +2797,75 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTY100</v>
       </c>
       <c r="C32" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTY100</v>
       </c>
       <c r="D32" s="1">
-        <v>55488.1</v>
+        <v>23465.05</v>
       </c>
       <c r="E32" s="2">
-        <v>-0.64</v>
+        <v>-0.73</v>
       </c>
       <c r="F32" s="2">
-        <v>-0.64</v>
+        <v>-2.77</v>
       </c>
       <c r="G32" s="2">
-        <v>1.57</v>
+        <v>-1.14</v>
       </c>
       <c r="H32" s="2">
-        <v>-6.87</v>
+        <v>-12.08</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>56910.46</v>
+        <v>25023.62</v>
       </c>
       <c r="K32" s="1">
-        <v>55393.42</v>
+        <v>23729.98</v>
       </c>
       <c r="L32" s="1">
-        <v>56433.5</v>
+        <v>24513.28</v>
       </c>
       <c r="M32" s="3">
-        <v>-244.5</v>
+        <v>-219.95</v>
       </c>
       <c r="N32" s="3">
-        <v>-408.33</v>
+        <v>-255.84</v>
       </c>
       <c r="O32" s="3">
-        <v>-306.23</v>
+        <v>-362.29</v>
       </c>
       <c r="P32" s="3">
-        <v>-90.13</v>
+        <v>-199.92</v>
       </c>
       <c r="Q32" s="3">
-        <v>1705.86</v>
+        <v>310.24</v>
       </c>
       <c r="R32" s="3">
-        <v>2296.75</v>
+        <v>704.22</v>
       </c>
       <c r="S32" s="3">
-        <v>48.25</v>
-      </c>
-      <c r="T32" t="str">
+        <v>38.79</v>
+      </c>
+      <c r="T32" s="3">
+        <v>12.05</v>
+      </c>
+      <c r="U32" s="3">
+        <v>32.28</v>
+      </c>
+      <c r="V32" s="3">
+        <v>43.23</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="str">
         <v/>
       </c>
     </row>
@@ -2394,60 +2874,75 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="C33" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="D33" s="1">
-        <v>24753.65</v>
+        <v>15814</v>
       </c>
       <c r="E33" s="2">
-        <v>-0.64</v>
+        <v>-0.77</v>
       </c>
       <c r="F33" s="2">
-        <v>-0.64</v>
+        <v>-4.77</v>
       </c>
       <c r="G33" s="2">
-        <v>-1.85</v>
+        <v>-0.61</v>
       </c>
       <c r="H33" s="2">
-        <v>-8.58</v>
+        <v>-28.11</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>26278.33</v>
+        <v>18368.85</v>
       </c>
       <c r="K33" s="1">
-        <v>24891.72</v>
+        <v>16039.25</v>
       </c>
       <c r="L33" s="1">
-        <v>26249.17</v>
+        <v>17081.63</v>
       </c>
       <c r="M33" s="3">
-        <v>-435.9</v>
+        <v>-276.62</v>
       </c>
       <c r="N33" s="3">
-        <v>-463.99</v>
+        <v>-352.76</v>
       </c>
       <c r="O33" s="3">
-        <v>-331.06</v>
+        <v>-691.79</v>
       </c>
       <c r="P33" s="3">
-        <v>-64.27</v>
+        <v>-515.15</v>
       </c>
       <c r="Q33" s="3">
-        <v>1160.65</v>
+        <v>247.62</v>
       </c>
       <c r="R33" s="3">
-        <v>1598.86</v>
+        <v>923.32</v>
       </c>
       <c r="S33" s="3">
-        <v>35.34</v>
-      </c>
-      <c r="T33" t="str">
+        <v>41.48</v>
+      </c>
+      <c r="T33" s="3">
+        <v>13.13</v>
+      </c>
+      <c r="U33" s="3">
+        <v>28.86</v>
+      </c>
+      <c r="V33" s="3">
+        <v>38.28</v>
+      </c>
+      <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="str">
         <v/>
       </c>
     </row>
@@ -2456,60 +2951,75 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>CNXPHARMA</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="C34" t="str">
-        <v>CNXPHARMA</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="D34" s="1">
-        <v>25615</v>
+        <v>26656.3</v>
       </c>
       <c r="E34" s="2">
-        <v>-0.65</v>
+        <v>-0.78</v>
       </c>
       <c r="F34" s="2">
-        <v>-0.65</v>
+        <v>-3.77</v>
       </c>
       <c r="G34" s="2">
-        <v>-3.11</v>
+        <v>-0.15</v>
       </c>
       <c r="H34" s="2">
-        <v>12.72</v>
+        <v>-7.19</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>24332</v>
+        <v>27362.11</v>
       </c>
       <c r="K34" s="1">
-        <v>25961.9</v>
+        <v>27050.18</v>
       </c>
       <c r="L34" s="1">
-        <v>26504.8</v>
+        <v>27268.91</v>
       </c>
       <c r="M34" s="3">
-        <v>-232.47</v>
+        <v>-60.86</v>
       </c>
       <c r="N34" s="3">
-        <v>-146.16</v>
+        <v>-42.96</v>
       </c>
       <c r="O34" s="3">
-        <v>600.81</v>
+        <v>-53.67</v>
       </c>
       <c r="P34" s="3">
-        <v>797.18</v>
+        <v>14.75</v>
       </c>
       <c r="Q34" s="3">
-        <v>1776.15</v>
+        <v>629.95</v>
       </c>
       <c r="R34" s="3">
-        <v>1607.67</v>
+        <v>871.88</v>
       </c>
       <c r="S34" s="3">
-        <v>36.7</v>
-      </c>
-      <c r="T34" t="str">
+        <v>41.15</v>
+      </c>
+      <c r="T34" s="3">
+        <v>16.31</v>
+      </c>
+      <c r="U34" s="3">
+        <v>26.01</v>
+      </c>
+      <c r="V34" s="3">
+        <v>14.86</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="str">
         <v/>
       </c>
     </row>
@@ -2518,60 +3028,75 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="C35" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="D35" s="1">
-        <v>9039.85</v>
+        <v>10365.6</v>
       </c>
       <c r="E35" s="2">
-        <v>-0.66</v>
+        <v>-0.79</v>
       </c>
       <c r="F35" s="2">
-        <v>-0.66</v>
+        <v>-4.79</v>
       </c>
       <c r="G35" s="2">
-        <v>-2.9</v>
+        <v>-0.67</v>
       </c>
       <c r="H35" s="2">
-        <v>-5</v>
+        <v>-29.49</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>9765.12</v>
+        <v>12171.86</v>
       </c>
       <c r="K35" s="1">
-        <v>9068.56</v>
+        <v>10516.32</v>
       </c>
       <c r="L35" s="1">
-        <v>9541.65</v>
+        <v>11205.53</v>
       </c>
       <c r="M35" s="3">
-        <v>-162.81</v>
+        <v>-184.1</v>
       </c>
       <c r="N35" s="3">
-        <v>-170.28</v>
+        <v>-233.93</v>
       </c>
       <c r="O35" s="3">
-        <v>-173.46</v>
+        <v>-499.42</v>
       </c>
       <c r="P35" s="3">
-        <v>-64.9</v>
+        <v>-388.23</v>
       </c>
       <c r="Q35" s="3">
-        <v>396.78</v>
+        <v>-25.75</v>
       </c>
       <c r="R35" s="3">
-        <v>509.72</v>
+        <v>422.27</v>
       </c>
       <c r="S35" s="3">
-        <v>38.35</v>
-      </c>
-      <c r="T35" t="str">
+        <v>41.34</v>
+      </c>
+      <c r="T35" s="3">
+        <v>13.03</v>
+      </c>
+      <c r="U35" s="3">
+        <v>28.92</v>
+      </c>
+      <c r="V35" s="3">
+        <v>38.66</v>
+      </c>
+      <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="str">
         <v/>
       </c>
     </row>
@@ -2580,60 +3105,75 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="C36" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="D36" s="1">
-        <v>32625.05</v>
+        <v>15387</v>
       </c>
       <c r="E36" s="2">
-        <v>-0.68</v>
+        <v>-0.83</v>
       </c>
       <c r="F36" s="2">
-        <v>-0.68</v>
+        <v>-1.89</v>
       </c>
       <c r="G36" s="2">
-        <v>-0.72</v>
+        <v>-4.65</v>
       </c>
       <c r="H36" s="2">
-        <v>-3.92</v>
+        <v>5.1</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>33702.89</v>
+        <v>15444.88</v>
       </c>
       <c r="K36" s="1">
-        <v>32686.26</v>
+        <v>15655.56</v>
       </c>
       <c r="L36" s="1">
-        <v>34069.02</v>
+        <v>16324.25</v>
       </c>
       <c r="M36" s="3">
-        <v>-413.87</v>
+        <v>-264.42</v>
       </c>
       <c r="N36" s="3">
-        <v>-478.8</v>
+        <v>-219.88</v>
       </c>
       <c r="O36" s="3">
-        <v>-214.67</v>
+        <v>161.13</v>
       </c>
       <c r="P36" s="3">
-        <v>103.15</v>
+        <v>338.5</v>
       </c>
       <c r="Q36" s="3">
-        <v>2028.91</v>
+        <v>968.83</v>
       </c>
       <c r="R36" s="3">
-        <v>2435.7</v>
+        <v>992.24</v>
       </c>
       <c r="S36" s="3">
-        <v>40.77</v>
-      </c>
-      <c r="T36" t="str">
+        <v>28.44</v>
+      </c>
+      <c r="T36" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="U36" s="3">
+        <v>31.18</v>
+      </c>
+      <c r="V36" s="3">
+        <v>41.01</v>
+      </c>
+      <c r="W36" s="3">
+        <v>0</v>
+      </c>
+      <c r="X36" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="str">
         <v/>
       </c>
     </row>
@@ -2642,60 +3182,75 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="C37" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="D37" s="1">
-        <v>8666.5</v>
+        <v>4647.95</v>
       </c>
       <c r="E37" s="2">
-        <v>-0.68</v>
+        <v>-0.86</v>
       </c>
       <c r="F37" s="2">
-        <v>-0.68</v>
+        <v>-2.95</v>
       </c>
       <c r="G37" s="2">
         <v>-0.77</v>
       </c>
       <c r="H37" s="2">
-        <v>-9.88</v>
+        <v>-10.29</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>9235.48</v>
+        <v>4912.71</v>
       </c>
       <c r="K37" s="1">
-        <v>8665.13</v>
+        <v>4697.8</v>
       </c>
       <c r="L37" s="1">
-        <v>9047.92</v>
+        <v>4858.01</v>
       </c>
       <c r="M37" s="3">
-        <v>-121.13</v>
+        <v>-41.95</v>
       </c>
       <c r="N37" s="3">
-        <v>-138.2</v>
+        <v>-52.54</v>
       </c>
       <c r="O37" s="3">
-        <v>-158.3</v>
+        <v>-54.23</v>
       </c>
       <c r="P37" s="3">
-        <v>-78.79</v>
+        <v>-17.96</v>
       </c>
       <c r="Q37" s="3">
-        <v>272.98</v>
+        <v>216.38</v>
       </c>
       <c r="R37" s="3">
-        <v>433.98</v>
+        <v>298.7</v>
       </c>
       <c r="S37" s="3">
-        <v>42.27</v>
-      </c>
-      <c r="T37" t="str">
+        <v>39.8</v>
+      </c>
+      <c r="T37" s="3">
+        <v>14.17</v>
+      </c>
+      <c r="U37" s="3">
+        <v>32.25</v>
+      </c>
+      <c r="V37" s="3">
+        <v>37.43</v>
+      </c>
+      <c r="W37" s="3">
+        <v>0</v>
+      </c>
+      <c r="X37" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="str">
         <v/>
       </c>
     </row>
@@ -2704,60 +3259,75 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>NIFTYAUTO</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="C38" t="str">
-        <v>NIFTYAUTO</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="D38" s="1">
-        <v>25591.25</v>
+        <v>5878.45</v>
       </c>
       <c r="E38" s="2">
-        <v>-0.69</v>
+        <v>-0.9</v>
       </c>
       <c r="F38" s="2">
-        <v>-0.69</v>
+        <v>-3.08</v>
       </c>
       <c r="G38" s="2">
-        <v>-2.67</v>
+        <v>-5.62</v>
       </c>
       <c r="H38" s="2">
-        <v>-9.22</v>
+        <v>-7.65</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
       </c>
       <c r="J38" s="1">
-        <v>26954.81</v>
+        <v>6742.77</v>
       </c>
       <c r="K38" s="1">
-        <v>25514.14</v>
+        <v>6010.92</v>
       </c>
       <c r="L38" s="1">
-        <v>27441.73</v>
+        <v>6291.9</v>
       </c>
       <c r="M38" s="3">
-        <v>-557.94</v>
+        <v>-105.7</v>
       </c>
       <c r="N38" s="3">
-        <v>-651.27</v>
+        <v>-95.71</v>
       </c>
       <c r="O38" s="3">
-        <v>-250.8</v>
+        <v>-209.53</v>
       </c>
       <c r="P38" s="3">
-        <v>102.74</v>
+        <v>-148.33</v>
       </c>
       <c r="Q38" s="3">
-        <v>1507.35</v>
+        <v>223.11</v>
       </c>
       <c r="R38" s="3">
-        <v>1816.97</v>
+        <v>401.77</v>
       </c>
       <c r="S38" s="3">
-        <v>41.75</v>
-      </c>
-      <c r="T38" t="str">
+        <v>26.49</v>
+      </c>
+      <c r="T38" s="3">
+        <v>8.48</v>
+      </c>
+      <c r="U38" s="3">
+        <v>37.24</v>
+      </c>
+      <c r="V38" s="3">
+        <v>44.49</v>
+      </c>
+      <c r="W38" s="3">
+        <v>0</v>
+      </c>
+      <c r="X38" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="str">
         <v/>
       </c>
     </row>
@@ -2766,60 +3336,75 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="C39" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="D39" s="1">
-        <v>47321.65</v>
+        <v>42680.7</v>
       </c>
       <c r="E39" s="2">
-        <v>-0.75</v>
+        <v>-0.99</v>
       </c>
       <c r="F39" s="2">
-        <v>-0.75</v>
+        <v>-4.34</v>
       </c>
       <c r="G39" s="2">
-        <v>-1.12</v>
+        <v>-4.11</v>
       </c>
       <c r="H39" s="2">
-        <v>7.58</v>
+        <v>-23.06</v>
       </c>
       <c r="I39" s="1">
         <v>0</v>
       </c>
       <c r="J39" s="1">
-        <v>44905.83</v>
+        <v>48906.86</v>
       </c>
       <c r="K39" s="1">
-        <v>47713.56</v>
+        <v>43930.43</v>
       </c>
       <c r="L39" s="1">
-        <v>48453.83</v>
+        <v>45760.39</v>
       </c>
       <c r="M39" s="3">
-        <v>-244.43</v>
+        <v>-661.47</v>
       </c>
       <c r="N39" s="3">
-        <v>-212.11</v>
+        <v>-546.4</v>
       </c>
       <c r="O39" s="3">
-        <v>882.81</v>
+        <v>-1702.06</v>
       </c>
       <c r="P39" s="3">
-        <v>1147.23</v>
+        <v>-1361.49</v>
       </c>
       <c r="Q39" s="3">
-        <v>-226.03</v>
+        <v>-2219.83</v>
       </c>
       <c r="R39" s="3">
-        <v>-997.05</v>
+        <v>-976.78</v>
       </c>
       <c r="S39" s="3">
-        <v>42.55</v>
-      </c>
-      <c r="T39" t="str">
+        <v>33.59</v>
+      </c>
+      <c r="T39" s="3">
+        <v>11.63</v>
+      </c>
+      <c r="U39" s="3">
+        <v>35.81</v>
+      </c>
+      <c r="V39" s="3">
+        <v>38.05</v>
+      </c>
+      <c r="W39" s="3">
+        <v>0</v>
+      </c>
+      <c r="X39" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="str">
         <v/>
       </c>
     </row>
@@ -2828,60 +3413,75 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="C40" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="D40" s="1">
-        <v>13528.95</v>
+        <v>8425</v>
       </c>
       <c r="E40" s="2">
-        <v>-0.75</v>
+        <v>-0.99</v>
       </c>
       <c r="F40" s="2">
-        <v>-0.75</v>
+        <v>-2.83</v>
       </c>
       <c r="G40" s="2">
-        <v>-1.61</v>
+        <v>4.96</v>
       </c>
       <c r="H40" s="2">
-        <v>-6.51</v>
+        <v>-10.59</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
       </c>
       <c r="J40" s="1">
-        <v>14159.07</v>
+        <v>8251.92</v>
       </c>
       <c r="K40" s="1">
-        <v>13598.82</v>
+        <v>8439.22</v>
       </c>
       <c r="L40" s="1">
-        <v>14196.36</v>
+        <v>8527.3</v>
       </c>
       <c r="M40" s="3">
-        <v>-193.83</v>
+        <v>19.93</v>
       </c>
       <c r="N40" s="3">
-        <v>-207.46</v>
+        <v>-27.5</v>
       </c>
       <c r="O40" s="3">
-        <v>-154.36</v>
+        <v>58.7</v>
       </c>
       <c r="P40" s="3">
-        <v>-12.01</v>
+        <v>57.78</v>
       </c>
       <c r="Q40" s="3">
-        <v>86.95</v>
+        <v>365.18</v>
       </c>
       <c r="R40" s="3">
-        <v>120.57</v>
+        <v>512.28</v>
       </c>
       <c r="S40" s="3">
-        <v>37.92</v>
-      </c>
-      <c r="T40" t="str">
+        <v>51</v>
+      </c>
+      <c r="T40" s="3">
+        <v>21.84</v>
+      </c>
+      <c r="U40" s="3">
+        <v>24.18</v>
+      </c>
+      <c r="V40" s="3">
+        <v>21.46</v>
+      </c>
+      <c r="W40" s="3">
+        <v>0</v>
+      </c>
+      <c r="X40" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="str">
         <v/>
       </c>
     </row>
@@ -2890,60 +3490,75 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>NIFTY200</v>
       </c>
       <c r="C41" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>NIFTY200</v>
       </c>
       <c r="D41" s="1">
-        <v>49213.65</v>
+        <v>12892.4</v>
       </c>
       <c r="E41" s="2">
-        <v>-0.79</v>
+        <v>-1.02</v>
       </c>
       <c r="F41" s="2">
-        <v>-0.79</v>
+        <v>-3.34</v>
       </c>
       <c r="G41" s="2">
-        <v>-0.73</v>
+        <v>-2.11</v>
       </c>
       <c r="H41" s="2">
-        <v>3.46</v>
+        <v>-11.29</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
       </c>
       <c r="J41" s="1">
-        <v>49073.99</v>
+        <v>13785.02</v>
       </c>
       <c r="K41" s="1">
-        <v>49647.66</v>
+        <v>13109.8</v>
       </c>
       <c r="L41" s="1">
-        <v>51027.93</v>
+        <v>13608.22</v>
       </c>
       <c r="M41" s="3">
-        <v>-415.43</v>
+        <v>-149.46</v>
       </c>
       <c r="N41" s="3">
-        <v>-431.09</v>
+        <v>-156.82</v>
       </c>
       <c r="O41" s="3">
-        <v>190.45</v>
+        <v>-180.45</v>
       </c>
       <c r="P41" s="3">
-        <v>574.97</v>
+        <v>-71.22</v>
       </c>
       <c r="Q41" s="3">
-        <v>135.15</v>
+        <v>255.4</v>
       </c>
       <c r="R41" s="3">
-        <v>-284.13</v>
+        <v>461.47</v>
       </c>
       <c r="S41" s="3">
-        <v>39.46</v>
-      </c>
-      <c r="T41" t="str">
+        <v>34.9</v>
+      </c>
+      <c r="T41" s="3">
+        <v>10.63</v>
+      </c>
+      <c r="U41" s="3">
+        <v>36.32</v>
+      </c>
+      <c r="V41" s="3">
+        <v>46.59</v>
+      </c>
+      <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="str">
         <v/>
       </c>
     </row>
@@ -2952,60 +3567,75 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="C42" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="D42" s="1">
-        <v>15660.05</v>
+        <v>24403</v>
       </c>
       <c r="E42" s="2">
-        <v>-0.8</v>
+        <v>-1.03</v>
       </c>
       <c r="F42" s="2">
-        <v>-0.8</v>
+        <v>-3.88</v>
       </c>
       <c r="G42" s="2">
-        <v>-2.23</v>
+        <v>-1</v>
       </c>
       <c r="H42" s="2">
-        <v>-1.97</v>
+        <v>-11.63</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
       </c>
       <c r="J42" s="1">
-        <v>16012.47</v>
+        <v>26207.11</v>
       </c>
       <c r="K42" s="1">
-        <v>15758.92</v>
+        <v>24840.22</v>
       </c>
       <c r="L42" s="1">
-        <v>16493.32</v>
+        <v>25484.01</v>
       </c>
       <c r="M42" s="3">
-        <v>-233.31</v>
+        <v>-191.42</v>
       </c>
       <c r="N42" s="3">
-        <v>-241.96</v>
+        <v>-187.78</v>
       </c>
       <c r="O42" s="3">
-        <v>-23.91</v>
+        <v>-378.42</v>
       </c>
       <c r="P42" s="3">
-        <v>140.68</v>
+        <v>-226.96</v>
       </c>
       <c r="Q42" s="3">
-        <v>379.4</v>
+        <v>627.93</v>
       </c>
       <c r="R42" s="3">
-        <v>332.77</v>
+        <v>1077.14</v>
       </c>
       <c r="S42" s="3">
-        <v>37.61</v>
-      </c>
-      <c r="T42" t="str">
+        <v>37.56</v>
+      </c>
+      <c r="T42" s="3">
+        <v>13.06</v>
+      </c>
+      <c r="U42" s="3">
+        <v>29.12</v>
+      </c>
+      <c r="V42" s="3">
+        <v>25.91</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="str">
         <v/>
       </c>
     </row>
@@ -3014,60 +3644,75 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="C43" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="D43" s="1">
-        <v>15557.6</v>
+        <v>25329.45</v>
       </c>
       <c r="E43" s="2">
-        <v>-0.8</v>
+        <v>-1.04</v>
       </c>
       <c r="F43" s="2">
-        <v>-0.8</v>
+        <v>-1.75</v>
       </c>
       <c r="G43" s="2">
-        <v>-3.6</v>
+        <v>-4.19</v>
       </c>
       <c r="H43" s="2">
-        <v>6.27</v>
+        <v>11.47</v>
       </c>
       <c r="I43" s="1">
         <v>0</v>
       </c>
       <c r="J43" s="1">
-        <v>15431.78</v>
+        <v>24375.25</v>
       </c>
       <c r="K43" s="1">
-        <v>15815.79</v>
+        <v>25744.37</v>
       </c>
       <c r="L43" s="1">
-        <v>16397.36</v>
+        <v>26439.2</v>
       </c>
       <c r="M43" s="3">
-        <v>-236.97</v>
+        <v>-286.8</v>
       </c>
       <c r="N43" s="3">
-        <v>-185.1</v>
+        <v>-206.14</v>
       </c>
       <c r="O43" s="3">
-        <v>174.74</v>
+        <v>578.03</v>
       </c>
       <c r="P43" s="3">
-        <v>341.22</v>
+        <v>792.63</v>
       </c>
       <c r="Q43" s="3">
-        <v>982.44</v>
+        <v>1753.37</v>
       </c>
       <c r="R43" s="3">
-        <v>994.96</v>
+        <v>1603.12</v>
       </c>
       <c r="S43" s="3">
-        <v>31.75</v>
-      </c>
-      <c r="T43" t="str">
+        <v>32.77</v>
+      </c>
+      <c r="T43" s="3">
+        <v>9.37</v>
+      </c>
+      <c r="U43" s="3">
+        <v>26.57</v>
+      </c>
+      <c r="V43" s="3">
+        <v>29.72</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="str">
         <v/>
       </c>
     </row>
@@ -3076,60 +3721,75 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="C44" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="D44" s="1">
-        <v>59774.7</v>
+        <v>5302.15</v>
       </c>
       <c r="E44" s="2">
-        <v>-0.81</v>
+        <v>-1.07</v>
       </c>
       <c r="F44" s="2">
-        <v>-0.81</v>
+        <v>-3.1</v>
       </c>
       <c r="G44" s="2">
-        <v>-1.64</v>
+        <v>-0.34</v>
       </c>
       <c r="H44" s="2">
-        <v>-3.46</v>
+        <v>-9.52</v>
       </c>
       <c r="I44" s="1">
         <v>0</v>
       </c>
       <c r="J44" s="1">
-        <v>61762.81</v>
+        <v>5545.89</v>
       </c>
       <c r="K44" s="1">
-        <v>60577.64</v>
+        <v>5364.15</v>
       </c>
       <c r="L44" s="1">
-        <v>62840.3</v>
+        <v>5511.3</v>
       </c>
       <c r="M44" s="3">
-        <v>-751.49</v>
+        <v>-31.66</v>
       </c>
       <c r="N44" s="3">
-        <v>-708.63</v>
+        <v>-45.89</v>
       </c>
       <c r="O44" s="3">
-        <v>-272.63</v>
+        <v>-50.65</v>
       </c>
       <c r="P44" s="3">
-        <v>235.93</v>
+        <v>-18.5</v>
       </c>
       <c r="Q44" s="3">
-        <v>-12.35</v>
+        <v>182.48</v>
       </c>
       <c r="R44" s="3">
-        <v>-175.4</v>
+        <v>260.16</v>
       </c>
       <c r="S44" s="3">
-        <v>35.21</v>
-      </c>
-      <c r="T44" t="str">
+        <v>41.44</v>
+      </c>
+      <c r="T44" s="3">
+        <v>15.19</v>
+      </c>
+      <c r="U44" s="3">
+        <v>31.21</v>
+      </c>
+      <c r="V44" s="3">
+        <v>38.99</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="str">
         <v/>
       </c>
     </row>
@@ -3138,60 +3798,75 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="C45" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="D45" s="1">
-        <v>5424.75</v>
+        <v>13171.4</v>
       </c>
       <c r="E45" s="2">
-        <v>-0.86</v>
+        <v>-1.09</v>
       </c>
       <c r="F45" s="2">
-        <v>-0.86</v>
+        <v>-3.37</v>
       </c>
       <c r="G45" s="2">
-        <v>1.96</v>
+        <v>-4.21</v>
       </c>
       <c r="H45" s="2">
-        <v>-7.43</v>
+        <v>-8.98</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
       </c>
       <c r="J45" s="1">
-        <v>5553.17</v>
+        <v>14142.86</v>
       </c>
       <c r="K45" s="1">
-        <v>5376.4</v>
+        <v>13453.69</v>
       </c>
       <c r="L45" s="1">
-        <v>5537.7</v>
+        <v>14109.82</v>
       </c>
       <c r="M45" s="3">
-        <v>-33.54</v>
+        <v>-219.72</v>
       </c>
       <c r="N45" s="3">
-        <v>-61.47</v>
+        <v>-208.32</v>
       </c>
       <c r="O45" s="3">
-        <v>-40.87</v>
+        <v>-182.88</v>
       </c>
       <c r="P45" s="3">
-        <v>-16.55</v>
+        <v>-17.71</v>
       </c>
       <c r="Q45" s="3">
-        <v>192.26</v>
+        <v>58.43</v>
       </c>
       <c r="R45" s="3">
-        <v>262.12</v>
+        <v>114.87</v>
       </c>
       <c r="S45" s="3">
-        <v>51.23</v>
-      </c>
-      <c r="T45" t="str">
+        <v>28.95</v>
+      </c>
+      <c r="T45" s="3">
+        <v>10.55</v>
+      </c>
+      <c r="U45" s="3">
+        <v>39.34</v>
+      </c>
+      <c r="V45" s="3">
+        <v>44.92</v>
+      </c>
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="str">
         <v/>
       </c>
     </row>
@@ -3200,60 +3875,75 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="C46" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="D46" s="1">
-        <v>48866.6</v>
+        <v>13600.85</v>
       </c>
       <c r="E46" s="2">
-        <v>-0.87</v>
+        <v>-1.14</v>
       </c>
       <c r="F46" s="2">
-        <v>-0.87</v>
+        <v>-2.53</v>
       </c>
       <c r="G46" s="2">
-        <v>-4.15</v>
+        <v>1.86</v>
       </c>
       <c r="H46" s="2">
-        <v>11.4</v>
+        <v>-11.06</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
       </c>
       <c r="J46" s="1">
-        <v>47289.89</v>
+        <v>14385.7</v>
       </c>
       <c r="K46" s="1">
-        <v>49886.15</v>
+        <v>13675.05</v>
       </c>
       <c r="L46" s="1">
-        <v>51712.18</v>
+        <v>14009.98</v>
       </c>
       <c r="M46" s="3">
-        <v>-742.76</v>
+        <v>-55.41</v>
       </c>
       <c r="N46" s="3">
-        <v>-535.44</v>
+        <v>-118.79</v>
       </c>
       <c r="O46" s="3">
-        <v>986.94</v>
+        <v>-227.8</v>
       </c>
       <c r="P46" s="3">
-        <v>1570.37</v>
+        <v>-163</v>
       </c>
       <c r="Q46" s="3">
-        <v>2197.92</v>
+        <v>-547.72</v>
       </c>
       <c r="R46" s="3">
-        <v>1477.16</v>
+        <v>-494.09</v>
       </c>
       <c r="S46" s="3">
-        <v>30.28</v>
-      </c>
-      <c r="T46" t="str">
+        <v>46.01</v>
+      </c>
+      <c r="T46" s="3">
+        <v>17.84</v>
+      </c>
+      <c r="U46" s="3">
+        <v>28.4</v>
+      </c>
+      <c r="V46" s="3">
+        <v>25.15</v>
+      </c>
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="str">
         <v/>
       </c>
     </row>
@@ -3262,60 +3952,75 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="C47" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="D47" s="1">
-        <v>7498.05</v>
+        <v>54287.35</v>
       </c>
       <c r="E47" s="2">
-        <v>-0.88</v>
+        <v>-1.16</v>
       </c>
       <c r="F47" s="2">
-        <v>-0.88</v>
+        <v>-2.79</v>
       </c>
       <c r="G47" s="2">
-        <v>-2.68</v>
+        <v>-0.63</v>
       </c>
       <c r="H47" s="2">
-        <v>-12.85</v>
+        <v>-8.89</v>
       </c>
       <c r="I47" s="1">
         <v>0</v>
       </c>
       <c r="J47" s="1">
-        <v>7697.42</v>
+        <v>56842.98</v>
       </c>
       <c r="K47" s="1">
-        <v>7532.36</v>
+        <v>55072.04</v>
       </c>
       <c r="L47" s="1">
-        <v>7797.25</v>
+        <v>56259.7</v>
       </c>
       <c r="M47" s="3">
-        <v>-85.41</v>
+        <v>-328.9</v>
       </c>
       <c r="N47" s="3">
-        <v>-86.41</v>
+        <v>-351.4</v>
       </c>
       <c r="O47" s="3">
-        <v>-56.58</v>
+        <v>-402.01</v>
       </c>
       <c r="P47" s="3">
-        <v>-16.6</v>
+        <v>-109.29</v>
       </c>
       <c r="Q47" s="3">
-        <v>-294.39</v>
+        <v>1610.08</v>
       </c>
       <c r="R47" s="3">
-        <v>-246.06</v>
+        <v>2277.6</v>
       </c>
       <c r="S47" s="3">
-        <v>42.35</v>
-      </c>
-      <c r="T47" t="str">
+        <v>37.74</v>
+      </c>
+      <c r="T47" s="3">
+        <v>11.74</v>
+      </c>
+      <c r="U47" s="3">
+        <v>26.88</v>
+      </c>
+      <c r="V47" s="3">
+        <v>23.01</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="str">
         <v/>
       </c>
     </row>
@@ -3324,60 +4029,75 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="C48" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="D48" s="1">
-        <v>13827.75</v>
+        <v>26195.65</v>
       </c>
       <c r="E48" s="2">
-        <v>-0.9</v>
+        <v>-1.18</v>
       </c>
       <c r="F48" s="2">
-        <v>-0.9</v>
+        <v>-3.73</v>
       </c>
       <c r="G48" s="2">
-        <v>3.56</v>
+        <v>-1.36</v>
       </c>
       <c r="H48" s="2">
-        <v>-9.58</v>
+        <v>-13.2</v>
       </c>
       <c r="I48" s="1">
         <v>0</v>
       </c>
       <c r="J48" s="1">
-        <v>14407.78</v>
+        <v>28527.81</v>
       </c>
       <c r="K48" s="1">
-        <v>13643.53</v>
+        <v>26693.86</v>
       </c>
       <c r="L48" s="1">
-        <v>14077.98</v>
+        <v>27555.3</v>
       </c>
       <c r="M48" s="3">
-        <v>-87.76</v>
+        <v>-260.62</v>
       </c>
       <c r="N48" s="3">
-        <v>-177.27</v>
+        <v>-263.46</v>
       </c>
       <c r="O48" s="3">
-        <v>-209.7</v>
+        <v>-507.71</v>
       </c>
       <c r="P48" s="3">
-        <v>-159.38</v>
+        <v>-301.14</v>
       </c>
       <c r="Q48" s="3">
-        <v>-529.62</v>
+        <v>1281.95</v>
       </c>
       <c r="R48" s="3">
-        <v>-490.47</v>
+        <v>1894.3</v>
       </c>
       <c r="S48" s="3">
-        <v>52.82</v>
-      </c>
-      <c r="T48" t="str">
+        <v>36</v>
+      </c>
+      <c r="T48" s="3">
+        <v>12.47</v>
+      </c>
+      <c r="U48" s="3">
+        <v>30.23</v>
+      </c>
+      <c r="V48" s="3">
+        <v>28.48</v>
+      </c>
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="str">
         <v/>
       </c>
     </row>
@@ -3386,60 +4106,75 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="C49" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="D49" s="1">
-        <v>30908.4</v>
+        <v>47649.75</v>
       </c>
       <c r="E49" s="2">
-        <v>-0.93</v>
+        <v>-1.19</v>
       </c>
       <c r="F49" s="2">
-        <v>-0.93</v>
+        <v>-3.34</v>
       </c>
       <c r="G49" s="2">
-        <v>0.01</v>
+        <v>-6.53</v>
       </c>
       <c r="H49" s="2">
-        <v>-7.27</v>
+        <v>8.63</v>
       </c>
       <c r="I49" s="1">
         <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>32376.25</v>
+        <v>47357.97</v>
       </c>
       <c r="K49" s="1">
-        <v>30895.21</v>
+        <v>49051.9</v>
       </c>
       <c r="L49" s="1">
-        <v>32105.82</v>
+        <v>51443.8</v>
       </c>
       <c r="M49" s="3">
-        <v>-349.66</v>
+        <v>-970.56</v>
       </c>
       <c r="N49" s="3">
-        <v>-440.21</v>
+        <v>-714.55</v>
       </c>
       <c r="O49" s="3">
-        <v>-363.4</v>
+        <v>889.87</v>
       </c>
       <c r="P49" s="3">
-        <v>-109.75</v>
+        <v>1550.96</v>
       </c>
       <c r="Q49" s="3">
-        <v>1850.76</v>
+        <v>2100.85</v>
       </c>
       <c r="R49" s="3">
-        <v>2377.64</v>
+        <v>1457.74</v>
       </c>
       <c r="S49" s="3">
-        <v>43.96</v>
-      </c>
-      <c r="T49" t="str">
+        <v>23.92</v>
+      </c>
+      <c r="T49" s="3">
+        <v>6.63</v>
+      </c>
+      <c r="U49" s="3">
+        <v>39.3</v>
+      </c>
+      <c r="V49" s="3">
+        <v>39.87</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="str">
         <v/>
       </c>
     </row>
@@ -3448,60 +4183,75 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTY500</v>
       </c>
       <c r="C50" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTY500</v>
       </c>
       <c r="D50" s="1">
-        <v>29239.8</v>
+        <v>21427.6</v>
       </c>
       <c r="E50" s="2">
-        <v>-0.93</v>
+        <v>-1.24</v>
       </c>
       <c r="F50" s="2">
-        <v>-0.93</v>
+        <v>-3.78</v>
       </c>
       <c r="G50" s="2">
-        <v>-3.61</v>
+        <v>-2.92</v>
       </c>
       <c r="H50" s="2">
-        <v>-4.35</v>
+        <v>-10.24</v>
       </c>
       <c r="I50" s="1">
         <v>0</v>
       </c>
       <c r="J50" s="1">
-        <v>31419.18</v>
+        <v>22832.04</v>
       </c>
       <c r="K50" s="1">
-        <v>29759.56</v>
+        <v>21881.73</v>
       </c>
       <c r="L50" s="1">
-        <v>31753.46</v>
+        <v>22745.63</v>
       </c>
       <c r="M50" s="3">
-        <v>-646.57</v>
+        <v>-271.94</v>
       </c>
       <c r="N50" s="3">
-        <v>-629.11</v>
+        <v>-263.85</v>
       </c>
       <c r="O50" s="3">
-        <v>-404.61</v>
+        <v>-241.67</v>
       </c>
       <c r="P50" s="3">
-        <v>84.87</v>
+        <v>-45.53</v>
       </c>
       <c r="Q50" s="3">
-        <v>2038.85</v>
+        <v>484.75</v>
       </c>
       <c r="R50" s="3">
-        <v>2407.67</v>
+        <v>798.9</v>
       </c>
       <c r="S50" s="3">
-        <v>29.24</v>
-      </c>
-      <c r="T50" t="str">
+        <v>31.86</v>
+      </c>
+      <c r="T50" s="3">
+        <v>10.04</v>
+      </c>
+      <c r="U50" s="3">
+        <v>40.02</v>
+      </c>
+      <c r="V50" s="3">
+        <v>47.39</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="str">
         <v/>
       </c>
     </row>
@@ -3510,60 +4260,75 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="C51" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="D51" s="1">
-        <v>18743.65</v>
+        <v>5510.75</v>
       </c>
       <c r="E51" s="2">
-        <v>-0.93</v>
+        <v>-1.25</v>
       </c>
       <c r="F51" s="2">
-        <v>-0.93</v>
+        <v>-2.14</v>
       </c>
       <c r="G51" s="2">
-        <v>-0.22</v>
+        <v>0.7</v>
       </c>
       <c r="H51" s="2">
-        <v>-11.29</v>
+        <v>-13.7</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
       </c>
       <c r="J51" s="1">
-        <v>19890.8</v>
+        <v>5948.69</v>
       </c>
       <c r="K51" s="1">
-        <v>18774.85</v>
+        <v>5543.59</v>
       </c>
       <c r="L51" s="1">
-        <v>19583.61</v>
+        <v>5678.67</v>
       </c>
       <c r="M51" s="3">
-        <v>-232.6</v>
+        <v>-25.74</v>
       </c>
       <c r="N51" s="3">
-        <v>-284.84</v>
+        <v>-49.34</v>
       </c>
       <c r="O51" s="3">
-        <v>-295.29</v>
+        <v>-122.29</v>
       </c>
       <c r="P51" s="3">
-        <v>-144.6</v>
+        <v>-96.45</v>
       </c>
       <c r="Q51" s="3">
-        <v>760.52</v>
+        <v>21.8</v>
       </c>
       <c r="R51" s="3">
-        <v>1111.92</v>
+        <v>138.84</v>
       </c>
       <c r="S51" s="3">
-        <v>41.67</v>
-      </c>
-      <c r="T51" t="str">
+        <v>44.76</v>
+      </c>
+      <c r="T51" s="3">
+        <v>17.18</v>
+      </c>
+      <c r="U51" s="3">
+        <v>29.76</v>
+      </c>
+      <c r="V51" s="3">
+        <v>34.56</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="str">
         <v/>
       </c>
     </row>
@@ -3572,60 +4337,75 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="C52" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="D52" s="1">
-        <v>9124.3</v>
+        <v>7356.85</v>
       </c>
       <c r="E52" s="2">
-        <v>-0.94</v>
+        <v>-1.28</v>
       </c>
       <c r="F52" s="2">
-        <v>-0.94</v>
+        <v>-2.75</v>
       </c>
       <c r="G52" s="2">
-        <v>-1.64</v>
+        <v>-4.51</v>
       </c>
       <c r="H52" s="2">
-        <v>17.77</v>
+        <v>-14.5</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
       </c>
       <c r="J52" s="1">
-        <v>8827.02</v>
+        <v>7679.73</v>
       </c>
       <c r="K52" s="1">
-        <v>9190.46</v>
+        <v>7468.9</v>
       </c>
       <c r="L52" s="1">
-        <v>9511</v>
+        <v>7753.04</v>
       </c>
       <c r="M52" s="3">
-        <v>-89.98</v>
+        <v>-96.56</v>
       </c>
       <c r="N52" s="3">
-        <v>-101.8</v>
+        <v>-90.05</v>
       </c>
       <c r="O52" s="3">
-        <v>126.12</v>
+        <v>-67.85</v>
       </c>
       <c r="P52" s="3">
-        <v>239.91</v>
+        <v>-18.85</v>
       </c>
       <c r="Q52" s="3">
-        <v>628</v>
+        <v>-305.65</v>
       </c>
       <c r="R52" s="3">
-        <v>527.7</v>
+        <v>-248.31</v>
       </c>
       <c r="S52" s="3">
-        <v>43.27</v>
-      </c>
-      <c r="T52" t="str">
+        <v>38.24</v>
+      </c>
+      <c r="T52" s="3">
+        <v>13.5</v>
+      </c>
+      <c r="U52" s="3">
+        <v>30.05</v>
+      </c>
+      <c r="V52" s="3">
+        <v>26.15</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="str">
         <v/>
       </c>
     </row>
@@ -3634,60 +4414,75 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>Nifty Total Market</v>
       </c>
       <c r="C53" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>NIFTYTOTALMKT</v>
       </c>
       <c r="D53" s="1">
-        <v>10919.1</v>
+        <v>12105.3</v>
       </c>
       <c r="E53" s="2">
-        <v>-0.96</v>
+        <v>-1.29</v>
       </c>
       <c r="F53" s="2">
-        <v>-0.96</v>
+        <v>-3.94</v>
       </c>
       <c r="G53" s="2">
-        <v>3.6</v>
+        <v>-3.2</v>
       </c>
       <c r="H53" s="2">
-        <v>-12.53</v>
+        <v>-9.62</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
       </c>
       <c r="J53" s="1">
-        <v>11239.26</v>
+        <v>12856.69</v>
       </c>
       <c r="K53" s="1">
-        <v>10717.61</v>
+        <v>12377.17</v>
       </c>
       <c r="L53" s="1">
-        <v>11122.31</v>
+        <v>12865.16</v>
       </c>
       <c r="M53" s="3">
-        <v>-79.61</v>
+        <v>-155.97</v>
       </c>
       <c r="N53" s="3">
-        <v>-160.82</v>
+        <v>-147.15</v>
       </c>
       <c r="O53" s="3">
-        <v>-112.2</v>
+        <v>-115.47</v>
       </c>
       <c r="P53" s="3">
-        <v>-75.56</v>
+        <v>-2.6</v>
       </c>
       <c r="Q53" s="3">
-        <v>33.84</v>
+        <v>611.22</v>
       </c>
       <c r="R53" s="3">
-        <v>177.01</v>
+        <v>822.32</v>
       </c>
       <c r="S53" s="3">
-        <v>54.85</v>
-      </c>
-      <c r="T53" t="str">
+        <v>31.07</v>
+      </c>
+      <c r="T53" s="3">
+        <v>10.06</v>
+      </c>
+      <c r="U53" s="3">
+        <v>41.11</v>
+      </c>
+      <c r="V53" s="3">
+        <v>46.7</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="str">
         <v/>
       </c>
     </row>
@@ -3696,60 +4491,75 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="C54" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="D54" s="1">
-        <v>23895.45</v>
+        <v>1563.4</v>
       </c>
       <c r="E54" s="2">
-        <v>-0.98</v>
+        <v>-1.33</v>
       </c>
       <c r="F54" s="2">
-        <v>-0.98</v>
+        <v>-5.15</v>
       </c>
       <c r="G54" s="2">
-        <v>0.68</v>
+        <v>-1.25</v>
       </c>
       <c r="H54" s="2">
-        <v>-10.47</v>
+        <v>8.22</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
       </c>
       <c r="J54" s="1">
-        <v>25067.57</v>
+        <v>1469.5</v>
       </c>
       <c r="K54" s="1">
-        <v>23835.75</v>
+        <v>1600.49</v>
       </c>
       <c r="L54" s="1">
-        <v>24637.3</v>
+        <v>1574.14</v>
       </c>
       <c r="M54" s="3">
-        <v>-217.66</v>
+        <v>13.19</v>
       </c>
       <c r="N54" s="3">
-        <v>-296.58</v>
+        <v>14.44</v>
       </c>
       <c r="O54" s="3">
-        <v>-327.95</v>
+        <v>30.99</v>
       </c>
       <c r="P54" s="3">
-        <v>-193.05</v>
+        <v>31.31</v>
       </c>
       <c r="Q54" s="3">
-        <v>344.58</v>
+        <v>-74.96</v>
       </c>
       <c r="R54" s="3">
-        <v>711.08</v>
+        <v>-105.89</v>
       </c>
       <c r="S54" s="3">
-        <v>46.2</v>
-      </c>
-      <c r="T54" t="str">
+        <v>46.1</v>
+      </c>
+      <c r="T54" s="3">
+        <v>21.64</v>
+      </c>
+      <c r="U54" s="3">
+        <v>33.44</v>
+      </c>
+      <c r="V54" s="3">
+        <v>17.65</v>
+      </c>
+      <c r="W54" s="3">
+        <v>0</v>
+      </c>
+      <c r="X54" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="str">
         <v/>
       </c>
     </row>
@@ -3758,60 +4568,75 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="C55" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="D55" s="1">
-        <v>5190.85</v>
+        <v>15209.55</v>
       </c>
       <c r="E55" s="2">
-        <v>-0.98</v>
+        <v>-1.39</v>
       </c>
       <c r="F55" s="2">
-        <v>-0.98</v>
+        <v>-4</v>
       </c>
       <c r="G55" s="2">
-        <v>1.99</v>
+        <v>-3.48</v>
       </c>
       <c r="H55" s="2">
-        <v>11.48</v>
+        <v>-9.76</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
       </c>
       <c r="J55" s="1">
-        <v>5100.82</v>
+        <v>16287.1</v>
       </c>
       <c r="K55" s="1">
-        <v>5229.32</v>
+        <v>15574.1</v>
       </c>
       <c r="L55" s="1">
-        <v>5309.82</v>
+        <v>16271.59</v>
       </c>
       <c r="M55" s="3">
-        <v>-20.36</v>
+        <v>-223.57</v>
       </c>
       <c r="N55" s="3">
-        <v>-30.17</v>
+        <v>-212.26</v>
       </c>
       <c r="O55" s="3">
-        <v>38.14</v>
+        <v>-170.83</v>
       </c>
       <c r="P55" s="3">
-        <v>88.65</v>
+        <v>-6.87</v>
       </c>
       <c r="Q55" s="3">
-        <v>374.58</v>
+        <v>891.89</v>
       </c>
       <c r="R55" s="3">
-        <v>327.38</v>
+        <v>1173.87</v>
       </c>
       <c r="S55" s="3">
-        <v>45.87</v>
-      </c>
-      <c r="T55" t="str">
+        <v>29.7</v>
+      </c>
+      <c r="T55" s="3">
+        <v>8.94</v>
+      </c>
+      <c r="U55" s="3">
+        <v>41.56</v>
+      </c>
+      <c r="V55" s="3">
+        <v>49.31</v>
+      </c>
+      <c r="W55" s="3">
+        <v>0</v>
+      </c>
+      <c r="X55" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="str">
         <v/>
       </c>
     </row>
@@ -3820,60 +4645,75 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="C56" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="D56" s="1">
-        <v>18935.75</v>
+        <v>8792.3</v>
       </c>
       <c r="E56" s="2">
-        <v>-1.01</v>
+        <v>-1.41</v>
       </c>
       <c r="F56" s="2">
-        <v>-1.01</v>
+        <v>-3.38</v>
       </c>
       <c r="G56" s="2">
-        <v>-1.61</v>
+        <v>-5.56</v>
       </c>
       <c r="H56" s="2">
-        <v>6.9</v>
+        <v>-7.6</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
       </c>
       <c r="J56" s="1">
-        <v>18179.82</v>
+        <v>9757.44</v>
       </c>
       <c r="K56" s="1">
-        <v>19223.48</v>
+        <v>8981.6</v>
       </c>
       <c r="L56" s="1">
-        <v>19680.38</v>
+        <v>9476.27</v>
       </c>
       <c r="M56" s="3">
-        <v>-154.16</v>
+        <v>-170.17</v>
       </c>
       <c r="N56" s="3">
-        <v>-129.79</v>
+        <v>-167.85</v>
       </c>
       <c r="O56" s="3">
-        <v>339.32</v>
+        <v>-193.2</v>
       </c>
       <c r="P56" s="3">
-        <v>496.14</v>
+        <v>-68.85</v>
       </c>
       <c r="Q56" s="3">
-        <v>892.77</v>
+        <v>377.04</v>
       </c>
       <c r="R56" s="3">
-        <v>862.73</v>
+        <v>505.77</v>
       </c>
       <c r="S56" s="3">
-        <v>37.74</v>
-      </c>
-      <c r="T56" t="str">
+        <v>29.94</v>
+      </c>
+      <c r="T56" s="3">
+        <v>12</v>
+      </c>
+      <c r="U56" s="3">
+        <v>36.69</v>
+      </c>
+      <c r="V56" s="3">
+        <v>42.16</v>
+      </c>
+      <c r="W56" s="3">
+        <v>0</v>
+      </c>
+      <c r="X56" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="str">
         <v/>
       </c>
     </row>
@@ -3882,60 +4722,75 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="C57" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="D57" s="1">
-        <v>13203.35</v>
+        <v>18680</v>
       </c>
       <c r="E57" s="2">
-        <v>-1.01</v>
+        <v>-1.42</v>
       </c>
       <c r="F57" s="2">
-        <v>-1.01</v>
+        <v>-4.06</v>
       </c>
       <c r="G57" s="2">
-        <v>0.25</v>
+        <v>-1.39</v>
       </c>
       <c r="H57" s="2">
-        <v>-9.15</v>
+        <v>-12.75</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
       </c>
       <c r="J57" s="1">
-        <v>13806.77</v>
+        <v>20086.53</v>
       </c>
       <c r="K57" s="1">
-        <v>13206.34</v>
+        <v>19063.77</v>
       </c>
       <c r="L57" s="1">
-        <v>13681.72</v>
+        <v>19769.3</v>
       </c>
       <c r="M57" s="3">
-        <v>-134.36</v>
+        <v>-183.77</v>
       </c>
       <c r="N57" s="3">
-        <v>-171.64</v>
+        <v>-210.33</v>
       </c>
       <c r="O57" s="3">
-        <v>-155.64</v>
+        <v>-303.22</v>
       </c>
       <c r="P57" s="3">
-        <v>-66.26</v>
+        <v>-146.4</v>
       </c>
       <c r="Q57" s="3">
-        <v>280.21</v>
+        <v>462.8</v>
       </c>
       <c r="R57" s="3">
-        <v>466.43</v>
+        <v>790.61</v>
       </c>
       <c r="S57" s="3">
-        <v>43.96</v>
-      </c>
-      <c r="T57" t="str">
+        <v>36.05</v>
+      </c>
+      <c r="T57" s="3">
+        <v>12.87</v>
+      </c>
+      <c r="U57" s="3">
+        <v>35.23</v>
+      </c>
+      <c r="V57" s="3">
+        <v>41.25</v>
+      </c>
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="str">
         <v/>
       </c>
     </row>
@@ -3944,60 +4799,75 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>NIFTY500</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="C58" t="str">
-        <v>NIFTY500</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="D58" s="1">
-        <v>22041.6</v>
+        <v>15081.85</v>
       </c>
       <c r="E58" s="2">
-        <v>-1.03</v>
+        <v>-1.44</v>
       </c>
       <c r="F58" s="2">
-        <v>-1.03</v>
+        <v>-4.47</v>
       </c>
       <c r="G58" s="2">
-        <v>-0.14</v>
+        <v>-5.84</v>
       </c>
       <c r="H58" s="2">
-        <v>-7.67</v>
+        <v>-5.59</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
       </c>
       <c r="J58" s="1">
-        <v>22863.34</v>
+        <v>16004.23</v>
       </c>
       <c r="K58" s="1">
-        <v>22092.51</v>
+        <v>15527.97</v>
       </c>
       <c r="L58" s="1">
-        <v>22869.12</v>
+        <v>16383.51</v>
       </c>
       <c r="M58" s="3">
-        <v>-225.46</v>
+        <v>-288.64</v>
       </c>
       <c r="N58" s="3">
-        <v>-275.42</v>
+        <v>-254.72</v>
       </c>
       <c r="O58" s="3">
-        <v>-192.69</v>
+        <v>-70.03</v>
       </c>
       <c r="P58" s="3">
-        <v>-35.73</v>
+        <v>131.46</v>
       </c>
       <c r="Q58" s="3">
-        <v>533.73</v>
+        <v>333.27</v>
       </c>
       <c r="R58" s="3">
-        <v>808.69</v>
+        <v>323.55</v>
       </c>
       <c r="S58" s="3">
-        <v>42.32</v>
-      </c>
-      <c r="T58" t="str">
+        <v>26.71</v>
+      </c>
+      <c r="T58" s="3">
+        <v>8.92</v>
+      </c>
+      <c r="U58" s="3">
+        <v>43.22</v>
+      </c>
+      <c r="V58" s="3">
+        <v>47.7</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="str">
         <v/>
       </c>
     </row>
@@ -4006,60 +4876,75 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="C59" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="D59" s="1">
-        <v>15678.75</v>
+        <v>31640.45</v>
       </c>
       <c r="E59" s="2">
-        <v>-1.04</v>
+        <v>-1.45</v>
       </c>
       <c r="F59" s="2">
-        <v>-1.04</v>
+        <v>-3.68</v>
       </c>
       <c r="G59" s="2">
-        <v>-0.5</v>
+        <v>-3.71</v>
       </c>
       <c r="H59" s="2">
-        <v>-6.98</v>
+        <v>-6.82</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
       </c>
       <c r="J59" s="1">
-        <v>16307.73</v>
+        <v>33676.94</v>
       </c>
       <c r="K59" s="1">
-        <v>15746.43</v>
+        <v>32361.46</v>
       </c>
       <c r="L59" s="1">
-        <v>16366.58</v>
+        <v>33854.46</v>
       </c>
       <c r="M59" s="3">
-        <v>-185.36</v>
+        <v>-474.3</v>
       </c>
       <c r="N59" s="3">
-        <v>-216.84</v>
+        <v>-462.62</v>
       </c>
       <c r="O59" s="3">
-        <v>-133.4</v>
+        <v>-293.22</v>
       </c>
       <c r="P59" s="3">
-        <v>0.61</v>
+        <v>87.44</v>
       </c>
       <c r="Q59" s="3">
-        <v>929.32</v>
+        <v>1950.37</v>
       </c>
       <c r="R59" s="3">
-        <v>1181.35</v>
+        <v>2419.99</v>
       </c>
       <c r="S59" s="3">
-        <v>40.18</v>
-      </c>
-      <c r="T59" t="str">
+        <v>29.92</v>
+      </c>
+      <c r="T59" s="3">
+        <v>9.78</v>
+      </c>
+      <c r="U59" s="3">
+        <v>38.82</v>
+      </c>
+      <c r="V59" s="3">
+        <v>48.07</v>
+      </c>
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="str">
         <v/>
       </c>
     </row>
@@ -4068,60 +4953,75 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="C60" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="D60" s="1">
-        <v>16767.85</v>
+        <v>15117.8</v>
       </c>
       <c r="E60" s="2">
-        <v>-1.05</v>
+        <v>-1.56</v>
       </c>
       <c r="F60" s="2">
-        <v>-1.05</v>
+        <v>-4.46</v>
       </c>
       <c r="G60" s="2">
-        <v>-1.53</v>
+        <v>-4.02</v>
       </c>
       <c r="H60" s="2">
-        <v>-2.82</v>
+        <v>-8.29</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
       </c>
       <c r="J60" s="1">
-        <v>17231.35</v>
+        <v>16013.54</v>
       </c>
       <c r="K60" s="1">
-        <v>16936.71</v>
+        <v>15535.59</v>
       </c>
       <c r="L60" s="1">
-        <v>17751.15</v>
+        <v>16188.45</v>
       </c>
       <c r="M60" s="3">
-        <v>-261.77</v>
+        <v>-217.14</v>
       </c>
       <c r="N60" s="3">
-        <v>-278.24</v>
+        <v>-191.38</v>
       </c>
       <c r="O60" s="3">
-        <v>-33.85</v>
+        <v>-102.62</v>
       </c>
       <c r="P60" s="3">
-        <v>164.81</v>
+        <v>56.11</v>
       </c>
       <c r="Q60" s="3">
-        <v>915.94</v>
+        <v>890.57</v>
       </c>
       <c r="R60" s="3">
-        <v>1051.43</v>
+        <v>1142.8</v>
       </c>
       <c r="S60" s="3">
-        <v>35.32</v>
-      </c>
-      <c r="T60" t="str">
+        <v>27.82</v>
+      </c>
+      <c r="T60" s="3">
+        <v>9.23</v>
+      </c>
+      <c r="U60" s="3">
+        <v>44.48</v>
+      </c>
+      <c r="V60" s="3">
+        <v>47.02</v>
+      </c>
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="str">
         <v/>
       </c>
     </row>
@@ -4130,60 +5030,75 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="C61" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="D61" s="1">
-        <v>15656.8</v>
+        <v>14516.75</v>
       </c>
       <c r="E61" s="2">
-        <v>-1.05</v>
+        <v>-1.57</v>
       </c>
       <c r="F61" s="2">
-        <v>-1.05</v>
+        <v>-4.33</v>
       </c>
       <c r="G61" s="2">
-        <v>-0.59</v>
+        <v>-6.07</v>
       </c>
       <c r="H61" s="2">
-        <v>-5.02</v>
+        <v>-5.81</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
       </c>
       <c r="J61" s="1">
-        <v>16029.65</v>
+        <v>15625.39</v>
       </c>
       <c r="K61" s="1">
-        <v>15736.72</v>
+        <v>14946.58</v>
       </c>
       <c r="L61" s="1">
-        <v>16277.41</v>
+        <v>15847.78</v>
       </c>
       <c r="M61" s="3">
-        <v>-162.34</v>
+        <v>-301.4</v>
       </c>
       <c r="N61" s="3">
-        <v>-186.97</v>
+        <v>-273.48</v>
       </c>
       <c r="O61" s="3">
-        <v>-59.62</v>
+        <v>-119.2</v>
       </c>
       <c r="P61" s="3">
-        <v>64.71</v>
+        <v>96.42</v>
       </c>
       <c r="Q61" s="3">
-        <v>933.56</v>
+        <v>1221.05</v>
       </c>
       <c r="R61" s="3">
-        <v>1151.4</v>
+        <v>1438.69</v>
       </c>
       <c r="S61" s="3">
-        <v>39.94</v>
-      </c>
-      <c r="T61" t="str">
+        <v>26.18</v>
+      </c>
+      <c r="T61" s="3">
+        <v>8.05</v>
+      </c>
+      <c r="U61" s="3">
+        <v>43.95</v>
+      </c>
+      <c r="V61" s="3">
+        <v>50.33</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="str">
         <v/>
       </c>
     </row>
@@ -4192,60 +5107,75 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>Nifty Total Market</v>
+        <v>CNXPSE</v>
       </c>
       <c r="C62" t="str">
-        <v>NIFTYTOTALMKT</v>
+        <v>CNXPSE</v>
       </c>
       <c r="D62" s="1">
-        <v>12469.05</v>
+        <v>8885.75</v>
       </c>
       <c r="E62" s="2">
-        <v>-1.05</v>
+        <v>-1.64</v>
       </c>
       <c r="F62" s="2">
-        <v>-1.05</v>
+        <v>-3.91</v>
       </c>
       <c r="G62" s="2">
-        <v>-0.29</v>
+        <v>-5.07</v>
       </c>
       <c r="H62" s="2">
-        <v>-6.9</v>
+        <v>-9.82</v>
       </c>
       <c r="I62" s="1">
         <v>0</v>
       </c>
       <c r="J62" s="1">
-        <v>12872.91</v>
+        <v>9984.3</v>
       </c>
       <c r="K62" s="1">
-        <v>12505.65</v>
+        <v>9123.11</v>
       </c>
       <c r="L62" s="1">
-        <v>12934.02</v>
+        <v>9519.4</v>
       </c>
       <c r="M62" s="3">
-        <v>-125.26</v>
+        <v>-141.61</v>
       </c>
       <c r="N62" s="3">
-        <v>-150.83</v>
+        <v>-129.11</v>
       </c>
       <c r="O62" s="3">
-        <v>-86.46</v>
+        <v>-244.33</v>
       </c>
       <c r="P62" s="3">
-        <v>3.2</v>
+        <v>-150.14</v>
       </c>
       <c r="Q62" s="3">
-        <v>640.24</v>
+        <v>776.06</v>
       </c>
       <c r="R62" s="3">
-        <v>828.13</v>
+        <v>1088.64</v>
       </c>
       <c r="S62" s="3">
-        <v>41.93</v>
-      </c>
-      <c r="T62" t="str">
+        <v>27.83</v>
+      </c>
+      <c r="T62" s="3">
+        <v>8.58</v>
+      </c>
+      <c r="U62" s="3">
+        <v>40.86</v>
+      </c>
+      <c r="V62" s="3">
+        <v>48.21</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="str">
         <v/>
       </c>
     </row>
@@ -4254,60 +5184,75 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="C63" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="D63" s="1">
-        <v>10938.6</v>
+        <v>34520.05</v>
       </c>
       <c r="E63" s="2">
-        <v>-1.05</v>
+        <v>-1.66</v>
       </c>
       <c r="F63" s="2">
-        <v>-1.05</v>
+        <v>-4.62</v>
       </c>
       <c r="G63" s="2">
-        <v>-1.21</v>
+        <v>-5.78</v>
       </c>
       <c r="H63" s="2">
-        <v>-10.99</v>
+        <v>-2.28</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
       </c>
       <c r="J63" s="1">
-        <v>11510.65</v>
+        <v>37722.41</v>
       </c>
       <c r="K63" s="1">
-        <v>10982.36</v>
+        <v>35665.35</v>
       </c>
       <c r="L63" s="1">
-        <v>11533.73</v>
+        <v>37328.98</v>
       </c>
       <c r="M63" s="3">
-        <v>-165.76</v>
+        <v>-621.4</v>
       </c>
       <c r="N63" s="3">
-        <v>-187.83</v>
+        <v>-515.77</v>
       </c>
       <c r="O63" s="3">
-        <v>-142.76</v>
+        <v>-592.5</v>
       </c>
       <c r="P63" s="3">
-        <v>-39.79</v>
+        <v>-87.54</v>
       </c>
       <c r="Q63" s="3">
-        <v>225.56</v>
+        <v>889.89</v>
       </c>
       <c r="R63" s="3">
-        <v>395.78</v>
+        <v>1219.3</v>
       </c>
       <c r="S63" s="3">
-        <v>40.46</v>
-      </c>
-      <c r="T63" t="str">
+        <v>24.92</v>
+      </c>
+      <c r="T63" s="3">
+        <v>11.8</v>
+      </c>
+      <c r="U63" s="3">
+        <v>44.96</v>
+      </c>
+      <c r="V63" s="3">
+        <v>33.86</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="str">
         <v/>
       </c>
     </row>
@@ -4316,60 +5261,75 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>CNXMIDCAP</v>
+        <v>CNXMNC</v>
       </c>
       <c r="C64" t="str">
-        <v>CNXMIDCAP</v>
+        <v>CNXMNC</v>
       </c>
       <c r="D64" s="1">
-        <v>58487.95</v>
+        <v>27765.7</v>
       </c>
       <c r="E64" s="2">
-        <v>-1.09</v>
+        <v>-1.96</v>
       </c>
       <c r="F64" s="2">
-        <v>-1.09</v>
+        <v>-5.93</v>
       </c>
       <c r="G64" s="2">
-        <v>-1.42</v>
+        <v>-8.47</v>
       </c>
       <c r="H64" s="2">
-        <v>-3.3</v>
+        <v>-9.17</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
       </c>
       <c r="J64" s="1">
-        <v>60345.06</v>
+        <v>31386.59</v>
       </c>
       <c r="K64" s="1">
-        <v>59144.52</v>
+        <v>29044.94</v>
       </c>
       <c r="L64" s="1">
-        <v>61831.43</v>
+        <v>31421.13</v>
       </c>
       <c r="M64" s="3">
-        <v>-847.38</v>
+        <v>-832.31</v>
       </c>
       <c r="N64" s="3">
-        <v>-899.29</v>
+        <v>-698.23</v>
       </c>
       <c r="O64" s="3">
-        <v>-224.86</v>
+        <v>-522.2</v>
       </c>
       <c r="P64" s="3">
-        <v>439.1</v>
+        <v>61.35</v>
       </c>
       <c r="Q64" s="3">
-        <v>2942.36</v>
+        <v>1921.26</v>
       </c>
       <c r="R64" s="3">
-        <v>3494.39</v>
+        <v>2384.15</v>
       </c>
       <c r="S64" s="3">
-        <v>35.55</v>
-      </c>
-      <c r="T64" t="str">
+        <v>19.44</v>
+      </c>
+      <c r="T64" s="3">
+        <v>6.64</v>
+      </c>
+      <c r="U64" s="3">
+        <v>51.27</v>
+      </c>
+      <c r="V64" s="3">
+        <v>58.86</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="str">
         <v/>
       </c>
     </row>
@@ -4378,60 +5338,75 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>Nifty midcap 150</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="C65" t="str">
-        <v>NIFTYMIDCAP150</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="D65" s="1">
-        <v>21499.3</v>
+        <v>56812.1</v>
       </c>
       <c r="E65" s="2">
-        <v>-1.09</v>
+        <v>-2.05</v>
       </c>
       <c r="F65" s="2">
-        <v>-1.09</v>
+        <v>-5.73</v>
       </c>
       <c r="G65" s="2">
-        <v>-1.68</v>
+        <v>-6.52</v>
       </c>
       <c r="H65" s="2">
-        <v>-3.49</v>
+        <v>-8.24</v>
       </c>
       <c r="I65" s="1">
         <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>22194.72</v>
+        <v>61702.99</v>
       </c>
       <c r="K65" s="1">
-        <v>21742.54</v>
+        <v>59262.32</v>
       </c>
       <c r="L65" s="1">
-        <v>22724.19</v>
+        <v>62465.58</v>
       </c>
       <c r="M65" s="3">
-        <v>-313.55</v>
+        <v>-1173.13</v>
       </c>
       <c r="N65" s="3">
-        <v>-328.14</v>
+        <v>-867.23</v>
       </c>
       <c r="O65" s="3">
-        <v>-80.46</v>
+        <v>-508.97</v>
       </c>
       <c r="P65" s="3">
-        <v>162.72</v>
+        <v>188.66</v>
       </c>
       <c r="Q65" s="3">
-        <v>1726.57</v>
+        <v>-248.68</v>
       </c>
       <c r="R65" s="3">
-        <v>2031.93</v>
+        <v>-222.67</v>
       </c>
       <c r="S65" s="3">
-        <v>34.69</v>
-      </c>
-      <c r="T65" t="str">
+        <v>22.73</v>
+      </c>
+      <c r="T65" s="3">
+        <v>7.22</v>
+      </c>
+      <c r="U65" s="3">
+        <v>48.27</v>
+      </c>
+      <c r="V65" s="3">
+        <v>43.55</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="str">
         <v/>
       </c>
     </row>
@@ -4440,60 +5415,75 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>NIFTY100ESG</v>
+        <v>Nifty midcap 150</v>
       </c>
       <c r="C66" t="str">
-        <v>NIFTY100ESG</v>
+        <v>NIFTYMIDCAP150</v>
       </c>
       <c r="D66" s="1">
-        <v>4737.1</v>
+        <v>20592.75</v>
       </c>
       <c r="E66" s="2">
-        <v>-1.09</v>
+        <v>-2.07</v>
       </c>
       <c r="F66" s="2">
-        <v>-1.09</v>
+        <v>-5.26</v>
       </c>
       <c r="G66" s="2">
-        <v>1.14</v>
+        <v>-5.83</v>
       </c>
       <c r="H66" s="2">
-        <v>-8.57</v>
+        <v>-7.56</v>
       </c>
       <c r="I66" s="1">
         <v>0</v>
       </c>
       <c r="J66" s="1">
-        <v>4919.82</v>
+        <v>22176.63</v>
       </c>
       <c r="K66" s="1">
-        <v>4714.02</v>
+        <v>21361.29</v>
       </c>
       <c r="L66" s="1">
-        <v>4884.75</v>
+        <v>22574.75</v>
       </c>
       <c r="M66" s="3">
-        <v>-43.77</v>
+        <v>-417.73</v>
       </c>
       <c r="N66" s="3">
-        <v>-63.54</v>
+        <v>-353.09</v>
       </c>
       <c r="O66" s="3">
-        <v>-47.12</v>
+        <v>-152.78</v>
       </c>
       <c r="P66" s="3">
-        <v>-16.54</v>
+        <v>148.25</v>
       </c>
       <c r="Q66" s="3">
-        <v>223.49</v>
+        <v>1654.26</v>
       </c>
       <c r="R66" s="3">
-        <v>300.13</v>
+        <v>2017.46</v>
       </c>
       <c r="S66" s="3">
-        <v>47.48</v>
-      </c>
-      <c r="T66" t="str">
+        <v>23.29</v>
+      </c>
+      <c r="T66" s="3">
+        <v>7.88</v>
+      </c>
+      <c r="U66" s="3">
+        <v>48.75</v>
+      </c>
+      <c r="V66" s="3">
+        <v>49.67</v>
+      </c>
+      <c r="W66" s="3">
+        <v>0</v>
+      </c>
+      <c r="X66" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="str">
         <v/>
       </c>
     </row>
@@ -4502,60 +5492,75 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="C67" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="D67" s="1">
-        <v>22888.95</v>
+        <v>16066.4</v>
       </c>
       <c r="E67" s="2">
-        <v>-1.11</v>
+        <v>-2.1</v>
       </c>
       <c r="F67" s="2">
-        <v>-1.11</v>
+        <v>-5.19</v>
       </c>
       <c r="G67" s="2">
-        <v>1.19</v>
+        <v>-5.65</v>
       </c>
       <c r="H67" s="2">
-        <v>-12.4</v>
+        <v>-6.88</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
       </c>
       <c r="J67" s="1">
-        <v>24168.4</v>
+        <v>17219.19</v>
       </c>
       <c r="K67" s="1">
-        <v>22798.07</v>
+        <v>16647.11</v>
       </c>
       <c r="L67" s="1">
-        <v>23514.27</v>
+        <v>17635.02</v>
       </c>
       <c r="M67" s="3">
-        <v>-185.04</v>
+        <v>-336.34</v>
       </c>
       <c r="N67" s="3">
-        <v>-273.79</v>
+        <v>-293.24</v>
       </c>
       <c r="O67" s="3">
-        <v>-378</v>
+        <v>-89.81</v>
       </c>
       <c r="P67" s="3">
-        <v>-273.57</v>
+        <v>153.62</v>
       </c>
       <c r="Q67" s="3">
-        <v>200.23</v>
+        <v>859.98</v>
       </c>
       <c r="R67" s="3">
-        <v>600.9</v>
+        <v>1040.24</v>
       </c>
       <c r="S67" s="3">
-        <v>47.72</v>
-      </c>
-      <c r="T67" t="str">
+        <v>24.09</v>
+      </c>
+      <c r="T67" s="3">
+        <v>8.3</v>
+      </c>
+      <c r="U67" s="3">
+        <v>44.75</v>
+      </c>
+      <c r="V67" s="3">
+        <v>48.24</v>
+      </c>
+      <c r="W67" s="3">
+        <v>0</v>
+      </c>
+      <c r="X67" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="str">
         <v/>
       </c>
     </row>
@@ -4564,60 +5569,75 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="C68" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="D68" s="1">
-        <v>20045.25</v>
+        <v>13033.05</v>
       </c>
       <c r="E68" s="2">
-        <v>-1.11</v>
+        <v>-2.12</v>
       </c>
       <c r="F68" s="2">
-        <v>-1.11</v>
+        <v>-4.99</v>
       </c>
       <c r="G68" s="2">
-        <v>-1.81</v>
+        <v>-5.08</v>
       </c>
       <c r="H68" s="2">
-        <v>-0.85</v>
+        <v>-5.4</v>
       </c>
       <c r="I68" s="1">
         <v>0</v>
       </c>
       <c r="J68" s="1">
-        <v>20269.45</v>
+        <v>13996.84</v>
       </c>
       <c r="K68" s="1">
-        <v>20294.36</v>
+        <v>13483.59</v>
       </c>
       <c r="L68" s="1">
-        <v>21071.25</v>
+        <v>14305.74</v>
       </c>
       <c r="M68" s="3">
-        <v>-252.22</v>
+        <v>-271.86</v>
       </c>
       <c r="N68" s="3">
-        <v>-253.81</v>
+        <v>-246.11</v>
       </c>
       <c r="O68" s="3">
-        <v>46.95</v>
+        <v>-95.59</v>
       </c>
       <c r="P68" s="3">
-        <v>255.26</v>
+        <v>122.16</v>
       </c>
       <c r="Q68" s="3">
-        <v>1600.32</v>
+        <v>844.78</v>
       </c>
       <c r="R68" s="3">
-        <v>1827.81</v>
+        <v>995.64</v>
       </c>
       <c r="S68" s="3">
-        <v>35.17</v>
-      </c>
-      <c r="T68" t="str">
+        <v>25.6</v>
+      </c>
+      <c r="T68" s="3">
+        <v>8.87</v>
+      </c>
+      <c r="U68" s="3">
+        <v>41.89</v>
+      </c>
+      <c r="V68" s="3">
+        <v>45.32</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="str">
         <v/>
       </c>
     </row>
@@ -4626,60 +5646,75 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="C69" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="D69" s="1">
-        <v>13565.15</v>
+        <v>21727.8</v>
       </c>
       <c r="E69" s="2">
-        <v>-1.11</v>
+        <v>-2.14</v>
       </c>
       <c r="F69" s="2">
-        <v>-1.11</v>
+        <v>-5.39</v>
       </c>
       <c r="G69" s="2">
-        <v>-1.21</v>
+        <v>-4.56</v>
       </c>
       <c r="H69" s="2">
-        <v>-1.54</v>
+        <v>-9.69</v>
       </c>
       <c r="I69" s="1">
         <v>0</v>
       </c>
       <c r="J69" s="1">
-        <v>14003.41</v>
+        <v>23481.91</v>
       </c>
       <c r="K69" s="1">
-        <v>13704.6</v>
+        <v>22531.45</v>
       </c>
       <c r="L69" s="1">
-        <v>14407.94</v>
+        <v>23665.6</v>
       </c>
       <c r="M69" s="3">
-        <v>-218.84</v>
+        <v>-367.53</v>
       </c>
       <c r="N69" s="3">
-        <v>-240.63</v>
+        <v>-312.41</v>
       </c>
       <c r="O69" s="3">
-        <v>-53.14</v>
+        <v>-256.55</v>
       </c>
       <c r="P69" s="3">
-        <v>130.65</v>
+        <v>20.79</v>
       </c>
       <c r="Q69" s="3">
-        <v>887.23</v>
+        <v>963.56</v>
       </c>
       <c r="R69" s="3">
-        <v>1004.13</v>
+        <v>1347.55</v>
       </c>
       <c r="S69" s="3">
-        <v>36.03</v>
-      </c>
-      <c r="T69" t="str">
+        <v>26.17</v>
+      </c>
+      <c r="T69" s="3">
+        <v>10.69</v>
+      </c>
+      <c r="U69" s="3">
+        <v>47.02</v>
+      </c>
+      <c r="V69" s="3">
+        <v>41.23</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="str">
         <v/>
       </c>
     </row>
@@ -4688,60 +5723,75 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="C70" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="D70" s="1">
-        <v>35840.55</v>
+        <v>46788.25</v>
       </c>
       <c r="E70" s="2">
-        <v>-1.12</v>
+        <v>-2.18</v>
       </c>
       <c r="F70" s="2">
-        <v>-1.12</v>
+        <v>-5.68</v>
       </c>
       <c r="G70" s="2">
-        <v>-2.15</v>
+        <v>-5.62</v>
       </c>
       <c r="H70" s="2">
-        <v>-2.49</v>
+        <v>-1.63</v>
       </c>
       <c r="I70" s="1">
         <v>0</v>
       </c>
       <c r="J70" s="1">
-        <v>37126.93</v>
+        <v>49077.2</v>
       </c>
       <c r="K70" s="1">
-        <v>36345.95</v>
+        <v>48691.57</v>
       </c>
       <c r="L70" s="1">
-        <v>38605.84</v>
+        <v>50765.67</v>
       </c>
       <c r="M70" s="3">
-        <v>-700.92</v>
+        <v>-743.9</v>
       </c>
       <c r="N70" s="3">
-        <v>-737.05</v>
+        <v>-528.11</v>
       </c>
       <c r="O70" s="3">
-        <v>-143</v>
+        <v>-3.03</v>
       </c>
       <c r="P70" s="3">
-        <v>326.12</v>
+        <v>536.27</v>
       </c>
       <c r="Q70" s="3">
-        <v>685.97</v>
+        <v>-58.33</v>
       </c>
       <c r="R70" s="3">
-        <v>949.36</v>
+        <v>-322.83</v>
       </c>
       <c r="S70" s="3">
-        <v>34.08</v>
-      </c>
-      <c r="T70" t="str">
+        <v>24.75</v>
+      </c>
+      <c r="T70" s="3">
+        <v>7.78</v>
+      </c>
+      <c r="U70" s="3">
+        <v>47.99</v>
+      </c>
+      <c r="V70" s="3">
+        <v>44.09</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="str">
         <v/>
       </c>
     </row>
@@ -4750,60 +5800,75 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="C71" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="D71" s="1">
-        <v>17435.15</v>
+        <v>55800.65</v>
       </c>
       <c r="E71" s="2">
-        <v>-1.15</v>
+        <v>-2.21</v>
       </c>
       <c r="F71" s="2">
-        <v>-1.15</v>
+        <v>-5.63</v>
       </c>
       <c r="G71" s="2">
-        <v>-2.04</v>
+        <v>-5.95</v>
       </c>
       <c r="H71" s="2">
-        <v>4.5</v>
+        <v>-7.74</v>
       </c>
       <c r="I71" s="1">
         <v>0</v>
       </c>
       <c r="J71" s="1">
-        <v>16946.17</v>
+        <v>60295.21</v>
       </c>
       <c r="K71" s="1">
-        <v>17687.1</v>
+        <v>58034.89</v>
       </c>
       <c r="L71" s="1">
-        <v>18138.87</v>
+        <v>61416.78</v>
       </c>
       <c r="M71" s="3">
-        <v>-154.43</v>
+        <v>-1161.74</v>
       </c>
       <c r="N71" s="3">
-        <v>-136.52</v>
+        <v>-971.27</v>
       </c>
       <c r="O71" s="3">
-        <v>238.04</v>
+        <v>-439.23</v>
       </c>
       <c r="P71" s="3">
-        <v>389.47</v>
+        <v>396.23</v>
       </c>
       <c r="Q71" s="3">
-        <v>1339.23</v>
+        <v>2727.99</v>
       </c>
       <c r="R71" s="3">
-        <v>1435.09</v>
+        <v>3451.52</v>
       </c>
       <c r="S71" s="3">
-        <v>36.74</v>
-      </c>
-      <c r="T71" t="str">
+        <v>23.59</v>
+      </c>
+      <c r="T71" s="3">
+        <v>7.52</v>
+      </c>
+      <c r="U71" s="3">
+        <v>48.47</v>
+      </c>
+      <c r="V71" s="3">
+        <v>50.15</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="str">
         <v/>
       </c>
     </row>
@@ -4812,60 +5877,75 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="C72" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="D72" s="1">
-        <v>7373.5</v>
+        <v>8070.7</v>
       </c>
       <c r="E72" s="2">
-        <v>-1.15</v>
+        <v>-2.26</v>
       </c>
       <c r="F72" s="2">
-        <v>-1.15</v>
+        <v>-0.3</v>
       </c>
       <c r="G72" s="2">
-        <v>4.2</v>
+        <v>0.68</v>
       </c>
       <c r="H72" s="2">
-        <v>-2.5</v>
+        <v>-5.42</v>
       </c>
       <c r="I72" s="1">
         <v>0</v>
       </c>
       <c r="J72" s="1">
-        <v>7336.18</v>
+        <v>8571.95</v>
       </c>
       <c r="K72" s="1">
-        <v>7277.83</v>
+        <v>8152.13</v>
       </c>
       <c r="L72" s="1">
-        <v>7418.47</v>
+        <v>8345.06</v>
       </c>
       <c r="M72" s="3">
-        <v>-14.64</v>
+        <v>-35.55</v>
       </c>
       <c r="N72" s="3">
-        <v>-58.79</v>
+        <v>-62.29</v>
       </c>
       <c r="O72" s="3">
-        <v>2.99</v>
+        <v>-89.97</v>
       </c>
       <c r="P72" s="3">
-        <v>32.07</v>
+        <v>-32.65</v>
       </c>
       <c r="Q72" s="3">
-        <v>473.87</v>
+        <v>560.95</v>
       </c>
       <c r="R72" s="3">
-        <v>552.98</v>
+        <v>682.51</v>
       </c>
       <c r="S72" s="3">
-        <v>54.92</v>
-      </c>
-      <c r="T72" t="str">
+        <v>44.6</v>
+      </c>
+      <c r="T72" s="3">
+        <v>20.41</v>
+      </c>
+      <c r="U72" s="3">
+        <v>22.71</v>
+      </c>
+      <c r="V72" s="3">
+        <v>18.58</v>
+      </c>
+      <c r="W72" s="3">
+        <v>0</v>
+      </c>
+      <c r="X72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="str">
         <v/>
       </c>
     </row>
@@ -4874,60 +5954,75 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="C73" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="D73" s="1">
-        <v>22698.65</v>
+        <v>65828.6</v>
       </c>
       <c r="E73" s="2">
-        <v>-1.16</v>
+        <v>-2.27</v>
       </c>
       <c r="F73" s="2">
-        <v>-1.16</v>
+        <v>-4.58</v>
       </c>
       <c r="G73" s="2">
-        <v>-0.3</v>
+        <v>-5.62</v>
       </c>
       <c r="H73" s="2">
-        <v>-5.65</v>
+        <v>-5.1</v>
       </c>
       <c r="I73" s="1">
         <v>0</v>
       </c>
       <c r="J73" s="1">
-        <v>23508.76</v>
+        <v>70018.75</v>
       </c>
       <c r="K73" s="1">
-        <v>22906.09</v>
+        <v>67998.34</v>
       </c>
       <c r="L73" s="1">
-        <v>23833.06</v>
+        <v>71491.06</v>
       </c>
       <c r="M73" s="3">
-        <v>-257.13</v>
+        <v>-1177.52</v>
       </c>
       <c r="N73" s="3">
-        <v>-301.12</v>
+        <v>-1032.13</v>
       </c>
       <c r="O73" s="3">
-        <v>-179.1</v>
+        <v>-344.01</v>
       </c>
       <c r="P73" s="3">
-        <v>36.28</v>
+        <v>549.61</v>
       </c>
       <c r="Q73" s="3">
-        <v>1041.01</v>
+        <v>2518.21</v>
       </c>
       <c r="R73" s="3">
-        <v>1363.04</v>
+        <v>3153.26</v>
       </c>
       <c r="S73" s="3">
-        <v>38.63</v>
-      </c>
-      <c r="T73" t="str">
+        <v>26.84</v>
+      </c>
+      <c r="T73" s="3">
+        <v>8.92</v>
+      </c>
+      <c r="U73" s="3">
+        <v>43.18</v>
+      </c>
+      <c r="V73" s="3">
+        <v>47.66</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="str">
         <v/>
       </c>
     </row>
@@ -4936,60 +6031,75 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="C74" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="D74" s="1">
-        <v>19244.1</v>
+        <v>26325</v>
       </c>
       <c r="E74" s="2">
-        <v>-1.16</v>
+        <v>-2.32</v>
       </c>
       <c r="F74" s="2">
-        <v>-1.16</v>
+        <v>-7.19</v>
       </c>
       <c r="G74" s="2">
-        <v>1.59</v>
-      </c>
-      <c r="H74" s="2">
-        <v>-10.12</v>
+        <v>-7.19</v>
+      </c>
+      <c r="H74" t="str">
+        <v/>
       </c>
       <c r="I74" s="1">
         <v>0</v>
       </c>
-      <c r="J74" s="1">
-        <v>20122.6</v>
+      <c r="J74" t="str">
+        <v/>
       </c>
       <c r="K74" s="1">
-        <v>19201.68</v>
+        <v>27601.95</v>
       </c>
       <c r="L74" s="1">
-        <v>19894.51</v>
+        <v>29242.38</v>
       </c>
       <c r="M74" s="3">
-        <v>-157.5</v>
+        <v>-581.26</v>
       </c>
       <c r="N74" s="3">
-        <v>-252.48</v>
+        <v>-450.01</v>
       </c>
       <c r="O74" s="3">
-        <v>-258.22</v>
+        <v>-256.82</v>
       </c>
       <c r="P74" s="3">
-        <v>-137.4</v>
+        <v>158.35</v>
       </c>
       <c r="Q74" s="3">
-        <v>507.8</v>
+        <v>156.03</v>
       </c>
       <c r="R74" s="3">
-        <v>799.61</v>
+        <v>172.48</v>
       </c>
       <c r="S74" s="3">
-        <v>46.93</v>
-      </c>
-      <c r="T74" t="str">
+        <v>25.08</v>
+      </c>
+      <c r="T74" s="3">
+        <v>11.18</v>
+      </c>
+      <c r="U74" s="3">
+        <v>46.39</v>
+      </c>
+      <c r="V74" s="3">
+        <v>39.31</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="str">
         <v/>
       </c>
     </row>
@@ -4998,60 +6108,75 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>CNXREALTY</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="C75" t="str">
-        <v>CNXREALTY</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="D75" s="1">
-        <v>816.05</v>
+        <v>23827.1</v>
       </c>
       <c r="E75" s="2">
-        <v>-1.2</v>
+        <v>-2.32</v>
       </c>
       <c r="F75" s="2">
-        <v>-1.2</v>
+        <v>-7.42</v>
       </c>
       <c r="G75" s="2">
-        <v>-3.69</v>
+        <v>-9.23</v>
       </c>
       <c r="H75" s="2">
-        <v>-7.05</v>
+        <v>5.68</v>
       </c>
       <c r="I75" s="1">
         <v>0</v>
       </c>
       <c r="J75" s="1">
-        <v>822.91</v>
+        <v>23624.75</v>
       </c>
       <c r="K75" s="1">
-        <v>824.12</v>
+        <v>25056.82</v>
       </c>
       <c r="L75" s="1">
-        <v>867.25</v>
+        <v>26074.8</v>
       </c>
       <c r="M75" s="3">
-        <v>-13.57</v>
+        <v>-431.12</v>
       </c>
       <c r="N75" s="3">
-        <v>-14.54</v>
+        <v>-225.33</v>
       </c>
       <c r="O75" s="3">
-        <v>0.89</v>
+        <v>565.85</v>
       </c>
       <c r="P75" s="3">
-        <v>10.72</v>
+        <v>848.15</v>
       </c>
       <c r="Q75" s="3">
-        <v>2.54</v>
+        <v>2245.38</v>
       </c>
       <c r="R75" s="3">
-        <v>10.09</v>
+        <v>2341.77</v>
       </c>
       <c r="S75" s="3">
-        <v>41.05</v>
-      </c>
-      <c r="T75" t="str">
+        <v>25.8</v>
+      </c>
+      <c r="T75" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="U75" s="3">
+        <v>51.06</v>
+      </c>
+      <c r="V75" s="3">
+        <v>33.44</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="str">
         <v/>
       </c>
     </row>
@@ -5060,60 +6185,75 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="C76" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="D76" s="1">
-        <v>11392.1</v>
+        <v>19071.8</v>
       </c>
       <c r="E76" s="2">
-        <v>-1.22</v>
+        <v>-2.33</v>
       </c>
       <c r="F76" s="2">
-        <v>-1.22</v>
+        <v>-5.91</v>
       </c>
       <c r="G76" s="2">
-        <v>2.21</v>
+        <v>-6.58</v>
       </c>
       <c r="H76" s="2">
-        <v>-14.19</v>
+        <v>-5.67</v>
       </c>
       <c r="I76" s="1">
         <v>0</v>
       </c>
       <c r="J76" s="1">
-        <v>12199.92</v>
+        <v>20259.6</v>
       </c>
       <c r="K76" s="1">
-        <v>11310.44</v>
+        <v>19886.07</v>
       </c>
       <c r="L76" s="1">
-        <v>11584.13</v>
+        <v>20941.94</v>
       </c>
       <c r="M76" s="3">
-        <v>-59.98</v>
+        <v>-379.38</v>
       </c>
       <c r="N76" s="3">
-        <v>-115.63</v>
+        <v>-293.14</v>
       </c>
       <c r="O76" s="3">
-        <v>-258.76</v>
+        <v>-30.7</v>
       </c>
       <c r="P76" s="3">
-        <v>-234.58</v>
+        <v>239.72</v>
       </c>
       <c r="Q76" s="3">
-        <v>-124.74</v>
+        <v>1522.67</v>
       </c>
       <c r="R76" s="3">
-        <v>115.49</v>
+        <v>1812.28</v>
       </c>
       <c r="S76" s="3">
-        <v>50.91</v>
-      </c>
-      <c r="T76" t="str">
+        <v>22.43</v>
+      </c>
+      <c r="T76" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="U76" s="3">
+        <v>53.33</v>
+      </c>
+      <c r="V76" s="3">
+        <v>48.25</v>
+      </c>
+      <c r="W76" s="3">
+        <v>0</v>
+      </c>
+      <c r="X76" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="str">
         <v/>
       </c>
     </row>
@@ -5122,60 +6262,75 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="C77" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="D77" s="1">
-        <v>30099.85</v>
+        <v>784.35</v>
       </c>
       <c r="E77" s="2">
-        <v>-1.25</v>
+        <v>-2.38</v>
       </c>
       <c r="F77" s="2">
-        <v>-1.25</v>
+        <v>-5.04</v>
       </c>
       <c r="G77" s="2">
-        <v>3.74</v>
+        <v>-7.43</v>
       </c>
       <c r="H77" s="2">
-        <v>-10.57</v>
+        <v>-10.66</v>
       </c>
       <c r="I77" s="1">
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>30995.16</v>
+        <v>821.76</v>
       </c>
       <c r="K77" s="1">
-        <v>29659.55</v>
+        <v>811.59</v>
       </c>
       <c r="L77" s="1">
-        <v>30157.43</v>
+        <v>861.67</v>
       </c>
       <c r="M77" s="3">
-        <v>-65.9</v>
+        <v>-16.39</v>
       </c>
       <c r="N77" s="3">
-        <v>-249.18</v>
+        <v>-14.88</v>
       </c>
       <c r="O77" s="3">
-        <v>-346.4</v>
+        <v>-1.64</v>
       </c>
       <c r="P77" s="3">
-        <v>-314.78</v>
+        <v>10.22</v>
       </c>
       <c r="Q77" s="3">
-        <v>495.29</v>
+        <v>0.01</v>
       </c>
       <c r="R77" s="3">
-        <v>993.55</v>
+        <v>9.58</v>
       </c>
       <c r="S77" s="3">
-        <v>55.9</v>
-      </c>
-      <c r="T77" t="str">
+        <v>32.65</v>
+      </c>
+      <c r="T77" s="3">
+        <v>12.73</v>
+      </c>
+      <c r="U77" s="3">
+        <v>36.25</v>
+      </c>
+      <c r="V77" s="3">
+        <v>27.1</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="str">
         <v/>
       </c>
     </row>
@@ -5184,60 +6339,75 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="C78" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="D78" s="1">
-        <v>15866</v>
+        <v>27301.75</v>
       </c>
       <c r="E78" s="2">
-        <v>-1.27</v>
+        <v>-2.47</v>
       </c>
       <c r="F78" s="2">
-        <v>-1.27</v>
+        <v>-6.15</v>
       </c>
       <c r="G78" s="2">
-        <v>-2.6</v>
+        <v>-7.51</v>
       </c>
       <c r="H78" s="2">
-        <v>-0.86</v>
+        <v>-12.35</v>
       </c>
       <c r="I78" s="1">
         <v>0</v>
       </c>
       <c r="J78" s="1">
-        <v>16134.51</v>
+        <v>30366.63</v>
       </c>
       <c r="K78" s="1">
-        <v>16147.79</v>
+        <v>28588.86</v>
       </c>
       <c r="L78" s="1">
-        <v>16888.42</v>
+        <v>30194.41</v>
       </c>
       <c r="M78" s="3">
-        <v>-238.03</v>
+        <v>-592.61</v>
       </c>
       <c r="N78" s="3">
-        <v>-235.4</v>
+        <v>-435.76</v>
       </c>
       <c r="O78" s="3">
-        <v>43.53</v>
+        <v>-430.86</v>
       </c>
       <c r="P78" s="3">
-        <v>234.52</v>
+        <v>-104.64</v>
       </c>
       <c r="Q78" s="3">
-        <v>1565.9</v>
+        <v>1361.55</v>
       </c>
       <c r="R78" s="3">
-        <v>1751.51</v>
+        <v>1982.03</v>
       </c>
       <c r="S78" s="3">
-        <v>35.7</v>
-      </c>
-      <c r="T78" t="str">
+        <v>23.16</v>
+      </c>
+      <c r="T78" s="3">
+        <v>7.9</v>
+      </c>
+      <c r="U78" s="3">
+        <v>47.59</v>
+      </c>
+      <c r="V78" s="3">
+        <v>40.68</v>
+      </c>
+      <c r="W78" s="3">
+        <v>0</v>
+      </c>
+      <c r="X78" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="str">
         <v/>
       </c>
     </row>
@@ -5246,60 +6416,75 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>Nifty IT</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="C79" t="str">
-        <v>CNXIT</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="D79" s="1">
-        <v>31516.3</v>
+        <v>4930.05</v>
       </c>
       <c r="E79" s="2">
-        <v>-1.28</v>
+        <v>-2.5</v>
       </c>
       <c r="F79" s="2">
-        <v>-1.28</v>
+        <v>-5.95</v>
       </c>
       <c r="G79" s="2">
-        <v>13.76</v>
+        <v>-3.14</v>
       </c>
       <c r="H79" s="2">
-        <v>-16.81</v>
+        <v>5.88</v>
       </c>
       <c r="I79" s="1">
         <v>0</v>
       </c>
       <c r="J79" s="1">
-        <v>30903.39</v>
+        <v>5106.68</v>
       </c>
       <c r="K79" s="1">
-        <v>29999.76</v>
+        <v>5130.1</v>
       </c>
       <c r="L79" s="1">
-        <v>29809.61</v>
+        <v>5294.25</v>
       </c>
       <c r="M79" s="3">
-        <v>395.38</v>
+        <v>-58.04</v>
       </c>
       <c r="N79" s="3">
-        <v>-87.44</v>
+        <v>-37.62</v>
       </c>
       <c r="O79" s="3">
-        <v>-195.07</v>
+        <v>17.34</v>
       </c>
       <c r="P79" s="3">
-        <v>-527.2</v>
+        <v>84.49</v>
       </c>
       <c r="Q79" s="3">
-        <v>-1699.24</v>
+        <v>353.78</v>
       </c>
       <c r="R79" s="3">
-        <v>-1155.4</v>
+        <v>323.22</v>
       </c>
       <c r="S79" s="3">
-        <v>68.53</v>
-      </c>
-      <c r="T79" t="str">
+        <v>33.17</v>
+      </c>
+      <c r="T79" s="3">
+        <v>14.11</v>
+      </c>
+      <c r="U79" s="3">
+        <v>35.52</v>
+      </c>
+      <c r="V79" s="3">
+        <v>22.2</v>
+      </c>
+      <c r="W79" s="3">
+        <v>0</v>
+      </c>
+      <c r="X79" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="str">
         <v/>
       </c>
     </row>
@@ -5308,60 +6493,75 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="C80" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="D80" s="1">
-        <v>8336.65</v>
+        <v>23666.85</v>
       </c>
       <c r="E80" s="2">
-        <v>-1.32</v>
+        <v>-2.56</v>
       </c>
       <c r="F80" s="2">
-        <v>-1.32</v>
+        <v>-6.1</v>
       </c>
       <c r="G80" s="2">
-        <v>3.21</v>
+        <v>-6.8</v>
       </c>
       <c r="H80" s="2">
-        <v>-17</v>
+        <v>-5.28</v>
       </c>
       <c r="I80" s="1">
         <v>0</v>
       </c>
       <c r="J80" s="1">
-        <v>8788.93</v>
+        <v>25466.45</v>
       </c>
       <c r="K80" s="1">
-        <v>8269.57</v>
+        <v>24754.22</v>
       </c>
       <c r="L80" s="1">
-        <v>8415.39</v>
+        <v>26109.43</v>
       </c>
       <c r="M80" s="3">
-        <v>-20.17</v>
+        <v>-484.27</v>
       </c>
       <c r="N80" s="3">
-        <v>-63.71</v>
+        <v>-363.85</v>
       </c>
       <c r="O80" s="3">
-        <v>-157.19</v>
+        <v>-111.79</v>
       </c>
       <c r="P80" s="3">
-        <v>-157.96</v>
+        <v>204.73</v>
       </c>
       <c r="Q80" s="3">
-        <v>-302.52</v>
+        <v>1.84</v>
       </c>
       <c r="R80" s="3">
-        <v>-191.83</v>
+        <v>-68.08</v>
       </c>
       <c r="S80" s="3">
-        <v>52.96</v>
-      </c>
-      <c r="T80" t="str">
+        <v>24.96</v>
+      </c>
+      <c r="T80" s="3">
+        <v>7.96</v>
+      </c>
+      <c r="U80" s="3">
+        <v>46.37</v>
+      </c>
+      <c r="V80" s="3">
+        <v>39.95</v>
+      </c>
+      <c r="W80" s="3">
+        <v>0</v>
+      </c>
+      <c r="X80" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="str">
         <v/>
       </c>
     </row>
@@ -5370,60 +6570,75 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="C81" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="D81" s="1">
-        <v>8552.4</v>
+        <v>15043.45</v>
       </c>
       <c r="E81" s="2">
-        <v>-1.36</v>
+        <v>-2.56</v>
       </c>
       <c r="F81" s="2">
-        <v>-1.36</v>
+        <v>-6.39</v>
       </c>
       <c r="G81" s="2">
-        <v>6.55</v>
+        <v>-7.65</v>
       </c>
       <c r="H81" s="2">
-        <v>-9.23</v>
+        <v>-6</v>
       </c>
       <c r="I81" s="1">
         <v>0</v>
       </c>
       <c r="J81" s="1">
-        <v>8266.39</v>
+        <v>16126.11</v>
       </c>
       <c r="K81" s="1">
-        <v>8389.27</v>
+        <v>15773.12</v>
       </c>
       <c r="L81" s="1">
-        <v>8541.32</v>
+        <v>16777.1</v>
       </c>
       <c r="M81" s="3">
-        <v>-4.23</v>
+        <v>-353.58</v>
       </c>
       <c r="N81" s="3">
-        <v>-71.71</v>
+        <v>-273.59</v>
       </c>
       <c r="O81" s="3">
-        <v>68.86</v>
+        <v>-22.09</v>
       </c>
       <c r="P81" s="3">
-        <v>59.81</v>
+        <v>221.39</v>
       </c>
       <c r="Q81" s="3">
-        <v>375.34</v>
+        <v>1500.29</v>
       </c>
       <c r="R81" s="3">
-        <v>514.31</v>
+        <v>1738.39</v>
       </c>
       <c r="S81" s="3">
-        <v>58.1</v>
-      </c>
-      <c r="T81" t="str">
+        <v>24.61</v>
+      </c>
+      <c r="T81" s="3">
+        <v>9.2</v>
+      </c>
+      <c r="U81" s="3">
+        <v>45.78</v>
+      </c>
+      <c r="V81" s="3">
+        <v>43.14</v>
+      </c>
+      <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="str">
         <v/>
       </c>
     </row>
@@ -5432,60 +6647,75 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="C82" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="D82" s="1">
-        <v>3813</v>
+        <v>49069.75</v>
       </c>
       <c r="E82" s="2">
-        <v>-1.36</v>
+        <v>-2.59</v>
       </c>
       <c r="F82" s="2">
-        <v>-1.36</v>
+        <v>-6.2</v>
       </c>
       <c r="G82" s="2">
-        <v>0.81</v>
+        <v>-7.23</v>
       </c>
       <c r="H82" s="2">
-        <v>-12.41</v>
+        <v>-6.9</v>
       </c>
       <c r="I82" s="1">
         <v>0</v>
       </c>
       <c r="J82" s="1">
-        <v>4040.15</v>
+        <v>52524.13</v>
       </c>
       <c r="K82" s="1">
-        <v>3803.95</v>
+        <v>51482.54</v>
       </c>
       <c r="L82" s="1">
-        <v>3939.04</v>
+        <v>53982.39</v>
       </c>
       <c r="M82" s="3">
-        <v>-36.3</v>
+        <v>-947.88</v>
       </c>
       <c r="N82" s="3">
-        <v>-50.99</v>
+        <v>-620.66</v>
       </c>
       <c r="O82" s="3">
-        <v>-64.32</v>
+        <v>-126.79</v>
       </c>
       <c r="P82" s="3">
-        <v>-42.15</v>
+        <v>413.04</v>
       </c>
       <c r="Q82" s="3">
-        <v>127.86</v>
+        <v>-909.94</v>
       </c>
       <c r="R82" s="3">
-        <v>207.1</v>
+        <v>-1153.68</v>
       </c>
       <c r="S82" s="3">
-        <v>46.26</v>
-      </c>
-      <c r="T82" t="str">
+        <v>24.22</v>
+      </c>
+      <c r="T82" s="3">
+        <v>7.98</v>
+      </c>
+      <c r="U82" s="3">
+        <v>50.9</v>
+      </c>
+      <c r="V82" s="3">
+        <v>40.6</v>
+      </c>
+      <c r="W82" s="3">
+        <v>0</v>
+      </c>
+      <c r="X82" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="str">
         <v/>
       </c>
     </row>
@@ -5494,60 +6724,75 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="C83" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="D83" s="1">
-        <v>26836.5</v>
+        <v>8561.2</v>
       </c>
       <c r="E83" s="2">
-        <v>-1.38</v>
+        <v>-2.6</v>
       </c>
       <c r="F83" s="2">
-        <v>-1.38</v>
+        <v>-7.05</v>
       </c>
       <c r="G83" s="2">
-        <v>1.05</v>
+        <v>-7.71</v>
       </c>
       <c r="H83" s="2">
-        <v>-11.07</v>
+        <v>10.5</v>
       </c>
       <c r="I83" s="1">
         <v>0</v>
       </c>
       <c r="J83" s="1">
-        <v>28581.69</v>
+        <v>8842.66</v>
       </c>
       <c r="K83" s="1">
-        <v>26935.59</v>
+        <v>8980.74</v>
       </c>
       <c r="L83" s="1">
-        <v>27702.92</v>
+        <v>9456.74</v>
       </c>
       <c r="M83" s="3">
-        <v>-198.76</v>
+        <v>-161.86</v>
       </c>
       <c r="N83" s="3">
-        <v>-288.55</v>
+        <v>-118.83</v>
       </c>
       <c r="O83" s="3">
-        <v>-456.58</v>
+        <v>81.2</v>
       </c>
       <c r="P83" s="3">
-        <v>-290.92</v>
+        <v>230.92</v>
       </c>
       <c r="Q83" s="3">
-        <v>1333.07</v>
+        <v>583.08</v>
       </c>
       <c r="R83" s="3">
-        <v>1904.53</v>
+        <v>518.72</v>
       </c>
       <c r="S83" s="3">
-        <v>44.54</v>
-      </c>
-      <c r="T83" t="str">
+        <v>29.31</v>
+      </c>
+      <c r="T83" s="3">
+        <v>14.22</v>
+      </c>
+      <c r="U83" s="3">
+        <v>44.26</v>
+      </c>
+      <c r="V83" s="3">
+        <v>27.3</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="str">
         <v/>
       </c>
     </row>
@@ -5556,60 +6801,75 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>NIFTYFMCG</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="C84" t="str">
-        <v>NIFTYFMCG</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="D84" s="1">
-        <v>43975.5</v>
+        <v>33922</v>
       </c>
       <c r="E84" s="2">
-        <v>-1.44</v>
+        <v>-2.63</v>
       </c>
       <c r="F84" s="2">
-        <v>-1.44</v>
+        <v>-6.42</v>
       </c>
       <c r="G84" s="2">
-        <v>-1.2</v>
+        <v>-7.39</v>
       </c>
       <c r="H84" s="2">
-        <v>-20.73</v>
+        <v>-7.71</v>
       </c>
       <c r="I84" s="1">
         <v>0</v>
       </c>
       <c r="J84" s="1">
-        <v>49087.83</v>
+        <v>37099.43</v>
       </c>
       <c r="K84" s="1">
-        <v>44615.97</v>
+        <v>35538.35</v>
       </c>
       <c r="L84" s="1">
-        <v>46121.99</v>
+        <v>38271.87</v>
       </c>
       <c r="M84" s="3">
-        <v>-456.81</v>
+        <v>-914.61</v>
       </c>
       <c r="N84" s="3">
-        <v>-504.62</v>
+        <v>-785.28</v>
       </c>
       <c r="O84" s="3">
-        <v>-1598.77</v>
+        <v>-296.05</v>
       </c>
       <c r="P84" s="3">
-        <v>-1340.83</v>
+        <v>295.51</v>
       </c>
       <c r="Q84" s="3">
-        <v>-2116.54</v>
+        <v>532.92</v>
       </c>
       <c r="R84" s="3">
-        <v>-956.12</v>
+        <v>918.75</v>
       </c>
       <c r="S84" s="3">
-        <v>40.88</v>
-      </c>
-      <c r="T84" t="str">
+        <v>22.78</v>
+      </c>
+      <c r="T84" s="3">
+        <v>6.32</v>
+      </c>
+      <c r="U84" s="3">
+        <v>45.13</v>
+      </c>
+      <c r="V84" s="3">
+        <v>56</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" t="str">
         <v/>
       </c>
     </row>
@@ -5618,60 +6878,75 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="C85" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="D85" s="1">
-        <v>24987.1</v>
+        <v>44470.2</v>
       </c>
       <c r="E85" s="2">
-        <v>-1.58</v>
+        <v>-2.65</v>
       </c>
       <c r="F85" s="2">
-        <v>-1.58</v>
+        <v>-6.73</v>
       </c>
       <c r="G85" s="2">
-        <v>1.37</v>
+        <v>-7.08</v>
       </c>
       <c r="H85" s="2">
-        <v>-9.51</v>
+        <v>1.1</v>
       </c>
       <c r="I85" s="1">
         <v>0</v>
       </c>
       <c r="J85" s="1">
-        <v>26250.15</v>
+        <v>44929.21</v>
       </c>
       <c r="K85" s="1">
-        <v>25067.99</v>
+        <v>46643.68</v>
       </c>
       <c r="L85" s="1">
-        <v>25597.84</v>
+        <v>48280.02</v>
       </c>
       <c r="M85" s="3">
-        <v>-121.71</v>
+        <v>-654.52</v>
       </c>
       <c r="N85" s="3">
-        <v>-206.59</v>
+        <v>-358.76</v>
       </c>
       <c r="O85" s="3">
-        <v>-331.83</v>
+        <v>655.34</v>
       </c>
       <c r="P85" s="3">
-        <v>-217.64</v>
+        <v>1101.74</v>
       </c>
       <c r="Q85" s="3">
-        <v>674.52</v>
+        <v>-453.49</v>
       </c>
       <c r="R85" s="3">
-        <v>1086.46</v>
+        <v>-1042.54</v>
       </c>
       <c r="S85" s="3">
-        <v>46.17</v>
-      </c>
-      <c r="T85" t="str">
+        <v>25.55</v>
+      </c>
+      <c r="T85" s="3">
+        <v>11.54</v>
+      </c>
+      <c r="U85" s="3">
+        <v>50.12</v>
+      </c>
+      <c r="V85" s="3">
+        <v>32.55</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" t="str">
         <v/>
       </c>
     </row>
@@ -5680,60 +6955,75 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="C86" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="D86" s="1">
-        <v>27914.3</v>
+        <v>11478.2</v>
       </c>
       <c r="E86" s="2">
-        <v>-1.59</v>
+        <v>-2.71</v>
       </c>
       <c r="F86" s="2">
-        <v>-1.59</v>
+        <v>-5.4</v>
       </c>
       <c r="G86" s="2">
-        <v>-1.58</v>
-      </c>
-      <c r="H86" t="str">
-        <v/>
+        <v>-10.05</v>
+      </c>
+      <c r="H86" s="2">
+        <v>2.78</v>
       </c>
       <c r="I86" s="1">
         <v>0</v>
       </c>
-      <c r="J86" t="str">
-        <v/>
+      <c r="J86" s="1">
+        <v>12483.72</v>
       </c>
       <c r="K86" s="1">
-        <v>28297.32</v>
+        <v>11951.39</v>
       </c>
       <c r="L86" s="1">
-        <v>29468.3</v>
+        <v>12804.74</v>
       </c>
       <c r="M86" s="3">
-        <v>-354.18</v>
+        <v>-315.57</v>
       </c>
       <c r="N86" s="3">
-        <v>-394.92</v>
+        <v>-267.05</v>
       </c>
       <c r="O86" s="3">
-        <v>-130.04</v>
+        <v>-15.01</v>
       </c>
       <c r="P86" s="3">
-        <v>183.71</v>
+        <v>202.89</v>
       </c>
       <c r="Q86" s="3">
-        <v>282.81</v>
+        <v>1107.38</v>
       </c>
       <c r="R86" s="3">
-        <v>197.84</v>
+        <v>1124.17</v>
       </c>
       <c r="S86" s="3">
-        <v>37.94</v>
-      </c>
-      <c r="T86" t="str">
+        <v>27.87</v>
+      </c>
+      <c r="T86" s="3">
+        <v>10.69</v>
+      </c>
+      <c r="U86" s="3">
+        <v>40.86</v>
+      </c>
+      <c r="V86" s="3">
+        <v>35.32</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="str">
         <v/>
       </c>
     </row>
@@ -5742,60 +7032,75 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="C87" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="D87" s="1">
-        <v>25306.15</v>
+        <v>16385.15</v>
       </c>
       <c r="E87" s="2">
-        <v>-1.67</v>
+        <v>-2.79</v>
       </c>
       <c r="F87" s="2">
-        <v>-1.67</v>
+        <v>-7.1</v>
       </c>
       <c r="G87" s="2">
-        <v>-3.6</v>
+        <v>-7.94</v>
       </c>
       <c r="H87" s="2">
-        <v>12.24</v>
+        <v>-1.8</v>
       </c>
       <c r="I87" s="1">
         <v>0</v>
       </c>
       <c r="J87" s="1">
-        <v>23595.54</v>
+        <v>16949.08</v>
       </c>
       <c r="K87" s="1">
-        <v>25736.65</v>
+        <v>17248.25</v>
       </c>
       <c r="L87" s="1">
-        <v>26179.41</v>
+        <v>18042.86</v>
       </c>
       <c r="M87" s="3">
-        <v>-172.58</v>
+        <v>-312.85</v>
       </c>
       <c r="N87" s="3">
-        <v>-106.49</v>
+        <v>-196.4</v>
       </c>
       <c r="O87" s="3">
-        <v>683.83</v>
+        <v>154.28</v>
       </c>
       <c r="P87" s="3">
-        <v>871.75</v>
+        <v>372.72</v>
       </c>
       <c r="Q87" s="3">
-        <v>2363.37</v>
+        <v>1255.47</v>
       </c>
       <c r="R87" s="3">
-        <v>2365.37</v>
+        <v>1418.33</v>
       </c>
       <c r="S87" s="3">
-        <v>39.28</v>
-      </c>
-      <c r="T87" t="str">
+        <v>21.82</v>
+      </c>
+      <c r="T87" s="3">
+        <v>10.42</v>
+      </c>
+      <c r="U87" s="3">
+        <v>54.48</v>
+      </c>
+      <c r="V87" s="3">
+        <v>38</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="str">
         <v/>
       </c>
     </row>
@@ -5804,60 +7109,75 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="C88" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="D88" s="1">
-        <v>27189.1</v>
+        <v>49910.3</v>
       </c>
       <c r="E88" s="2">
-        <v>-1.85</v>
+        <v>-2.81</v>
       </c>
       <c r="F88" s="2">
-        <v>-1.85</v>
+        <v>-7.31</v>
       </c>
       <c r="G88" s="2">
-        <v>1.85</v>
+        <v>-7.71</v>
       </c>
       <c r="H88" s="2">
-        <v>-5.33</v>
+        <v>-0.79</v>
       </c>
       <c r="I88" s="1">
         <v>0</v>
       </c>
       <c r="J88" s="1">
-        <v>27387.51</v>
+        <v>52196.32</v>
       </c>
       <c r="K88" s="1">
-        <v>27263.36</v>
+        <v>52935.13</v>
       </c>
       <c r="L88" s="1">
-        <v>27306.52</v>
+        <v>55465.02</v>
       </c>
       <c r="M88" s="3">
-        <v>29.87</v>
+        <v>-970.06</v>
       </c>
       <c r="N88" s="3">
-        <v>-52.8</v>
+        <v>-524.45</v>
       </c>
       <c r="O88" s="3">
-        <v>-11.17</v>
+        <v>487.96</v>
       </c>
       <c r="P88" s="3">
-        <v>23.26</v>
+        <v>1112.5</v>
       </c>
       <c r="Q88" s="3">
-        <v>672.45</v>
+        <v>3454.54</v>
       </c>
       <c r="R88" s="3">
-        <v>880.38</v>
+        <v>3839.75</v>
       </c>
       <c r="S88" s="3">
-        <v>49.64</v>
-      </c>
-      <c r="T88" t="str">
+        <v>24.65</v>
+      </c>
+      <c r="T88" s="3">
+        <v>10.04</v>
+      </c>
+      <c r="U88" s="3">
+        <v>51.41</v>
+      </c>
+      <c r="V88" s="3">
+        <v>33.58</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" t="str">
         <v/>
       </c>
     </row>
@@ -5866,60 +7186,75 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="C89" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="D89" s="1">
-        <v>16229.05</v>
+        <v>17739.45</v>
       </c>
       <c r="E89" s="2">
-        <v>-2.27</v>
+        <v>-2.94</v>
       </c>
       <c r="F89" s="2">
-        <v>-2.27</v>
+        <v>-7.27</v>
       </c>
       <c r="G89" s="2">
-        <v>2</v>
+        <v>-7.83</v>
       </c>
       <c r="H89" s="2">
-        <v>-26.22</v>
+        <v>0.14</v>
       </c>
       <c r="I89" s="1">
         <v>0</v>
       </c>
       <c r="J89" s="1">
-        <v>18456.36</v>
+        <v>18188.33</v>
       </c>
       <c r="K89" s="1">
-        <v>16125.26</v>
+        <v>18723.09</v>
       </c>
       <c r="L89" s="1">
-        <v>17256.4</v>
+        <v>19579.65</v>
       </c>
       <c r="M89" s="3">
-        <v>-299.59</v>
+        <v>-338.91</v>
       </c>
       <c r="N89" s="3">
-        <v>-425.54</v>
+        <v>-201.47</v>
       </c>
       <c r="O89" s="3">
-        <v>-658.68</v>
+        <v>243.89</v>
       </c>
       <c r="P89" s="3">
-        <v>-508.53</v>
+        <v>477.06</v>
       </c>
       <c r="Q89" s="3">
-        <v>280.73</v>
+        <v>797.34</v>
       </c>
       <c r="R89" s="3">
-        <v>929.94</v>
+        <v>843.64</v>
       </c>
       <c r="S89" s="3">
-        <v>46.74</v>
-      </c>
-      <c r="T89" t="str">
+        <v>22.66</v>
+      </c>
+      <c r="T89" s="3">
+        <v>11.15</v>
+      </c>
+      <c r="U89" s="3">
+        <v>54.17</v>
+      </c>
+      <c r="V89" s="3">
+        <v>35.27</v>
+      </c>
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="str">
         <v/>
       </c>
     </row>
@@ -5928,66 +7263,81 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="C90" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="D90" s="1">
-        <v>10639.55</v>
+        <v>8924.75</v>
       </c>
       <c r="E90" s="2">
-        <v>-2.27</v>
+        <v>-3.15</v>
       </c>
       <c r="F90" s="2">
-        <v>-2.27</v>
+        <v>-6.87</v>
       </c>
       <c r="G90" s="2">
-        <v>1.95</v>
+        <v>-7.35</v>
       </c>
       <c r="H90" s="2">
-        <v>-27.62</v>
+        <v>3.7</v>
       </c>
       <c r="I90" s="1">
         <v>0</v>
       </c>
       <c r="J90" s="1">
-        <v>12233.4</v>
+        <v>8982.85</v>
       </c>
       <c r="K90" s="1">
-        <v>10574.3</v>
+        <v>9395.06</v>
       </c>
       <c r="L90" s="1">
-        <v>11321.07</v>
+        <v>9789.56</v>
       </c>
       <c r="M90" s="3">
-        <v>-198.96</v>
+        <v>-153.48</v>
       </c>
       <c r="N90" s="3">
-        <v>-281.64</v>
+        <v>-92.78</v>
       </c>
       <c r="O90" s="3">
-        <v>-477.57</v>
+        <v>171.72</v>
       </c>
       <c r="P90" s="3">
-        <v>-383.86</v>
+        <v>288.86</v>
       </c>
       <c r="Q90" s="3">
-        <v>-3.9</v>
+        <v>702.31</v>
       </c>
       <c r="R90" s="3">
-        <v>426.64</v>
+        <v>712.09</v>
       </c>
       <c r="S90" s="3">
-        <v>46.61</v>
-      </c>
-      <c r="T90" t="str">
+        <v>24.61</v>
+      </c>
+      <c r="T90" s="3">
+        <v>11.37</v>
+      </c>
+      <c r="U90" s="3">
+        <v>50.49</v>
+      </c>
+      <c r="V90" s="3">
+        <v>33.74</v>
+      </c>
+      <c r="W90" s="3">
+        <v>0</v>
+      </c>
+      <c r="X90" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y90" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T90"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y90"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/index.xlsx
+++ b/index.xlsx
@@ -487,67 +487,67 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>India VIX</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="C2" t="str">
-        <v>INDIAVIX</v>
+        <v>NIFTYALPHA50</v>
       </c>
       <c r="D2" s="1">
-        <v>16.86</v>
+        <v>51181.5</v>
       </c>
       <c r="E2" s="2">
-        <v>6.98</v>
+        <v>2.55</v>
       </c>
       <c r="F2" s="2">
-        <v>19.91</v>
+        <v>2.55</v>
       </c>
       <c r="G2" s="2">
-        <v>24.98</v>
+        <v>-5.36</v>
       </c>
       <c r="H2" s="2">
-        <v>77.85</v>
+        <v>1.73</v>
       </c>
       <c r="I2" s="1">
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>14.91</v>
+        <v>52200.26</v>
       </c>
       <c r="K2" s="1">
-        <v>15.13</v>
+        <v>52616.29</v>
       </c>
       <c r="L2" s="1">
-        <v>12.6</v>
+        <v>55348.14</v>
       </c>
       <c r="M2" s="3">
-        <v>0.9</v>
+        <v>-1058.59</v>
       </c>
       <c r="N2" s="3">
-        <v>0.73</v>
+        <v>-631.28</v>
       </c>
       <c r="O2" s="3">
-        <v>-0.19</v>
+        <v>213.47</v>
       </c>
       <c r="P2" s="3">
-        <v>-0.73</v>
+        <v>932.69</v>
       </c>
       <c r="Q2" s="3">
-        <v>0.08</v>
+        <v>3555.95</v>
       </c>
       <c r="R2" s="3">
-        <v>0.05</v>
+        <v>3860.03</v>
       </c>
       <c r="S2" s="3">
-        <v>66.5</v>
+        <v>34.48</v>
       </c>
       <c r="T2" s="3">
-        <v>19.58</v>
+        <v>8.55</v>
       </c>
       <c r="U2" s="3">
-        <v>13.36</v>
+        <v>45.64</v>
       </c>
       <c r="V2" s="3">
-        <v>17.68</v>
+        <v>36.07</v>
       </c>
       <c r="W2" s="3">
         <v>0</v>
@@ -564,67 +564,67 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="C3" t="str">
-        <v>NIFTY50DIVPOINT</v>
+        <v>NIFTY500MOMENTM50</v>
       </c>
       <c r="D3" s="1">
-        <v>204.22</v>
+        <v>50221.55</v>
       </c>
       <c r="E3" s="2">
-        <v>1.02</v>
+        <v>2.35</v>
       </c>
       <c r="F3" s="2">
-        <v>1.02</v>
+        <v>2.35</v>
       </c>
       <c r="G3" s="2">
-        <v>3.78</v>
+        <v>-5.05</v>
       </c>
       <c r="H3" s="2">
-        <v>-18.03</v>
+        <v>-4.72</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <v>180.43</v>
+        <v>52510.51</v>
       </c>
       <c r="K3" s="1">
-        <v>200.88</v>
+        <v>51253.27</v>
       </c>
       <c r="L3" s="1">
-        <v>195.12</v>
+        <v>53875.24</v>
       </c>
       <c r="M3" s="3">
-        <v>2.78</v>
+        <v>-996.06</v>
       </c>
       <c r="N3" s="3">
-        <v>2.61</v>
+        <v>-695.74</v>
       </c>
       <c r="O3" s="3">
-        <v>11.94</v>
+        <v>-330.62</v>
       </c>
       <c r="P3" s="3">
-        <v>5.7</v>
+        <v>264.31</v>
       </c>
       <c r="Q3" s="3">
-        <v>5.47</v>
+        <v>-818.06</v>
       </c>
       <c r="R3" s="3">
-        <v>7.68</v>
+        <v>-1135.31</v>
       </c>
       <c r="S3" s="3">
-        <v>100</v>
+        <v>34.88</v>
       </c>
       <c r="T3" s="3">
-        <v>99.62</v>
+        <v>6.91</v>
       </c>
       <c r="U3" s="3">
-        <v>0.38</v>
+        <v>44.85</v>
       </c>
       <c r="V3" s="3">
-        <v>97</v>
+        <v>42.94</v>
       </c>
       <c r="W3" s="3">
         <v>0</v>
@@ -641,67 +641,67 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>NIFTY50PR1XINV</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="C4" t="str">
-        <v>NIFTY50PR1XINV</v>
+        <v>NIFTYINDTOURISM</v>
       </c>
       <c r="D4" s="1">
-        <v>236.6</v>
+        <v>7529.45</v>
       </c>
       <c r="E4" s="2">
-        <v>0.4</v>
+        <v>2.35</v>
       </c>
       <c r="F4" s="2">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="G4" s="2">
-        <v>0.28</v>
+        <v>-2.27</v>
       </c>
       <c r="H4" s="2">
-        <v>18.3</v>
+        <v>-12.49</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>219.26</v>
+        <v>7674.26</v>
       </c>
       <c r="K4" s="1">
-        <v>234.95</v>
+        <v>7479.91</v>
       </c>
       <c r="L4" s="1">
-        <v>227.92</v>
+        <v>7741.94</v>
       </c>
       <c r="M4" s="3">
-        <v>1.87</v>
+        <v>-85.83</v>
       </c>
       <c r="N4" s="3">
-        <v>2.4</v>
+        <v>-89.2</v>
       </c>
       <c r="O4" s="3">
-        <v>4.76</v>
+        <v>-74.02</v>
       </c>
       <c r="P4" s="3">
-        <v>3.47</v>
+        <v>-29.88</v>
       </c>
       <c r="Q4" s="3">
-        <v>-0.58</v>
+        <v>-291.89</v>
       </c>
       <c r="R4" s="3">
-        <v>-4.76</v>
+        <v>-245.56</v>
       </c>
       <c r="S4" s="3">
-        <v>58.23</v>
+        <v>47.5</v>
       </c>
       <c r="T4" s="3">
-        <v>28.84</v>
+        <v>16.13</v>
       </c>
       <c r="U4" s="3">
-        <v>12.4</v>
+        <v>26.17</v>
       </c>
       <c r="V4" s="3">
-        <v>43.12</v>
+        <v>25.98</v>
       </c>
       <c r="W4" s="3">
         <v>0</v>
@@ -718,67 +718,67 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="C5" t="str">
-        <v>NIFTY50TR1XINV</v>
+        <v>NIFTYMETAL</v>
       </c>
       <c r="D5" s="1">
-        <v>191.9</v>
+        <v>11731.55</v>
       </c>
       <c r="E5" s="2">
-        <v>0.39</v>
+        <v>2.21</v>
       </c>
       <c r="F5" s="2">
-        <v>2.51</v>
+        <v>2.21</v>
       </c>
       <c r="G5" s="2">
-        <v>0.26</v>
+        <v>-8.06</v>
       </c>
       <c r="H5" s="2">
-        <v>17.26</v>
+        <v>5.05</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>178.68</v>
+        <v>12486.09</v>
       </c>
       <c r="K5" s="1">
-        <v>190.56</v>
+        <v>11911.42</v>
       </c>
       <c r="L5" s="1">
-        <v>184.9</v>
+        <v>12775.95</v>
       </c>
       <c r="M5" s="3">
-        <v>1.5</v>
+        <v>-314.44</v>
       </c>
       <c r="N5" s="3">
-        <v>1.92</v>
+        <v>-276.53</v>
       </c>
       <c r="O5" s="3">
-        <v>3.55</v>
+        <v>-75.27</v>
       </c>
       <c r="P5" s="3">
-        <v>2.49</v>
+        <v>147.26</v>
       </c>
       <c r="Q5" s="3">
-        <v>-2.44</v>
+        <v>1127.59</v>
       </c>
       <c r="R5" s="3">
-        <v>-6.02</v>
+        <v>1128.21</v>
       </c>
       <c r="S5" s="3">
-        <v>58.14</v>
+        <v>36.15</v>
       </c>
       <c r="T5" s="3">
-        <v>28.85</v>
+        <v>10.25</v>
       </c>
       <c r="U5" s="3">
-        <v>12.58</v>
+        <v>36.88</v>
       </c>
       <c r="V5" s="3">
-        <v>42.66</v>
+        <v>36.83</v>
       </c>
       <c r="W5" s="3">
         <v>0</v>
@@ -795,67 +795,67 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="C6" t="str">
-        <v>NIFTYGS48YR</v>
+        <v>NIFTYMIDSMLHLTH</v>
       </c>
       <c r="D6" s="1">
-        <v>3276.92</v>
+        <v>48694</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.01</v>
+        <v>2.19</v>
       </c>
       <c r="F6" s="2">
-        <v>-0.14</v>
+        <v>2.19</v>
       </c>
       <c r="G6" s="2">
-        <v>-0.96</v>
+        <v>-4.49</v>
       </c>
       <c r="H6" s="2">
-        <v>1.68</v>
+        <v>11.01</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>3280.43</v>
+        <v>47382.23</v>
       </c>
       <c r="K6" s="1">
-        <v>3284.34</v>
+        <v>48986.82</v>
       </c>
       <c r="L6" s="1">
-        <v>3319.89</v>
+        <v>51371.99</v>
       </c>
       <c r="M6" s="3">
-        <v>-12.05</v>
+        <v>-944.01</v>
       </c>
       <c r="N6" s="3">
-        <v>-11.31</v>
+        <v>-760.44</v>
       </c>
       <c r="O6" s="3">
-        <v>7.72</v>
+        <v>684.38</v>
       </c>
       <c r="P6" s="3">
-        <v>17.99</v>
+        <v>1377.64</v>
       </c>
       <c r="Q6" s="3">
-        <v>139.48</v>
+        <v>2184.16</v>
       </c>
       <c r="R6" s="3">
-        <v>155.41</v>
+        <v>1474.4</v>
       </c>
       <c r="S6" s="3">
-        <v>25.04</v>
+        <v>36.98</v>
       </c>
       <c r="T6" s="3">
-        <v>10.4</v>
+        <v>10.23</v>
       </c>
       <c r="U6" s="3">
-        <v>45.94</v>
+        <v>34.79</v>
       </c>
       <c r="V6" s="3">
-        <v>48.97</v>
+        <v>40.92</v>
       </c>
       <c r="W6" s="3">
         <v>0</v>
@@ -872,67 +872,67 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="C7" t="str">
-        <v>NIFTYGS1115YR</v>
+        <v>NIFTY200MOMENTM30</v>
       </c>
       <c r="D7" s="1">
-        <v>3284.16</v>
+        <v>27862.75</v>
       </c>
       <c r="E7" s="2">
-        <v>-0.05</v>
+        <v>2.05</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.57</v>
+        <v>2.05</v>
       </c>
       <c r="G7" s="2">
-        <v>-1.13</v>
+        <v>-5.61</v>
       </c>
       <c r="H7" s="2">
-        <v>1.3</v>
+        <v>-10.55</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>3295.35</v>
+        <v>30349.35</v>
       </c>
       <c r="K7" s="1">
-        <v>3294.53</v>
+        <v>28456.84</v>
       </c>
       <c r="L7" s="1">
-        <v>3347.55</v>
+        <v>30123.15</v>
       </c>
       <c r="M7" s="3">
-        <v>-17.47</v>
+        <v>-616.75</v>
       </c>
       <c r="N7" s="3">
-        <v>-17.24</v>
+        <v>-471.96</v>
       </c>
       <c r="O7" s="3">
-        <v>7.47</v>
+        <v>-540.32</v>
       </c>
       <c r="P7" s="3">
-        <v>21.48</v>
+        <v>-191.77</v>
       </c>
       <c r="Q7" s="3">
-        <v>136.34</v>
+        <v>1406.3</v>
       </c>
       <c r="R7" s="3">
-        <v>153.87</v>
+        <v>1990.98</v>
       </c>
       <c r="S7" s="3">
-        <v>32.06</v>
+        <v>33.05</v>
       </c>
       <c r="T7" s="3">
-        <v>8.59</v>
+        <v>6.94</v>
       </c>
       <c r="U7" s="3">
-        <v>37.49</v>
+        <v>41.84</v>
       </c>
       <c r="V7" s="3">
-        <v>50.12</v>
+        <v>42.88</v>
       </c>
       <c r="W7" s="3">
         <v>0</v>
@@ -949,67 +949,67 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="C8" t="str">
-        <v>NIFTYGS813YR</v>
+        <v>NIFTYM150MOMNTM50</v>
       </c>
       <c r="D8" s="1">
-        <v>2965.74</v>
+        <v>57955.6</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.06</v>
+        <v>2.01</v>
       </c>
       <c r="F8" s="2">
-        <v>-0.57</v>
+        <v>2.01</v>
       </c>
       <c r="G8" s="2">
-        <v>-1.6</v>
+        <v>-4.64</v>
       </c>
       <c r="H8" s="2">
-        <v>-0.04</v>
+        <v>-6.4</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>3001.35</v>
+        <v>61681.34</v>
       </c>
       <c r="K8" s="1">
-        <v>2979.03</v>
+        <v>59024.73</v>
       </c>
       <c r="L8" s="1">
-        <v>3025.27</v>
+        <v>62328.51</v>
       </c>
       <c r="M8" s="3">
-        <v>-16.31</v>
+        <v>-1210.4</v>
       </c>
       <c r="N8" s="3">
-        <v>-14.7</v>
+        <v>-935.87</v>
       </c>
       <c r="O8" s="3">
-        <v>-0.06</v>
+        <v>-736.86</v>
       </c>
       <c r="P8" s="3">
-        <v>11.34</v>
+        <v>3.56</v>
       </c>
       <c r="Q8" s="3">
-        <v>114.39</v>
+        <v>-157.46</v>
       </c>
       <c r="R8" s="3">
-        <v>132.76</v>
+        <v>-204.43</v>
       </c>
       <c r="S8" s="3">
-        <v>24.53</v>
+        <v>33.3</v>
       </c>
       <c r="T8" s="3">
-        <v>11.19</v>
+        <v>6.88</v>
       </c>
       <c r="U8" s="3">
-        <v>46.17</v>
+        <v>42.24</v>
       </c>
       <c r="V8" s="3">
-        <v>50.89</v>
+        <v>45.58</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
@@ -1026,67 +1026,67 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="C9" t="str">
-        <v>NIFTYGS10YR</v>
+        <v>NIFTYCAPITALMKT</v>
       </c>
       <c r="D9" s="1">
-        <v>2595.75</v>
+        <v>5018.6</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.07</v>
+        <v>1.8</v>
       </c>
       <c r="F9" s="2">
-        <v>-0.59</v>
+        <v>1.8</v>
       </c>
       <c r="G9" s="2">
-        <v>-1.61</v>
+        <v>-1.4</v>
       </c>
       <c r="H9" s="2">
-        <v>-0.62</v>
+        <v>7.78</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>2632.21</v>
+        <v>5108.62</v>
       </c>
       <c r="K9" s="1">
-        <v>2607.13</v>
+        <v>5109.83</v>
       </c>
       <c r="L9" s="1">
-        <v>2648</v>
+        <v>5287.83</v>
       </c>
       <c r="M9" s="3">
-        <v>-14.46</v>
+        <v>-63.71</v>
       </c>
       <c r="N9" s="3">
-        <v>-13.13</v>
+        <v>-42.84</v>
       </c>
       <c r="O9" s="3">
-        <v>-2.22</v>
+        <v>-0.18</v>
       </c>
       <c r="P9" s="3">
-        <v>7.41</v>
+        <v>67.56</v>
       </c>
       <c r="Q9" s="3">
-        <v>89.59</v>
+        <v>360.84</v>
       </c>
       <c r="R9" s="3">
-        <v>106.33</v>
+        <v>324.63</v>
       </c>
       <c r="S9" s="3">
-        <v>26.14</v>
+        <v>39.71</v>
       </c>
       <c r="T9" s="3">
-        <v>14.19</v>
+        <v>12.59</v>
       </c>
       <c r="U9" s="3">
-        <v>40.39</v>
+        <v>32.21</v>
       </c>
       <c r="V9" s="3">
-        <v>38.57</v>
+        <v>23.74</v>
       </c>
       <c r="W9" s="3">
         <v>0</v>
@@ -1103,67 +1103,67 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>India VIX</v>
       </c>
       <c r="C10" t="str">
-        <v>NIFTYGS10YRCLN</v>
+        <v>INDIAVIX</v>
       </c>
       <c r="D10" s="1">
-        <v>837.21</v>
+        <v>17.16</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.09</v>
+        <v>1.78</v>
       </c>
       <c r="F10" s="2">
-        <v>-0.75</v>
+        <v>1.78</v>
       </c>
       <c r="G10" s="2">
-        <v>-2.1</v>
+        <v>27.21</v>
       </c>
       <c r="H10" s="2">
-        <v>-6.08</v>
+        <v>81.01</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>873.57</v>
+        <v>14.95</v>
       </c>
       <c r="K10" s="1">
-        <v>842.1</v>
+        <v>15.5</v>
       </c>
       <c r="L10" s="1">
-        <v>860.68</v>
+        <v>12.71</v>
       </c>
       <c r="M10" s="3">
-        <v>-6.56</v>
+        <v>1.01</v>
       </c>
       <c r="N10" s="3">
-        <v>-6.1</v>
+        <v>0.79</v>
       </c>
       <c r="O10" s="3">
-        <v>-8.84</v>
+        <v>0.1</v>
       </c>
       <c r="P10" s="3">
-        <v>-5.65</v>
+        <v>-0.56</v>
       </c>
       <c r="Q10" s="3">
-        <v>-17.29</v>
+        <v>0.1</v>
       </c>
       <c r="R10" s="3">
-        <v>-14.21</v>
+        <v>0.06</v>
       </c>
       <c r="S10" s="3">
-        <v>20.5</v>
+        <v>67.62</v>
       </c>
       <c r="T10" s="3">
-        <v>9.83</v>
+        <v>22.62</v>
       </c>
       <c r="U10" s="3">
-        <v>45.2</v>
+        <v>12.67</v>
       </c>
       <c r="V10" s="3">
-        <v>53.22</v>
+        <v>18.43</v>
       </c>
       <c r="W10" s="3">
         <v>0</v>
@@ -1180,67 +1180,67 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="C11" t="str">
-        <v>NIFTYGSCOMPSITE</v>
+        <v>NIFTYHEALTHCARE</v>
       </c>
       <c r="D11" s="1">
-        <v>3057.33</v>
+        <v>15658.7</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.1</v>
+        <v>1.77</v>
       </c>
       <c r="F11" s="2">
-        <v>-0.61</v>
+        <v>1.77</v>
       </c>
       <c r="G11" s="2">
-        <v>-1.51</v>
+        <v>-2.97</v>
       </c>
       <c r="H11" s="2">
-        <v>0.16</v>
+        <v>6.96</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>3085.96</v>
+        <v>15450.11</v>
       </c>
       <c r="K11" s="1">
-        <v>3071.1</v>
+        <v>15656.13</v>
       </c>
       <c r="L11" s="1">
-        <v>3117.26</v>
+        <v>16304.78</v>
       </c>
       <c r="M11" s="3">
-        <v>-16.11</v>
+        <v>-248.63</v>
       </c>
       <c r="N11" s="3">
-        <v>-14.56</v>
+        <v>-225.63</v>
       </c>
       <c r="O11" s="3">
-        <v>2.23</v>
+        <v>116.19</v>
       </c>
       <c r="P11" s="3">
-        <v>13.89</v>
+        <v>294.04</v>
       </c>
       <c r="Q11" s="3">
-        <v>118.23</v>
+        <v>990.51</v>
       </c>
       <c r="R11" s="3">
-        <v>136.49</v>
+        <v>996.57</v>
       </c>
       <c r="S11" s="3">
-        <v>26.6</v>
+        <v>40.17</v>
       </c>
       <c r="T11" s="3">
-        <v>11.51</v>
+        <v>9.04</v>
       </c>
       <c r="U11" s="3">
-        <v>44.83</v>
+        <v>28.52</v>
       </c>
       <c r="V11" s="3">
-        <v>48.31</v>
+        <v>41.79</v>
       </c>
       <c r="W11" s="3">
         <v>0</v>
@@ -1257,67 +1257,67 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="C12" t="str">
-        <v>NIFTYSERVSECTOR</v>
+        <v>CNXPHARMA</v>
       </c>
       <c r="D12" s="1">
-        <v>29934.75</v>
+        <v>25774.25</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.21</v>
+        <v>1.76</v>
       </c>
       <c r="F12" s="2">
-        <v>-1.79</v>
+        <v>1.76</v>
       </c>
       <c r="G12" s="2">
-        <v>3.17</v>
+        <v>-2.51</v>
       </c>
       <c r="H12" s="2">
-        <v>-11.06</v>
+        <v>13.42</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>30941.95</v>
+        <v>24390.96</v>
       </c>
       <c r="K12" s="1">
-        <v>29821.3</v>
+        <v>25749.81</v>
       </c>
       <c r="L12" s="1">
-        <v>30083.38</v>
+        <v>26419.44</v>
       </c>
       <c r="M12" s="3">
-        <v>21.38</v>
+        <v>-268.28</v>
       </c>
       <c r="N12" s="3">
-        <v>-124.43</v>
+        <v>-218.56</v>
       </c>
       <c r="O12" s="3">
-        <v>-359.57</v>
+        <v>515.16</v>
       </c>
       <c r="P12" s="3">
-        <v>-317.41</v>
+        <v>737.13</v>
       </c>
       <c r="Q12" s="3">
-        <v>482.12</v>
+        <v>1788.85</v>
       </c>
       <c r="R12" s="3">
-        <v>990.92</v>
+        <v>1610.21</v>
       </c>
       <c r="S12" s="3">
-        <v>52.88</v>
+        <v>43.84</v>
       </c>
       <c r="T12" s="3">
-        <v>19.34</v>
+        <v>10.91</v>
       </c>
       <c r="U12" s="3">
-        <v>24.14</v>
+        <v>24.35</v>
       </c>
       <c r="V12" s="3">
-        <v>27.11</v>
+        <v>30.32</v>
       </c>
       <c r="W12" s="3">
         <v>0</v>
@@ -1334,67 +1334,67 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="C13" t="str">
-        <v>BHARATBOND-APR30</v>
+        <v>NIFTY200ALPHA30</v>
       </c>
       <c r="D13" s="1">
-        <v>1596.15</v>
+        <v>24078.65</v>
       </c>
       <c r="E13" s="2">
-        <v>-0.22</v>
+        <v>1.74</v>
       </c>
       <c r="F13" s="2">
-        <v>-0.33</v>
+        <v>1.74</v>
       </c>
       <c r="G13" s="2">
-        <v>-0.67</v>
+        <v>-5.18</v>
       </c>
       <c r="H13" s="2">
-        <v>1.87</v>
+        <v>-3.63</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>1586.81</v>
+        <v>25461.29</v>
       </c>
       <c r="K13" s="1">
-        <v>1601.81</v>
+        <v>24631.39</v>
       </c>
       <c r="L13" s="1">
-        <v>1608.58</v>
+        <v>26048.7</v>
       </c>
       <c r="M13" s="3">
-        <v>-2.7</v>
+        <v>-510.37</v>
       </c>
       <c r="N13" s="3">
-        <v>-1.81</v>
+        <v>-393.15</v>
       </c>
       <c r="O13" s="3">
-        <v>6.53</v>
+        <v>-221.51</v>
       </c>
       <c r="P13" s="3">
-        <v>9.29</v>
+        <v>119.48</v>
       </c>
       <c r="Q13" s="3">
-        <v>34.48</v>
+        <v>34.69</v>
       </c>
       <c r="R13" s="3">
-        <v>33.04</v>
+        <v>-61.51</v>
       </c>
       <c r="S13" s="3">
-        <v>23.28</v>
+        <v>33.08</v>
       </c>
       <c r="T13" s="3">
-        <v>19.64</v>
+        <v>6.99</v>
       </c>
       <c r="U13" s="3">
-        <v>70.91</v>
+        <v>42.11</v>
       </c>
       <c r="V13" s="3">
-        <v>28.2</v>
+        <v>42.21</v>
       </c>
       <c r="W13" s="3">
         <v>0</v>
@@ -1411,67 +1411,67 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="C14" t="str">
-        <v>NIFTYGROWSECT15</v>
+        <v>NIFTYMIDLIQ15</v>
       </c>
       <c r="D14" s="1">
-        <v>10889.35</v>
+        <v>15289.05</v>
       </c>
       <c r="E14" s="2">
-        <v>-0.25</v>
+        <v>1.63</v>
       </c>
       <c r="F14" s="2">
-        <v>-1.23</v>
+        <v>1.63</v>
       </c>
       <c r="G14" s="2">
-        <v>3.32</v>
+        <v>-6.14</v>
       </c>
       <c r="H14" s="2">
-        <v>-12.77</v>
+        <v>-4.47</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>11216.63</v>
+        <v>16122.23</v>
       </c>
       <c r="K14" s="1">
-        <v>10811.35</v>
+        <v>15685.11</v>
       </c>
       <c r="L14" s="1">
-        <v>11067.8</v>
+        <v>16735.81</v>
       </c>
       <c r="M14" s="3">
-        <v>-22.75</v>
+        <v>-371.75</v>
       </c>
       <c r="N14" s="3">
-        <v>-98.95</v>
+        <v>-293.22</v>
       </c>
       <c r="O14" s="3">
-        <v>-114.58</v>
+        <v>-104.88</v>
       </c>
       <c r="P14" s="3">
-        <v>-76.04</v>
+        <v>156.14</v>
       </c>
       <c r="Q14" s="3">
-        <v>31.47</v>
+        <v>1519.88</v>
       </c>
       <c r="R14" s="3">
-        <v>176.53</v>
+        <v>1742.31</v>
       </c>
       <c r="S14" s="3">
-        <v>52.9</v>
+        <v>31.85</v>
       </c>
       <c r="T14" s="3">
-        <v>19.03</v>
+        <v>8.29</v>
       </c>
       <c r="U14" s="3">
-        <v>23.31</v>
+        <v>41.86</v>
       </c>
       <c r="V14" s="3">
-        <v>32.43</v>
+        <v>44.85</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1488,67 +1488,67 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="C15" t="str">
-        <v>NIFTYCONSUMPTION</v>
+        <v>NIFTYSMALLCAP50</v>
       </c>
       <c r="D15" s="1">
-        <v>10726.75</v>
+        <v>9067.1</v>
       </c>
       <c r="E15" s="2">
-        <v>-0.25</v>
+        <v>1.6</v>
       </c>
       <c r="F15" s="2">
-        <v>-2.97</v>
+        <v>1.6</v>
       </c>
       <c r="G15" s="2">
-        <v>-3.12</v>
+        <v>-5.87</v>
       </c>
       <c r="H15" s="2">
-        <v>-12.72</v>
+        <v>5.36</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>11488.94</v>
+        <v>8985.17</v>
       </c>
       <c r="K15" s="1">
-        <v>10883.66</v>
+        <v>9335.43</v>
       </c>
       <c r="L15" s="1">
-        <v>11448.4</v>
+        <v>9772.61</v>
       </c>
       <c r="M15" s="3">
-        <v>-176.46</v>
+        <v>-171.32</v>
       </c>
       <c r="N15" s="3">
-        <v>-180.36</v>
+        <v>-108.49</v>
       </c>
       <c r="O15" s="3">
-        <v>-159.66</v>
+        <v>119.09</v>
       </c>
       <c r="P15" s="3">
-        <v>-43.17</v>
+        <v>254.91</v>
       </c>
       <c r="Q15" s="3">
-        <v>208.66</v>
+        <v>713.66</v>
       </c>
       <c r="R15" s="3">
-        <v>392.4</v>
+        <v>714.36</v>
       </c>
       <c r="S15" s="3">
-        <v>34.37</v>
+        <v>31.96</v>
       </c>
       <c r="T15" s="3">
-        <v>9.32</v>
+        <v>9.86</v>
       </c>
       <c r="U15" s="3">
-        <v>36.63</v>
+        <v>48.09</v>
       </c>
       <c r="V15" s="3">
-        <v>47.5</v>
+        <v>36.04</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1565,67 +1565,67 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="C16" t="str">
-        <v>NIFTYTOP10EW</v>
+        <v>NIFTYCOMMODITIES</v>
       </c>
       <c r="D16" s="1">
-        <v>8281.2</v>
+        <v>8932.7</v>
       </c>
       <c r="E16" s="2">
-        <v>-0.26</v>
+        <v>1.6</v>
       </c>
       <c r="F16" s="2">
-        <v>-1.98</v>
+        <v>1.6</v>
       </c>
       <c r="G16" s="2">
-        <v>2.53</v>
+        <v>-4.05</v>
       </c>
       <c r="H16" s="2">
-        <v>-17.56</v>
+        <v>-6.12</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>8763.47</v>
+        <v>9754.18</v>
       </c>
       <c r="K16" s="1">
-        <v>8285.07</v>
+        <v>8972.71</v>
       </c>
       <c r="L16" s="1">
-        <v>8388.81</v>
+        <v>9456.52</v>
       </c>
       <c r="M16" s="3">
-        <v>-8.14</v>
+        <v>-163.48</v>
       </c>
       <c r="N16" s="3">
-        <v>-37.3</v>
+        <v>-166.97</v>
       </c>
       <c r="O16" s="3">
-        <v>-161.61</v>
+        <v>-213.51</v>
       </c>
       <c r="P16" s="3">
-        <v>-158.84</v>
+        <v>-97.78</v>
       </c>
       <c r="Q16" s="3">
-        <v>-306.95</v>
+        <v>388.24</v>
       </c>
       <c r="R16" s="3">
-        <v>-192.72</v>
+        <v>508.01</v>
       </c>
       <c r="S16" s="3">
-        <v>49.51</v>
+        <v>38.67</v>
       </c>
       <c r="T16" s="3">
-        <v>17.93</v>
+        <v>12.62</v>
       </c>
       <c r="U16" s="3">
-        <v>24.71</v>
+        <v>32.95</v>
       </c>
       <c r="V16" s="3">
-        <v>22.6</v>
+        <v>42.34</v>
       </c>
       <c r="W16" s="3">
         <v>0</v>
@@ -1642,67 +1642,67 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>Nifty IT</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="C17" t="str">
-        <v>CNXIT</v>
+        <v>NIFTYMS400MQ100</v>
       </c>
       <c r="D17" s="1">
-        <v>31995.5</v>
+        <v>47530.5</v>
       </c>
       <c r="E17" s="2">
-        <v>-0.27</v>
+        <v>1.59</v>
       </c>
       <c r="F17" s="2">
-        <v>0.22</v>
+        <v>1.59</v>
       </c>
       <c r="G17" s="2">
-        <v>15.49</v>
+        <v>-4.13</v>
       </c>
       <c r="H17" s="2">
-        <v>-15.54</v>
+        <v>-0.07</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>30815.06</v>
+        <v>49076.85</v>
       </c>
       <c r="K17" s="1">
-        <v>30967.15</v>
+        <v>48480.47</v>
       </c>
       <c r="L17" s="1">
-        <v>29839.55</v>
+        <v>50669.02</v>
       </c>
       <c r="M17" s="3">
-        <v>749.33</v>
+        <v>-794.46</v>
       </c>
       <c r="N17" s="3">
-        <v>287.49</v>
+        <v>-581.38</v>
       </c>
       <c r="O17" s="3">
-        <v>-156.84</v>
+        <v>-191.61</v>
       </c>
       <c r="P17" s="3">
-        <v>-519.55</v>
+        <v>390.7</v>
       </c>
       <c r="Q17" s="3">
-        <v>-1661.02</v>
+        <v>0.88</v>
       </c>
       <c r="R17" s="3">
-        <v>-1147.75</v>
+        <v>-310.98</v>
       </c>
       <c r="S17" s="3">
-        <v>68.05</v>
+        <v>33.5</v>
       </c>
       <c r="T17" s="3">
-        <v>30.99</v>
+        <v>6.87</v>
       </c>
       <c r="U17" s="3">
-        <v>13.96</v>
+        <v>42.86</v>
       </c>
       <c r="V17" s="3">
-        <v>30.24</v>
+        <v>46.11</v>
       </c>
       <c r="W17" s="3">
         <v>0</v>
@@ -1719,67 +1719,67 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="C18" t="str">
-        <v>NIFTYGS15YRPLUS</v>
+        <v>CNXENERGY</v>
       </c>
       <c r="D18" s="1">
-        <v>3451.53</v>
+        <v>35022.35</v>
       </c>
       <c r="E18" s="2">
-        <v>-0.3</v>
+        <v>1.46</v>
       </c>
       <c r="F18" s="2">
-        <v>-1.03</v>
+        <v>1.46</v>
       </c>
       <c r="G18" s="2">
-        <v>-2</v>
+        <v>-4.4</v>
       </c>
       <c r="H18" s="2">
-        <v>-1.18</v>
+        <v>-0.86</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>3495.25</v>
+        <v>37719.99</v>
       </c>
       <c r="K18" s="1">
-        <v>3476.87</v>
+        <v>35548.44</v>
       </c>
       <c r="L18" s="1">
-        <v>3532.03</v>
+        <v>37253.89</v>
       </c>
       <c r="M18" s="3">
-        <v>-19.7</v>
+        <v>-636.01</v>
       </c>
       <c r="N18" s="3">
-        <v>-16.41</v>
+        <v>-539.82</v>
       </c>
       <c r="O18" s="3">
-        <v>1.42</v>
+        <v>-704.61</v>
       </c>
       <c r="P18" s="3">
-        <v>15.15</v>
+        <v>-210.95</v>
       </c>
       <c r="Q18" s="3">
-        <v>117.46</v>
+        <v>929.96</v>
       </c>
       <c r="R18" s="3">
-        <v>141.63</v>
+        <v>1227.31</v>
       </c>
       <c r="S18" s="3">
-        <v>30.33</v>
+        <v>33.63</v>
       </c>
       <c r="T18" s="3">
-        <v>15.28</v>
+        <v>10.52</v>
       </c>
       <c r="U18" s="3">
-        <v>39.06</v>
+        <v>40.1</v>
       </c>
       <c r="V18" s="3">
-        <v>31.32</v>
+        <v>35.62</v>
       </c>
       <c r="W18" s="3">
         <v>0</v>
@@ -1796,67 +1796,67 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="C19" t="str">
-        <v>BHARATBOND-APR31</v>
+        <v>NIFTYINDDIGITAL</v>
       </c>
       <c r="D19" s="1">
-        <v>1440.45</v>
+        <v>8546.4</v>
       </c>
       <c r="E19" s="2">
-        <v>-0.35</v>
+        <v>1.44</v>
       </c>
       <c r="F19" s="2">
-        <v>-0.45</v>
+        <v>1.44</v>
       </c>
       <c r="G19" s="2">
-        <v>-0.92</v>
+        <v>6.48</v>
       </c>
       <c r="H19" s="2">
-        <v>1.11</v>
+        <v>-9.3</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>1440.86</v>
+        <v>8247.23</v>
       </c>
       <c r="K19" s="1">
-        <v>1447.48</v>
+        <v>8458.71</v>
       </c>
       <c r="L19" s="1">
-        <v>1457.8</v>
+        <v>8522.88</v>
       </c>
       <c r="M19" s="3">
-        <v>-3.84</v>
+        <v>28.28</v>
       </c>
       <c r="N19" s="3">
-        <v>-2.97</v>
+        <v>-16.35</v>
       </c>
       <c r="O19" s="3">
-        <v>3.8</v>
+        <v>65.7</v>
       </c>
       <c r="P19" s="3">
-        <v>7.24</v>
+        <v>59.36</v>
       </c>
       <c r="Q19" s="3">
-        <v>28.73</v>
+        <v>374.86</v>
       </c>
       <c r="R19" s="3">
-        <v>28.47</v>
+        <v>514.22</v>
       </c>
       <c r="S19" s="3">
-        <v>18.6</v>
+        <v>56.06</v>
       </c>
       <c r="T19" s="3">
-        <v>18.03</v>
+        <v>19.36</v>
       </c>
       <c r="U19" s="3">
-        <v>75.39</v>
+        <v>22.83</v>
       </c>
       <c r="V19" s="3">
-        <v>34.98</v>
+        <v>20.52</v>
       </c>
       <c r="W19" s="3">
         <v>0</v>
@@ -1873,67 +1873,67 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="C20" t="str">
-        <v>NIFTY50VALUE20</v>
+        <v>CNXSMALLCAP</v>
       </c>
       <c r="D20" s="1">
-        <v>11280.35</v>
+        <v>17985</v>
       </c>
       <c r="E20" s="2">
-        <v>-0.36</v>
+        <v>1.38</v>
       </c>
       <c r="F20" s="2">
-        <v>-2.18</v>
+        <v>1.38</v>
       </c>
       <c r="G20" s="2">
-        <v>1.21</v>
+        <v>-6.55</v>
       </c>
       <c r="H20" s="2">
-        <v>-15.03</v>
+        <v>1.53</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>12171.5</v>
+        <v>18189.73</v>
       </c>
       <c r="K20" s="1">
-        <v>11317.59</v>
+        <v>18588.89</v>
       </c>
       <c r="L20" s="1">
-        <v>11538.09</v>
+        <v>19542.92</v>
       </c>
       <c r="M20" s="3">
-        <v>-43.96</v>
+        <v>-379.49</v>
       </c>
       <c r="N20" s="3">
-        <v>-81.17</v>
+        <v>-237.07</v>
       </c>
       <c r="O20" s="3">
-        <v>-267.67</v>
+        <v>133.48</v>
       </c>
       <c r="P20" s="3">
-        <v>-236.36</v>
+        <v>408.34</v>
       </c>
       <c r="Q20" s="3">
-        <v>-133.65</v>
+        <v>816.93</v>
       </c>
       <c r="R20" s="3">
-        <v>113.71</v>
+        <v>847.56</v>
       </c>
       <c r="S20" s="3">
-        <v>46.06</v>
+        <v>29.34</v>
       </c>
       <c r="T20" s="3">
-        <v>16.2</v>
+        <v>9.78</v>
       </c>
       <c r="U20" s="3">
-        <v>27.76</v>
+        <v>50.44</v>
       </c>
       <c r="V20" s="3">
-        <v>29.04</v>
+        <v>37.57</v>
       </c>
       <c r="W20" s="3">
         <v>0</v>
@@ -1950,67 +1950,67 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="C21" t="str">
-        <v>NIFTY</v>
+        <v>NIFTYMULTIINFRA</v>
       </c>
       <c r="D21" s="1">
-        <v>22600</v>
+        <v>13352.05</v>
       </c>
       <c r="E21" s="2">
-        <v>-0.39</v>
+        <v>1.37</v>
       </c>
       <c r="F21" s="2">
-        <v>-2.36</v>
+        <v>1.37</v>
       </c>
       <c r="G21" s="2">
-        <v>-0.09</v>
+        <v>-2.89</v>
       </c>
       <c r="H21" s="2">
-        <v>-13.51</v>
+        <v>-7.73</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
       </c>
       <c r="J21" s="1">
-        <v>24118.84</v>
+        <v>14136.78</v>
       </c>
       <c r="K21" s="1">
-        <v>22747.25</v>
+        <v>13435.21</v>
       </c>
       <c r="L21" s="1">
-        <v>23403.72</v>
+        <v>14083.08</v>
       </c>
       <c r="M21" s="3">
-        <v>-169.46</v>
+        <v>-214.3</v>
       </c>
       <c r="N21" s="3">
-        <v>-222.63</v>
+        <v>-209.52</v>
       </c>
       <c r="O21" s="3">
-        <v>-401.05</v>
+        <v>-215.84</v>
       </c>
       <c r="P21" s="3">
-        <v>-278.18</v>
+        <v>-57.34</v>
       </c>
       <c r="Q21" s="3">
-        <v>177.18</v>
+        <v>72.84</v>
       </c>
       <c r="R21" s="3">
-        <v>596.29</v>
+        <v>117.75</v>
       </c>
       <c r="S21" s="3">
-        <v>42.39</v>
+        <v>37.58</v>
       </c>
       <c r="T21" s="3">
-        <v>13.43</v>
+        <v>11.09</v>
       </c>
       <c r="U21" s="3">
-        <v>28.3</v>
+        <v>34.87</v>
       </c>
       <c r="V21" s="3">
-        <v>36.33</v>
+        <v>45.41</v>
       </c>
       <c r="W21" s="3">
         <v>0</v>
@@ -2027,67 +2027,67 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="C22" t="str">
-        <v>BHARATBOND-APR32</v>
+        <v>NIFTYMULTIMFG</v>
       </c>
       <c r="D22" s="1">
-        <v>1300.19</v>
+        <v>15286.05</v>
       </c>
       <c r="E22" s="2">
-        <v>-0.41</v>
+        <v>1.35</v>
       </c>
       <c r="F22" s="2">
-        <v>-0.58</v>
+        <v>1.35</v>
       </c>
       <c r="G22" s="2">
-        <v>-1.17</v>
+        <v>-4.56</v>
       </c>
       <c r="H22" s="2">
-        <v>0.16</v>
+        <v>-4.31</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
       </c>
       <c r="J22" s="1">
-        <v>1308</v>
+        <v>16000.49</v>
       </c>
       <c r="K22" s="1">
-        <v>1308.25</v>
+        <v>15483.98</v>
       </c>
       <c r="L22" s="1">
-        <v>1321.23</v>
+        <v>16347.16</v>
       </c>
       <c r="M22" s="3">
-        <v>-4.72</v>
+        <v>-290.59</v>
       </c>
       <c r="N22" s="3">
-        <v>-3.8</v>
+        <v>-261.9</v>
       </c>
       <c r="O22" s="3">
-        <v>1.7</v>
+        <v>-126.04</v>
       </c>
       <c r="P22" s="3">
-        <v>5.61</v>
+        <v>79.96</v>
       </c>
       <c r="Q22" s="3">
-        <v>23.49</v>
+        <v>349.56</v>
       </c>
       <c r="R22" s="3">
-        <v>24.11</v>
+        <v>326.8</v>
       </c>
       <c r="S22" s="3">
-        <v>16.61</v>
+        <v>34.48</v>
       </c>
       <c r="T22" s="3">
-        <v>17.75</v>
+        <v>8.13</v>
       </c>
       <c r="U22" s="3">
-        <v>80.17</v>
+        <v>38.96</v>
       </c>
       <c r="V22" s="3">
-        <v>39.45</v>
+        <v>48.97</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -2104,67 +2104,67 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="C23" t="str">
-        <v>NIFTY100LOWVOL30</v>
+        <v>NIFTYOILANDGAS</v>
       </c>
       <c r="D23" s="1">
-        <v>18563.55</v>
+        <v>10520.95</v>
       </c>
       <c r="E23" s="2">
-        <v>-0.42</v>
+        <v>1.35</v>
       </c>
       <c r="F23" s="2">
-        <v>-1.88</v>
+        <v>1.35</v>
       </c>
       <c r="G23" s="2">
-        <v>-1.18</v>
+        <v>-0.88</v>
       </c>
       <c r="H23" s="2">
-        <v>-12.15</v>
+        <v>-13.98</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <v>19854.88</v>
+        <v>11282.93</v>
       </c>
       <c r="K23" s="1">
-        <v>18709.42</v>
+        <v>10492.06</v>
       </c>
       <c r="L23" s="1">
-        <v>19462.17</v>
+        <v>10855.13</v>
       </c>
       <c r="M23" s="3">
-        <v>-216.15</v>
+        <v>-109.89</v>
       </c>
       <c r="N23" s="3">
-        <v>-252.08</v>
+        <v>-129.34</v>
       </c>
       <c r="O23" s="3">
-        <v>-309.66</v>
+        <v>-233.14</v>
       </c>
       <c r="P23" s="3">
-        <v>-147.47</v>
+        <v>-175.66</v>
       </c>
       <c r="Q23" s="3">
-        <v>746.15</v>
+        <v>79.23</v>
       </c>
       <c r="R23" s="3">
-        <v>1109.05</v>
+        <v>280.64</v>
       </c>
       <c r="S23" s="3">
-        <v>37.55</v>
+        <v>45.04</v>
       </c>
       <c r="T23" s="3">
-        <v>9.64</v>
+        <v>17.68</v>
       </c>
       <c r="U23" s="3">
-        <v>28.24</v>
+        <v>29.63</v>
       </c>
       <c r="V23" s="3">
-        <v>48.95</v>
+        <v>31.06</v>
       </c>
       <c r="W23" s="3">
         <v>0</v>
@@ -2181,67 +2181,67 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="C24" t="str">
-        <v>CNXINFRA</v>
+        <v>NIFTY50TR2XLEV</v>
       </c>
       <c r="D24" s="1">
-        <v>8554.25</v>
+        <v>16020.75</v>
       </c>
       <c r="E24" s="2">
-        <v>-0.44</v>
+        <v>1.31</v>
       </c>
       <c r="F24" s="2">
-        <v>-1.96</v>
+        <v>1.31</v>
       </c>
       <c r="G24" s="2">
-        <v>-2.06</v>
+        <v>0.69</v>
       </c>
       <c r="H24" s="2">
-        <v>-11.04</v>
+        <v>-27.17</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <v>9221.18</v>
+        <v>18338.84</v>
       </c>
       <c r="K24" s="1">
-        <v>8630.32</v>
+        <v>16035.88</v>
       </c>
       <c r="L24" s="1">
-        <v>8996.44</v>
+        <v>17028.08</v>
       </c>
       <c r="M24" s="3">
-        <v>-113.42</v>
+        <v>-259.06</v>
       </c>
       <c r="N24" s="3">
-        <v>-126.4</v>
+        <v>-334.02</v>
       </c>
       <c r="O24" s="3">
-        <v>-167.26</v>
+        <v>-707.92</v>
       </c>
       <c r="P24" s="3">
-        <v>-80.58</v>
+        <v>-553.7</v>
       </c>
       <c r="Q24" s="3">
-        <v>264.02</v>
+        <v>264.11</v>
       </c>
       <c r="R24" s="3">
-        <v>432.19</v>
+        <v>926.62</v>
       </c>
       <c r="S24" s="3">
-        <v>37.31</v>
+        <v>45.04</v>
       </c>
       <c r="T24" s="3">
-        <v>13.74</v>
+        <v>12</v>
       </c>
       <c r="U24" s="3">
-        <v>31.24</v>
+        <v>26.39</v>
       </c>
       <c r="V24" s="3">
-        <v>42.52</v>
+        <v>38.22</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -2258,67 +2258,67 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="C25" t="str">
-        <v>NIFTY100LIQ15</v>
+        <v>NIFTY50PR2XLEV</v>
       </c>
       <c r="D25" s="1">
-        <v>7283.05</v>
+        <v>10501.1</v>
       </c>
       <c r="E25" s="2">
-        <v>-0.44</v>
+        <v>1.31</v>
       </c>
       <c r="F25" s="2">
-        <v>-2.36</v>
+        <v>1.31</v>
       </c>
       <c r="G25" s="2">
-        <v>2.92</v>
+        <v>0.63</v>
       </c>
       <c r="H25" s="2">
-        <v>-3.69</v>
+        <v>-28.57</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <v>7333.45</v>
+        <v>12150.78</v>
       </c>
       <c r="K25" s="1">
-        <v>7294.32</v>
+        <v>10513.55</v>
       </c>
       <c r="L25" s="1">
-        <v>7395.36</v>
+        <v>11170.09</v>
       </c>
       <c r="M25" s="3">
-        <v>-3.25</v>
+        <v>-172.67</v>
       </c>
       <c r="N25" s="3">
-        <v>-32.05</v>
+        <v>-221.68</v>
       </c>
       <c r="O25" s="3">
-        <v>-4.23</v>
+        <v>-508.08</v>
       </c>
       <c r="P25" s="3">
-        <v>30.63</v>
+        <v>-412.2</v>
       </c>
       <c r="Q25" s="3">
-        <v>466.66</v>
+        <v>-14.94</v>
       </c>
       <c r="R25" s="3">
-        <v>551.54</v>
+        <v>424.43</v>
       </c>
       <c r="S25" s="3">
-        <v>49.44</v>
+        <v>44.9</v>
       </c>
       <c r="T25" s="3">
-        <v>19.57</v>
+        <v>11.91</v>
       </c>
       <c r="U25" s="3">
-        <v>26.75</v>
+        <v>26.45</v>
       </c>
       <c r="V25" s="3">
-        <v>27.99</v>
+        <v>38.6</v>
       </c>
       <c r="W25" s="3">
         <v>0</v>
@@ -2335,67 +2335,67 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="C26" t="str">
-        <v>BHARATBOND-APR33</v>
+        <v>NIFTYMIDCAP50</v>
       </c>
       <c r="D26" s="1">
-        <v>1255.18</v>
+        <v>16266.85</v>
       </c>
       <c r="E26" s="2">
-        <v>-0.5</v>
+        <v>1.25</v>
       </c>
       <c r="F26" s="2">
-        <v>-0.72</v>
+        <v>1.25</v>
       </c>
       <c r="G26" s="2">
-        <v>-1.42</v>
+        <v>-4.47</v>
       </c>
       <c r="H26" s="2">
-        <v>-0.5</v>
+        <v>-5.72</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>1268.31</v>
+        <v>17213.81</v>
       </c>
       <c r="K26" s="1">
-        <v>1264.42</v>
+        <v>16577.97</v>
       </c>
       <c r="L26" s="1">
-        <v>1279.52</v>
+        <v>17593.24</v>
       </c>
       <c r="M26" s="3">
-        <v>-5.57</v>
+        <v>-346.52</v>
       </c>
       <c r="N26" s="3">
-        <v>-4.46</v>
+        <v>-303.9</v>
       </c>
       <c r="O26" s="3">
-        <v>0.63</v>
+        <v>-162.68</v>
       </c>
       <c r="P26" s="3">
-        <v>4.83</v>
+        <v>90.36</v>
       </c>
       <c r="Q26" s="3">
-        <v>20.72</v>
+        <v>875.97</v>
       </c>
       <c r="R26" s="3">
-        <v>21.84</v>
+        <v>1043.44</v>
       </c>
       <c r="S26" s="3">
-        <v>15.49</v>
+        <v>31.26</v>
       </c>
       <c r="T26" s="3">
-        <v>15.75</v>
+        <v>7.43</v>
       </c>
       <c r="U26" s="3">
-        <v>81.79</v>
+        <v>40.47</v>
       </c>
       <c r="V26" s="3">
-        <v>42.25</v>
+        <v>49.72</v>
       </c>
       <c r="W26" s="3">
         <v>0</v>
@@ -2412,67 +2412,67 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="C27" t="str">
-        <v>NIFTY100ESGSECLDR</v>
+        <v>CNXINFRA</v>
       </c>
       <c r="D27" s="1">
-        <v>3753.2</v>
+        <v>8661.2</v>
       </c>
       <c r="E27" s="2">
-        <v>-0.55</v>
+        <v>1.25</v>
       </c>
       <c r="F27" s="2">
-        <v>-2.91</v>
+        <v>1.25</v>
       </c>
       <c r="G27" s="2">
-        <v>-0.77</v>
+        <v>-0.83</v>
       </c>
       <c r="H27" s="2">
-        <v>-13.78</v>
+        <v>-9.93</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>4031.76</v>
+        <v>9216.09</v>
       </c>
       <c r="K27" s="1">
-        <v>3789.4</v>
+        <v>8635.93</v>
       </c>
       <c r="L27" s="1">
-        <v>3917.9</v>
+        <v>8981.47</v>
       </c>
       <c r="M27" s="3">
-        <v>-35.3</v>
+        <v>-103.57</v>
       </c>
       <c r="N27" s="3">
-        <v>-43.02</v>
+        <v>-121.84</v>
       </c>
       <c r="O27" s="3">
-        <v>-69.09</v>
+        <v>-175.63</v>
       </c>
       <c r="P27" s="3">
-        <v>-43.1</v>
+        <v>-99.59</v>
       </c>
       <c r="Q27" s="3">
-        <v>123.09</v>
+        <v>272.56</v>
       </c>
       <c r="R27" s="3">
-        <v>206.14</v>
+        <v>433.9</v>
       </c>
       <c r="S27" s="3">
-        <v>40.11</v>
+        <v>44.47</v>
       </c>
       <c r="T27" s="3">
-        <v>14.07</v>
+        <v>15.55</v>
       </c>
       <c r="U27" s="3">
-        <v>31.41</v>
+        <v>28.03</v>
       </c>
       <c r="V27" s="3">
-        <v>37.56</v>
+        <v>41.53</v>
       </c>
       <c r="W27" s="3">
         <v>0</v>
@@ -2489,67 +2489,67 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>NIFTYAUTO</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="C28" t="str">
-        <v>NIFTYAUTO</v>
+        <v>CNXMIDCAP</v>
       </c>
       <c r="D28" s="1">
-        <v>24862.3</v>
+        <v>56465.4</v>
       </c>
       <c r="E28" s="2">
-        <v>-0.6</v>
+        <v>1.19</v>
       </c>
       <c r="F28" s="2">
-        <v>-3.52</v>
+        <v>1.19</v>
       </c>
       <c r="G28" s="2">
-        <v>-5.44</v>
+        <v>-4.83</v>
       </c>
       <c r="H28" s="2">
-        <v>-11.8</v>
+        <v>-6.64</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
       </c>
       <c r="J28" s="1">
-        <v>26911.8</v>
+        <v>60273.79</v>
       </c>
       <c r="K28" s="1">
-        <v>25282.21</v>
+        <v>57749.53</v>
       </c>
       <c r="L28" s="1">
-        <v>27168.61</v>
+        <v>61265.6</v>
       </c>
       <c r="M28" s="3">
-        <v>-551.37</v>
+        <v>-1218.17</v>
       </c>
       <c r="N28" s="3">
-        <v>-601.04</v>
+        <v>-1020.65</v>
       </c>
       <c r="O28" s="3">
-        <v>-308.95</v>
+        <v>-703.37</v>
       </c>
       <c r="P28" s="3">
-        <v>91.11</v>
+        <v>176.31</v>
       </c>
       <c r="Q28" s="3">
-        <v>1449.2</v>
+        <v>2781.02</v>
       </c>
       <c r="R28" s="3">
-        <v>1805.34</v>
+        <v>3462.12</v>
       </c>
       <c r="S28" s="3">
-        <v>34.23</v>
+        <v>30.24</v>
       </c>
       <c r="T28" s="3">
-        <v>10.26</v>
+        <v>6.72</v>
       </c>
       <c r="U28" s="3">
-        <v>36.28</v>
+        <v>44.13</v>
       </c>
       <c r="V28" s="3">
-        <v>55.28</v>
+        <v>51.82</v>
       </c>
       <c r="W28" s="3">
         <v>0</v>
@@ -2566,67 +2566,67 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="C29" t="str">
-        <v>NIFTYOILANDGAS</v>
+        <v>NIFTYINDDEFENCE</v>
       </c>
       <c r="D29" s="1">
-        <v>10380.55</v>
+        <v>8661.95</v>
       </c>
       <c r="E29" s="2">
-        <v>-0.62</v>
+        <v>1.18</v>
       </c>
       <c r="F29" s="2">
-        <v>-1.67</v>
+        <v>1.18</v>
       </c>
       <c r="G29" s="2">
-        <v>-2.2</v>
+        <v>-6.63</v>
       </c>
       <c r="H29" s="2">
-        <v>-15.13</v>
+        <v>11.8</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
       </c>
       <c r="J29" s="1">
-        <v>11291.49</v>
+        <v>8847.33</v>
       </c>
       <c r="K29" s="1">
-        <v>10485.64</v>
+        <v>8922.78</v>
       </c>
       <c r="L29" s="1">
-        <v>10870.59</v>
+        <v>9436.77</v>
       </c>
       <c r="M29" s="3">
-        <v>-120.55</v>
+        <v>-178.05</v>
       </c>
       <c r="N29" s="3">
-        <v>-134.21</v>
+        <v>-130.67</v>
       </c>
       <c r="O29" s="3">
-        <v>-230.43</v>
+        <v>29.55</v>
       </c>
       <c r="P29" s="3">
-        <v>-161.29</v>
+        <v>190.65</v>
       </c>
       <c r="Q29" s="3">
-        <v>68.02</v>
+        <v>591.12</v>
       </c>
       <c r="R29" s="3">
-        <v>278.4</v>
+        <v>520.33</v>
       </c>
       <c r="S29" s="3">
-        <v>36.85</v>
+        <v>33.74</v>
       </c>
       <c r="T29" s="3">
-        <v>16.24</v>
+        <v>13.05</v>
       </c>
       <c r="U29" s="3">
-        <v>33.12</v>
+        <v>41.72</v>
       </c>
       <c r="V29" s="3">
-        <v>31.51</v>
+        <v>29.08</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2643,67 +2643,67 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="C30" t="str">
-        <v>NIFTY50EQLWGT</v>
+        <v>NIFTYSMALLCAP250</v>
       </c>
       <c r="D30" s="1">
-        <v>30366.85</v>
+        <v>16570.5</v>
       </c>
       <c r="E30" s="2">
-        <v>-0.64</v>
+        <v>1.13</v>
       </c>
       <c r="F30" s="2">
-        <v>-2.67</v>
+        <v>1.13</v>
       </c>
       <c r="G30" s="2">
-        <v>-1.74</v>
+        <v>-6.9</v>
       </c>
       <c r="H30" s="2">
-        <v>-8.89</v>
+        <v>-0.68</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>32337.72</v>
+        <v>16948.59</v>
       </c>
       <c r="K30" s="1">
-        <v>30731.31</v>
+        <v>17125.03</v>
       </c>
       <c r="L30" s="1">
-        <v>31919.58</v>
+        <v>18007.55</v>
       </c>
       <c r="M30" s="3">
-        <v>-352.25</v>
+        <v>-349.8</v>
       </c>
       <c r="N30" s="3">
-        <v>-393.41</v>
+        <v>-227.08</v>
       </c>
       <c r="O30" s="3">
-        <v>-406.6</v>
+        <v>54.88</v>
       </c>
       <c r="P30" s="3">
-        <v>-118.39</v>
+        <v>309.15</v>
       </c>
       <c r="Q30" s="3">
-        <v>1807.56</v>
+        <v>1270.26</v>
       </c>
       <c r="R30" s="3">
-        <v>2369</v>
+        <v>1421.29</v>
       </c>
       <c r="S30" s="3">
-        <v>37.19</v>
+        <v>27.78</v>
       </c>
       <c r="T30" s="3">
-        <v>11.25</v>
+        <v>9.24</v>
       </c>
       <c r="U30" s="3">
-        <v>32.05</v>
+        <v>50.67</v>
       </c>
       <c r="V30" s="3">
-        <v>44.89</v>
+        <v>40.23</v>
       </c>
       <c r="W30" s="3">
         <v>0</v>
@@ -2720,67 +2720,67 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>CNXPSE</v>
       </c>
       <c r="C31" t="str">
-        <v>NIFTYALPHALOWVOL</v>
+        <v>CNXPSE</v>
       </c>
       <c r="D31" s="1">
-        <v>24348.8</v>
+        <v>8984.95</v>
       </c>
       <c r="E31" s="2">
-        <v>-0.68</v>
+        <v>1.12</v>
       </c>
       <c r="F31" s="2">
-        <v>-2.27</v>
+        <v>1.12</v>
       </c>
       <c r="G31" s="2">
-        <v>-3.45</v>
+        <v>-4.01</v>
       </c>
       <c r="H31" s="2">
-        <v>-10.08</v>
+        <v>-8.82</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>26241.6</v>
+        <v>9979.7</v>
       </c>
       <c r="K31" s="1">
-        <v>24699.33</v>
+        <v>9097.99</v>
       </c>
       <c r="L31" s="1">
-        <v>26060.84</v>
+        <v>9501.72</v>
       </c>
       <c r="M31" s="3">
-        <v>-437.51</v>
+        <v>-144.02</v>
       </c>
       <c r="N31" s="3">
-        <v>-449.38</v>
+        <v>-132.09</v>
       </c>
       <c r="O31" s="3">
-        <v>-363.36</v>
+        <v>-262.81</v>
       </c>
       <c r="P31" s="3">
-        <v>-70.73</v>
+        <v>-172.67</v>
       </c>
       <c r="Q31" s="3">
-        <v>1128.35</v>
+        <v>783.98</v>
       </c>
       <c r="R31" s="3">
-        <v>1592.4</v>
+        <v>1090.22</v>
       </c>
       <c r="S31" s="3">
-        <v>29.59</v>
+        <v>34.8</v>
       </c>
       <c r="T31" s="3">
-        <v>8.42</v>
+        <v>7.78</v>
       </c>
       <c r="U31" s="3">
-        <v>34.6</v>
+        <v>37.04</v>
       </c>
       <c r="V31" s="3">
-        <v>52.1</v>
+        <v>49.43</v>
       </c>
       <c r="W31" s="3">
         <v>0</v>
@@ -2797,67 +2797,67 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="C32" t="str">
-        <v>NIFTY100</v>
+        <v>NIFTYMIDSMALLCAP400</v>
       </c>
       <c r="D32" s="1">
-        <v>23465.05</v>
+        <v>19279.45</v>
       </c>
       <c r="E32" s="2">
-        <v>-0.73</v>
+        <v>1.09</v>
       </c>
       <c r="F32" s="2">
-        <v>-2.77</v>
+        <v>1.09</v>
       </c>
       <c r="G32" s="2">
-        <v>-1.14</v>
+        <v>-5.56</v>
       </c>
       <c r="H32" s="2">
-        <v>-12.08</v>
+        <v>-4.64</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
       </c>
       <c r="J32" s="1">
-        <v>25023.62</v>
+        <v>20254.67</v>
       </c>
       <c r="K32" s="1">
-        <v>23729.98</v>
+        <v>19775.77</v>
       </c>
       <c r="L32" s="1">
-        <v>24513.28</v>
+        <v>20894.85</v>
       </c>
       <c r="M32" s="3">
-        <v>-219.95</v>
+        <v>-405.83</v>
       </c>
       <c r="N32" s="3">
-        <v>-255.84</v>
+        <v>-315.68</v>
       </c>
       <c r="O32" s="3">
-        <v>-362.29</v>
+        <v>-128.29</v>
       </c>
       <c r="P32" s="3">
-        <v>-199.92</v>
+        <v>166.12</v>
       </c>
       <c r="Q32" s="3">
-        <v>310.24</v>
+        <v>1539.23</v>
       </c>
       <c r="R32" s="3">
-        <v>704.22</v>
+        <v>1815.59</v>
       </c>
       <c r="S32" s="3">
-        <v>38.79</v>
+        <v>28.75</v>
       </c>
       <c r="T32" s="3">
-        <v>12.05</v>
+        <v>7.21</v>
       </c>
       <c r="U32" s="3">
-        <v>32.28</v>
+        <v>48.91</v>
       </c>
       <c r="V32" s="3">
-        <v>43.23</v>
+        <v>50.11</v>
       </c>
       <c r="W32" s="3">
         <v>0</v>
@@ -2874,67 +2874,67 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="C33" t="str">
-        <v>NIFTY50TR2XLEV</v>
+        <v>NIFTYM150QLTY50</v>
       </c>
       <c r="D33" s="1">
-        <v>15814</v>
+        <v>21963.15</v>
       </c>
       <c r="E33" s="2">
-        <v>-0.77</v>
+        <v>1.08</v>
       </c>
       <c r="F33" s="2">
-        <v>-4.77</v>
+        <v>1.08</v>
       </c>
       <c r="G33" s="2">
-        <v>-0.61</v>
+        <v>-3.53</v>
       </c>
       <c r="H33" s="2">
-        <v>-28.11</v>
+        <v>-8.71</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>18368.85</v>
+        <v>23471.33</v>
       </c>
       <c r="K33" s="1">
-        <v>16039.25</v>
+        <v>22428.13</v>
       </c>
       <c r="L33" s="1">
-        <v>17081.63</v>
+        <v>23606.7</v>
       </c>
       <c r="M33" s="3">
-        <v>-276.62</v>
+        <v>-390.95</v>
       </c>
       <c r="N33" s="3">
-        <v>-352.76</v>
+        <v>-328.12</v>
       </c>
       <c r="O33" s="3">
-        <v>-691.79</v>
+        <v>-341.26</v>
       </c>
       <c r="P33" s="3">
-        <v>-515.15</v>
+        <v>-51.62</v>
       </c>
       <c r="Q33" s="3">
-        <v>247.62</v>
+        <v>982.33</v>
       </c>
       <c r="R33" s="3">
-        <v>923.32</v>
+        <v>1351.3</v>
       </c>
       <c r="S33" s="3">
-        <v>41.48</v>
+        <v>32.2</v>
       </c>
       <c r="T33" s="3">
-        <v>13.13</v>
+        <v>9.61</v>
       </c>
       <c r="U33" s="3">
-        <v>28.86</v>
+        <v>43.03</v>
       </c>
       <c r="V33" s="3">
-        <v>38.28</v>
+        <v>42.82</v>
       </c>
       <c r="W33" s="3">
         <v>0</v>
@@ -2951,67 +2951,67 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>Nifty midcap 150</v>
       </c>
       <c r="C34" t="str">
-        <v>NIFTYPVTBANK</v>
+        <v>NIFTYMIDCAP150</v>
       </c>
       <c r="D34" s="1">
-        <v>26656.3</v>
+        <v>20812.25</v>
       </c>
       <c r="E34" s="2">
-        <v>-0.78</v>
+        <v>1.07</v>
       </c>
       <c r="F34" s="2">
-        <v>-3.77</v>
+        <v>1.07</v>
       </c>
       <c r="G34" s="2">
-        <v>-0.15</v>
+        <v>-4.83</v>
       </c>
       <c r="H34" s="2">
-        <v>-7.19</v>
+        <v>-6.57</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>27362.11</v>
+        <v>22168.85</v>
       </c>
       <c r="K34" s="1">
-        <v>27050.18</v>
+        <v>21261.46</v>
       </c>
       <c r="L34" s="1">
-        <v>27268.91</v>
+        <v>22520.56</v>
       </c>
       <c r="M34" s="3">
-        <v>-60.86</v>
+        <v>-436.73</v>
       </c>
       <c r="N34" s="3">
-        <v>-42.96</v>
+        <v>-369.82</v>
       </c>
       <c r="O34" s="3">
-        <v>-53.67</v>
+        <v>-247.63</v>
       </c>
       <c r="P34" s="3">
-        <v>14.75</v>
+        <v>69.08</v>
       </c>
       <c r="Q34" s="3">
-        <v>629.95</v>
+        <v>1671.77</v>
       </c>
       <c r="R34" s="3">
-        <v>871.88</v>
+        <v>2020.97</v>
       </c>
       <c r="S34" s="3">
-        <v>41.15</v>
+        <v>29.69</v>
       </c>
       <c r="T34" s="3">
-        <v>16.31</v>
+        <v>7.04</v>
       </c>
       <c r="U34" s="3">
-        <v>26.01</v>
+        <v>44.35</v>
       </c>
       <c r="V34" s="3">
-        <v>14.86</v>
+        <v>51.31</v>
       </c>
       <c r="W34" s="3">
         <v>0</v>
@@ -3028,67 +3028,67 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="C35" t="str">
-        <v>NIFTY50PR2XLEV</v>
+        <v>NIFTYINDIAMFG</v>
       </c>
       <c r="D35" s="1">
-        <v>10365.6</v>
+        <v>14665.7</v>
       </c>
       <c r="E35" s="2">
-        <v>-0.79</v>
+        <v>1.03</v>
       </c>
       <c r="F35" s="2">
-        <v>-4.79</v>
+        <v>1.03</v>
       </c>
       <c r="G35" s="2">
-        <v>-0.67</v>
+        <v>-5.1</v>
       </c>
       <c r="H35" s="2">
-        <v>-29.49</v>
+        <v>-4.85</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>12171.86</v>
+        <v>15621.4</v>
       </c>
       <c r="K35" s="1">
-        <v>10516.32</v>
+        <v>14895.51</v>
       </c>
       <c r="L35" s="1">
-        <v>11205.53</v>
+        <v>15808.48</v>
       </c>
       <c r="M35" s="3">
-        <v>-184.1</v>
+        <v>-305.53</v>
       </c>
       <c r="N35" s="3">
-        <v>-233.93</v>
+        <v>-279.89</v>
       </c>
       <c r="O35" s="3">
-        <v>-499.42</v>
+        <v>-178.7</v>
       </c>
       <c r="P35" s="3">
-        <v>-388.23</v>
+        <v>41.4</v>
       </c>
       <c r="Q35" s="3">
-        <v>-25.75</v>
+        <v>1232.94</v>
       </c>
       <c r="R35" s="3">
-        <v>422.27</v>
+        <v>1441.07</v>
       </c>
       <c r="S35" s="3">
-        <v>41.34</v>
+        <v>32.19</v>
       </c>
       <c r="T35" s="3">
-        <v>13.03</v>
+        <v>7.37</v>
       </c>
       <c r="U35" s="3">
-        <v>28.92</v>
+        <v>40.23</v>
       </c>
       <c r="V35" s="3">
-        <v>38.66</v>
+        <v>51.66</v>
       </c>
       <c r="W35" s="3">
         <v>0</v>
@@ -3105,67 +3105,67 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="C36" t="str">
-        <v>NIFTYHEALTHCARE</v>
+        <v>NIFTYMIDSELECT</v>
       </c>
       <c r="D36" s="1">
-        <v>15387</v>
+        <v>13167.35</v>
       </c>
       <c r="E36" s="2">
-        <v>-0.83</v>
+        <v>1.03</v>
       </c>
       <c r="F36" s="2">
-        <v>-1.89</v>
+        <v>1.03</v>
       </c>
       <c r="G36" s="2">
-        <v>-4.65</v>
+        <v>-4.11</v>
       </c>
       <c r="H36" s="2">
-        <v>5.1</v>
+        <v>-4.43</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
       </c>
       <c r="J36" s="1">
-        <v>15444.88</v>
+        <v>13993.46</v>
       </c>
       <c r="K36" s="1">
-        <v>15655.56</v>
+        <v>13426.09</v>
       </c>
       <c r="L36" s="1">
-        <v>16324.25</v>
+        <v>14268.43</v>
       </c>
       <c r="M36" s="3">
-        <v>-264.42</v>
+        <v>-280.59</v>
       </c>
       <c r="N36" s="3">
-        <v>-219.88</v>
+        <v>-253.01</v>
       </c>
       <c r="O36" s="3">
-        <v>161.13</v>
+        <v>-155.5</v>
       </c>
       <c r="P36" s="3">
-        <v>338.5</v>
+        <v>66.63</v>
       </c>
       <c r="Q36" s="3">
-        <v>968.83</v>
+        <v>855.49</v>
       </c>
       <c r="R36" s="3">
-        <v>992.24</v>
+        <v>997.79</v>
       </c>
       <c r="S36" s="3">
-        <v>28.44</v>
+        <v>31.33</v>
       </c>
       <c r="T36" s="3">
-        <v>6.2</v>
+        <v>8.01</v>
       </c>
       <c r="U36" s="3">
-        <v>31.18</v>
+        <v>39.54</v>
       </c>
       <c r="V36" s="3">
-        <v>41.01</v>
+        <v>46.82</v>
       </c>
       <c r="W36" s="3">
         <v>0</v>
@@ -3182,67 +3182,67 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>NIFTY100ESG</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="C37" t="str">
-        <v>NIFTY100ESG</v>
+        <v>CNXNIFTYJUNIOR</v>
       </c>
       <c r="D37" s="1">
-        <v>4647.95</v>
+        <v>66477.15</v>
       </c>
       <c r="E37" s="2">
-        <v>-0.86</v>
+        <v>0.99</v>
       </c>
       <c r="F37" s="2">
-        <v>-2.95</v>
+        <v>0.99</v>
       </c>
       <c r="G37" s="2">
-        <v>-0.77</v>
+        <v>-4.69</v>
       </c>
       <c r="H37" s="2">
-        <v>-10.29</v>
+        <v>-4.16</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>4912.71</v>
+        <v>70002.76</v>
       </c>
       <c r="K37" s="1">
-        <v>4697.8</v>
+        <v>67721.76</v>
       </c>
       <c r="L37" s="1">
-        <v>4858.01</v>
+        <v>71325.64</v>
       </c>
       <c r="M37" s="3">
-        <v>-41.95</v>
+        <v>-1228.19</v>
       </c>
       <c r="N37" s="3">
-        <v>-52.54</v>
+        <v>-1071.34</v>
       </c>
       <c r="O37" s="3">
-        <v>-54.23</v>
+        <v>-615.96</v>
       </c>
       <c r="P37" s="3">
-        <v>-17.96</v>
+        <v>316.49</v>
       </c>
       <c r="Q37" s="3">
-        <v>216.38</v>
+        <v>2569.94</v>
       </c>
       <c r="R37" s="3">
-        <v>298.7</v>
+        <v>3163.61</v>
       </c>
       <c r="S37" s="3">
-        <v>39.8</v>
+        <v>32.44</v>
       </c>
       <c r="T37" s="3">
-        <v>14.17</v>
+        <v>8.06</v>
       </c>
       <c r="U37" s="3">
-        <v>32.25</v>
+        <v>39.56</v>
       </c>
       <c r="V37" s="3">
-        <v>37.43</v>
+        <v>48.98</v>
       </c>
       <c r="W37" s="3">
         <v>0</v>
@@ -3259,67 +3259,67 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="C38" t="str">
-        <v>NIFTYCPSE</v>
+        <v>NIFTY100EQLWGT</v>
       </c>
       <c r="D38" s="1">
-        <v>5878.45</v>
+        <v>31937.4</v>
       </c>
       <c r="E38" s="2">
-        <v>-0.9</v>
+        <v>0.94</v>
       </c>
       <c r="F38" s="2">
-        <v>-3.08</v>
+        <v>0.94</v>
       </c>
       <c r="G38" s="2">
-        <v>-5.62</v>
+        <v>-2.81</v>
       </c>
       <c r="H38" s="2">
-        <v>-7.65</v>
+        <v>-5.94</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
       </c>
       <c r="J38" s="1">
-        <v>6742.77</v>
+        <v>33666.21</v>
       </c>
       <c r="K38" s="1">
-        <v>6010.92</v>
+        <v>32284.36</v>
       </c>
       <c r="L38" s="1">
-        <v>6291.9</v>
+        <v>33783.28</v>
       </c>
       <c r="M38" s="3">
-        <v>-105.7</v>
+        <v>-478.63</v>
       </c>
       <c r="N38" s="3">
-        <v>-95.71</v>
+        <v>-465.82</v>
       </c>
       <c r="O38" s="3">
-        <v>-209.53</v>
+        <v>-385.67</v>
       </c>
       <c r="P38" s="3">
-        <v>-148.33</v>
+        <v>-7.18</v>
       </c>
       <c r="Q38" s="3">
-        <v>223.11</v>
+        <v>1974.06</v>
       </c>
       <c r="R38" s="3">
-        <v>401.77</v>
+        <v>2424.73</v>
       </c>
       <c r="S38" s="3">
-        <v>26.49</v>
+        <v>35.82</v>
       </c>
       <c r="T38" s="3">
-        <v>8.48</v>
+        <v>8.81</v>
       </c>
       <c r="U38" s="3">
-        <v>37.24</v>
+        <v>34.96</v>
       </c>
       <c r="V38" s="3">
-        <v>44.49</v>
+        <v>48.91</v>
       </c>
       <c r="W38" s="3">
         <v>0</v>
@@ -3336,67 +3336,67 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>NIFTYFMCG</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="C39" t="str">
-        <v>NIFTYFMCG</v>
+        <v>NIFTYALPHALOWVOL</v>
       </c>
       <c r="D39" s="1">
-        <v>42680.7</v>
+        <v>24577.65</v>
       </c>
       <c r="E39" s="2">
-        <v>-0.99</v>
+        <v>0.94</v>
       </c>
       <c r="F39" s="2">
-        <v>-4.34</v>
+        <v>0.94</v>
       </c>
       <c r="G39" s="2">
-        <v>-4.11</v>
+        <v>-2.55</v>
       </c>
       <c r="H39" s="2">
-        <v>-23.06</v>
+        <v>-9.23</v>
       </c>
       <c r="I39" s="1">
         <v>0</v>
       </c>
       <c r="J39" s="1">
-        <v>48906.86</v>
+        <v>26228.98</v>
       </c>
       <c r="K39" s="1">
-        <v>43930.43</v>
+        <v>24677.2</v>
       </c>
       <c r="L39" s="1">
-        <v>45760.39</v>
+        <v>26001.05</v>
       </c>
       <c r="M39" s="3">
-        <v>-661.47</v>
+        <v>-419.57</v>
       </c>
       <c r="N39" s="3">
-        <v>-546.4</v>
+        <v>-443.42</v>
       </c>
       <c r="O39" s="3">
-        <v>-1702.06</v>
+        <v>-421.99</v>
       </c>
       <c r="P39" s="3">
-        <v>-1361.49</v>
+        <v>-140.98</v>
       </c>
       <c r="Q39" s="3">
-        <v>-2219.83</v>
+        <v>1146.61</v>
       </c>
       <c r="R39" s="3">
-        <v>-976.78</v>
+        <v>1596.05</v>
       </c>
       <c r="S39" s="3">
-        <v>33.59</v>
+        <v>36.37</v>
       </c>
       <c r="T39" s="3">
-        <v>11.63</v>
+        <v>9.14</v>
       </c>
       <c r="U39" s="3">
-        <v>35.81</v>
+        <v>31.2</v>
       </c>
       <c r="V39" s="3">
-        <v>38.05</v>
+        <v>52.29</v>
       </c>
       <c r="W39" s="3">
         <v>0</v>
@@ -3413,67 +3413,67 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="C40" t="str">
-        <v>NIFTYINDDIGITAL</v>
+        <v>NIFTY500MULTICAP</v>
       </c>
       <c r="D40" s="1">
-        <v>8425</v>
+        <v>15255.45</v>
       </c>
       <c r="E40" s="2">
-        <v>-0.99</v>
+        <v>0.91</v>
       </c>
       <c r="F40" s="2">
-        <v>-2.83</v>
+        <v>0.91</v>
       </c>
       <c r="G40" s="2">
-        <v>4.96</v>
+        <v>-3.14</v>
       </c>
       <c r="H40" s="2">
-        <v>-10.59</v>
+        <v>-7.46</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
       </c>
       <c r="J40" s="1">
-        <v>8251.92</v>
+        <v>16007.28</v>
       </c>
       <c r="K40" s="1">
-        <v>8439.22</v>
+        <v>15484.66</v>
       </c>
       <c r="L40" s="1">
-        <v>8527.3</v>
+        <v>16157.95</v>
       </c>
       <c r="M40" s="3">
-        <v>19.93</v>
+        <v>-226.41</v>
       </c>
       <c r="N40" s="3">
-        <v>-27.5</v>
+        <v>-198.39</v>
       </c>
       <c r="O40" s="3">
-        <v>58.7</v>
+        <v>-151.21</v>
       </c>
       <c r="P40" s="3">
-        <v>57.78</v>
+        <v>14.65</v>
       </c>
       <c r="Q40" s="3">
-        <v>365.18</v>
+        <v>901.55</v>
       </c>
       <c r="R40" s="3">
-        <v>512.28</v>
+        <v>1145</v>
       </c>
       <c r="S40" s="3">
-        <v>51</v>
+        <v>33.72</v>
       </c>
       <c r="T40" s="3">
-        <v>21.84</v>
+        <v>8.24</v>
       </c>
       <c r="U40" s="3">
-        <v>24.18</v>
+        <v>40.56</v>
       </c>
       <c r="V40" s="3">
-        <v>21.46</v>
+        <v>48.39</v>
       </c>
       <c r="W40" s="3">
         <v>0</v>
@@ -3490,67 +3490,67 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="C41" t="str">
-        <v>NIFTY200</v>
+        <v>NIFTYLARGEMID250</v>
       </c>
       <c r="D41" s="1">
-        <v>12892.4</v>
+        <v>15345.7</v>
       </c>
       <c r="E41" s="2">
-        <v>-1.02</v>
+        <v>0.9</v>
       </c>
       <c r="F41" s="2">
-        <v>-3.34</v>
+        <v>0.9</v>
       </c>
       <c r="G41" s="2">
-        <v>-2.11</v>
+        <v>-2.61</v>
       </c>
       <c r="H41" s="2">
-        <v>-11.29</v>
+        <v>-8.95</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
       </c>
       <c r="J41" s="1">
-        <v>13785.02</v>
+        <v>16279.33</v>
       </c>
       <c r="K41" s="1">
-        <v>13109.8</v>
+        <v>15532.57</v>
       </c>
       <c r="L41" s="1">
-        <v>13608.22</v>
+        <v>16239.03</v>
       </c>
       <c r="M41" s="3">
-        <v>-149.46</v>
+        <v>-228.01</v>
       </c>
       <c r="N41" s="3">
-        <v>-156.82</v>
+        <v>-215.41</v>
       </c>
       <c r="O41" s="3">
-        <v>-180.45</v>
+        <v>-214.18</v>
       </c>
       <c r="P41" s="3">
-        <v>-71.22</v>
+        <v>-48.33</v>
       </c>
       <c r="Q41" s="3">
-        <v>255.4</v>
+        <v>902.75</v>
       </c>
       <c r="R41" s="3">
-        <v>461.47</v>
+        <v>1176.04</v>
       </c>
       <c r="S41" s="3">
-        <v>34.9</v>
+        <v>35.31</v>
       </c>
       <c r="T41" s="3">
-        <v>10.63</v>
+        <v>8.02</v>
       </c>
       <c r="U41" s="3">
-        <v>36.32</v>
+        <v>37.62</v>
       </c>
       <c r="V41" s="3">
-        <v>46.59</v>
+        <v>50.42</v>
       </c>
       <c r="W41" s="3">
         <v>0</v>
@@ -3567,67 +3567,67 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="C42" t="str">
-        <v>NIFTYFINSERVICE</v>
+        <v>NIFTYSML250MQ100</v>
       </c>
       <c r="D42" s="1">
-        <v>24403</v>
+        <v>44860.15</v>
       </c>
       <c r="E42" s="2">
-        <v>-1.03</v>
+        <v>0.88</v>
       </c>
       <c r="F42" s="2">
-        <v>-3.88</v>
+        <v>0.88</v>
       </c>
       <c r="G42" s="2">
-        <v>-1</v>
+        <v>-6.26</v>
       </c>
       <c r="H42" s="2">
-        <v>-11.63</v>
+        <v>1.99</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
       </c>
       <c r="J42" s="1">
-        <v>26207.11</v>
+        <v>44933.86</v>
       </c>
       <c r="K42" s="1">
-        <v>24840.22</v>
+        <v>46319.4</v>
       </c>
       <c r="L42" s="1">
-        <v>25484.01</v>
+        <v>48206.22</v>
       </c>
       <c r="M42" s="3">
-        <v>-191.42</v>
+        <v>-762.08</v>
       </c>
       <c r="N42" s="3">
-        <v>-187.78</v>
+        <v>-439.42</v>
       </c>
       <c r="O42" s="3">
-        <v>-378.42</v>
+        <v>408.54</v>
       </c>
       <c r="P42" s="3">
-        <v>-226.96</v>
+        <v>963.1</v>
       </c>
       <c r="Q42" s="3">
-        <v>627.93</v>
+        <v>-422.39</v>
       </c>
       <c r="R42" s="3">
-        <v>1077.14</v>
+        <v>-1036.32</v>
       </c>
       <c r="S42" s="3">
-        <v>37.56</v>
+        <v>29.96</v>
       </c>
       <c r="T42" s="3">
-        <v>13.06</v>
+        <v>10.36</v>
       </c>
       <c r="U42" s="3">
-        <v>29.12</v>
+        <v>47.55</v>
       </c>
       <c r="V42" s="3">
-        <v>25.91</v>
+        <v>34.81</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -3644,67 +3644,67 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>CNXPHARMA</v>
+        <v>Nifty IT</v>
       </c>
       <c r="C43" t="str">
-        <v>CNXPHARMA</v>
+        <v>CNXIT</v>
       </c>
       <c r="D43" s="1">
-        <v>25329.45</v>
+        <v>32273.05</v>
       </c>
       <c r="E43" s="2">
-        <v>-1.04</v>
+        <v>0.87</v>
       </c>
       <c r="F43" s="2">
-        <v>-1.75</v>
+        <v>0.87</v>
       </c>
       <c r="G43" s="2">
-        <v>-4.19</v>
+        <v>16.49</v>
       </c>
       <c r="H43" s="2">
-        <v>11.47</v>
+        <v>-14.81</v>
       </c>
       <c r="I43" s="1">
         <v>0</v>
       </c>
       <c r="J43" s="1">
-        <v>24375.25</v>
+        <v>30785.57</v>
       </c>
       <c r="K43" s="1">
-        <v>25744.37</v>
+        <v>31204.58</v>
       </c>
       <c r="L43" s="1">
-        <v>26439.2</v>
+        <v>29858.36</v>
       </c>
       <c r="M43" s="3">
-        <v>-286.8</v>
+        <v>816.78</v>
       </c>
       <c r="N43" s="3">
-        <v>-206.14</v>
+        <v>393.35</v>
       </c>
       <c r="O43" s="3">
-        <v>578.03</v>
+        <v>35.64</v>
       </c>
       <c r="P43" s="3">
-        <v>792.63</v>
+        <v>-408.51</v>
       </c>
       <c r="Q43" s="3">
-        <v>1753.37</v>
+        <v>-1638.88</v>
       </c>
       <c r="R43" s="3">
-        <v>1603.12</v>
+        <v>-1143.32</v>
       </c>
       <c r="S43" s="3">
-        <v>32.77</v>
+        <v>69.55</v>
       </c>
       <c r="T43" s="3">
-        <v>9.37</v>
+        <v>28.15</v>
       </c>
       <c r="U43" s="3">
-        <v>26.57</v>
+        <v>12.68</v>
       </c>
       <c r="V43" s="3">
-        <v>29.72</v>
+        <v>30.78</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -3721,67 +3721,67 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTY500</v>
       </c>
       <c r="C44" t="str">
-        <v>NIFTY50VALUE30</v>
+        <v>NIFTY500</v>
       </c>
       <c r="D44" s="1">
-        <v>5302.15</v>
+        <v>21608.75</v>
       </c>
       <c r="E44" s="2">
-        <v>-1.07</v>
+        <v>0.85</v>
       </c>
       <c r="F44" s="2">
-        <v>-3.1</v>
+        <v>0.85</v>
       </c>
       <c r="G44" s="2">
-        <v>-0.34</v>
+        <v>-2.1</v>
       </c>
       <c r="H44" s="2">
-        <v>-9.52</v>
+        <v>-9.48</v>
       </c>
       <c r="I44" s="1">
         <v>0</v>
       </c>
       <c r="J44" s="1">
-        <v>5545.89</v>
+        <v>22820.53</v>
       </c>
       <c r="K44" s="1">
-        <v>5364.15</v>
+        <v>21832.09</v>
       </c>
       <c r="L44" s="1">
-        <v>5511.3</v>
+        <v>22704.36</v>
       </c>
       <c r="M44" s="3">
-        <v>-31.66</v>
+        <v>-276.82</v>
       </c>
       <c r="N44" s="3">
-        <v>-45.89</v>
+        <v>-266.44</v>
       </c>
       <c r="O44" s="3">
-        <v>-50.65</v>
+        <v>-292.68</v>
       </c>
       <c r="P44" s="3">
-        <v>-18.5</v>
+        <v>-94.96</v>
       </c>
       <c r="Q44" s="3">
-        <v>182.48</v>
+        <v>499.2</v>
       </c>
       <c r="R44" s="3">
-        <v>260.16</v>
+        <v>801.79</v>
       </c>
       <c r="S44" s="3">
-        <v>41.44</v>
+        <v>37.13</v>
       </c>
       <c r="T44" s="3">
-        <v>15.19</v>
+        <v>9.02</v>
       </c>
       <c r="U44" s="3">
-        <v>31.21</v>
+        <v>36.33</v>
       </c>
       <c r="V44" s="3">
-        <v>38.99</v>
+        <v>48.31</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
@@ -3798,67 +3798,67 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="C45" t="str">
-        <v>NIFTYMULTIINFRA</v>
+        <v>NIFTY50EQLWGT</v>
       </c>
       <c r="D45" s="1">
-        <v>13171.4</v>
+        <v>30618.45</v>
       </c>
       <c r="E45" s="2">
-        <v>-1.09</v>
+        <v>0.83</v>
       </c>
       <c r="F45" s="2">
-        <v>-3.37</v>
+        <v>0.83</v>
       </c>
       <c r="G45" s="2">
-        <v>-4.21</v>
+        <v>-0.93</v>
       </c>
       <c r="H45" s="2">
-        <v>-8.98</v>
+        <v>-8.14</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
       </c>
       <c r="J45" s="1">
-        <v>14142.86</v>
+        <v>32323.71</v>
       </c>
       <c r="K45" s="1">
-        <v>13453.69</v>
+        <v>30710.79</v>
       </c>
       <c r="L45" s="1">
-        <v>14109.82</v>
+        <v>31862.83</v>
       </c>
       <c r="M45" s="3">
-        <v>-219.72</v>
+        <v>-338.27</v>
       </c>
       <c r="N45" s="3">
-        <v>-208.32</v>
+        <v>-382.38</v>
       </c>
       <c r="O45" s="3">
-        <v>-182.88</v>
+        <v>-454.43</v>
       </c>
       <c r="P45" s="3">
-        <v>-17.71</v>
+        <v>-185.6</v>
       </c>
       <c r="Q45" s="3">
-        <v>58.43</v>
+        <v>1827.63</v>
       </c>
       <c r="R45" s="3">
-        <v>114.87</v>
+        <v>2373.01</v>
       </c>
       <c r="S45" s="3">
-        <v>28.95</v>
+        <v>41.98</v>
       </c>
       <c r="T45" s="3">
-        <v>10.55</v>
+        <v>10.2</v>
       </c>
       <c r="U45" s="3">
-        <v>39.34</v>
+        <v>29.05</v>
       </c>
       <c r="V45" s="3">
-        <v>44.92</v>
+        <v>45.12</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -3875,67 +3875,67 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>Nifty Total Market</v>
       </c>
       <c r="C46" t="str">
-        <v>NIFTYTATA25CAP</v>
+        <v>NIFTYTOTALMKT</v>
       </c>
       <c r="D46" s="1">
-        <v>13600.85</v>
+        <v>12205.35</v>
       </c>
       <c r="E46" s="2">
-        <v>-1.14</v>
+        <v>0.83</v>
       </c>
       <c r="F46" s="2">
-        <v>-2.53</v>
+        <v>0.83</v>
       </c>
       <c r="G46" s="2">
-        <v>1.86</v>
+        <v>-2.4</v>
       </c>
       <c r="H46" s="2">
-        <v>-11.06</v>
+        <v>-8.87</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
       </c>
       <c r="J46" s="1">
-        <v>14385.7</v>
+        <v>12850.64</v>
       </c>
       <c r="K46" s="1">
-        <v>13675.05</v>
+        <v>12345.93</v>
       </c>
       <c r="L46" s="1">
-        <v>14009.98</v>
+        <v>12841.96</v>
       </c>
       <c r="M46" s="3">
-        <v>-55.41</v>
+        <v>-160.07</v>
       </c>
       <c r="N46" s="3">
-        <v>-118.79</v>
+        <v>-149.73</v>
       </c>
       <c r="O46" s="3">
-        <v>-227.8</v>
+        <v>-146.83</v>
       </c>
       <c r="P46" s="3">
-        <v>-163</v>
+        <v>-31.45</v>
       </c>
       <c r="Q46" s="3">
-        <v>-547.72</v>
+        <v>619.21</v>
       </c>
       <c r="R46" s="3">
-        <v>-494.09</v>
+        <v>823.92</v>
       </c>
       <c r="S46" s="3">
-        <v>46.01</v>
+        <v>36.29</v>
       </c>
       <c r="T46" s="3">
-        <v>17.84</v>
+        <v>9.04</v>
       </c>
       <c r="U46" s="3">
-        <v>28.4</v>
+        <v>37.33</v>
       </c>
       <c r="V46" s="3">
-        <v>25.15</v>
+        <v>47.72</v>
       </c>
       <c r="W46" s="3">
         <v>0</v>
@@ -3952,67 +3952,67 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="C47" t="str">
-        <v>BANKNIFTY</v>
+        <v>NIFTYTOP10EW</v>
       </c>
       <c r="D47" s="1">
-        <v>54287.35</v>
+        <v>8350.05</v>
       </c>
       <c r="E47" s="2">
-        <v>-1.16</v>
+        <v>0.83</v>
       </c>
       <c r="F47" s="2">
-        <v>-2.79</v>
+        <v>0.83</v>
       </c>
       <c r="G47" s="2">
-        <v>-0.63</v>
+        <v>3.38</v>
       </c>
       <c r="H47" s="2">
-        <v>-8.89</v>
+        <v>-16.87</v>
       </c>
       <c r="I47" s="1">
         <v>0</v>
       </c>
       <c r="J47" s="1">
-        <v>56842.98</v>
+        <v>8755.27</v>
       </c>
       <c r="K47" s="1">
-        <v>55072.04</v>
+        <v>8296.89</v>
       </c>
       <c r="L47" s="1">
-        <v>56259.7</v>
+        <v>8382.31</v>
       </c>
       <c r="M47" s="3">
-        <v>-328.9</v>
+        <v>-1.79</v>
       </c>
       <c r="N47" s="3">
-        <v>-351.4</v>
+        <v>-30.2</v>
       </c>
       <c r="O47" s="3">
-        <v>-402.01</v>
+        <v>-152.19</v>
       </c>
       <c r="P47" s="3">
-        <v>-109.29</v>
+        <v>-157.51</v>
       </c>
       <c r="Q47" s="3">
-        <v>1610.08</v>
+        <v>-301.46</v>
       </c>
       <c r="R47" s="3">
-        <v>2277.6</v>
+        <v>-191.62</v>
       </c>
       <c r="S47" s="3">
-        <v>37.74</v>
+        <v>53.7</v>
       </c>
       <c r="T47" s="3">
-        <v>11.74</v>
+        <v>16.49</v>
       </c>
       <c r="U47" s="3">
-        <v>26.88</v>
+        <v>22.73</v>
       </c>
       <c r="V47" s="3">
-        <v>23.01</v>
+        <v>22.12</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -4029,67 +4029,67 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTY200</v>
       </c>
       <c r="C48" t="str">
-        <v>NIFTYFINSRV2550</v>
+        <v>NIFTY200</v>
       </c>
       <c r="D48" s="1">
-        <v>26195.65</v>
+        <v>12998.35</v>
       </c>
       <c r="E48" s="2">
-        <v>-1.18</v>
+        <v>0.82</v>
       </c>
       <c r="F48" s="2">
-        <v>-3.73</v>
+        <v>0.82</v>
       </c>
       <c r="G48" s="2">
-        <v>-1.36</v>
+        <v>-1.3</v>
       </c>
       <c r="H48" s="2">
-        <v>-13.2</v>
+        <v>-10.56</v>
       </c>
       <c r="I48" s="1">
         <v>0</v>
       </c>
       <c r="J48" s="1">
-        <v>28527.81</v>
+        <v>13777.21</v>
       </c>
       <c r="K48" s="1">
-        <v>26693.86</v>
+        <v>13089.54</v>
       </c>
       <c r="L48" s="1">
-        <v>27555.3</v>
+        <v>13584.05</v>
       </c>
       <c r="M48" s="3">
-        <v>-260.62</v>
+        <v>-148.8</v>
       </c>
       <c r="N48" s="3">
-        <v>-263.46</v>
+        <v>-155.22</v>
       </c>
       <c r="O48" s="3">
-        <v>-507.71</v>
+        <v>-204.09</v>
       </c>
       <c r="P48" s="3">
-        <v>-301.14</v>
+        <v>-97.79</v>
       </c>
       <c r="Q48" s="3">
-        <v>1281.95</v>
+        <v>263.85</v>
       </c>
       <c r="R48" s="3">
-        <v>1894.3</v>
+        <v>463.16</v>
       </c>
       <c r="S48" s="3">
-        <v>36</v>
+        <v>39.76</v>
       </c>
       <c r="T48" s="3">
-        <v>12.47</v>
+        <v>9.6</v>
       </c>
       <c r="U48" s="3">
-        <v>30.23</v>
+        <v>32.83</v>
       </c>
       <c r="V48" s="3">
-        <v>28.48</v>
+        <v>47.18</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -4106,67 +4106,67 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="C49" t="str">
-        <v>NIFTYMIDSMLHLTH</v>
+        <v>NIFTY100LIQ15</v>
       </c>
       <c r="D49" s="1">
-        <v>47649.75</v>
+        <v>7340</v>
       </c>
       <c r="E49" s="2">
-        <v>-1.19</v>
+        <v>0.78</v>
       </c>
       <c r="F49" s="2">
-        <v>-3.34</v>
+        <v>0.78</v>
       </c>
       <c r="G49" s="2">
-        <v>-6.53</v>
+        <v>3.73</v>
       </c>
       <c r="H49" s="2">
-        <v>8.63</v>
+        <v>-2.94</v>
       </c>
       <c r="I49" s="1">
         <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>47357.97</v>
+        <v>7332.17</v>
       </c>
       <c r="K49" s="1">
-        <v>49051.9</v>
+        <v>7302.63</v>
       </c>
       <c r="L49" s="1">
-        <v>51443.8</v>
+        <v>7388.14</v>
       </c>
       <c r="M49" s="3">
-        <v>-970.56</v>
+        <v>1.25</v>
       </c>
       <c r="N49" s="3">
-        <v>-714.55</v>
+        <v>-25.39</v>
       </c>
       <c r="O49" s="3">
-        <v>889.87</v>
+        <v>-4.58</v>
       </c>
       <c r="P49" s="3">
-        <v>1550.96</v>
+        <v>23.59</v>
       </c>
       <c r="Q49" s="3">
-        <v>2100.85</v>
+        <v>471.2</v>
       </c>
       <c r="R49" s="3">
-        <v>1457.74</v>
+        <v>552.45</v>
       </c>
       <c r="S49" s="3">
-        <v>23.92</v>
+        <v>52.82</v>
       </c>
       <c r="T49" s="3">
-        <v>6.63</v>
+        <v>17.79</v>
       </c>
       <c r="U49" s="3">
-        <v>39.3</v>
+        <v>24.32</v>
       </c>
       <c r="V49" s="3">
-        <v>39.87</v>
+        <v>27.1</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -4183,67 +4183,67 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>NIFTY500</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="C50" t="str">
-        <v>NIFTY500</v>
+        <v>NIFTYSERVSECTOR</v>
       </c>
       <c r="D50" s="1">
-        <v>21427.6</v>
+        <v>30162.5</v>
       </c>
       <c r="E50" s="2">
-        <v>-1.24</v>
+        <v>0.76</v>
       </c>
       <c r="F50" s="2">
-        <v>-3.78</v>
+        <v>0.76</v>
       </c>
       <c r="G50" s="2">
-        <v>-2.92</v>
+        <v>3.96</v>
       </c>
       <c r="H50" s="2">
-        <v>-10.24</v>
+        <v>-10.38</v>
       </c>
       <c r="I50" s="1">
         <v>0</v>
       </c>
       <c r="J50" s="1">
-        <v>22832.04</v>
+        <v>30923.89</v>
       </c>
       <c r="K50" s="1">
-        <v>21881.73</v>
+        <v>29883.33</v>
       </c>
       <c r="L50" s="1">
-        <v>22745.63</v>
+        <v>30063.06</v>
       </c>
       <c r="M50" s="3">
-        <v>-271.94</v>
+        <v>50.49</v>
       </c>
       <c r="N50" s="3">
-        <v>-263.85</v>
+        <v>-89.45</v>
       </c>
       <c r="O50" s="3">
-        <v>-241.67</v>
+        <v>-327.11</v>
       </c>
       <c r="P50" s="3">
-        <v>-45.53</v>
+        <v>-319.35</v>
       </c>
       <c r="Q50" s="3">
-        <v>484.75</v>
+        <v>500.28</v>
       </c>
       <c r="R50" s="3">
-        <v>798.9</v>
+        <v>994.55</v>
       </c>
       <c r="S50" s="3">
-        <v>31.86</v>
+        <v>56.23</v>
       </c>
       <c r="T50" s="3">
-        <v>10.04</v>
+        <v>17.61</v>
       </c>
       <c r="U50" s="3">
-        <v>40.02</v>
+        <v>21.98</v>
       </c>
       <c r="V50" s="3">
-        <v>47.39</v>
+        <v>25.96</v>
       </c>
       <c r="W50" s="3">
         <v>0</v>
@@ -4260,67 +4260,67 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTY100</v>
       </c>
       <c r="C51" t="str">
-        <v>NIFTYDIVOPPS50</v>
+        <v>NIFTY100</v>
       </c>
       <c r="D51" s="1">
-        <v>5510.75</v>
+        <v>23637.1</v>
       </c>
       <c r="E51" s="2">
-        <v>-1.25</v>
+        <v>0.73</v>
       </c>
       <c r="F51" s="2">
-        <v>-2.14</v>
+        <v>0.73</v>
       </c>
       <c r="G51" s="2">
-        <v>0.7</v>
+        <v>-0.41</v>
       </c>
       <c r="H51" s="2">
-        <v>-13.7</v>
+        <v>-11.44</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
       </c>
       <c r="J51" s="1">
-        <v>5948.69</v>
+        <v>25008.19</v>
       </c>
       <c r="K51" s="1">
-        <v>5543.59</v>
+        <v>23713.09</v>
       </c>
       <c r="L51" s="1">
-        <v>5678.67</v>
+        <v>24474</v>
       </c>
       <c r="M51" s="3">
-        <v>-25.74</v>
+        <v>-212.77</v>
       </c>
       <c r="N51" s="3">
-        <v>-49.34</v>
+        <v>-247.22</v>
       </c>
       <c r="O51" s="3">
-        <v>-122.29</v>
+        <v>-389.01</v>
       </c>
       <c r="P51" s="3">
-        <v>-96.45</v>
+        <v>-237.74</v>
       </c>
       <c r="Q51" s="3">
-        <v>21.8</v>
+        <v>323.97</v>
       </c>
       <c r="R51" s="3">
-        <v>138.84</v>
+        <v>706.96</v>
       </c>
       <c r="S51" s="3">
-        <v>44.76</v>
+        <v>42.99</v>
       </c>
       <c r="T51" s="3">
-        <v>17.18</v>
+        <v>10.94</v>
       </c>
       <c r="U51" s="3">
-        <v>29.76</v>
+        <v>29.31</v>
       </c>
       <c r="V51" s="3">
-        <v>34.56</v>
+        <v>43.4</v>
       </c>
       <c r="W51" s="3">
         <v>0</v>
@@ -4337,67 +4337,67 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="C52" t="str">
-        <v>NIFTYINDTOURISM</v>
+        <v>NIFTY50VALUE30</v>
       </c>
       <c r="D52" s="1">
-        <v>7356.85</v>
+        <v>5340.6</v>
       </c>
       <c r="E52" s="2">
-        <v>-1.28</v>
+        <v>0.73</v>
       </c>
       <c r="F52" s="2">
-        <v>-2.75</v>
+        <v>0.73</v>
       </c>
       <c r="G52" s="2">
-        <v>-4.51</v>
+        <v>0.38</v>
       </c>
       <c r="H52" s="2">
-        <v>-14.5</v>
+        <v>-8.86</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
       </c>
       <c r="J52" s="1">
-        <v>7679.73</v>
+        <v>5543.38</v>
       </c>
       <c r="K52" s="1">
-        <v>7468.9</v>
+        <v>5359.87</v>
       </c>
       <c r="L52" s="1">
-        <v>7753.04</v>
+        <v>5502.51</v>
       </c>
       <c r="M52" s="3">
-        <v>-96.56</v>
+        <v>-31.23</v>
       </c>
       <c r="N52" s="3">
-        <v>-90.05</v>
+        <v>-42.96</v>
       </c>
       <c r="O52" s="3">
-        <v>-67.85</v>
+        <v>-55.6</v>
       </c>
       <c r="P52" s="3">
-        <v>-18.85</v>
+        <v>-25.92</v>
       </c>
       <c r="Q52" s="3">
-        <v>-305.65</v>
+        <v>185.54</v>
       </c>
       <c r="R52" s="3">
-        <v>-248.31</v>
+        <v>260.77</v>
       </c>
       <c r="S52" s="3">
-        <v>38.24</v>
+        <v>45.16</v>
       </c>
       <c r="T52" s="3">
-        <v>13.5</v>
+        <v>13.78</v>
       </c>
       <c r="U52" s="3">
-        <v>30.05</v>
+        <v>29.82</v>
       </c>
       <c r="V52" s="3">
-        <v>26.15</v>
+        <v>38.84</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -4414,67 +4414,67 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>Nifty Total Market</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="C53" t="str">
-        <v>NIFTYTOTALMKT</v>
+        <v>NIFTYCONSUMPTION</v>
       </c>
       <c r="D53" s="1">
-        <v>12105.3</v>
+        <v>10804.45</v>
       </c>
       <c r="E53" s="2">
-        <v>-1.29</v>
+        <v>0.72</v>
       </c>
       <c r="F53" s="2">
-        <v>-3.94</v>
+        <v>0.72</v>
       </c>
       <c r="G53" s="2">
-        <v>-3.2</v>
+        <v>-2.42</v>
       </c>
       <c r="H53" s="2">
-        <v>-9.62</v>
+        <v>-12.08</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
       </c>
       <c r="J53" s="1">
-        <v>12856.69</v>
+        <v>11481.78</v>
       </c>
       <c r="K53" s="1">
-        <v>12377.17</v>
+        <v>10869.26</v>
       </c>
       <c r="L53" s="1">
-        <v>12865.16</v>
+        <v>11422.64</v>
       </c>
       <c r="M53" s="3">
-        <v>-155.97</v>
+        <v>-171.64</v>
       </c>
       <c r="N53" s="3">
-        <v>-147.15</v>
+        <v>-178.62</v>
       </c>
       <c r="O53" s="3">
-        <v>-115.47</v>
+        <v>-185.64</v>
       </c>
       <c r="P53" s="3">
-        <v>-2.6</v>
+        <v>-71.67</v>
       </c>
       <c r="Q53" s="3">
-        <v>611.22</v>
+        <v>214.86</v>
       </c>
       <c r="R53" s="3">
-        <v>822.32</v>
+        <v>393.64</v>
       </c>
       <c r="S53" s="3">
-        <v>31.07</v>
+        <v>38.41</v>
       </c>
       <c r="T53" s="3">
-        <v>10.06</v>
+        <v>9.47</v>
       </c>
       <c r="U53" s="3">
-        <v>41.11</v>
+        <v>33.19</v>
       </c>
       <c r="V53" s="3">
-        <v>46.7</v>
+        <v>48.08</v>
       </c>
       <c r="W53" s="3">
         <v>0</v>
@@ -4491,67 +4491,67 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="C54" t="str">
-        <v>NIFTYMEDIA</v>
+        <v>NIFTY200QUALITY30</v>
       </c>
       <c r="D54" s="1">
-        <v>1563.4</v>
+        <v>18808.5</v>
       </c>
       <c r="E54" s="2">
-        <v>-1.33</v>
+        <v>0.69</v>
       </c>
       <c r="F54" s="2">
-        <v>-5.15</v>
+        <v>0.69</v>
       </c>
       <c r="G54" s="2">
-        <v>-1.25</v>
+        <v>-0.71</v>
       </c>
       <c r="H54" s="2">
-        <v>8.22</v>
+        <v>-12.15</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
       </c>
       <c r="J54" s="1">
-        <v>1469.5</v>
+        <v>20073.77</v>
       </c>
       <c r="K54" s="1">
-        <v>1600.49</v>
+        <v>19017.36</v>
       </c>
       <c r="L54" s="1">
-        <v>1574.14</v>
+        <v>19727.89</v>
       </c>
       <c r="M54" s="3">
-        <v>13.19</v>
+        <v>-191.96</v>
       </c>
       <c r="N54" s="3">
-        <v>14.44</v>
+        <v>-206.66</v>
       </c>
       <c r="O54" s="3">
-        <v>30.99</v>
+        <v>-337.73</v>
       </c>
       <c r="P54" s="3">
-        <v>31.31</v>
+        <v>-184.66</v>
       </c>
       <c r="Q54" s="3">
-        <v>-74.96</v>
+        <v>473.06</v>
       </c>
       <c r="R54" s="3">
-        <v>-105.89</v>
+        <v>792.66</v>
       </c>
       <c r="S54" s="3">
-        <v>46.1</v>
+        <v>39.66</v>
       </c>
       <c r="T54" s="3">
-        <v>21.64</v>
+        <v>11.74</v>
       </c>
       <c r="U54" s="3">
-        <v>33.44</v>
+        <v>34.17</v>
       </c>
       <c r="V54" s="3">
-        <v>17.65</v>
+        <v>41.79</v>
       </c>
       <c r="W54" s="3">
         <v>0</v>
@@ -4568,67 +4568,67 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTY</v>
       </c>
       <c r="C55" t="str">
-        <v>NIFTYLARGEMID250</v>
+        <v>NIFTY</v>
       </c>
       <c r="D55" s="1">
-        <v>15209.55</v>
+        <v>22753.2</v>
       </c>
       <c r="E55" s="2">
-        <v>-1.39</v>
+        <v>0.68</v>
       </c>
       <c r="F55" s="2">
-        <v>-4</v>
+        <v>0.68</v>
       </c>
       <c r="G55" s="2">
-        <v>-3.48</v>
+        <v>0.59</v>
       </c>
       <c r="H55" s="2">
-        <v>-9.76</v>
+        <v>-12.92</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
       </c>
       <c r="J55" s="1">
-        <v>16287.1</v>
+        <v>24101.87</v>
       </c>
       <c r="K55" s="1">
-        <v>15574.1</v>
+        <v>22748.33</v>
       </c>
       <c r="L55" s="1">
-        <v>16271.59</v>
+        <v>23370.07</v>
       </c>
       <c r="M55" s="3">
-        <v>-223.57</v>
+        <v>-157.18</v>
       </c>
       <c r="N55" s="3">
-        <v>-212.26</v>
+        <v>-209.54</v>
       </c>
       <c r="O55" s="3">
-        <v>-170.83</v>
+        <v>-411.8</v>
       </c>
       <c r="P55" s="3">
-        <v>-6.87</v>
+        <v>-304.9</v>
       </c>
       <c r="Q55" s="3">
-        <v>891.89</v>
+        <v>189.4</v>
       </c>
       <c r="R55" s="3">
-        <v>1173.87</v>
+        <v>598.73</v>
       </c>
       <c r="S55" s="3">
-        <v>29.7</v>
+        <v>46.08</v>
       </c>
       <c r="T55" s="3">
-        <v>8.94</v>
+        <v>12.26</v>
       </c>
       <c r="U55" s="3">
-        <v>41.56</v>
+        <v>25.84</v>
       </c>
       <c r="V55" s="3">
-        <v>49.31</v>
+        <v>36.28</v>
       </c>
       <c r="W55" s="3">
         <v>0</v>
@@ -4645,67 +4645,67 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="C56" t="str">
-        <v>NIFTYCOMMODITIES</v>
+        <v>CNXREALTY</v>
       </c>
       <c r="D56" s="1">
-        <v>8792.3</v>
+        <v>789.7</v>
       </c>
       <c r="E56" s="2">
-        <v>-1.41</v>
+        <v>0.68</v>
       </c>
       <c r="F56" s="2">
-        <v>-3.38</v>
+        <v>0.68</v>
       </c>
       <c r="G56" s="2">
-        <v>-5.56</v>
+        <v>-6.8</v>
       </c>
       <c r="H56" s="2">
-        <v>-7.6</v>
+        <v>-10.05</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
       </c>
       <c r="J56" s="1">
-        <v>9757.44</v>
+        <v>821.28</v>
       </c>
       <c r="K56" s="1">
-        <v>8981.6</v>
+        <v>807.61</v>
       </c>
       <c r="L56" s="1">
-        <v>9476.27</v>
+        <v>859.67</v>
       </c>
       <c r="M56" s="3">
-        <v>-170.17</v>
+        <v>-17.14</v>
       </c>
       <c r="N56" s="3">
-        <v>-167.85</v>
+        <v>-15.33</v>
       </c>
       <c r="O56" s="3">
-        <v>-193.2</v>
+        <v>-5.63</v>
       </c>
       <c r="P56" s="3">
-        <v>-68.85</v>
+        <v>7.05</v>
       </c>
       <c r="Q56" s="3">
-        <v>377.04</v>
+        <v>0.44</v>
       </c>
       <c r="R56" s="3">
-        <v>505.77</v>
+        <v>9.67</v>
       </c>
       <c r="S56" s="3">
-        <v>29.94</v>
+        <v>35.19</v>
       </c>
       <c r="T56" s="3">
-        <v>12</v>
+        <v>11.87</v>
       </c>
       <c r="U56" s="3">
-        <v>36.69</v>
+        <v>33.79</v>
       </c>
       <c r="V56" s="3">
-        <v>42.16</v>
+        <v>28.59</v>
       </c>
       <c r="W56" s="3">
         <v>0</v>
@@ -4722,67 +4722,67 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>CNXMNC</v>
       </c>
       <c r="C57" t="str">
-        <v>NIFTY200QUALITY30</v>
+        <v>CNXMNC</v>
       </c>
       <c r="D57" s="1">
-        <v>18680</v>
+        <v>27943.6</v>
       </c>
       <c r="E57" s="2">
-        <v>-1.42</v>
+        <v>0.64</v>
       </c>
       <c r="F57" s="2">
-        <v>-4.06</v>
+        <v>0.64</v>
       </c>
       <c r="G57" s="2">
-        <v>-1.39</v>
+        <v>-7.88</v>
       </c>
       <c r="H57" s="2">
-        <v>-12.75</v>
+        <v>-8.59</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
       </c>
       <c r="J57" s="1">
-        <v>20086.53</v>
+        <v>31373.13</v>
       </c>
       <c r="K57" s="1">
-        <v>19063.77</v>
+        <v>28844.7</v>
       </c>
       <c r="L57" s="1">
-        <v>19769.3</v>
+        <v>31303.45</v>
       </c>
       <c r="M57" s="3">
-        <v>-183.77</v>
+        <v>-870.88</v>
       </c>
       <c r="N57" s="3">
-        <v>-210.33</v>
+        <v>-732.76</v>
       </c>
       <c r="O57" s="3">
-        <v>-303.22</v>
+        <v>-704.18</v>
       </c>
       <c r="P57" s="3">
-        <v>-146.4</v>
+        <v>-91.76</v>
       </c>
       <c r="Q57" s="3">
-        <v>462.8</v>
+        <v>1935.45</v>
       </c>
       <c r="R57" s="3">
-        <v>790.61</v>
+        <v>2386.99</v>
       </c>
       <c r="S57" s="3">
-        <v>36.05</v>
+        <v>23.05</v>
       </c>
       <c r="T57" s="3">
-        <v>12.87</v>
+        <v>6.11</v>
       </c>
       <c r="U57" s="3">
-        <v>35.23</v>
+        <v>47.65</v>
       </c>
       <c r="V57" s="3">
-        <v>41.25</v>
+        <v>60.18</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
@@ -4799,67 +4799,67 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="C58" t="str">
-        <v>NIFTYMULTIMFG</v>
+        <v>NIFTYCPSE</v>
       </c>
       <c r="D58" s="1">
-        <v>15081.85</v>
+        <v>5916</v>
       </c>
       <c r="E58" s="2">
-        <v>-1.44</v>
+        <v>0.64</v>
       </c>
       <c r="F58" s="2">
-        <v>-4.47</v>
+        <v>0.64</v>
       </c>
       <c r="G58" s="2">
-        <v>-5.84</v>
+        <v>-5.02</v>
       </c>
       <c r="H58" s="2">
-        <v>-5.59</v>
+        <v>-7.06</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
       </c>
       <c r="J58" s="1">
-        <v>16004.23</v>
+        <v>6740.37</v>
       </c>
       <c r="K58" s="1">
-        <v>15527.97</v>
+        <v>5993.66</v>
       </c>
       <c r="L58" s="1">
-        <v>16383.51</v>
+        <v>6280.88</v>
       </c>
       <c r="M58" s="3">
-        <v>-288.64</v>
+        <v>-106.88</v>
       </c>
       <c r="N58" s="3">
-        <v>-254.72</v>
+        <v>-97.94</v>
       </c>
       <c r="O58" s="3">
-        <v>-70.03</v>
+        <v>-221.25</v>
       </c>
       <c r="P58" s="3">
-        <v>131.46</v>
+        <v>-162.91</v>
       </c>
       <c r="Q58" s="3">
-        <v>333.27</v>
+        <v>226.1</v>
       </c>
       <c r="R58" s="3">
-        <v>323.55</v>
+        <v>402.37</v>
       </c>
       <c r="S58" s="3">
-        <v>26.71</v>
+        <v>31.12</v>
       </c>
       <c r="T58" s="3">
-        <v>8.92</v>
+        <v>7.79</v>
       </c>
       <c r="U58" s="3">
-        <v>43.22</v>
+        <v>34.21</v>
       </c>
       <c r="V58" s="3">
-        <v>47.7</v>
+        <v>45.81</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -4876,67 +4876,67 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="C59" t="str">
-        <v>NIFTY100EQLWGT</v>
+        <v>NIFTYPVTBANK</v>
       </c>
       <c r="D59" s="1">
-        <v>31640.45</v>
+        <v>26825.3</v>
       </c>
       <c r="E59" s="2">
-        <v>-1.45</v>
+        <v>0.63</v>
       </c>
       <c r="F59" s="2">
-        <v>-3.68</v>
+        <v>0.63</v>
       </c>
       <c r="G59" s="2">
-        <v>-3.71</v>
+        <v>0.49</v>
       </c>
       <c r="H59" s="2">
-        <v>-6.82</v>
+        <v>-6.6</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
       </c>
       <c r="J59" s="1">
-        <v>33676.94</v>
+        <v>27352.3</v>
       </c>
       <c r="K59" s="1">
-        <v>32361.46</v>
+        <v>27009.3</v>
       </c>
       <c r="L59" s="1">
-        <v>33854.46</v>
+        <v>27257.25</v>
       </c>
       <c r="M59" s="3">
-        <v>-474.3</v>
+        <v>-75.26</v>
       </c>
       <c r="N59" s="3">
-        <v>-462.62</v>
+        <v>-49.42</v>
       </c>
       <c r="O59" s="3">
-        <v>-293.22</v>
+        <v>-83.18</v>
       </c>
       <c r="P59" s="3">
-        <v>87.44</v>
+        <v>-4.83</v>
       </c>
       <c r="Q59" s="3">
-        <v>1950.37</v>
+        <v>643.43</v>
       </c>
       <c r="R59" s="3">
-        <v>2419.99</v>
+        <v>874.57</v>
       </c>
       <c r="S59" s="3">
-        <v>29.92</v>
+        <v>44.66</v>
       </c>
       <c r="T59" s="3">
-        <v>9.78</v>
+        <v>15.5</v>
       </c>
       <c r="U59" s="3">
-        <v>38.82</v>
+        <v>24.72</v>
       </c>
       <c r="V59" s="3">
-        <v>48.07</v>
+        <v>15.44</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
@@ -4953,67 +4953,67 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="C60" t="str">
-        <v>NIFTY500MULTICAP</v>
+        <v>NIFTY50VALUE20</v>
       </c>
       <c r="D60" s="1">
-        <v>15117.8</v>
+        <v>11350.55</v>
       </c>
       <c r="E60" s="2">
-        <v>-1.56</v>
+        <v>0.62</v>
       </c>
       <c r="F60" s="2">
-        <v>-4.46</v>
+        <v>0.62</v>
       </c>
       <c r="G60" s="2">
-        <v>-4.02</v>
+        <v>1.84</v>
       </c>
       <c r="H60" s="2">
-        <v>-8.29</v>
+        <v>-14.5</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
       </c>
       <c r="J60" s="1">
-        <v>16013.54</v>
+        <v>12162.16</v>
       </c>
       <c r="K60" s="1">
-        <v>15535.59</v>
+        <v>11323.59</v>
       </c>
       <c r="L60" s="1">
-        <v>16188.45</v>
+        <v>11523.99</v>
       </c>
       <c r="M60" s="3">
-        <v>-217.14</v>
+        <v>-37.74</v>
       </c>
       <c r="N60" s="3">
-        <v>-191.38</v>
+        <v>-72.48</v>
       </c>
       <c r="O60" s="3">
-        <v>-102.62</v>
+        <v>-261.72</v>
       </c>
       <c r="P60" s="3">
-        <v>56.11</v>
+        <v>-241.43</v>
       </c>
       <c r="Q60" s="3">
-        <v>890.57</v>
+        <v>-128.05</v>
       </c>
       <c r="R60" s="3">
-        <v>1142.8</v>
+        <v>114.83</v>
       </c>
       <c r="S60" s="3">
-        <v>27.82</v>
+        <v>49.45</v>
       </c>
       <c r="T60" s="3">
-        <v>9.23</v>
+        <v>14.88</v>
       </c>
       <c r="U60" s="3">
-        <v>44.48</v>
+        <v>25.5</v>
       </c>
       <c r="V60" s="3">
-        <v>47.02</v>
+        <v>28.85</v>
       </c>
       <c r="W60" s="3">
         <v>0</v>
@@ -5030,67 +5030,67 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="C61" t="str">
-        <v>NIFTYINDIAMFG</v>
+        <v>NIFTY100ESG</v>
       </c>
       <c r="D61" s="1">
-        <v>14516.75</v>
+        <v>4676.75</v>
       </c>
       <c r="E61" s="2">
-        <v>-1.57</v>
+        <v>0.62</v>
       </c>
       <c r="F61" s="2">
-        <v>-4.33</v>
+        <v>0.62</v>
       </c>
       <c r="G61" s="2">
-        <v>-6.07</v>
+        <v>-0.15</v>
       </c>
       <c r="H61" s="2">
-        <v>-5.81</v>
+        <v>-9.74</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
       </c>
       <c r="J61" s="1">
-        <v>15625.39</v>
+        <v>4910.04</v>
       </c>
       <c r="K61" s="1">
-        <v>14946.58</v>
+        <v>4693.97</v>
       </c>
       <c r="L61" s="1">
-        <v>15847.78</v>
+        <v>4849.39</v>
       </c>
       <c r="M61" s="3">
-        <v>-301.4</v>
+        <v>-40.76</v>
       </c>
       <c r="N61" s="3">
-        <v>-273.48</v>
+        <v>-50.18</v>
       </c>
       <c r="O61" s="3">
-        <v>-119.2</v>
+        <v>-60.85</v>
       </c>
       <c r="P61" s="3">
-        <v>96.42</v>
+        <v>-26.54</v>
       </c>
       <c r="Q61" s="3">
-        <v>1221.05</v>
+        <v>218.68</v>
       </c>
       <c r="R61" s="3">
-        <v>1438.69</v>
+        <v>299.16</v>
       </c>
       <c r="S61" s="3">
-        <v>26.18</v>
+        <v>43.2</v>
       </c>
       <c r="T61" s="3">
-        <v>8.05</v>
+        <v>12.8</v>
       </c>
       <c r="U61" s="3">
-        <v>43.95</v>
+        <v>30.16</v>
       </c>
       <c r="V61" s="3">
-        <v>50.33</v>
+        <v>37.65</v>
       </c>
       <c r="W61" s="3">
         <v>0</v>
@@ -5107,67 +5107,67 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="C62" t="str">
-        <v>CNXPSE</v>
+        <v>NIFTY100ESGSECLDR</v>
       </c>
       <c r="D62" s="1">
-        <v>8885.75</v>
+        <v>3775.2</v>
       </c>
       <c r="E62" s="2">
-        <v>-1.64</v>
+        <v>0.59</v>
       </c>
       <c r="F62" s="2">
-        <v>-3.91</v>
+        <v>0.59</v>
       </c>
       <c r="G62" s="2">
-        <v>-5.07</v>
+        <v>-0.19</v>
       </c>
       <c r="H62" s="2">
-        <v>-9.82</v>
+        <v>-13.28</v>
       </c>
       <c r="I62" s="1">
         <v>0</v>
       </c>
       <c r="J62" s="1">
-        <v>9984.3</v>
+        <v>4028.78</v>
       </c>
       <c r="K62" s="1">
-        <v>9123.11</v>
+        <v>3786.82</v>
       </c>
       <c r="L62" s="1">
-        <v>9519.4</v>
+        <v>3911.18</v>
       </c>
       <c r="M62" s="3">
-        <v>-141.61</v>
+        <v>-34.04</v>
       </c>
       <c r="N62" s="3">
-        <v>-129.11</v>
+        <v>-41.22</v>
       </c>
       <c r="O62" s="3">
-        <v>-244.33</v>
+        <v>-73.13</v>
       </c>
       <c r="P62" s="3">
-        <v>-150.14</v>
+        <v>-49.11</v>
       </c>
       <c r="Q62" s="3">
-        <v>776.06</v>
+        <v>124.85</v>
       </c>
       <c r="R62" s="3">
-        <v>1088.64</v>
+        <v>206.49</v>
       </c>
       <c r="S62" s="3">
-        <v>27.83</v>
+        <v>43.3</v>
       </c>
       <c r="T62" s="3">
-        <v>8.58</v>
+        <v>12.8</v>
       </c>
       <c r="U62" s="3">
-        <v>40.86</v>
+        <v>28.63</v>
       </c>
       <c r="V62" s="3">
-        <v>48.21</v>
+        <v>37.61</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
@@ -5184,67 +5184,67 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>CNXENERGY</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="C63" t="str">
-        <v>CNXENERGY</v>
+        <v>NIFTY100LOWVOL30</v>
       </c>
       <c r="D63" s="1">
-        <v>34520.05</v>
+        <v>18670.3</v>
       </c>
       <c r="E63" s="2">
-        <v>-1.66</v>
+        <v>0.58</v>
       </c>
       <c r="F63" s="2">
-        <v>-4.62</v>
+        <v>0.58</v>
       </c>
       <c r="G63" s="2">
-        <v>-5.78</v>
+        <v>-0.61</v>
       </c>
       <c r="H63" s="2">
-        <v>-2.28</v>
+        <v>-11.64</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
       </c>
       <c r="J63" s="1">
-        <v>37722.41</v>
+        <v>19842.75</v>
       </c>
       <c r="K63" s="1">
-        <v>35665.35</v>
+        <v>18702.31</v>
       </c>
       <c r="L63" s="1">
-        <v>37328.98</v>
+        <v>19424.04</v>
       </c>
       <c r="M63" s="3">
-        <v>-621.4</v>
+        <v>-204.94</v>
       </c>
       <c r="N63" s="3">
-        <v>-515.77</v>
+        <v>-242.65</v>
       </c>
       <c r="O63" s="3">
-        <v>-592.5</v>
+        <v>-333.97</v>
       </c>
       <c r="P63" s="3">
-        <v>-87.54</v>
+        <v>-184.77</v>
       </c>
       <c r="Q63" s="3">
-        <v>889.89</v>
+        <v>754.66</v>
       </c>
       <c r="R63" s="3">
-        <v>1219.3</v>
+        <v>1110.75</v>
       </c>
       <c r="S63" s="3">
-        <v>24.92</v>
+        <v>41.44</v>
       </c>
       <c r="T63" s="3">
-        <v>11.8</v>
+        <v>8.93</v>
       </c>
       <c r="U63" s="3">
-        <v>44.96</v>
+        <v>26.16</v>
       </c>
       <c r="V63" s="3">
-        <v>33.86</v>
+        <v>48.96</v>
       </c>
       <c r="W63" s="3">
         <v>0</v>
@@ -5261,67 +5261,67 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="C64" t="str">
-        <v>CNXMNC</v>
+        <v>NIFTYDIVOPPS50</v>
       </c>
       <c r="D64" s="1">
-        <v>27765.7</v>
+        <v>5539.2</v>
       </c>
       <c r="E64" s="2">
-        <v>-1.96</v>
+        <v>0.52</v>
       </c>
       <c r="F64" s="2">
-        <v>-5.93</v>
+        <v>0.52</v>
       </c>
       <c r="G64" s="2">
-        <v>-8.47</v>
+        <v>1.22</v>
       </c>
       <c r="H64" s="2">
-        <v>-9.17</v>
+        <v>-13.25</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
       </c>
       <c r="J64" s="1">
-        <v>31386.59</v>
+        <v>5944.58</v>
       </c>
       <c r="K64" s="1">
-        <v>29044.94</v>
+        <v>5542.79</v>
       </c>
       <c r="L64" s="1">
-        <v>31421.13</v>
+        <v>5669.49</v>
       </c>
       <c r="M64" s="3">
-        <v>-832.31</v>
+        <v>-23.96</v>
       </c>
       <c r="N64" s="3">
-        <v>-698.23</v>
+        <v>-44.27</v>
       </c>
       <c r="O64" s="3">
-        <v>-522.2</v>
+        <v>-121.86</v>
       </c>
       <c r="P64" s="3">
-        <v>61.35</v>
+        <v>-101.53</v>
       </c>
       <c r="Q64" s="3">
-        <v>1921.26</v>
+        <v>24.07</v>
       </c>
       <c r="R64" s="3">
-        <v>2384.15</v>
+        <v>139.3</v>
       </c>
       <c r="S64" s="3">
-        <v>19.44</v>
+        <v>47.42</v>
       </c>
       <c r="T64" s="3">
-        <v>6.64</v>
+        <v>15.54</v>
       </c>
       <c r="U64" s="3">
-        <v>51.27</v>
+        <v>28.34</v>
       </c>
       <c r="V64" s="3">
-        <v>58.86</v>
+        <v>34.18</v>
       </c>
       <c r="W64" s="3">
         <v>0</v>
@@ -5338,67 +5338,67 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="C65" t="str">
-        <v>NIFTYM150MOMNTM50</v>
+        <v>NIFTYAUTO</v>
       </c>
       <c r="D65" s="1">
-        <v>56812.1</v>
+        <v>24970.75</v>
       </c>
       <c r="E65" s="2">
-        <v>-2.05</v>
+        <v>0.44</v>
       </c>
       <c r="F65" s="2">
-        <v>-5.73</v>
+        <v>0.44</v>
       </c>
       <c r="G65" s="2">
-        <v>-6.52</v>
+        <v>-5.03</v>
       </c>
       <c r="H65" s="2">
-        <v>-8.24</v>
+        <v>-11.42</v>
       </c>
       <c r="I65" s="1">
         <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>61702.99</v>
+        <v>26894.25</v>
       </c>
       <c r="K65" s="1">
-        <v>59262.32</v>
+        <v>25225.58</v>
       </c>
       <c r="L65" s="1">
-        <v>62465.58</v>
+        <v>27080.76</v>
       </c>
       <c r="M65" s="3">
-        <v>-1173.13</v>
+        <v>-540.62</v>
       </c>
       <c r="N65" s="3">
-        <v>-867.23</v>
+        <v>-588.96</v>
       </c>
       <c r="O65" s="3">
-        <v>-508.97</v>
+        <v>-404.95</v>
       </c>
       <c r="P65" s="3">
-        <v>188.66</v>
+        <v>-8.1</v>
       </c>
       <c r="Q65" s="3">
-        <v>-248.68</v>
+        <v>1457.85</v>
       </c>
       <c r="R65" s="3">
-        <v>-222.67</v>
+        <v>1807.07</v>
       </c>
       <c r="S65" s="3">
-        <v>22.73</v>
+        <v>36.26</v>
       </c>
       <c r="T65" s="3">
-        <v>7.22</v>
+        <v>9.49</v>
       </c>
       <c r="U65" s="3">
-        <v>48.27</v>
+        <v>33.55</v>
       </c>
       <c r="V65" s="3">
-        <v>43.55</v>
+        <v>55.32</v>
       </c>
       <c r="W65" s="3">
         <v>0</v>
@@ -5415,67 +5415,67 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>Nifty midcap 150</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="C66" t="str">
-        <v>NIFTYMIDCAP150</v>
+        <v>NIFTYMICROCAP250</v>
       </c>
       <c r="D66" s="1">
-        <v>20592.75</v>
+        <v>23921.55</v>
       </c>
       <c r="E66" s="2">
-        <v>-2.07</v>
+        <v>0.4</v>
       </c>
       <c r="F66" s="2">
-        <v>-5.26</v>
+        <v>0.4</v>
       </c>
       <c r="G66" s="2">
-        <v>-5.83</v>
+        <v>-8.87</v>
       </c>
       <c r="H66" s="2">
-        <v>-7.56</v>
+        <v>6.1</v>
       </c>
       <c r="I66" s="1">
         <v>0</v>
       </c>
       <c r="J66" s="1">
-        <v>22176.63</v>
+        <v>23631.39</v>
       </c>
       <c r="K66" s="1">
-        <v>21361.29</v>
+        <v>24850.41</v>
       </c>
       <c r="L66" s="1">
-        <v>22574.75</v>
+        <v>26031.33</v>
       </c>
       <c r="M66" s="3">
-        <v>-417.73</v>
+        <v>-499.1</v>
       </c>
       <c r="N66" s="3">
-        <v>-353.09</v>
+        <v>-280.09</v>
       </c>
       <c r="O66" s="3">
-        <v>-152.78</v>
+        <v>396.37</v>
       </c>
       <c r="P66" s="3">
-        <v>148.25</v>
+        <v>757.8</v>
       </c>
       <c r="Q66" s="3">
-        <v>1654.26</v>
+        <v>2252.91</v>
       </c>
       <c r="R66" s="3">
-        <v>2017.46</v>
+        <v>2343.28</v>
       </c>
       <c r="S66" s="3">
-        <v>23.29</v>
+        <v>27.64</v>
       </c>
       <c r="T66" s="3">
-        <v>7.88</v>
+        <v>9.66</v>
       </c>
       <c r="U66" s="3">
-        <v>48.75</v>
+        <v>46.98</v>
       </c>
       <c r="V66" s="3">
-        <v>49.67</v>
+        <v>35.75</v>
       </c>
       <c r="W66" s="3">
         <v>0</v>
@@ -5492,67 +5492,67 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="C67" t="str">
-        <v>NIFTYMIDCAP50</v>
+        <v>NIFTYGROWSECT15</v>
       </c>
       <c r="D67" s="1">
-        <v>16066.4</v>
+        <v>10927.15</v>
       </c>
       <c r="E67" s="2">
-        <v>-2.1</v>
+        <v>0.35</v>
       </c>
       <c r="F67" s="2">
-        <v>-5.19</v>
+        <v>0.35</v>
       </c>
       <c r="G67" s="2">
-        <v>-5.65</v>
+        <v>3.68</v>
       </c>
       <c r="H67" s="2">
-        <v>-6.88</v>
+        <v>-12.47</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
       </c>
       <c r="J67" s="1">
-        <v>17219.19</v>
+        <v>11208.45</v>
       </c>
       <c r="K67" s="1">
-        <v>16647.11</v>
+        <v>10832.41</v>
       </c>
       <c r="L67" s="1">
-        <v>17635.02</v>
+        <v>11051.88</v>
       </c>
       <c r="M67" s="3">
-        <v>-336.34</v>
+        <v>-10.42</v>
       </c>
       <c r="N67" s="3">
-        <v>-293.24</v>
+        <v>-81.24</v>
       </c>
       <c r="O67" s="3">
-        <v>-89.81</v>
+        <v>-108.74</v>
       </c>
       <c r="P67" s="3">
-        <v>153.62</v>
+        <v>-82.58</v>
       </c>
       <c r="Q67" s="3">
-        <v>859.98</v>
+        <v>34.48</v>
       </c>
       <c r="R67" s="3">
-        <v>1040.24</v>
+        <v>177.14</v>
       </c>
       <c r="S67" s="3">
-        <v>24.09</v>
+        <v>54.39</v>
       </c>
       <c r="T67" s="3">
-        <v>8.3</v>
+        <v>17.61</v>
       </c>
       <c r="U67" s="3">
-        <v>44.75</v>
+        <v>21.56</v>
       </c>
       <c r="V67" s="3">
-        <v>48.24</v>
+        <v>30.83</v>
       </c>
       <c r="W67" s="3">
         <v>0</v>
@@ -5569,67 +5569,67 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="C68" t="str">
-        <v>NIFTYMIDSELECT</v>
+        <v>NIFTYPSUBANK</v>
       </c>
       <c r="D68" s="1">
-        <v>13033.05</v>
+        <v>8093.8</v>
       </c>
       <c r="E68" s="2">
-        <v>-2.12</v>
+        <v>0.29</v>
       </c>
       <c r="F68" s="2">
-        <v>-4.99</v>
+        <v>0.29</v>
       </c>
       <c r="G68" s="2">
-        <v>-5.08</v>
+        <v>0.97</v>
       </c>
       <c r="H68" s="2">
-        <v>-5.4</v>
+        <v>-5.15</v>
       </c>
       <c r="I68" s="1">
         <v>0</v>
       </c>
       <c r="J68" s="1">
-        <v>13996.84</v>
+        <v>8569.56</v>
       </c>
       <c r="K68" s="1">
-        <v>13483.59</v>
+        <v>8141.52</v>
       </c>
       <c r="L68" s="1">
-        <v>14305.74</v>
+        <v>8330.58</v>
       </c>
       <c r="M68" s="3">
-        <v>-271.86</v>
+        <v>-37.38</v>
       </c>
       <c r="N68" s="3">
-        <v>-246.11</v>
+        <v>-57.31</v>
       </c>
       <c r="O68" s="3">
-        <v>-95.59</v>
+        <v>-96.89</v>
       </c>
       <c r="P68" s="3">
-        <v>122.16</v>
+        <v>-45.5</v>
       </c>
       <c r="Q68" s="3">
-        <v>844.78</v>
+        <v>562.79</v>
       </c>
       <c r="R68" s="3">
-        <v>995.64</v>
+        <v>682.88</v>
       </c>
       <c r="S68" s="3">
-        <v>25.6</v>
+        <v>45.74</v>
       </c>
       <c r="T68" s="3">
-        <v>8.87</v>
+        <v>18.98</v>
       </c>
       <c r="U68" s="3">
-        <v>41.89</v>
+        <v>24.78</v>
       </c>
       <c r="V68" s="3">
-        <v>45.32</v>
+        <v>18.2</v>
       </c>
       <c r="W68" s="3">
         <v>0</v>
@@ -5646,67 +5646,67 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="C69" t="str">
-        <v>NIFTYM150QLTY50</v>
+        <v>NIFTYFMCG</v>
       </c>
       <c r="D69" s="1">
-        <v>21727.8</v>
+        <v>42800.75</v>
       </c>
       <c r="E69" s="2">
-        <v>-2.14</v>
+        <v>0.28</v>
       </c>
       <c r="F69" s="2">
-        <v>-5.39</v>
+        <v>0.28</v>
       </c>
       <c r="G69" s="2">
-        <v>-4.56</v>
+        <v>-3.84</v>
       </c>
       <c r="H69" s="2">
-        <v>-9.69</v>
+        <v>-22.85</v>
       </c>
       <c r="I69" s="1">
         <v>0</v>
       </c>
       <c r="J69" s="1">
-        <v>23481.91</v>
+        <v>48852.27</v>
       </c>
       <c r="K69" s="1">
-        <v>22531.45</v>
+        <v>43725.04</v>
       </c>
       <c r="L69" s="1">
-        <v>23665.6</v>
+        <v>45647.82</v>
       </c>
       <c r="M69" s="3">
-        <v>-367.53</v>
+        <v>-712.46</v>
       </c>
       <c r="N69" s="3">
-        <v>-312.41</v>
+        <v>-579.61</v>
       </c>
       <c r="O69" s="3">
-        <v>-256.55</v>
+        <v>-1797.49</v>
       </c>
       <c r="P69" s="3">
-        <v>20.79</v>
+        <v>-1448.69</v>
       </c>
       <c r="Q69" s="3">
-        <v>963.56</v>
+        <v>-2210.25</v>
       </c>
       <c r="R69" s="3">
-        <v>1347.55</v>
+        <v>-974.87</v>
       </c>
       <c r="S69" s="3">
-        <v>26.17</v>
+        <v>34.83</v>
       </c>
       <c r="T69" s="3">
-        <v>10.69</v>
+        <v>10.75</v>
       </c>
       <c r="U69" s="3">
-        <v>47.02</v>
+        <v>34.44</v>
       </c>
       <c r="V69" s="3">
-        <v>41.23</v>
+        <v>39.08</v>
       </c>
       <c r="W69" s="3">
         <v>0</v>
@@ -5723,67 +5723,67 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="C70" t="str">
-        <v>NIFTYMS400MQ100</v>
+        <v>NIFTYFINSERVICE</v>
       </c>
       <c r="D70" s="1">
-        <v>46788.25</v>
+        <v>24454.35</v>
       </c>
       <c r="E70" s="2">
-        <v>-2.18</v>
+        <v>0.21</v>
       </c>
       <c r="F70" s="2">
-        <v>-5.68</v>
+        <v>0.21</v>
       </c>
       <c r="G70" s="2">
-        <v>-5.62</v>
+        <v>-0.79</v>
       </c>
       <c r="H70" s="2">
-        <v>-1.63</v>
+        <v>-11.44</v>
       </c>
       <c r="I70" s="1">
         <v>0</v>
       </c>
       <c r="J70" s="1">
-        <v>49077.2</v>
+        <v>26191.05</v>
       </c>
       <c r="K70" s="1">
-        <v>48691.57</v>
+        <v>24770.06</v>
       </c>
       <c r="L70" s="1">
-        <v>50765.67</v>
+        <v>25444.57</v>
       </c>
       <c r="M70" s="3">
-        <v>-743.9</v>
+        <v>-210.19</v>
       </c>
       <c r="N70" s="3">
-        <v>-528.11</v>
+        <v>-192.26</v>
       </c>
       <c r="O70" s="3">
-        <v>-3.03</v>
+        <v>-424.2</v>
       </c>
       <c r="P70" s="3">
-        <v>536.27</v>
+        <v>-266.41</v>
       </c>
       <c r="Q70" s="3">
-        <v>-58.33</v>
+        <v>632.02</v>
       </c>
       <c r="R70" s="3">
-        <v>-322.83</v>
+        <v>1077.96</v>
       </c>
       <c r="S70" s="3">
-        <v>24.75</v>
+        <v>38.73</v>
       </c>
       <c r="T70" s="3">
-        <v>7.78</v>
+        <v>12.19</v>
       </c>
       <c r="U70" s="3">
-        <v>47.99</v>
+        <v>28.27</v>
       </c>
       <c r="V70" s="3">
-        <v>44.09</v>
+        <v>26.9</v>
       </c>
       <c r="W70" s="3">
         <v>0</v>
@@ -5800,67 +5800,67 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="C71" t="str">
-        <v>CNXMIDCAP</v>
+        <v>NIFTYFINSRV2550</v>
       </c>
       <c r="D71" s="1">
-        <v>55800.65</v>
+        <v>26242.55</v>
       </c>
       <c r="E71" s="2">
-        <v>-2.21</v>
+        <v>0.18</v>
       </c>
       <c r="F71" s="2">
-        <v>-5.63</v>
+        <v>0.18</v>
       </c>
       <c r="G71" s="2">
-        <v>-5.95</v>
+        <v>-1.18</v>
       </c>
       <c r="H71" s="2">
-        <v>-7.74</v>
+        <v>-13.04</v>
       </c>
       <c r="I71" s="1">
         <v>0</v>
       </c>
       <c r="J71" s="1">
-        <v>60295.21</v>
+        <v>28507.78</v>
       </c>
       <c r="K71" s="1">
-        <v>58034.89</v>
+        <v>26611.8</v>
       </c>
       <c r="L71" s="1">
-        <v>61416.78</v>
+        <v>27503.64</v>
       </c>
       <c r="M71" s="3">
-        <v>-1161.74</v>
+        <v>-280.13</v>
       </c>
       <c r="N71" s="3">
-        <v>-971.27</v>
+        <v>-266.79</v>
       </c>
       <c r="O71" s="3">
-        <v>-439.23</v>
+        <v>-562.75</v>
       </c>
       <c r="P71" s="3">
-        <v>396.23</v>
+        <v>-353.46</v>
       </c>
       <c r="Q71" s="3">
-        <v>2727.99</v>
+        <v>1285.69</v>
       </c>
       <c r="R71" s="3">
-        <v>3451.52</v>
+        <v>1895.05</v>
       </c>
       <c r="S71" s="3">
-        <v>23.59</v>
+        <v>37.01</v>
       </c>
       <c r="T71" s="3">
-        <v>7.52</v>
+        <v>11.59</v>
       </c>
       <c r="U71" s="3">
-        <v>48.47</v>
+        <v>29.99</v>
       </c>
       <c r="V71" s="3">
-        <v>50.15</v>
+        <v>29.61</v>
       </c>
       <c r="W71" s="3">
         <v>0</v>
@@ -5877,67 +5877,67 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="C72" t="str">
-        <v>NIFTYPSUBANK</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="D72" s="1">
-        <v>8070.7</v>
+        <v>54366.7</v>
       </c>
       <c r="E72" s="2">
-        <v>-2.26</v>
+        <v>0.15</v>
       </c>
       <c r="F72" s="2">
-        <v>-0.3</v>
+        <v>0.15</v>
       </c>
       <c r="G72" s="2">
-        <v>0.68</v>
+        <v>-0.49</v>
       </c>
       <c r="H72" s="2">
-        <v>-5.42</v>
+        <v>-8.75</v>
       </c>
       <c r="I72" s="1">
         <v>0</v>
       </c>
       <c r="J72" s="1">
-        <v>8571.95</v>
+        <v>56816.25</v>
       </c>
       <c r="K72" s="1">
-        <v>8152.13</v>
+        <v>54943.8</v>
       </c>
       <c r="L72" s="1">
-        <v>8345.06</v>
+        <v>56189.32</v>
       </c>
       <c r="M72" s="3">
-        <v>-35.55</v>
+        <v>-363.92</v>
       </c>
       <c r="N72" s="3">
-        <v>-62.29</v>
+        <v>-353.9</v>
       </c>
       <c r="O72" s="3">
-        <v>-89.97</v>
+        <v>-495.53</v>
       </c>
       <c r="P72" s="3">
-        <v>-32.65</v>
+        <v>-186.53</v>
       </c>
       <c r="Q72" s="3">
-        <v>560.95</v>
+        <v>1616.41</v>
       </c>
       <c r="R72" s="3">
-        <v>682.51</v>
+        <v>2278.86</v>
       </c>
       <c r="S72" s="3">
-        <v>44.6</v>
+        <v>38.74</v>
       </c>
       <c r="T72" s="3">
-        <v>20.41</v>
+        <v>11.02</v>
       </c>
       <c r="U72" s="3">
-        <v>22.71</v>
+        <v>26.88</v>
       </c>
       <c r="V72" s="3">
-        <v>18.58</v>
+        <v>24.35</v>
       </c>
       <c r="W72" s="3">
         <v>0</v>
@@ -5954,67 +5954,67 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="C73" t="str">
-        <v>CNXNIFTYJUNIOR</v>
+        <v>NIFTYCHEMICALS</v>
       </c>
       <c r="D73" s="1">
-        <v>65828.6</v>
+        <v>26353.4</v>
       </c>
       <c r="E73" s="2">
-        <v>-2.27</v>
+        <v>0.11</v>
       </c>
       <c r="F73" s="2">
-        <v>-4.58</v>
+        <v>0.11</v>
       </c>
       <c r="G73" s="2">
-        <v>-5.62</v>
-      </c>
-      <c r="H73" s="2">
-        <v>-5.1</v>
+        <v>-7.09</v>
+      </c>
+      <c r="H73" t="str">
+        <v/>
       </c>
       <c r="I73" s="1">
         <v>0</v>
       </c>
-      <c r="J73" s="1">
-        <v>70018.75</v>
+      <c r="J73" t="str">
+        <v/>
       </c>
       <c r="K73" s="1">
-        <v>67998.34</v>
+        <v>27374.94</v>
       </c>
       <c r="L73" s="1">
-        <v>71491.06</v>
+        <v>29160.65</v>
       </c>
       <c r="M73" s="3">
-        <v>-1177.52</v>
+        <v>-647.18</v>
       </c>
       <c r="N73" s="3">
-        <v>-1032.13</v>
+        <v>-489.44</v>
       </c>
       <c r="O73" s="3">
-        <v>-344.01</v>
+        <v>-422.68</v>
       </c>
       <c r="P73" s="3">
-        <v>549.61</v>
+        <v>42.14</v>
       </c>
       <c r="Q73" s="3">
-        <v>2518.21</v>
+        <v>158.3</v>
       </c>
       <c r="R73" s="3">
-        <v>3153.26</v>
+        <v>172.94</v>
       </c>
       <c r="S73" s="3">
-        <v>26.84</v>
+        <v>25.6</v>
       </c>
       <c r="T73" s="3">
-        <v>8.92</v>
+        <v>10.48</v>
       </c>
       <c r="U73" s="3">
-        <v>43.18</v>
+        <v>45.17</v>
       </c>
       <c r="V73" s="3">
-        <v>47.66</v>
+        <v>40.96</v>
       </c>
       <c r="W73" s="3">
         <v>0</v>
@@ -6031,67 +6031,67 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="C74" t="str">
-        <v>NIFTYCHEMICALS</v>
+        <v>BHARATBOND-APR32</v>
       </c>
       <c r="D74" s="1">
-        <v>26325</v>
+        <v>1300.92</v>
       </c>
       <c r="E74" s="2">
-        <v>-2.32</v>
+        <v>0.06</v>
       </c>
       <c r="F74" s="2">
-        <v>-7.19</v>
+        <v>0.06</v>
       </c>
       <c r="G74" s="2">
-        <v>-7.19</v>
-      </c>
-      <c r="H74" t="str">
-        <v/>
+        <v>-1.11</v>
+      </c>
+      <c r="H74" s="2">
+        <v>0.21</v>
       </c>
       <c r="I74" s="1">
         <v>0</v>
       </c>
-      <c r="J74" t="str">
-        <v/>
+      <c r="J74" s="1">
+        <v>1308.02</v>
       </c>
       <c r="K74" s="1">
-        <v>27601.95</v>
+        <v>1306.92</v>
       </c>
       <c r="L74" s="1">
-        <v>29242.38</v>
+        <v>1320.54</v>
       </c>
       <c r="M74" s="3">
-        <v>-581.26</v>
+        <v>-5.03</v>
       </c>
       <c r="N74" s="3">
-        <v>-450.01</v>
+        <v>-4.04</v>
       </c>
       <c r="O74" s="3">
-        <v>-256.82</v>
+        <v>0.37</v>
       </c>
       <c r="P74" s="3">
-        <v>158.35</v>
+        <v>4.56</v>
       </c>
       <c r="Q74" s="3">
-        <v>156.03</v>
+        <v>23.55</v>
       </c>
       <c r="R74" s="3">
-        <v>172.48</v>
+        <v>24.12</v>
       </c>
       <c r="S74" s="3">
-        <v>25.08</v>
+        <v>19.42</v>
       </c>
       <c r="T74" s="3">
-        <v>11.18</v>
+        <v>19.95</v>
       </c>
       <c r="U74" s="3">
-        <v>46.39</v>
+        <v>77.59</v>
       </c>
       <c r="V74" s="3">
-        <v>39.31</v>
+        <v>40.86</v>
       </c>
       <c r="W74" s="3">
         <v>0</v>
@@ -6108,67 +6108,67 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="C75" t="str">
-        <v>NIFTYMICROCAP250</v>
+        <v>NIFTYGS15YRPLUS</v>
       </c>
       <c r="D75" s="1">
-        <v>23827.1</v>
+        <v>3453.38</v>
       </c>
       <c r="E75" s="2">
-        <v>-2.32</v>
+        <v>0.05</v>
       </c>
       <c r="F75" s="2">
-        <v>-7.42</v>
+        <v>0.05</v>
       </c>
       <c r="G75" s="2">
-        <v>-9.23</v>
+        <v>-1.94</v>
       </c>
       <c r="H75" s="2">
-        <v>5.68</v>
+        <v>-1.13</v>
       </c>
       <c r="I75" s="1">
         <v>0</v>
       </c>
       <c r="J75" s="1">
-        <v>23624.75</v>
+        <v>3495.08</v>
       </c>
       <c r="K75" s="1">
-        <v>25056.82</v>
+        <v>3472.6</v>
       </c>
       <c r="L75" s="1">
-        <v>26074.8</v>
+        <v>3529.21</v>
       </c>
       <c r="M75" s="3">
-        <v>-431.12</v>
+        <v>-20.41</v>
       </c>
       <c r="N75" s="3">
-        <v>-225.33</v>
+        <v>-17.21</v>
       </c>
       <c r="O75" s="3">
-        <v>565.85</v>
+        <v>-3.59</v>
       </c>
       <c r="P75" s="3">
-        <v>848.15</v>
+        <v>11.41</v>
       </c>
       <c r="Q75" s="3">
-        <v>2245.38</v>
+        <v>117.61</v>
       </c>
       <c r="R75" s="3">
-        <v>2341.77</v>
+        <v>141.66</v>
       </c>
       <c r="S75" s="3">
-        <v>25.8</v>
+        <v>31.33</v>
       </c>
       <c r="T75" s="3">
-        <v>10.5</v>
+        <v>14.87</v>
       </c>
       <c r="U75" s="3">
-        <v>51.06</v>
+        <v>38.02</v>
       </c>
       <c r="V75" s="3">
-        <v>33.44</v>
+        <v>32.21</v>
       </c>
       <c r="W75" s="3">
         <v>0</v>
@@ -6185,67 +6185,67 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="C76" t="str">
-        <v>NIFTYMIDSMALLCAP400</v>
+        <v>BHARATBOND-APR30</v>
       </c>
       <c r="D76" s="1">
-        <v>19071.8</v>
+        <v>1596.65</v>
       </c>
       <c r="E76" s="2">
-        <v>-2.33</v>
+        <v>0.03</v>
       </c>
       <c r="F76" s="2">
-        <v>-5.91</v>
+        <v>0.03</v>
       </c>
       <c r="G76" s="2">
-        <v>-6.58</v>
+        <v>-0.64</v>
       </c>
       <c r="H76" s="2">
-        <v>-5.67</v>
+        <v>1.9</v>
       </c>
       <c r="I76" s="1">
         <v>0</v>
       </c>
       <c r="J76" s="1">
-        <v>20259.6</v>
+        <v>1586.97</v>
       </c>
       <c r="K76" s="1">
-        <v>19886.07</v>
+        <v>1600.87</v>
       </c>
       <c r="L76" s="1">
-        <v>20941.94</v>
+        <v>1608.2</v>
       </c>
       <c r="M76" s="3">
-        <v>-379.38</v>
+        <v>-2.96</v>
       </c>
       <c r="N76" s="3">
-        <v>-293.14</v>
+        <v>-2.04</v>
       </c>
       <c r="O76" s="3">
-        <v>-30.7</v>
+        <v>5.43</v>
       </c>
       <c r="P76" s="3">
-        <v>239.72</v>
+        <v>8.52</v>
       </c>
       <c r="Q76" s="3">
-        <v>1522.67</v>
+        <v>34.52</v>
       </c>
       <c r="R76" s="3">
-        <v>1812.28</v>
+        <v>33.05</v>
       </c>
       <c r="S76" s="3">
-        <v>22.43</v>
+        <v>25.47</v>
       </c>
       <c r="T76" s="3">
-        <v>8.1</v>
+        <v>18.9</v>
       </c>
       <c r="U76" s="3">
-        <v>53.33</v>
+        <v>68.23</v>
       </c>
       <c r="V76" s="3">
-        <v>48.25</v>
+        <v>30.23</v>
       </c>
       <c r="W76" s="3">
         <v>0</v>
@@ -6262,67 +6262,67 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>CNXREALTY</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="C77" t="str">
-        <v>CNXREALTY</v>
+        <v>BHARATBOND-APR31</v>
       </c>
       <c r="D77" s="1">
-        <v>784.35</v>
+        <v>1440.84</v>
       </c>
       <c r="E77" s="2">
-        <v>-2.38</v>
+        <v>0.03</v>
       </c>
       <c r="F77" s="2">
-        <v>-5.04</v>
+        <v>0.03</v>
       </c>
       <c r="G77" s="2">
-        <v>-7.43</v>
+        <v>-0.9</v>
       </c>
       <c r="H77" s="2">
-        <v>-10.66</v>
+        <v>1.13</v>
       </c>
       <c r="I77" s="1">
         <v>0</v>
       </c>
       <c r="J77" s="1">
-        <v>821.76</v>
+        <v>1440.95</v>
       </c>
       <c r="K77" s="1">
-        <v>811.59</v>
+        <v>1446.27</v>
       </c>
       <c r="L77" s="1">
-        <v>861.67</v>
+        <v>1457.26</v>
       </c>
       <c r="M77" s="3">
-        <v>-16.39</v>
+        <v>-4.15</v>
       </c>
       <c r="N77" s="3">
-        <v>-14.88</v>
+        <v>-3.2</v>
       </c>
       <c r="O77" s="3">
-        <v>-1.64</v>
+        <v>2.54</v>
       </c>
       <c r="P77" s="3">
-        <v>10.22</v>
+        <v>6.3</v>
       </c>
       <c r="Q77" s="3">
-        <v>0.01</v>
+        <v>28.76</v>
       </c>
       <c r="R77" s="3">
-        <v>9.58</v>
+        <v>28.47</v>
       </c>
       <c r="S77" s="3">
-        <v>32.65</v>
+        <v>20.25</v>
       </c>
       <c r="T77" s="3">
-        <v>12.73</v>
+        <v>17.93</v>
       </c>
       <c r="U77" s="3">
-        <v>36.25</v>
+        <v>73.95</v>
       </c>
       <c r="V77" s="3">
-        <v>27.1</v>
+        <v>36.84</v>
       </c>
       <c r="W77" s="3">
         <v>0</v>
@@ -6339,67 +6339,67 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="C78" t="str">
-        <v>NIFTY200MOMENTM30</v>
+        <v>NIFTYGS48YR</v>
       </c>
       <c r="D78" s="1">
-        <v>27301.75</v>
+        <v>3277.41</v>
       </c>
       <c r="E78" s="2">
-        <v>-2.47</v>
+        <v>0.02</v>
       </c>
       <c r="F78" s="2">
-        <v>-6.15</v>
+        <v>0.02</v>
       </c>
       <c r="G78" s="2">
-        <v>-7.51</v>
+        <v>-0.94</v>
       </c>
       <c r="H78" s="2">
-        <v>-12.35</v>
+        <v>1.7</v>
       </c>
       <c r="I78" s="1">
         <v>0</v>
       </c>
       <c r="J78" s="1">
-        <v>30366.63</v>
+        <v>3280.69</v>
       </c>
       <c r="K78" s="1">
-        <v>28588.86</v>
+        <v>3283.08</v>
       </c>
       <c r="L78" s="1">
-        <v>30194.41</v>
+        <v>3318.47</v>
       </c>
       <c r="M78" s="3">
-        <v>-592.61</v>
+        <v>-11.86</v>
       </c>
       <c r="N78" s="3">
-        <v>-435.76</v>
+        <v>-11.42</v>
       </c>
       <c r="O78" s="3">
-        <v>-430.86</v>
+        <v>4.88</v>
       </c>
       <c r="P78" s="3">
-        <v>-104.64</v>
+        <v>15.37</v>
       </c>
       <c r="Q78" s="3">
-        <v>1361.55</v>
+        <v>139.52</v>
       </c>
       <c r="R78" s="3">
-        <v>1982.03</v>
+        <v>155.41</v>
       </c>
       <c r="S78" s="3">
-        <v>23.16</v>
+        <v>25.86</v>
       </c>
       <c r="T78" s="3">
-        <v>7.9</v>
+        <v>12.19</v>
       </c>
       <c r="U78" s="3">
-        <v>47.59</v>
+        <v>44.27</v>
       </c>
       <c r="V78" s="3">
-        <v>40.68</v>
+        <v>49.53</v>
       </c>
       <c r="W78" s="3">
         <v>0</v>
@@ -6416,67 +6416,67 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="C79" t="str">
-        <v>NIFTYCAPITALMKT</v>
+        <v>NIFTYGS813YR</v>
       </c>
       <c r="D79" s="1">
-        <v>4930.05</v>
+        <v>2966.26</v>
       </c>
       <c r="E79" s="2">
-        <v>-2.5</v>
+        <v>0.02</v>
       </c>
       <c r="F79" s="2">
-        <v>-5.95</v>
+        <v>0.02</v>
       </c>
       <c r="G79" s="2">
-        <v>-3.14</v>
+        <v>-1.58</v>
       </c>
       <c r="H79" s="2">
-        <v>5.88</v>
+        <v>-0.02</v>
       </c>
       <c r="I79" s="1">
         <v>0</v>
       </c>
       <c r="J79" s="1">
-        <v>5106.68</v>
+        <v>3001.33</v>
       </c>
       <c r="K79" s="1">
-        <v>5130.1</v>
+        <v>2976.7</v>
       </c>
       <c r="L79" s="1">
-        <v>5294.25</v>
+        <v>3023.32</v>
       </c>
       <c r="M79" s="3">
-        <v>-58.04</v>
+        <v>-16.34</v>
       </c>
       <c r="N79" s="3">
-        <v>-37.62</v>
+        <v>-15.03</v>
       </c>
       <c r="O79" s="3">
-        <v>17.34</v>
+        <v>-3.56</v>
       </c>
       <c r="P79" s="3">
-        <v>84.49</v>
+        <v>8.36</v>
       </c>
       <c r="Q79" s="3">
-        <v>353.78</v>
+        <v>114.43</v>
       </c>
       <c r="R79" s="3">
-        <v>323.22</v>
+        <v>132.76</v>
       </c>
       <c r="S79" s="3">
-        <v>33.17</v>
+        <v>25.13</v>
       </c>
       <c r="T79" s="3">
-        <v>14.11</v>
+        <v>12.27</v>
       </c>
       <c r="U79" s="3">
-        <v>35.52</v>
+        <v>44.07</v>
       </c>
       <c r="V79" s="3">
-        <v>22.2</v>
+        <v>51.29</v>
       </c>
       <c r="W79" s="3">
         <v>0</v>
@@ -6493,67 +6493,67 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="C80" t="str">
-        <v>NIFTY200ALPHA30</v>
+        <v>NIFTYGSCOMPSITE</v>
       </c>
       <c r="D80" s="1">
-        <v>23666.85</v>
+        <v>3057.5</v>
       </c>
       <c r="E80" s="2">
-        <v>-2.56</v>
+        <v>0.01</v>
       </c>
       <c r="F80" s="2">
-        <v>-6.1</v>
+        <v>0.01</v>
       </c>
       <c r="G80" s="2">
-        <v>-6.8</v>
+        <v>-1.51</v>
       </c>
       <c r="H80" s="2">
-        <v>-5.28</v>
+        <v>0.17</v>
       </c>
       <c r="I80" s="1">
         <v>0</v>
       </c>
       <c r="J80" s="1">
-        <v>25466.45</v>
+        <v>3085.98</v>
       </c>
       <c r="K80" s="1">
-        <v>24754.22</v>
+        <v>3068.62</v>
       </c>
       <c r="L80" s="1">
-        <v>26109.43</v>
+        <v>3115.23</v>
       </c>
       <c r="M80" s="3">
-        <v>-484.27</v>
+        <v>-16.22</v>
       </c>
       <c r="N80" s="3">
-        <v>-363.85</v>
+        <v>-14.89</v>
       </c>
       <c r="O80" s="3">
-        <v>-111.79</v>
+        <v>-1.47</v>
       </c>
       <c r="P80" s="3">
-        <v>204.73</v>
+        <v>10.82</v>
       </c>
       <c r="Q80" s="3">
-        <v>1.84</v>
+        <v>118.24</v>
       </c>
       <c r="R80" s="3">
-        <v>-68.08</v>
+        <v>136.5</v>
       </c>
       <c r="S80" s="3">
-        <v>24.96</v>
+        <v>26.77</v>
       </c>
       <c r="T80" s="3">
-        <v>7.96</v>
+        <v>11.11</v>
       </c>
       <c r="U80" s="3">
-        <v>46.37</v>
+        <v>43.25</v>
       </c>
       <c r="V80" s="3">
-        <v>39.95</v>
+        <v>49.09</v>
       </c>
       <c r="W80" s="3">
         <v>0</v>
@@ -6570,67 +6570,67 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="C81" t="str">
-        <v>NIFTYMIDLIQ15</v>
+        <v>NIFTYGS10YR</v>
       </c>
       <c r="D81" s="1">
-        <v>15043.45</v>
+        <v>2595.95</v>
       </c>
       <c r="E81" s="2">
-        <v>-2.56</v>
+        <v>0.01</v>
       </c>
       <c r="F81" s="2">
-        <v>-6.39</v>
+        <v>0.01</v>
       </c>
       <c r="G81" s="2">
-        <v>-7.65</v>
+        <v>-1.6</v>
       </c>
       <c r="H81" s="2">
-        <v>-6</v>
+        <v>-0.61</v>
       </c>
       <c r="I81" s="1">
         <v>0</v>
       </c>
       <c r="J81" s="1">
-        <v>16126.11</v>
+        <v>2632.11</v>
       </c>
       <c r="K81" s="1">
-        <v>15773.12</v>
+        <v>2605.09</v>
       </c>
       <c r="L81" s="1">
-        <v>16777.1</v>
+        <v>2646.22</v>
       </c>
       <c r="M81" s="3">
-        <v>-353.58</v>
+        <v>-14.47</v>
       </c>
       <c r="N81" s="3">
-        <v>-273.59</v>
+        <v>-13.4</v>
       </c>
       <c r="O81" s="3">
-        <v>-22.09</v>
+        <v>-5.2</v>
       </c>
       <c r="P81" s="3">
-        <v>221.39</v>
+        <v>4.89</v>
       </c>
       <c r="Q81" s="3">
-        <v>1500.29</v>
+        <v>89.61</v>
       </c>
       <c r="R81" s="3">
-        <v>1738.39</v>
+        <v>106.33</v>
       </c>
       <c r="S81" s="3">
-        <v>24.61</v>
+        <v>26.38</v>
       </c>
       <c r="T81" s="3">
-        <v>9.2</v>
+        <v>15.33</v>
       </c>
       <c r="U81" s="3">
-        <v>45.78</v>
+        <v>38.25</v>
       </c>
       <c r="V81" s="3">
-        <v>43.14</v>
+        <v>38.87</v>
       </c>
       <c r="W81" s="3">
         <v>0</v>
@@ -6647,67 +6647,67 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="C82" t="str">
-        <v>NIFTY500MOMENTM50</v>
+        <v>NIFTY50DIVPOINT</v>
       </c>
       <c r="D82" s="1">
-        <v>49069.75</v>
+        <v>204.22</v>
       </c>
       <c r="E82" s="2">
-        <v>-2.59</v>
+        <v>0</v>
       </c>
       <c r="F82" s="2">
-        <v>-6.2</v>
+        <v>0</v>
       </c>
       <c r="G82" s="2">
-        <v>-7.23</v>
+        <v>3.78</v>
       </c>
       <c r="H82" s="2">
-        <v>-6.9</v>
+        <v>-18.03</v>
       </c>
       <c r="I82" s="1">
         <v>0</v>
       </c>
       <c r="J82" s="1">
-        <v>52524.13</v>
+        <v>180.21</v>
       </c>
       <c r="K82" s="1">
-        <v>51482.54</v>
+        <v>201.48</v>
       </c>
       <c r="L82" s="1">
-        <v>53982.39</v>
+        <v>195.45</v>
       </c>
       <c r="M82" s="3">
-        <v>-947.88</v>
+        <v>2.88</v>
       </c>
       <c r="N82" s="3">
-        <v>-620.66</v>
+        <v>2.66</v>
       </c>
       <c r="O82" s="3">
-        <v>-126.79</v>
+        <v>12.32</v>
       </c>
       <c r="P82" s="3">
-        <v>413.04</v>
+        <v>7.02</v>
       </c>
       <c r="Q82" s="3">
-        <v>-909.94</v>
+        <v>5.47</v>
       </c>
       <c r="R82" s="3">
-        <v>-1153.68</v>
+        <v>7.68</v>
       </c>
       <c r="S82" s="3">
-        <v>24.22</v>
+        <v>100</v>
       </c>
       <c r="T82" s="3">
-        <v>7.98</v>
+        <v>99.62</v>
       </c>
       <c r="U82" s="3">
-        <v>50.9</v>
+        <v>0.38</v>
       </c>
       <c r="V82" s="3">
-        <v>40.6</v>
+        <v>97.16</v>
       </c>
       <c r="W82" s="3">
         <v>0</v>
@@ -6724,67 +6724,67 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="C83" t="str">
-        <v>NIFTYINDDEFENCE</v>
+        <v>BHARATBOND-APR33</v>
       </c>
       <c r="D83" s="1">
-        <v>8561.2</v>
+        <v>1255.08</v>
       </c>
       <c r="E83" s="2">
-        <v>-2.6</v>
+        <v>-0.01</v>
       </c>
       <c r="F83" s="2">
-        <v>-7.05</v>
+        <v>-0.01</v>
       </c>
       <c r="G83" s="2">
-        <v>-7.71</v>
+        <v>-1.42</v>
       </c>
       <c r="H83" s="2">
-        <v>10.5</v>
+        <v>-0.51</v>
       </c>
       <c r="I83" s="1">
         <v>0</v>
       </c>
       <c r="J83" s="1">
-        <v>8842.66</v>
+        <v>1268.29</v>
       </c>
       <c r="K83" s="1">
-        <v>8980.74</v>
+        <v>1262.72</v>
       </c>
       <c r="L83" s="1">
-        <v>9456.74</v>
+        <v>1278.74</v>
       </c>
       <c r="M83" s="3">
-        <v>-161.86</v>
+        <v>-5.99</v>
       </c>
       <c r="N83" s="3">
-        <v>-118.83</v>
+        <v>-4.77</v>
       </c>
       <c r="O83" s="3">
-        <v>81.2</v>
+        <v>-0.92</v>
       </c>
       <c r="P83" s="3">
-        <v>230.92</v>
+        <v>3.68</v>
       </c>
       <c r="Q83" s="3">
-        <v>583.08</v>
+        <v>20.71</v>
       </c>
       <c r="R83" s="3">
-        <v>518.72</v>
+        <v>21.83</v>
       </c>
       <c r="S83" s="3">
-        <v>29.31</v>
+        <v>15.42</v>
       </c>
       <c r="T83" s="3">
-        <v>14.22</v>
+        <v>15.68</v>
       </c>
       <c r="U83" s="3">
-        <v>44.26</v>
+        <v>81.87</v>
       </c>
       <c r="V83" s="3">
-        <v>27.3</v>
+        <v>44.07</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -6801,67 +6801,67 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="C84" t="str">
-        <v>NIFTYCONSURDURBL</v>
+        <v>NIFTYGS10YRCLN</v>
       </c>
       <c r="D84" s="1">
-        <v>33922</v>
+        <v>836.78</v>
       </c>
       <c r="E84" s="2">
-        <v>-2.63</v>
+        <v>-0.05</v>
       </c>
       <c r="F84" s="2">
-        <v>-6.42</v>
+        <v>-0.05</v>
       </c>
       <c r="G84" s="2">
-        <v>-7.39</v>
+        <v>-2.16</v>
       </c>
       <c r="H84" s="2">
-        <v>-7.71</v>
+        <v>-6.13</v>
       </c>
       <c r="I84" s="1">
         <v>0</v>
       </c>
       <c r="J84" s="1">
-        <v>37099.43</v>
+        <v>873.29</v>
       </c>
       <c r="K84" s="1">
-        <v>35538.35</v>
+        <v>841.13</v>
       </c>
       <c r="L84" s="1">
-        <v>38271.87</v>
+        <v>859.84</v>
       </c>
       <c r="M84" s="3">
-        <v>-914.61</v>
+        <v>-6.58</v>
       </c>
       <c r="N84" s="3">
-        <v>-785.28</v>
+        <v>-6.2</v>
       </c>
       <c r="O84" s="3">
-        <v>-296.05</v>
+        <v>-9.78</v>
       </c>
       <c r="P84" s="3">
-        <v>295.51</v>
+        <v>-6.48</v>
       </c>
       <c r="Q84" s="3">
-        <v>532.92</v>
+        <v>-17.32</v>
       </c>
       <c r="R84" s="3">
-        <v>918.75</v>
+        <v>-14.22</v>
       </c>
       <c r="S84" s="3">
-        <v>22.78</v>
+        <v>20.1</v>
       </c>
       <c r="T84" s="3">
-        <v>6.32</v>
+        <v>9.82</v>
       </c>
       <c r="U84" s="3">
-        <v>45.13</v>
+        <v>42.87</v>
       </c>
       <c r="V84" s="3">
-        <v>56</v>
+        <v>53.9</v>
       </c>
       <c r="W84" s="3">
         <v>0</v>
@@ -6878,67 +6878,67 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="C85" t="str">
-        <v>NIFTYSML250MQ100</v>
+        <v>NIFTYTATA25CAP</v>
       </c>
       <c r="D85" s="1">
-        <v>44470.2</v>
+        <v>13591.6</v>
       </c>
       <c r="E85" s="2">
-        <v>-2.65</v>
+        <v>-0.07</v>
       </c>
       <c r="F85" s="2">
-        <v>-6.73</v>
+        <v>-0.07</v>
       </c>
       <c r="G85" s="2">
-        <v>-7.08</v>
+        <v>1.79</v>
       </c>
       <c r="H85" s="2">
-        <v>1.1</v>
+        <v>-11.12</v>
       </c>
       <c r="I85" s="1">
         <v>0</v>
       </c>
       <c r="J85" s="1">
-        <v>44929.21</v>
+        <v>14376.94</v>
       </c>
       <c r="K85" s="1">
-        <v>46643.68</v>
+        <v>13659.88</v>
       </c>
       <c r="L85" s="1">
-        <v>48280.02</v>
+        <v>13987.77</v>
       </c>
       <c r="M85" s="3">
-        <v>-654.52</v>
+        <v>-57.18</v>
       </c>
       <c r="N85" s="3">
-        <v>-358.76</v>
+        <v>-106.46</v>
       </c>
       <c r="O85" s="3">
-        <v>655.34</v>
+        <v>-234.36</v>
       </c>
       <c r="P85" s="3">
-        <v>1101.74</v>
+        <v>-177.27</v>
       </c>
       <c r="Q85" s="3">
-        <v>-453.49</v>
+        <v>-548.46</v>
       </c>
       <c r="R85" s="3">
-        <v>-1042.54</v>
+        <v>-494.23</v>
       </c>
       <c r="S85" s="3">
-        <v>25.55</v>
+        <v>45.74</v>
       </c>
       <c r="T85" s="3">
-        <v>11.54</v>
+        <v>16.41</v>
       </c>
       <c r="U85" s="3">
-        <v>50.12</v>
+        <v>26.87</v>
       </c>
       <c r="V85" s="3">
-        <v>32.55</v>
+        <v>25.08</v>
       </c>
       <c r="W85" s="3">
         <v>0</v>
@@ -6955,67 +6955,67 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="C86" t="str">
-        <v>NIFTYMETAL</v>
+        <v>NIFTYGS1115YR</v>
       </c>
       <c r="D86" s="1">
-        <v>11478.2</v>
+        <v>3280.86</v>
       </c>
       <c r="E86" s="2">
-        <v>-2.71</v>
+        <v>-0.1</v>
       </c>
       <c r="F86" s="2">
-        <v>-5.4</v>
+        <v>-0.1</v>
       </c>
       <c r="G86" s="2">
-        <v>-10.05</v>
+        <v>-1.23</v>
       </c>
       <c r="H86" s="2">
-        <v>2.78</v>
+        <v>1.2</v>
       </c>
       <c r="I86" s="1">
         <v>0</v>
       </c>
       <c r="J86" s="1">
-        <v>12483.72</v>
+        <v>3295.53</v>
       </c>
       <c r="K86" s="1">
-        <v>11951.39</v>
+        <v>3292.04</v>
       </c>
       <c r="L86" s="1">
-        <v>12804.74</v>
+        <v>3345.3</v>
       </c>
       <c r="M86" s="3">
-        <v>-315.57</v>
+        <v>-17.47</v>
       </c>
       <c r="N86" s="3">
-        <v>-267.05</v>
+        <v>-17.28</v>
       </c>
       <c r="O86" s="3">
-        <v>-15.01</v>
+        <v>3.13</v>
       </c>
       <c r="P86" s="3">
-        <v>202.89</v>
+        <v>17.81</v>
       </c>
       <c r="Q86" s="3">
-        <v>1107.38</v>
+        <v>136.08</v>
       </c>
       <c r="R86" s="3">
-        <v>1124.17</v>
+        <v>153.82</v>
       </c>
       <c r="S86" s="3">
-        <v>27.87</v>
+        <v>30.89</v>
       </c>
       <c r="T86" s="3">
-        <v>10.69</v>
+        <v>8.22</v>
       </c>
       <c r="U86" s="3">
-        <v>40.86</v>
+        <v>35.85</v>
       </c>
       <c r="V86" s="3">
-        <v>35.32</v>
+        <v>51.02</v>
       </c>
       <c r="W86" s="3">
         <v>0</v>
@@ -7032,67 +7032,67 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="C87" t="str">
-        <v>NIFTYSMALLCAP250</v>
+        <v>NIFTYCONSURDURBL</v>
       </c>
       <c r="D87" s="1">
-        <v>16385.15</v>
+        <v>33851.1</v>
       </c>
       <c r="E87" s="2">
-        <v>-2.79</v>
+        <v>-0.21</v>
       </c>
       <c r="F87" s="2">
-        <v>-7.1</v>
+        <v>-0.21</v>
       </c>
       <c r="G87" s="2">
-        <v>-7.94</v>
+        <v>-7.58</v>
       </c>
       <c r="H87" s="2">
-        <v>-1.8</v>
+        <v>-7.9</v>
       </c>
       <c r="I87" s="1">
         <v>0</v>
       </c>
       <c r="J87" s="1">
-        <v>16949.08</v>
+        <v>37084.64</v>
       </c>
       <c r="K87" s="1">
-        <v>17248.25</v>
+        <v>35231.58</v>
       </c>
       <c r="L87" s="1">
-        <v>18042.86</v>
+        <v>38146.43</v>
       </c>
       <c r="M87" s="3">
-        <v>-312.85</v>
+        <v>-994.64</v>
       </c>
       <c r="N87" s="3">
-        <v>-196.4</v>
+        <v>-827.15</v>
       </c>
       <c r="O87" s="3">
-        <v>154.28</v>
+        <v>-536.15</v>
       </c>
       <c r="P87" s="3">
-        <v>372.72</v>
+        <v>129.18</v>
       </c>
       <c r="Q87" s="3">
-        <v>1255.47</v>
+        <v>527.27</v>
       </c>
       <c r="R87" s="3">
-        <v>1418.33</v>
+        <v>917.62</v>
       </c>
       <c r="S87" s="3">
-        <v>21.82</v>
+        <v>22.46</v>
       </c>
       <c r="T87" s="3">
-        <v>10.42</v>
+        <v>5.87</v>
       </c>
       <c r="U87" s="3">
-        <v>54.48</v>
+        <v>41.94</v>
       </c>
       <c r="V87" s="3">
-        <v>38</v>
+        <v>57.39</v>
       </c>
       <c r="W87" s="3">
         <v>0</v>
@@ -7109,67 +7109,67 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="C88" t="str">
-        <v>NIFTYALPHA50</v>
+        <v>NIFTYMEDIA</v>
       </c>
       <c r="D88" s="1">
-        <v>49910.3</v>
+        <v>1558.1</v>
       </c>
       <c r="E88" s="2">
-        <v>-2.81</v>
+        <v>-0.34</v>
       </c>
       <c r="F88" s="2">
-        <v>-7.31</v>
+        <v>-0.34</v>
       </c>
       <c r="G88" s="2">
-        <v>-7.71</v>
+        <v>-1.59</v>
       </c>
       <c r="H88" s="2">
-        <v>-0.79</v>
+        <v>7.85</v>
       </c>
       <c r="I88" s="1">
         <v>0</v>
       </c>
       <c r="J88" s="1">
-        <v>52196.32</v>
+        <v>1470.05</v>
       </c>
       <c r="K88" s="1">
-        <v>52935.13</v>
+        <v>1592.78</v>
       </c>
       <c r="L88" s="1">
-        <v>55465.02</v>
+        <v>1573.92</v>
       </c>
       <c r="M88" s="3">
-        <v>-970.06</v>
+        <v>8.97</v>
       </c>
       <c r="N88" s="3">
-        <v>-524.45</v>
+        <v>13.34</v>
       </c>
       <c r="O88" s="3">
-        <v>487.96</v>
+        <v>28.19</v>
       </c>
       <c r="P88" s="3">
-        <v>1112.5</v>
+        <v>30.68</v>
       </c>
       <c r="Q88" s="3">
-        <v>3454.54</v>
+        <v>-75.38</v>
       </c>
       <c r="R88" s="3">
-        <v>3839.75</v>
+        <v>-105.97</v>
       </c>
       <c r="S88" s="3">
-        <v>24.65</v>
+        <v>45.23</v>
       </c>
       <c r="T88" s="3">
-        <v>10.04</v>
+        <v>20.31</v>
       </c>
       <c r="U88" s="3">
-        <v>51.41</v>
+        <v>31.38</v>
       </c>
       <c r="V88" s="3">
-        <v>33.58</v>
+        <v>17.91</v>
       </c>
       <c r="W88" s="3">
         <v>0</v>
@@ -7186,67 +7186,67 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTY50PR1XINV</v>
       </c>
       <c r="C89" t="str">
-        <v>CNXSMALLCAP</v>
+        <v>NIFTY50PR1XINV</v>
       </c>
       <c r="D89" s="1">
-        <v>17739.45</v>
+        <v>235.15</v>
       </c>
       <c r="E89" s="2">
-        <v>-2.94</v>
+        <v>-0.61</v>
       </c>
       <c r="F89" s="2">
-        <v>-7.27</v>
+        <v>-0.61</v>
       </c>
       <c r="G89" s="2">
-        <v>-7.83</v>
+        <v>-0.34</v>
       </c>
       <c r="H89" s="2">
-        <v>0.14</v>
+        <v>17.58</v>
       </c>
       <c r="I89" s="1">
         <v>0</v>
       </c>
       <c r="J89" s="1">
-        <v>18188.33</v>
+        <v>219.44</v>
       </c>
       <c r="K89" s="1">
-        <v>18723.09</v>
+        <v>234.99</v>
       </c>
       <c r="L89" s="1">
-        <v>19579.65</v>
+        <v>228.28</v>
       </c>
       <c r="M89" s="3">
-        <v>-338.91</v>
+        <v>1.75</v>
       </c>
       <c r="N89" s="3">
-        <v>-201.47</v>
+        <v>2.27</v>
       </c>
       <c r="O89" s="3">
-        <v>243.89</v>
+        <v>4.88</v>
       </c>
       <c r="P89" s="3">
-        <v>477.06</v>
+        <v>3.75</v>
       </c>
       <c r="Q89" s="3">
-        <v>797.34</v>
+        <v>-0.69</v>
       </c>
       <c r="R89" s="3">
-        <v>843.64</v>
+        <v>-4.78</v>
       </c>
       <c r="S89" s="3">
-        <v>22.66</v>
+        <v>54.78</v>
       </c>
       <c r="T89" s="3">
-        <v>11.15</v>
+        <v>26.3</v>
       </c>
       <c r="U89" s="3">
-        <v>54.17</v>
+        <v>11.31</v>
       </c>
       <c r="V89" s="3">
-        <v>35.27</v>
+        <v>42.89</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
@@ -7263,67 +7263,67 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="C90" t="str">
-        <v>NIFTYSMALLCAP50</v>
+        <v>NIFTY50TR1XINV</v>
       </c>
       <c r="D90" s="1">
-        <v>8924.75</v>
+        <v>190.65</v>
       </c>
       <c r="E90" s="2">
-        <v>-3.15</v>
+        <v>-0.65</v>
       </c>
       <c r="F90" s="2">
-        <v>-6.87</v>
+        <v>-0.65</v>
       </c>
       <c r="G90" s="2">
-        <v>-7.35</v>
+        <v>-0.39</v>
       </c>
       <c r="H90" s="2">
-        <v>3.7</v>
+        <v>16.5</v>
       </c>
       <c r="I90" s="1">
         <v>0</v>
       </c>
       <c r="J90" s="1">
-        <v>8982.85</v>
+        <v>178.82</v>
       </c>
       <c r="K90" s="1">
-        <v>9395.06</v>
+        <v>190.58</v>
       </c>
       <c r="L90" s="1">
-        <v>9789.56</v>
+        <v>185.18</v>
       </c>
       <c r="M90" s="3">
-        <v>-153.48</v>
+        <v>1.4</v>
       </c>
       <c r="N90" s="3">
-        <v>-92.78</v>
+        <v>1.82</v>
       </c>
       <c r="O90" s="3">
-        <v>171.72</v>
+        <v>3.66</v>
       </c>
       <c r="P90" s="3">
-        <v>288.86</v>
+        <v>2.72</v>
       </c>
       <c r="Q90" s="3">
-        <v>702.31</v>
+        <v>-2.54</v>
       </c>
       <c r="R90" s="3">
-        <v>712.09</v>
+        <v>-6.04</v>
       </c>
       <c r="S90" s="3">
-        <v>24.61</v>
+        <v>54.52</v>
       </c>
       <c r="T90" s="3">
-        <v>11.37</v>
+        <v>26.26</v>
       </c>
       <c r="U90" s="3">
-        <v>50.49</v>
+        <v>11.45</v>
       </c>
       <c r="V90" s="3">
-        <v>33.74</v>
+        <v>42.42</v>
       </c>
       <c r="W90" s="3">
         <v>0</v>
